--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,430 +28,394 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>03.09.20261</t>
-  </si>
-  <si>
-    <t>03.09.20262</t>
-  </si>
-  <si>
-    <t>03.09.20263</t>
-  </si>
-  <si>
-    <t>03.09.20264</t>
-  </si>
-  <si>
-    <t>03.09.20265</t>
-  </si>
-  <si>
-    <t>03.09.20266</t>
-  </si>
-  <si>
-    <t>03.09.20267</t>
-  </si>
-  <si>
-    <t>03.09.20268</t>
-  </si>
-  <si>
-    <t>03.09.20269</t>
-  </si>
-  <si>
-    <t>03.09.202610</t>
-  </si>
-  <si>
-    <t>03.09.202611</t>
-  </si>
-  <si>
-    <t>03.09.202612</t>
-  </si>
-  <si>
-    <t>03.09.202613</t>
-  </si>
-  <si>
-    <t>03.09.202614</t>
-  </si>
-  <si>
-    <t>03.09.202615</t>
-  </si>
-  <si>
-    <t>03.09.202616</t>
-  </si>
-  <si>
-    <t>03.09.202617</t>
-  </si>
-  <si>
-    <t>03.09.202618</t>
-  </si>
-  <si>
-    <t>03.09.202619</t>
-  </si>
-  <si>
-    <t>03.09.202620</t>
-  </si>
-  <si>
-    <t>03.09.202621</t>
-  </si>
-  <si>
-    <t>03.09.202622</t>
-  </si>
-  <si>
-    <t>03.09.202623</t>
-  </si>
-  <si>
-    <t>03.09.202624</t>
-  </si>
-  <si>
-    <t>03.09.202625</t>
-  </si>
-  <si>
-    <t>03.09.202626</t>
-  </si>
-  <si>
-    <t>03.09.202627</t>
-  </si>
-  <si>
-    <t>03.09.202628</t>
-  </si>
-  <si>
-    <t>03.09.202629</t>
-  </si>
-  <si>
-    <t>03.09.202630</t>
-  </si>
-  <si>
-    <t>03.09.202631</t>
-  </si>
-  <si>
-    <t>03.09.202632</t>
-  </si>
-  <si>
-    <t>03.09.202633</t>
-  </si>
-  <si>
-    <t>03.09.202634</t>
-  </si>
-  <si>
-    <t>03.09.202635</t>
-  </si>
-  <si>
-    <t>03.09.202636</t>
-  </si>
-  <si>
-    <t>03.09.202637</t>
-  </si>
-  <si>
-    <t>03.09.202638</t>
-  </si>
-  <si>
-    <t>03.09.202639</t>
-  </si>
-  <si>
-    <t>03.09.202640</t>
-  </si>
-  <si>
-    <t>03.09.202641</t>
-  </si>
-  <si>
-    <t>03.09.202642</t>
-  </si>
-  <si>
-    <t>03.09.202643</t>
-  </si>
-  <si>
-    <t>03.09.202644</t>
-  </si>
-  <si>
-    <t>03.09.202645</t>
-  </si>
-  <si>
-    <t>03.09.202646</t>
-  </si>
-  <si>
-    <t>03.09.202647</t>
-  </si>
-  <si>
-    <t>03.09.202648</t>
-  </si>
-  <si>
-    <t>03.09.202649</t>
-  </si>
-  <si>
-    <t>03.09.202650</t>
-  </si>
-  <si>
-    <t>03.09.202651</t>
-  </si>
-  <si>
-    <t>03.09.202652</t>
-  </si>
-  <si>
-    <t>03.09.202653</t>
-  </si>
-  <si>
-    <t>03.09.202654</t>
-  </si>
-  <si>
-    <t>03.09.202655</t>
-  </si>
-  <si>
-    <t>03.09.202656</t>
-  </si>
-  <si>
-    <t>03.09.202657</t>
-  </si>
-  <si>
-    <t>03.09.202658</t>
-  </si>
-  <si>
-    <t>03.09.202659</t>
-  </si>
-  <si>
-    <t>03.09.202660</t>
-  </si>
-  <si>
-    <t>03.09.202661</t>
-  </si>
-  <si>
-    <t>03.09.202662</t>
-  </si>
-  <si>
-    <t>03.09.202663</t>
-  </si>
-  <si>
-    <t>03.09.202664</t>
-  </si>
-  <si>
-    <t>03.09.202665</t>
-  </si>
-  <si>
-    <t>03.09.202666</t>
-  </si>
-  <si>
-    <t>03.09.202667</t>
-  </si>
-  <si>
-    <t>03.09.202668</t>
-  </si>
-  <si>
-    <t>03.09.202669</t>
-  </si>
-  <si>
-    <t>03.09.202670</t>
-  </si>
-  <si>
-    <t>03.09.202671</t>
-  </si>
-  <si>
-    <t>03.09.202672</t>
-  </si>
-  <si>
-    <t>03.09.202673</t>
-  </si>
-  <si>
-    <t>03.09.202674</t>
-  </si>
-  <si>
-    <t>03.09.202675</t>
-  </si>
-  <si>
-    <t>03.09.202676</t>
-  </si>
-  <si>
-    <t>03.09.202677</t>
-  </si>
-  <si>
-    <t>03.09.202678</t>
-  </si>
-  <si>
-    <t>03.09.202679</t>
-  </si>
-  <si>
-    <t>03.09.202680</t>
-  </si>
-  <si>
-    <t>03.09.202681</t>
-  </si>
-  <si>
-    <t>03.09.202682</t>
-  </si>
-  <si>
-    <t>03.09.202683</t>
-  </si>
-  <si>
-    <t>03.09.202684</t>
-  </si>
-  <si>
-    <t>03.09.202685</t>
-  </si>
-  <si>
-    <t>03.09.202686</t>
-  </si>
-  <si>
-    <t>03.09.202687</t>
-  </si>
-  <si>
-    <t>03.09.202688</t>
-  </si>
-  <si>
-    <t>03.09.202689</t>
-  </si>
-  <si>
-    <t>03.09.202690</t>
-  </si>
-  <si>
-    <t>03.09.202691</t>
-  </si>
-  <si>
-    <t>03.09.202692</t>
-  </si>
-  <si>
-    <t>03.09.202693</t>
-  </si>
-  <si>
-    <t>03.09.202694</t>
-  </si>
-  <si>
-    <t>03.09.202695</t>
-  </si>
-  <si>
-    <t>03.09.202696</t>
-  </si>
-  <si>
-    <t>04.09.20261</t>
-  </si>
-  <si>
-    <t>04.09.20262</t>
-  </si>
-  <si>
-    <t>04.09.20263</t>
-  </si>
-  <si>
-    <t>04.09.20264</t>
-  </si>
-  <si>
-    <t>04.09.20265</t>
-  </si>
-  <si>
-    <t>04.09.20266</t>
-  </si>
-  <si>
-    <t>04.09.20267</t>
-  </si>
-  <si>
-    <t>04.09.20268</t>
-  </si>
-  <si>
-    <t>04.09.20269</t>
-  </si>
-  <si>
-    <t>04.09.202610</t>
-  </si>
-  <si>
-    <t>04.09.202611</t>
-  </si>
-  <si>
-    <t>04.09.202612</t>
-  </si>
-  <si>
-    <t>04.09.202613</t>
-  </si>
-  <si>
-    <t>04.09.202614</t>
-  </si>
-  <si>
-    <t>04.09.202615</t>
-  </si>
-  <si>
-    <t>04.09.202616</t>
-  </si>
-  <si>
-    <t>04.09.202617</t>
-  </si>
-  <si>
-    <t>04.09.202618</t>
-  </si>
-  <si>
-    <t>04.09.202619</t>
-  </si>
-  <si>
-    <t>04.09.202620</t>
-  </si>
-  <si>
-    <t>04.09.202621</t>
-  </si>
-  <si>
-    <t>04.09.202622</t>
-  </si>
-  <si>
-    <t>04.09.202623</t>
-  </si>
-  <si>
-    <t>04.09.202624</t>
-  </si>
-  <si>
-    <t>04.09.202625</t>
-  </si>
-  <si>
-    <t>04.09.202626</t>
-  </si>
-  <si>
-    <t>04.09.202627</t>
-  </si>
-  <si>
-    <t>04.09.202628</t>
-  </si>
-  <si>
-    <t>04.09.202629</t>
-  </si>
-  <si>
-    <t>04.09.202630</t>
-  </si>
-  <si>
-    <t>04.09.202631</t>
-  </si>
-  <si>
-    <t>04.09.202632</t>
-  </si>
-  <si>
-    <t>04.09.202633</t>
-  </si>
-  <si>
-    <t>04.09.202634</t>
-  </si>
-  <si>
-    <t>04.09.202635</t>
-  </si>
-  <si>
-    <t>04.09.202636</t>
-  </si>
-  <si>
-    <t>04.09.202637</t>
-  </si>
-  <si>
-    <t>04.09.202638</t>
-  </si>
-  <si>
-    <t>04.09.202639</t>
-  </si>
-  <si>
-    <t>04.09.202640</t>
-  </si>
-  <si>
-    <t>04.09.202641</t>
-  </si>
-  <si>
-    <t>04.09.202642</t>
-  </si>
-  <si>
-    <t>04.09.202643</t>
-  </si>
-  <si>
-    <t>04.09.202644</t>
-  </si>
-  <si>
-    <t>04.09.202645</t>
-  </si>
-  <si>
-    <t>04.09.202646</t>
+    <t>12.09.20261</t>
+  </si>
+  <si>
+    <t>12.09.20262</t>
+  </si>
+  <si>
+    <t>12.09.20263</t>
+  </si>
+  <si>
+    <t>12.09.20264</t>
+  </si>
+  <si>
+    <t>12.09.20265</t>
+  </si>
+  <si>
+    <t>12.09.20266</t>
+  </si>
+  <si>
+    <t>12.09.20267</t>
+  </si>
+  <si>
+    <t>12.09.20268</t>
+  </si>
+  <si>
+    <t>12.09.20269</t>
+  </si>
+  <si>
+    <t>12.09.202610</t>
+  </si>
+  <si>
+    <t>12.09.202611</t>
+  </si>
+  <si>
+    <t>12.09.202612</t>
+  </si>
+  <si>
+    <t>12.09.202613</t>
+  </si>
+  <si>
+    <t>12.09.202614</t>
+  </si>
+  <si>
+    <t>12.09.202615</t>
+  </si>
+  <si>
+    <t>12.09.202616</t>
+  </si>
+  <si>
+    <t>12.09.202617</t>
+  </si>
+  <si>
+    <t>12.09.202618</t>
+  </si>
+  <si>
+    <t>12.09.202619</t>
+  </si>
+  <si>
+    <t>12.09.202620</t>
+  </si>
+  <si>
+    <t>12.09.202621</t>
+  </si>
+  <si>
+    <t>12.09.202622</t>
+  </si>
+  <si>
+    <t>12.09.202623</t>
+  </si>
+  <si>
+    <t>12.09.202624</t>
+  </si>
+  <si>
+    <t>12.09.202625</t>
+  </si>
+  <si>
+    <t>12.09.202626</t>
+  </si>
+  <si>
+    <t>12.09.202627</t>
+  </si>
+  <si>
+    <t>12.09.202628</t>
+  </si>
+  <si>
+    <t>12.09.202629</t>
+  </si>
+  <si>
+    <t>12.09.202630</t>
+  </si>
+  <si>
+    <t>12.09.202631</t>
+  </si>
+  <si>
+    <t>12.09.202632</t>
+  </si>
+  <si>
+    <t>12.09.202633</t>
+  </si>
+  <si>
+    <t>12.09.202634</t>
+  </si>
+  <si>
+    <t>12.09.202635</t>
+  </si>
+  <si>
+    <t>12.09.202636</t>
+  </si>
+  <si>
+    <t>12.09.202637</t>
+  </si>
+  <si>
+    <t>12.09.202638</t>
+  </si>
+  <si>
+    <t>12.09.202639</t>
+  </si>
+  <si>
+    <t>12.09.202640</t>
+  </si>
+  <si>
+    <t>12.09.202641</t>
+  </si>
+  <si>
+    <t>12.09.202642</t>
+  </si>
+  <si>
+    <t>12.09.202643</t>
+  </si>
+  <si>
+    <t>12.09.202644</t>
+  </si>
+  <si>
+    <t>12.09.202645</t>
+  </si>
+  <si>
+    <t>12.09.202646</t>
+  </si>
+  <si>
+    <t>12.09.202647</t>
+  </si>
+  <si>
+    <t>12.09.202648</t>
+  </si>
+  <si>
+    <t>12.09.202649</t>
+  </si>
+  <si>
+    <t>12.09.202650</t>
+  </si>
+  <si>
+    <t>12.09.202651</t>
+  </si>
+  <si>
+    <t>12.09.202652</t>
+  </si>
+  <si>
+    <t>12.09.202653</t>
+  </si>
+  <si>
+    <t>12.09.202654</t>
+  </si>
+  <si>
+    <t>12.09.202655</t>
+  </si>
+  <si>
+    <t>12.09.202656</t>
+  </si>
+  <si>
+    <t>12.09.202657</t>
+  </si>
+  <si>
+    <t>12.09.202658</t>
+  </si>
+  <si>
+    <t>12.09.202659</t>
+  </si>
+  <si>
+    <t>12.09.202660</t>
+  </si>
+  <si>
+    <t>12.09.202661</t>
+  </si>
+  <si>
+    <t>12.09.202662</t>
+  </si>
+  <si>
+    <t>12.09.202663</t>
+  </si>
+  <si>
+    <t>12.09.202664</t>
+  </si>
+  <si>
+    <t>12.09.202665</t>
+  </si>
+  <si>
+    <t>12.09.202666</t>
+  </si>
+  <si>
+    <t>12.09.202667</t>
+  </si>
+  <si>
+    <t>12.09.202668</t>
+  </si>
+  <si>
+    <t>12.09.202669</t>
+  </si>
+  <si>
+    <t>12.09.202670</t>
+  </si>
+  <si>
+    <t>12.09.202671</t>
+  </si>
+  <si>
+    <t>12.09.202672</t>
+  </si>
+  <si>
+    <t>12.09.202673</t>
+  </si>
+  <si>
+    <t>12.09.202674</t>
+  </si>
+  <si>
+    <t>12.09.202675</t>
+  </si>
+  <si>
+    <t>12.09.202676</t>
+  </si>
+  <si>
+    <t>12.09.202677</t>
+  </si>
+  <si>
+    <t>12.09.202678</t>
+  </si>
+  <si>
+    <t>12.09.202679</t>
+  </si>
+  <si>
+    <t>12.09.202680</t>
+  </si>
+  <si>
+    <t>12.09.202681</t>
+  </si>
+  <si>
+    <t>12.09.202682</t>
+  </si>
+  <si>
+    <t>12.09.202683</t>
+  </si>
+  <si>
+    <t>12.09.202684</t>
+  </si>
+  <si>
+    <t>12.09.202685</t>
+  </si>
+  <si>
+    <t>12.09.202686</t>
+  </si>
+  <si>
+    <t>12.09.202687</t>
+  </si>
+  <si>
+    <t>12.09.202688</t>
+  </si>
+  <si>
+    <t>12.09.202689</t>
+  </si>
+  <si>
+    <t>12.09.202690</t>
+  </si>
+  <si>
+    <t>12.09.202691</t>
+  </si>
+  <si>
+    <t>12.09.202692</t>
+  </si>
+  <si>
+    <t>12.09.202693</t>
+  </si>
+  <si>
+    <t>12.09.202694</t>
+  </si>
+  <si>
+    <t>12.09.202695</t>
+  </si>
+  <si>
+    <t>12.09.202696</t>
+  </si>
+  <si>
+    <t>13.09.20261</t>
+  </si>
+  <si>
+    <t>13.09.20262</t>
+  </si>
+  <si>
+    <t>13.09.20263</t>
+  </si>
+  <si>
+    <t>13.09.20264</t>
+  </si>
+  <si>
+    <t>13.09.20265</t>
+  </si>
+  <si>
+    <t>13.09.20266</t>
+  </si>
+  <si>
+    <t>13.09.20267</t>
+  </si>
+  <si>
+    <t>13.09.20268</t>
+  </si>
+  <si>
+    <t>13.09.20269</t>
+  </si>
+  <si>
+    <t>13.09.202610</t>
+  </si>
+  <si>
+    <t>13.09.202611</t>
+  </si>
+  <si>
+    <t>13.09.202612</t>
+  </si>
+  <si>
+    <t>13.09.202613</t>
+  </si>
+  <si>
+    <t>13.09.202614</t>
+  </si>
+  <si>
+    <t>13.09.202615</t>
+  </si>
+  <si>
+    <t>13.09.202616</t>
+  </si>
+  <si>
+    <t>13.09.202617</t>
+  </si>
+  <si>
+    <t>13.09.202618</t>
+  </si>
+  <si>
+    <t>13.09.202619</t>
+  </si>
+  <si>
+    <t>13.09.202620</t>
+  </si>
+  <si>
+    <t>13.09.202621</t>
+  </si>
+  <si>
+    <t>13.09.202622</t>
+  </si>
+  <si>
+    <t>13.09.202623</t>
+  </si>
+  <si>
+    <t>13.09.202624</t>
+  </si>
+  <si>
+    <t>13.09.202625</t>
+  </si>
+  <si>
+    <t>13.09.202626</t>
+  </si>
+  <si>
+    <t>13.09.202627</t>
+  </si>
+  <si>
+    <t>13.09.202628</t>
+  </si>
+  <si>
+    <t>13.09.202629</t>
+  </si>
+  <si>
+    <t>13.09.202630</t>
+  </si>
+  <si>
+    <t>13.09.202631</t>
+  </si>
+  <si>
+    <t>13.09.202632</t>
+  </si>
+  <si>
+    <t>13.09.202633</t>
+  </si>
+  <si>
+    <t>13.09.202634</t>
   </si>
 </sst>
 </file>
@@ -813,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -832,10 +796,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46268</v>
+        <v>46277</v>
       </c>
       <c r="B2">
-        <v>5398</v>
+        <v>5329</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -846,10 +810,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46268.01041666666</v>
+        <v>46277.01041666666</v>
       </c>
       <c r="B3">
-        <v>5317</v>
+        <v>5284</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -860,10 +824,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46268.02083333334</v>
+        <v>46277.02083333334</v>
       </c>
       <c r="B4">
-        <v>5294</v>
+        <v>5279</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -874,10 +838,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46268.03125</v>
+        <v>46277.03125</v>
       </c>
       <c r="B5">
-        <v>5270</v>
+        <v>5235</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -888,10 +852,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46268.04166666666</v>
+        <v>46277.04166666666</v>
       </c>
       <c r="B6">
-        <v>5193</v>
+        <v>5180</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -902,10 +866,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46268.05208333334</v>
+        <v>46277.05208333334</v>
       </c>
       <c r="B7">
-        <v>5129</v>
+        <v>5126</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -916,10 +880,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46268.0625</v>
+        <v>46277.0625</v>
       </c>
       <c r="B8">
-        <v>5197</v>
+        <v>5190</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -930,10 +894,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46268.07291666666</v>
+        <v>46277.07291666666</v>
       </c>
       <c r="B9">
-        <v>5162</v>
+        <v>5158</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -944,10 +908,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46268.08333333334</v>
+        <v>46277.08333333334</v>
       </c>
       <c r="B10">
-        <v>5232</v>
+        <v>5061</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -958,10 +922,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46268.09375</v>
+        <v>46277.09375</v>
       </c>
       <c r="B11">
-        <v>5285</v>
+        <v>5020</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -972,10 +936,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46268.10416666666</v>
+        <v>46277.10416666666</v>
       </c>
       <c r="B12">
-        <v>5345</v>
+        <v>5020</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -986,10 +950,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46268.11458333334</v>
+        <v>46277.11458333334</v>
       </c>
       <c r="B13">
-        <v>5313</v>
+        <v>5023</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1000,10 +964,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46268.125</v>
+        <v>46277.125</v>
       </c>
       <c r="B14">
-        <v>5272</v>
+        <v>5032</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1014,10 +978,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46268.13541666666</v>
+        <v>46277.13541666666</v>
       </c>
       <c r="B15">
-        <v>5278</v>
+        <v>5011</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1028,10 +992,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46268.14583333334</v>
+        <v>46277.14583333334</v>
       </c>
       <c r="B16">
-        <v>5270</v>
+        <v>5065</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1042,10 +1006,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46268.15625</v>
+        <v>46277.15625</v>
       </c>
       <c r="B17">
-        <v>5312</v>
+        <v>5037</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1056,10 +1020,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46268.16666666666</v>
+        <v>46277.16666666666</v>
       </c>
       <c r="B18">
-        <v>5448</v>
+        <v>5075</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1070,10 +1034,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46268.17708333334</v>
+        <v>46277.17708333334</v>
       </c>
       <c r="B19">
-        <v>5537</v>
+        <v>5059</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1084,10 +1048,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46268.1875</v>
+        <v>46277.1875</v>
       </c>
       <c r="B20">
-        <v>5493</v>
+        <v>5091</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1098,10 +1062,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46268.19791666666</v>
+        <v>46277.19791666666</v>
       </c>
       <c r="B21">
-        <v>5523</v>
+        <v>5079</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1112,10 +1076,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46268.20833333334</v>
+        <v>46277.20833333334</v>
       </c>
       <c r="B22">
-        <v>5533</v>
+        <v>5184</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1126,10 +1090,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46268.21875</v>
+        <v>46277.21875</v>
       </c>
       <c r="B23">
-        <v>5546</v>
+        <v>5189</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1140,10 +1104,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46268.22916666666</v>
+        <v>46277.22916666666</v>
       </c>
       <c r="B24">
-        <v>5648</v>
+        <v>5148</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1154,10 +1118,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46268.23958333334</v>
+        <v>46277.23958333334</v>
       </c>
       <c r="B25">
-        <v>5746</v>
+        <v>5130</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1168,10 +1132,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46268.25</v>
+        <v>46277.25</v>
       </c>
       <c r="B26">
-        <v>5923</v>
+        <v>5303</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1182,10 +1146,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46268.26041666666</v>
+        <v>46277.26041666666</v>
       </c>
       <c r="B27">
-        <v>6007</v>
+        <v>5311</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1196,10 +1160,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46268.27083333334</v>
+        <v>46277.27083333334</v>
       </c>
       <c r="B28">
-        <v>6096</v>
+        <v>5431</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1210,10 +1174,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46268.28125</v>
+        <v>46277.28125</v>
       </c>
       <c r="B29">
-        <v>6120</v>
+        <v>5455</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1224,10 +1188,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46268.29166666666</v>
+        <v>46277.29166666666</v>
       </c>
       <c r="B30">
-        <v>6120</v>
+        <v>5393</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1238,10 +1202,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46268.30208333334</v>
+        <v>46277.30208333334</v>
       </c>
       <c r="B31">
-        <v>6112</v>
+        <v>5438</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1252,10 +1216,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46268.3125</v>
+        <v>46277.3125</v>
       </c>
       <c r="B32">
-        <v>6054</v>
+        <v>5464</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1266,10 +1230,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46268.32291666666</v>
+        <v>46277.32291666666</v>
       </c>
       <c r="B33">
-        <v>5932</v>
+        <v>5517</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1280,10 +1244,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46268.33333333334</v>
+        <v>46277.33333333334</v>
       </c>
       <c r="B34">
-        <v>5772</v>
+        <v>5424</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1294,10 +1258,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46268.34375</v>
+        <v>46277.34375</v>
       </c>
       <c r="B35">
-        <v>5711</v>
+        <v>5435</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1308,10 +1272,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46268.35416666666</v>
+        <v>46277.35416666666</v>
       </c>
       <c r="B36">
-        <v>5650</v>
+        <v>5383</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1322,10 +1286,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46268.36458333334</v>
+        <v>46277.36458333334</v>
       </c>
       <c r="B37">
-        <v>5483</v>
+        <v>5361</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1336,10 +1300,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46268.375</v>
+        <v>46277.375</v>
       </c>
       <c r="B38">
-        <v>5350</v>
+        <v>5302</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1350,10 +1314,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46268.38541666666</v>
+        <v>46277.38541666666</v>
       </c>
       <c r="B39">
-        <v>5242</v>
+        <v>5349</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1364,10 +1328,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46268.39583333334</v>
+        <v>46277.39583333334</v>
       </c>
       <c r="B40">
-        <v>5148</v>
+        <v>5235</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1378,10 +1342,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46268.40625</v>
+        <v>46277.40625</v>
       </c>
       <c r="B41">
-        <v>4898</v>
+        <v>5188</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1392,10 +1356,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46268.41666666666</v>
+        <v>46277.41666666666</v>
       </c>
       <c r="B42">
-        <v>4803</v>
+        <v>5138</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1406,10 +1370,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46268.42708333334</v>
+        <v>46277.42708333334</v>
       </c>
       <c r="B43">
-        <v>4729</v>
+        <v>5100</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1420,10 +1384,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46268.4375</v>
+        <v>46277.4375</v>
       </c>
       <c r="B44">
-        <v>4673</v>
+        <v>5155</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1434,10 +1398,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46268.44791666666</v>
+        <v>46277.44791666666</v>
       </c>
       <c r="B45">
-        <v>4653</v>
+        <v>5208</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1448,10 +1412,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46268.45833333334</v>
+        <v>46277.45833333334</v>
       </c>
       <c r="B46">
-        <v>4625</v>
+        <v>5242</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1462,10 +1426,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46268.46875</v>
+        <v>46277.46875</v>
       </c>
       <c r="B47">
-        <v>4616</v>
+        <v>5307</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1476,10 +1440,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46268.47916666666</v>
+        <v>46277.47916666666</v>
       </c>
       <c r="B48">
-        <v>4661</v>
+        <v>5325</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1490,10 +1454,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46268.48958333334</v>
+        <v>46277.48958333334</v>
       </c>
       <c r="B49">
-        <v>4757</v>
+        <v>5441</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1504,10 +1468,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46268.5</v>
+        <v>46277.5</v>
       </c>
       <c r="B50">
-        <v>4822</v>
+        <v>5490</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1518,10 +1482,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46268.51041666666</v>
+        <v>46277.51041666666</v>
       </c>
       <c r="B51">
-        <v>4875</v>
+        <v>5519</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1532,10 +1496,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46268.52083333334</v>
+        <v>46277.52083333334</v>
       </c>
       <c r="B52">
-        <v>4947</v>
+        <v>5572</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1546,10 +1510,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46268.53125</v>
+        <v>46277.53125</v>
       </c>
       <c r="B53">
-        <v>5048</v>
+        <v>5520</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1560,10 +1524,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46268.54166666666</v>
+        <v>46277.54166666666</v>
       </c>
       <c r="B54">
-        <v>5075</v>
+        <v>5496</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1574,10 +1538,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46268.55208333334</v>
+        <v>46277.55208333334</v>
       </c>
       <c r="B55">
-        <v>5034</v>
+        <v>5482</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1588,10 +1552,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46268.5625</v>
+        <v>46277.5625</v>
       </c>
       <c r="B56">
-        <v>5045</v>
+        <v>5479</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1602,10 +1566,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46268.57291666666</v>
+        <v>46277.57291666666</v>
       </c>
       <c r="B57">
-        <v>5093</v>
+        <v>5480</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1616,10 +1580,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46268.58333333334</v>
+        <v>46277.58333333334</v>
       </c>
       <c r="B58">
-        <v>5130</v>
+        <v>5469</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1630,10 +1594,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46268.59375</v>
+        <v>46277.59375</v>
       </c>
       <c r="B59">
-        <v>5042</v>
+        <v>5391</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1644,10 +1608,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46268.60416666666</v>
+        <v>46277.60416666666</v>
       </c>
       <c r="B60">
-        <v>5172</v>
+        <v>5283</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1658,10 +1622,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46268.61458333334</v>
+        <v>46277.61458333334</v>
       </c>
       <c r="B61">
-        <v>5377</v>
+        <v>5306</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1672,10 +1636,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46268.625</v>
+        <v>46277.625</v>
       </c>
       <c r="B62">
-        <v>5349</v>
+        <v>5300</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1686,10 +1650,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46268.63541666666</v>
+        <v>46277.63541666666</v>
       </c>
       <c r="B63">
-        <v>5515</v>
+        <v>5285</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1700,10 +1664,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46268.64583333334</v>
+        <v>46277.64583333334</v>
       </c>
       <c r="B64">
-        <v>5552</v>
+        <v>5305</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1714,10 +1678,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46268.65625</v>
+        <v>46277.65625</v>
       </c>
       <c r="B65">
-        <v>5679</v>
+        <v>5418</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1728,10 +1692,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46268.66666666666</v>
+        <v>46277.66666666666</v>
       </c>
       <c r="B66">
-        <v>5871</v>
+        <v>5464</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1742,10 +1706,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46268.67708333334</v>
+        <v>46277.67708333334</v>
       </c>
       <c r="B67">
-        <v>6002</v>
+        <v>5524</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1756,10 +1720,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46268.6875</v>
+        <v>46277.6875</v>
       </c>
       <c r="B68">
-        <v>6168</v>
+        <v>5682</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1770,10 +1734,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46268.69791666666</v>
+        <v>46277.69791666666</v>
       </c>
       <c r="B69">
-        <v>6342</v>
+        <v>5750</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1784,10 +1748,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46268.70833333334</v>
+        <v>46277.70833333334</v>
       </c>
       <c r="B70">
-        <v>6393</v>
+        <v>5860</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1798,10 +1762,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46268.71875</v>
+        <v>46277.71875</v>
       </c>
       <c r="B71">
-        <v>6549</v>
+        <v>5889</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1812,10 +1776,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46268.72916666666</v>
+        <v>46277.72916666666</v>
       </c>
       <c r="B72">
-        <v>6737</v>
+        <v>5931</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1826,10 +1790,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46268.73958333334</v>
+        <v>46277.73958333334</v>
       </c>
       <c r="B73">
-        <v>6911</v>
+        <v>5960</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1840,10 +1804,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46268.75</v>
+        <v>46277.75</v>
       </c>
       <c r="B74">
-        <v>6837</v>
+        <v>5933</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -1854,10 +1818,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46268.76041666666</v>
+        <v>46277.76041666666</v>
       </c>
       <c r="B75">
-        <v>6910</v>
+        <v>5999</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -1868,10 +1832,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46268.77083333334</v>
+        <v>46277.77083333334</v>
       </c>
       <c r="B76">
-        <v>6886</v>
+        <v>6127</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -1882,10 +1846,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46268.78125</v>
+        <v>46277.78125</v>
       </c>
       <c r="B77">
-        <v>7028</v>
+        <v>6227</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -1896,10 +1860,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46268.79166666666</v>
+        <v>46277.79166666666</v>
       </c>
       <c r="B78">
-        <v>7060</v>
+        <v>6298</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -1910,10 +1874,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46268.80208333334</v>
+        <v>46277.80208333334</v>
       </c>
       <c r="B79">
-        <v>7099</v>
+        <v>6324</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -1924,10 +1888,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46268.8125</v>
+        <v>46277.8125</v>
       </c>
       <c r="B80">
-        <v>7210</v>
+        <v>6282</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -1938,10 +1902,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46268.82291666666</v>
+        <v>46277.82291666666</v>
       </c>
       <c r="B81">
-        <v>7143</v>
+        <v>6251</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -1952,10 +1916,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46268.83333333334</v>
+        <v>46277.83333333334</v>
       </c>
       <c r="B82">
-        <v>7069</v>
+        <v>6142</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -1966,10 +1930,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46268.84375</v>
+        <v>46277.84375</v>
       </c>
       <c r="B83">
-        <v>6954</v>
+        <v>6101</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -1980,10 +1944,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46268.85416666666</v>
+        <v>46277.85416666666</v>
       </c>
       <c r="B84">
-        <v>6846</v>
+        <v>5996</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -1994,10 +1958,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46268.86458333334</v>
+        <v>46277.86458333334</v>
       </c>
       <c r="B85">
-        <v>6729</v>
+        <v>5921</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2008,10 +1972,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46268.875</v>
+        <v>46277.875</v>
       </c>
       <c r="B86">
-        <v>6558</v>
+        <v>5711</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2022,10 +1986,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46268.88541666666</v>
+        <v>46277.88541666666</v>
       </c>
       <c r="B87">
-        <v>6401</v>
+        <v>5609</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2036,10 +2000,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46268.89583333334</v>
+        <v>46277.89583333334</v>
       </c>
       <c r="B88">
-        <v>6264</v>
+        <v>5536</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2050,10 +2014,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46268.90625</v>
+        <v>46277.90625</v>
       </c>
       <c r="B89">
-        <v>6131</v>
+        <v>5442</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2064,10 +2028,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46268.91666666666</v>
+        <v>46277.91666666666</v>
       </c>
       <c r="B90">
-        <v>6070</v>
+        <v>5413</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2078,10 +2042,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46268.92708333334</v>
+        <v>46277.92708333334</v>
       </c>
       <c r="B91">
-        <v>5984</v>
+        <v>5277</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2092,10 +2056,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46268.9375</v>
+        <v>46277.9375</v>
       </c>
       <c r="B92">
-        <v>5871</v>
+        <v>5219</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2106,10 +2070,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46268.94791666666</v>
+        <v>46277.94791666666</v>
       </c>
       <c r="B93">
-        <v>5797</v>
+        <v>5139</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2120,10 +2084,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46268.95833333334</v>
+        <v>46277.95833333334</v>
       </c>
       <c r="B94">
-        <v>5703</v>
+        <v>4989</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2134,10 +2098,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46268.96875</v>
+        <v>46277.96875</v>
       </c>
       <c r="B95">
-        <v>5639</v>
+        <v>4904</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2148,10 +2112,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46268.97916666666</v>
+        <v>46277.97916666666</v>
       </c>
       <c r="B96">
-        <v>5523</v>
+        <v>4890</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2162,10 +2126,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46268.98958333334</v>
+        <v>46277.98958333334</v>
       </c>
       <c r="B97">
-        <v>5495</v>
+        <v>4829</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2176,10 +2140,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="B98">
-        <v>5428</v>
+        <v>4781</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2190,10 +2154,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46269.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
       <c r="B99">
-        <v>5388</v>
+        <v>4681</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2204,10 +2168,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46269.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
       <c r="B100">
-        <v>5284</v>
+        <v>4650</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2218,10 +2182,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46269.03125</v>
+        <v>46278.03125</v>
       </c>
       <c r="B101">
-        <v>5287</v>
+        <v>4592</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2232,10 +2196,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46269.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="B102">
-        <v>5213</v>
+        <v>4580</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2246,10 +2210,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46269.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
       <c r="B103">
-        <v>5274</v>
+        <v>4617</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2260,10 +2224,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46269.0625</v>
+        <v>46278.0625</v>
       </c>
       <c r="B104">
-        <v>5284</v>
+        <v>4539</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2274,10 +2238,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46269.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
       <c r="B105">
-        <v>5249</v>
+        <v>4567</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2288,10 +2252,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46269.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="B106">
-        <v>5376</v>
+        <v>4447</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2302,10 +2266,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46269.09375</v>
+        <v>46278.09375</v>
       </c>
       <c r="B107">
-        <v>5356</v>
+        <v>4422</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2316,10 +2280,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46269.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
       <c r="B108">
-        <v>5344</v>
+        <v>4402</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2330,10 +2294,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46269.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
       <c r="B109">
-        <v>5352</v>
+        <v>4398</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2344,10 +2308,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46269.125</v>
+        <v>46278.125</v>
       </c>
       <c r="B110">
-        <v>5400</v>
+        <v>4368</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2358,10 +2322,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46269.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
       <c r="B111">
-        <v>5421</v>
+        <v>4395</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2372,10 +2336,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46269.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
       <c r="B112">
-        <v>5383</v>
+        <v>4413</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2386,10 +2350,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46269.15625</v>
+        <v>46278.15625</v>
       </c>
       <c r="B113">
-        <v>5396</v>
+        <v>4450</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2400,10 +2364,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46269.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
       <c r="B114">
-        <v>5418</v>
+        <v>4504</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2414,10 +2378,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46269.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
       <c r="B115">
-        <v>5408</v>
+        <v>4558</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2428,10 +2392,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46269.1875</v>
+        <v>46278.1875</v>
       </c>
       <c r="B116">
-        <v>5384</v>
+        <v>4541</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2442,10 +2406,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46269.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
       <c r="B117">
-        <v>5415</v>
+        <v>4574</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2456,10 +2420,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46269.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
       <c r="B118">
-        <v>5613</v>
+        <v>4563</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2470,10 +2434,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46269.21875</v>
+        <v>46278.21875</v>
       </c>
       <c r="B119">
-        <v>5633</v>
+        <v>4594</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2484,10 +2448,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46269.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
       <c r="B120">
-        <v>5634</v>
+        <v>4635</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2498,10 +2462,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46269.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
       <c r="B121">
-        <v>5698</v>
+        <v>4653</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2512,10 +2476,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46269.25</v>
+        <v>46278.25</v>
       </c>
       <c r="B122">
-        <v>5880</v>
+        <v>4699</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2526,10 +2490,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46269.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
       <c r="B123">
-        <v>5954</v>
+        <v>4671</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2540,10 +2504,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46269.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
       <c r="B124">
-        <v>6024</v>
+        <v>4750</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2554,10 +2518,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46269.28125</v>
+        <v>46278.28125</v>
       </c>
       <c r="B125">
-        <v>6067</v>
+        <v>4759</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2568,10 +2532,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46269.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
       <c r="B126">
-        <v>6057</v>
+        <v>4809</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2582,10 +2546,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46269.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
       <c r="B127">
-        <v>6051</v>
+        <v>4789</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2596,10 +2560,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46269.3125</v>
+        <v>46278.3125</v>
       </c>
       <c r="B128">
-        <v>6032</v>
+        <v>4688</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2610,10 +2574,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46269.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
       <c r="B129">
-        <v>6008</v>
+        <v>4721</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2624,10 +2588,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46269.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
       <c r="B130">
-        <v>5780</v>
+        <v>4692</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2638,184 +2602,16 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46269.34375</v>
+        <v>46278.34375</v>
       </c>
       <c r="B131">
-        <v>5781</v>
+        <v>4631</v>
       </c>
       <c r="C131">
         <v>34</v>
       </c>
       <c r="D131" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4">
-      <c r="A132" s="2">
-        <v>46269.35416666666</v>
-      </c>
-      <c r="B132">
-        <v>5648</v>
-      </c>
-      <c r="C132">
-        <v>35</v>
-      </c>
-      <c r="D132" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4">
-      <c r="A133" s="2">
-        <v>46269.36458333334</v>
-      </c>
-      <c r="B133">
-        <v>5443</v>
-      </c>
-      <c r="C133">
-        <v>36</v>
-      </c>
-      <c r="D133" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4">
-      <c r="A134" s="2">
-        <v>46269.375</v>
-      </c>
-      <c r="B134">
-        <v>5280</v>
-      </c>
-      <c r="C134">
-        <v>37</v>
-      </c>
-      <c r="D134" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4">
-      <c r="A135" s="2">
-        <v>46269.38541666666</v>
-      </c>
-      <c r="B135">
-        <v>5062</v>
-      </c>
-      <c r="C135">
-        <v>38</v>
-      </c>
-      <c r="D135" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4">
-      <c r="A136" s="2">
-        <v>46269.39583333334</v>
-      </c>
-      <c r="B136">
-        <v>4932</v>
-      </c>
-      <c r="C136">
-        <v>39</v>
-      </c>
-      <c r="D136" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4">
-      <c r="A137" s="2">
-        <v>46269.40625</v>
-      </c>
-      <c r="B137">
-        <v>4837</v>
-      </c>
-      <c r="C137">
-        <v>40</v>
-      </c>
-      <c r="D137" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4">
-      <c r="A138" s="2">
-        <v>46269.41666666666</v>
-      </c>
-      <c r="B138">
-        <v>4736</v>
-      </c>
-      <c r="C138">
-        <v>41</v>
-      </c>
-      <c r="D138" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4">
-      <c r="A139" s="2">
-        <v>46269.42708333334</v>
-      </c>
-      <c r="B139">
-        <v>4789</v>
-      </c>
-      <c r="C139">
-        <v>42</v>
-      </c>
-      <c r="D139" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4">
-      <c r="A140" s="2">
-        <v>46269.4375</v>
-      </c>
-      <c r="B140">
-        <v>4791</v>
-      </c>
-      <c r="C140">
-        <v>43</v>
-      </c>
-      <c r="D140" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4">
-      <c r="A141" s="2">
-        <v>46269.44791666666</v>
-      </c>
-      <c r="B141">
-        <v>4642</v>
-      </c>
-      <c r="C141">
-        <v>44</v>
-      </c>
-      <c r="D141" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4">
-      <c r="A142" s="2">
-        <v>46269.45833333334</v>
-      </c>
-      <c r="B142">
-        <v>4752</v>
-      </c>
-      <c r="C142">
-        <v>45</v>
-      </c>
-      <c r="D142" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4">
-      <c r="A143" s="2">
-        <v>46269.46875</v>
-      </c>
-      <c r="B143">
-        <v>4652</v>
-      </c>
-      <c r="C143">
-        <v>46</v>
-      </c>
-      <c r="D143" t="s">
-        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="524">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>12.09.20261</t>
-  </si>
-  <si>
-    <t>12.09.20262</t>
-  </si>
-  <si>
-    <t>12.09.20263</t>
-  </si>
-  <si>
-    <t>12.09.20264</t>
-  </si>
-  <si>
-    <t>12.09.20265</t>
-  </si>
-  <si>
-    <t>12.09.20266</t>
-  </si>
-  <si>
-    <t>12.09.20267</t>
-  </si>
-  <si>
-    <t>12.09.20268</t>
-  </si>
-  <si>
-    <t>12.09.20269</t>
-  </si>
-  <si>
-    <t>12.09.202610</t>
-  </si>
-  <si>
-    <t>12.09.202611</t>
-  </si>
-  <si>
-    <t>12.09.202612</t>
-  </si>
-  <si>
-    <t>12.09.202613</t>
-  </si>
-  <si>
-    <t>12.09.202614</t>
-  </si>
-  <si>
-    <t>12.09.202615</t>
-  </si>
-  <si>
-    <t>12.09.202616</t>
-  </si>
-  <si>
-    <t>12.09.202617</t>
-  </si>
-  <si>
-    <t>12.09.202618</t>
-  </si>
-  <si>
-    <t>12.09.202619</t>
-  </si>
-  <si>
-    <t>12.09.202620</t>
-  </si>
-  <si>
-    <t>12.09.202621</t>
-  </si>
-  <si>
-    <t>12.09.202622</t>
-  </si>
-  <si>
-    <t>12.09.202623</t>
-  </si>
-  <si>
-    <t>12.09.202624</t>
-  </si>
-  <si>
-    <t>12.09.202625</t>
-  </si>
-  <si>
-    <t>12.09.202626</t>
-  </si>
-  <si>
-    <t>12.09.202627</t>
-  </si>
-  <si>
-    <t>12.09.202628</t>
-  </si>
-  <si>
-    <t>12.09.202629</t>
-  </si>
-  <si>
-    <t>12.09.202630</t>
-  </si>
-  <si>
-    <t>12.09.202631</t>
-  </si>
-  <si>
-    <t>12.09.202632</t>
-  </si>
-  <si>
-    <t>12.09.202633</t>
-  </si>
-  <si>
-    <t>12.09.202634</t>
-  </si>
-  <si>
-    <t>12.09.202635</t>
-  </si>
-  <si>
-    <t>12.09.202636</t>
-  </si>
-  <si>
-    <t>12.09.202637</t>
-  </si>
-  <si>
-    <t>12.09.202638</t>
-  </si>
-  <si>
-    <t>12.09.202639</t>
-  </si>
-  <si>
-    <t>12.09.202640</t>
-  </si>
-  <si>
-    <t>12.09.202641</t>
-  </si>
-  <si>
-    <t>12.09.202642</t>
-  </si>
-  <si>
-    <t>12.09.202643</t>
-  </si>
-  <si>
-    <t>12.09.202644</t>
-  </si>
-  <si>
-    <t>12.09.202645</t>
-  </si>
-  <si>
-    <t>12.09.202646</t>
-  </si>
-  <si>
-    <t>12.09.202647</t>
-  </si>
-  <si>
-    <t>12.09.202648</t>
-  </si>
-  <si>
-    <t>12.09.202649</t>
-  </si>
-  <si>
-    <t>12.09.202650</t>
-  </si>
-  <si>
-    <t>12.09.202651</t>
-  </si>
-  <si>
-    <t>12.09.202652</t>
-  </si>
-  <si>
-    <t>12.09.202653</t>
-  </si>
-  <si>
-    <t>12.09.202654</t>
-  </si>
-  <si>
-    <t>12.09.202655</t>
-  </si>
-  <si>
-    <t>12.09.202656</t>
-  </si>
-  <si>
-    <t>12.09.202657</t>
-  </si>
-  <si>
-    <t>12.09.202658</t>
-  </si>
-  <si>
-    <t>12.09.202659</t>
-  </si>
-  <si>
-    <t>12.09.202660</t>
-  </si>
-  <si>
-    <t>12.09.202661</t>
-  </si>
-  <si>
-    <t>12.09.202662</t>
-  </si>
-  <si>
-    <t>12.09.202663</t>
-  </si>
-  <si>
-    <t>12.09.202664</t>
-  </si>
-  <si>
-    <t>12.09.202665</t>
-  </si>
-  <si>
-    <t>12.09.202666</t>
-  </si>
-  <si>
-    <t>12.09.202667</t>
-  </si>
-  <si>
-    <t>12.09.202668</t>
-  </si>
-  <si>
-    <t>12.09.202669</t>
-  </si>
-  <si>
-    <t>12.09.202670</t>
-  </si>
-  <si>
-    <t>12.09.202671</t>
-  </si>
-  <si>
-    <t>12.09.202672</t>
-  </si>
-  <si>
-    <t>12.09.202673</t>
-  </si>
-  <si>
-    <t>12.09.202674</t>
-  </si>
-  <si>
-    <t>12.09.202675</t>
-  </si>
-  <si>
-    <t>12.09.202676</t>
-  </si>
-  <si>
-    <t>12.09.202677</t>
-  </si>
-  <si>
-    <t>12.09.202678</t>
-  </si>
-  <si>
-    <t>12.09.202679</t>
-  </si>
-  <si>
-    <t>12.09.202680</t>
-  </si>
-  <si>
-    <t>12.09.202681</t>
-  </si>
-  <si>
-    <t>12.09.202682</t>
-  </si>
-  <si>
-    <t>12.09.202683</t>
-  </si>
-  <si>
-    <t>12.09.202684</t>
-  </si>
-  <si>
-    <t>12.09.202685</t>
-  </si>
-  <si>
-    <t>12.09.202686</t>
-  </si>
-  <si>
-    <t>12.09.202687</t>
-  </si>
-  <si>
-    <t>12.09.202688</t>
-  </si>
-  <si>
-    <t>12.09.202689</t>
-  </si>
-  <si>
-    <t>12.09.202690</t>
-  </si>
-  <si>
-    <t>12.09.202691</t>
-  </si>
-  <si>
-    <t>12.09.202692</t>
-  </si>
-  <si>
-    <t>12.09.202693</t>
-  </si>
-  <si>
-    <t>12.09.202694</t>
-  </si>
-  <si>
-    <t>12.09.202695</t>
-  </si>
-  <si>
-    <t>12.09.202696</t>
-  </si>
-  <si>
     <t>13.09.20261</t>
   </si>
   <si>
@@ -416,6 +128,1464 @@
   </si>
   <si>
     <t>13.09.202634</t>
+  </si>
+  <si>
+    <t>13.09.202635</t>
+  </si>
+  <si>
+    <t>13.09.202636</t>
+  </si>
+  <si>
+    <t>13.09.202637</t>
+  </si>
+  <si>
+    <t>13.09.202638</t>
+  </si>
+  <si>
+    <t>13.09.202639</t>
+  </si>
+  <si>
+    <t>13.09.202640</t>
+  </si>
+  <si>
+    <t>13.09.202641</t>
+  </si>
+  <si>
+    <t>13.09.202642</t>
+  </si>
+  <si>
+    <t>13.09.202643</t>
+  </si>
+  <si>
+    <t>13.09.202644</t>
+  </si>
+  <si>
+    <t>13.09.202645</t>
+  </si>
+  <si>
+    <t>13.09.202646</t>
+  </si>
+  <si>
+    <t>13.09.202647</t>
+  </si>
+  <si>
+    <t>13.09.202648</t>
+  </si>
+  <si>
+    <t>13.09.202649</t>
+  </si>
+  <si>
+    <t>13.09.202650</t>
+  </si>
+  <si>
+    <t>13.09.202651</t>
+  </si>
+  <si>
+    <t>13.09.202652</t>
+  </si>
+  <si>
+    <t>13.09.202653</t>
+  </si>
+  <si>
+    <t>13.09.202654</t>
+  </si>
+  <si>
+    <t>13.09.202655</t>
+  </si>
+  <si>
+    <t>13.09.202656</t>
+  </si>
+  <si>
+    <t>13.09.202657</t>
+  </si>
+  <si>
+    <t>13.09.202658</t>
+  </si>
+  <si>
+    <t>13.09.202659</t>
+  </si>
+  <si>
+    <t>13.09.202660</t>
+  </si>
+  <si>
+    <t>13.09.202661</t>
+  </si>
+  <si>
+    <t>13.09.202662</t>
+  </si>
+  <si>
+    <t>13.09.202663</t>
+  </si>
+  <si>
+    <t>13.09.202664</t>
+  </si>
+  <si>
+    <t>13.09.202665</t>
+  </si>
+  <si>
+    <t>13.09.202666</t>
+  </si>
+  <si>
+    <t>13.09.202667</t>
+  </si>
+  <si>
+    <t>13.09.202668</t>
+  </si>
+  <si>
+    <t>13.09.202669</t>
+  </si>
+  <si>
+    <t>13.09.202670</t>
+  </si>
+  <si>
+    <t>13.09.202671</t>
+  </si>
+  <si>
+    <t>13.09.202672</t>
+  </si>
+  <si>
+    <t>13.09.202673</t>
+  </si>
+  <si>
+    <t>13.09.202674</t>
+  </si>
+  <si>
+    <t>13.09.202675</t>
+  </si>
+  <si>
+    <t>13.09.202676</t>
+  </si>
+  <si>
+    <t>13.09.202677</t>
+  </si>
+  <si>
+    <t>13.09.202678</t>
+  </si>
+  <si>
+    <t>13.09.202679</t>
+  </si>
+  <si>
+    <t>13.09.202680</t>
+  </si>
+  <si>
+    <t>13.09.202681</t>
+  </si>
+  <si>
+    <t>13.09.202682</t>
+  </si>
+  <si>
+    <t>13.09.202683</t>
+  </si>
+  <si>
+    <t>13.09.202684</t>
+  </si>
+  <si>
+    <t>13.09.202685</t>
+  </si>
+  <si>
+    <t>13.09.202686</t>
+  </si>
+  <si>
+    <t>13.09.202687</t>
+  </si>
+  <si>
+    <t>13.09.202688</t>
+  </si>
+  <si>
+    <t>13.09.202689</t>
+  </si>
+  <si>
+    <t>13.09.202690</t>
+  </si>
+  <si>
+    <t>13.09.202691</t>
+  </si>
+  <si>
+    <t>13.09.202692</t>
+  </si>
+  <si>
+    <t>13.09.202693</t>
+  </si>
+  <si>
+    <t>13.09.202694</t>
+  </si>
+  <si>
+    <t>13.09.202695</t>
+  </si>
+  <si>
+    <t>13.09.202696</t>
+  </si>
+  <si>
+    <t>14.09.20261</t>
+  </si>
+  <si>
+    <t>14.09.20262</t>
+  </si>
+  <si>
+    <t>14.09.20263</t>
+  </si>
+  <si>
+    <t>14.09.20264</t>
+  </si>
+  <si>
+    <t>14.09.20265</t>
+  </si>
+  <si>
+    <t>14.09.20266</t>
+  </si>
+  <si>
+    <t>14.09.20267</t>
+  </si>
+  <si>
+    <t>14.09.20268</t>
+  </si>
+  <si>
+    <t>14.09.20269</t>
+  </si>
+  <si>
+    <t>14.09.202610</t>
+  </si>
+  <si>
+    <t>14.09.202611</t>
+  </si>
+  <si>
+    <t>14.09.202612</t>
+  </si>
+  <si>
+    <t>14.09.202613</t>
+  </si>
+  <si>
+    <t>14.09.202614</t>
+  </si>
+  <si>
+    <t>14.09.202615</t>
+  </si>
+  <si>
+    <t>14.09.202616</t>
+  </si>
+  <si>
+    <t>14.09.202617</t>
+  </si>
+  <si>
+    <t>14.09.202618</t>
+  </si>
+  <si>
+    <t>14.09.202619</t>
+  </si>
+  <si>
+    <t>14.09.202620</t>
+  </si>
+  <si>
+    <t>14.09.202621</t>
+  </si>
+  <si>
+    <t>14.09.202622</t>
+  </si>
+  <si>
+    <t>14.09.202623</t>
+  </si>
+  <si>
+    <t>14.09.202624</t>
+  </si>
+  <si>
+    <t>14.09.202625</t>
+  </si>
+  <si>
+    <t>14.09.202626</t>
+  </si>
+  <si>
+    <t>14.09.202627</t>
+  </si>
+  <si>
+    <t>14.09.202628</t>
+  </si>
+  <si>
+    <t>14.09.202629</t>
+  </si>
+  <si>
+    <t>14.09.202630</t>
+  </si>
+  <si>
+    <t>14.09.202631</t>
+  </si>
+  <si>
+    <t>14.09.202632</t>
+  </si>
+  <si>
+    <t>14.09.202633</t>
+  </si>
+  <si>
+    <t>14.09.202634</t>
+  </si>
+  <si>
+    <t>14.09.202635</t>
+  </si>
+  <si>
+    <t>14.09.202636</t>
+  </si>
+  <si>
+    <t>14.09.202637</t>
+  </si>
+  <si>
+    <t>14.09.202638</t>
+  </si>
+  <si>
+    <t>14.09.202639</t>
+  </si>
+  <si>
+    <t>14.09.202640</t>
+  </si>
+  <si>
+    <t>14.09.202641</t>
+  </si>
+  <si>
+    <t>14.09.202642</t>
+  </si>
+  <si>
+    <t>14.09.202643</t>
+  </si>
+  <si>
+    <t>14.09.202644</t>
+  </si>
+  <si>
+    <t>14.09.202645</t>
+  </si>
+  <si>
+    <t>14.09.202646</t>
+  </si>
+  <si>
+    <t>14.09.202647</t>
+  </si>
+  <si>
+    <t>14.09.202648</t>
+  </si>
+  <si>
+    <t>14.09.202649</t>
+  </si>
+  <si>
+    <t>14.09.202650</t>
+  </si>
+  <si>
+    <t>14.09.202651</t>
+  </si>
+  <si>
+    <t>14.09.202652</t>
+  </si>
+  <si>
+    <t>14.09.202653</t>
+  </si>
+  <si>
+    <t>14.09.202654</t>
+  </si>
+  <si>
+    <t>14.09.202655</t>
+  </si>
+  <si>
+    <t>14.09.202656</t>
+  </si>
+  <si>
+    <t>14.09.202657</t>
+  </si>
+  <si>
+    <t>14.09.202658</t>
+  </si>
+  <si>
+    <t>14.09.202659</t>
+  </si>
+  <si>
+    <t>14.09.202660</t>
+  </si>
+  <si>
+    <t>14.09.202661</t>
+  </si>
+  <si>
+    <t>14.09.202662</t>
+  </si>
+  <si>
+    <t>14.09.202663</t>
+  </si>
+  <si>
+    <t>14.09.202664</t>
+  </si>
+  <si>
+    <t>14.09.202665</t>
+  </si>
+  <si>
+    <t>14.09.202666</t>
+  </si>
+  <si>
+    <t>14.09.202667</t>
+  </si>
+  <si>
+    <t>14.09.202668</t>
+  </si>
+  <si>
+    <t>14.09.202669</t>
+  </si>
+  <si>
+    <t>14.09.202670</t>
+  </si>
+  <si>
+    <t>14.09.202671</t>
+  </si>
+  <si>
+    <t>14.09.202672</t>
+  </si>
+  <si>
+    <t>14.09.202673</t>
+  </si>
+  <si>
+    <t>14.09.202674</t>
+  </si>
+  <si>
+    <t>14.09.202675</t>
+  </si>
+  <si>
+    <t>14.09.202676</t>
+  </si>
+  <si>
+    <t>14.09.202677</t>
+  </si>
+  <si>
+    <t>14.09.202678</t>
+  </si>
+  <si>
+    <t>14.09.202679</t>
+  </si>
+  <si>
+    <t>14.09.202680</t>
+  </si>
+  <si>
+    <t>14.09.202681</t>
+  </si>
+  <si>
+    <t>14.09.202682</t>
+  </si>
+  <si>
+    <t>14.09.202683</t>
+  </si>
+  <si>
+    <t>14.09.202684</t>
+  </si>
+  <si>
+    <t>14.09.202685</t>
+  </si>
+  <si>
+    <t>14.09.202686</t>
+  </si>
+  <si>
+    <t>14.09.202687</t>
+  </si>
+  <si>
+    <t>14.09.202688</t>
+  </si>
+  <si>
+    <t>14.09.202689</t>
+  </si>
+  <si>
+    <t>14.09.202690</t>
+  </si>
+  <si>
+    <t>14.09.202691</t>
+  </si>
+  <si>
+    <t>14.09.202692</t>
+  </si>
+  <si>
+    <t>14.09.202693</t>
+  </si>
+  <si>
+    <t>14.09.202694</t>
+  </si>
+  <si>
+    <t>14.09.202695</t>
+  </si>
+  <si>
+    <t>14.09.202696</t>
+  </si>
+  <si>
+    <t>15.09.20261</t>
+  </si>
+  <si>
+    <t>15.09.20262</t>
+  </si>
+  <si>
+    <t>15.09.20263</t>
+  </si>
+  <si>
+    <t>15.09.20264</t>
+  </si>
+  <si>
+    <t>15.09.20265</t>
+  </si>
+  <si>
+    <t>15.09.20266</t>
+  </si>
+  <si>
+    <t>15.09.20267</t>
+  </si>
+  <si>
+    <t>15.09.20268</t>
+  </si>
+  <si>
+    <t>15.09.20269</t>
+  </si>
+  <si>
+    <t>15.09.202610</t>
+  </si>
+  <si>
+    <t>15.09.202611</t>
+  </si>
+  <si>
+    <t>15.09.202612</t>
+  </si>
+  <si>
+    <t>15.09.202613</t>
+  </si>
+  <si>
+    <t>15.09.202614</t>
+  </si>
+  <si>
+    <t>15.09.202615</t>
+  </si>
+  <si>
+    <t>15.09.202616</t>
+  </si>
+  <si>
+    <t>15.09.202617</t>
+  </si>
+  <si>
+    <t>15.09.202618</t>
+  </si>
+  <si>
+    <t>15.09.202619</t>
+  </si>
+  <si>
+    <t>15.09.202620</t>
+  </si>
+  <si>
+    <t>15.09.202621</t>
+  </si>
+  <si>
+    <t>15.09.202622</t>
+  </si>
+  <si>
+    <t>15.09.202623</t>
+  </si>
+  <si>
+    <t>15.09.202624</t>
+  </si>
+  <si>
+    <t>15.09.202625</t>
+  </si>
+  <si>
+    <t>15.09.202626</t>
+  </si>
+  <si>
+    <t>15.09.202627</t>
+  </si>
+  <si>
+    <t>15.09.202628</t>
+  </si>
+  <si>
+    <t>15.09.202629</t>
+  </si>
+  <si>
+    <t>15.09.202630</t>
+  </si>
+  <si>
+    <t>15.09.202631</t>
+  </si>
+  <si>
+    <t>15.09.202632</t>
+  </si>
+  <si>
+    <t>15.09.202633</t>
+  </si>
+  <si>
+    <t>15.09.202634</t>
+  </si>
+  <si>
+    <t>15.09.202635</t>
+  </si>
+  <si>
+    <t>15.09.202636</t>
+  </si>
+  <si>
+    <t>15.09.202637</t>
+  </si>
+  <si>
+    <t>15.09.202638</t>
+  </si>
+  <si>
+    <t>15.09.202639</t>
+  </si>
+  <si>
+    <t>15.09.202640</t>
+  </si>
+  <si>
+    <t>15.09.202641</t>
+  </si>
+  <si>
+    <t>15.09.202642</t>
+  </si>
+  <si>
+    <t>15.09.202643</t>
+  </si>
+  <si>
+    <t>15.09.202644</t>
+  </si>
+  <si>
+    <t>15.09.202645</t>
+  </si>
+  <si>
+    <t>15.09.202646</t>
+  </si>
+  <si>
+    <t>15.09.202647</t>
+  </si>
+  <si>
+    <t>15.09.202648</t>
+  </si>
+  <si>
+    <t>15.09.202649</t>
+  </si>
+  <si>
+    <t>15.09.202650</t>
+  </si>
+  <si>
+    <t>15.09.202651</t>
+  </si>
+  <si>
+    <t>15.09.202652</t>
+  </si>
+  <si>
+    <t>15.09.202653</t>
+  </si>
+  <si>
+    <t>15.09.202654</t>
+  </si>
+  <si>
+    <t>15.09.202655</t>
+  </si>
+  <si>
+    <t>15.09.202656</t>
+  </si>
+  <si>
+    <t>15.09.202657</t>
+  </si>
+  <si>
+    <t>15.09.202658</t>
+  </si>
+  <si>
+    <t>15.09.202659</t>
+  </si>
+  <si>
+    <t>15.09.202660</t>
+  </si>
+  <si>
+    <t>15.09.202661</t>
+  </si>
+  <si>
+    <t>15.09.202662</t>
+  </si>
+  <si>
+    <t>15.09.202663</t>
+  </si>
+  <si>
+    <t>15.09.202664</t>
+  </si>
+  <si>
+    <t>15.09.202665</t>
+  </si>
+  <si>
+    <t>15.09.202666</t>
+  </si>
+  <si>
+    <t>15.09.202667</t>
+  </si>
+  <si>
+    <t>15.09.202668</t>
+  </si>
+  <si>
+    <t>15.09.202669</t>
+  </si>
+  <si>
+    <t>15.09.202670</t>
+  </si>
+  <si>
+    <t>15.09.202671</t>
+  </si>
+  <si>
+    <t>15.09.202672</t>
+  </si>
+  <si>
+    <t>15.09.202673</t>
+  </si>
+  <si>
+    <t>15.09.202674</t>
+  </si>
+  <si>
+    <t>15.09.202675</t>
+  </si>
+  <si>
+    <t>15.09.202676</t>
+  </si>
+  <si>
+    <t>15.09.202677</t>
+  </si>
+  <si>
+    <t>15.09.202678</t>
+  </si>
+  <si>
+    <t>15.09.202679</t>
+  </si>
+  <si>
+    <t>15.09.202680</t>
+  </si>
+  <si>
+    <t>15.09.202681</t>
+  </si>
+  <si>
+    <t>15.09.202682</t>
+  </si>
+  <si>
+    <t>15.09.202683</t>
+  </si>
+  <si>
+    <t>15.09.202684</t>
+  </si>
+  <si>
+    <t>15.09.202685</t>
+  </si>
+  <si>
+    <t>15.09.202686</t>
+  </si>
+  <si>
+    <t>15.09.202687</t>
+  </si>
+  <si>
+    <t>15.09.202688</t>
+  </si>
+  <si>
+    <t>15.09.202689</t>
+  </si>
+  <si>
+    <t>15.09.202690</t>
+  </si>
+  <si>
+    <t>15.09.202691</t>
+  </si>
+  <si>
+    <t>15.09.202692</t>
+  </si>
+  <si>
+    <t>15.09.202693</t>
+  </si>
+  <si>
+    <t>15.09.202694</t>
+  </si>
+  <si>
+    <t>15.09.202695</t>
+  </si>
+  <si>
+    <t>15.09.202696</t>
+  </si>
+  <si>
+    <t>16.09.20261</t>
+  </si>
+  <si>
+    <t>16.09.20262</t>
+  </si>
+  <si>
+    <t>16.09.20263</t>
+  </si>
+  <si>
+    <t>16.09.20264</t>
+  </si>
+  <si>
+    <t>16.09.20265</t>
+  </si>
+  <si>
+    <t>16.09.20266</t>
+  </si>
+  <si>
+    <t>16.09.20267</t>
+  </si>
+  <si>
+    <t>16.09.20268</t>
+  </si>
+  <si>
+    <t>16.09.20269</t>
+  </si>
+  <si>
+    <t>16.09.202610</t>
+  </si>
+  <si>
+    <t>16.09.202611</t>
+  </si>
+  <si>
+    <t>16.09.202612</t>
+  </si>
+  <si>
+    <t>16.09.202613</t>
+  </si>
+  <si>
+    <t>16.09.202614</t>
+  </si>
+  <si>
+    <t>16.09.202615</t>
+  </si>
+  <si>
+    <t>16.09.202616</t>
+  </si>
+  <si>
+    <t>16.09.202617</t>
+  </si>
+  <si>
+    <t>16.09.202618</t>
+  </si>
+  <si>
+    <t>16.09.202619</t>
+  </si>
+  <si>
+    <t>16.09.202620</t>
+  </si>
+  <si>
+    <t>16.09.202621</t>
+  </si>
+  <si>
+    <t>16.09.202622</t>
+  </si>
+  <si>
+    <t>16.09.202623</t>
+  </si>
+  <si>
+    <t>16.09.202624</t>
+  </si>
+  <si>
+    <t>16.09.202625</t>
+  </si>
+  <si>
+    <t>16.09.202626</t>
+  </si>
+  <si>
+    <t>16.09.202627</t>
+  </si>
+  <si>
+    <t>16.09.202628</t>
+  </si>
+  <si>
+    <t>16.09.202629</t>
+  </si>
+  <si>
+    <t>16.09.202630</t>
+  </si>
+  <si>
+    <t>16.09.202631</t>
+  </si>
+  <si>
+    <t>16.09.202632</t>
+  </si>
+  <si>
+    <t>16.09.202633</t>
+  </si>
+  <si>
+    <t>16.09.202634</t>
+  </si>
+  <si>
+    <t>16.09.202635</t>
+  </si>
+  <si>
+    <t>16.09.202636</t>
+  </si>
+  <si>
+    <t>16.09.202637</t>
+  </si>
+  <si>
+    <t>16.09.202638</t>
+  </si>
+  <si>
+    <t>16.09.202639</t>
+  </si>
+  <si>
+    <t>16.09.202640</t>
+  </si>
+  <si>
+    <t>16.09.202641</t>
+  </si>
+  <si>
+    <t>16.09.202642</t>
+  </si>
+  <si>
+    <t>16.09.202643</t>
+  </si>
+  <si>
+    <t>16.09.202644</t>
+  </si>
+  <si>
+    <t>16.09.202645</t>
+  </si>
+  <si>
+    <t>16.09.202646</t>
+  </si>
+  <si>
+    <t>16.09.202647</t>
+  </si>
+  <si>
+    <t>16.09.202648</t>
+  </si>
+  <si>
+    <t>16.09.202649</t>
+  </si>
+  <si>
+    <t>16.09.202650</t>
+  </si>
+  <si>
+    <t>16.09.202651</t>
+  </si>
+  <si>
+    <t>16.09.202652</t>
+  </si>
+  <si>
+    <t>16.09.202653</t>
+  </si>
+  <si>
+    <t>16.09.202654</t>
+  </si>
+  <si>
+    <t>16.09.202655</t>
+  </si>
+  <si>
+    <t>16.09.202656</t>
+  </si>
+  <si>
+    <t>16.09.202657</t>
+  </si>
+  <si>
+    <t>16.09.202658</t>
+  </si>
+  <si>
+    <t>16.09.202659</t>
+  </si>
+  <si>
+    <t>16.09.202660</t>
+  </si>
+  <si>
+    <t>16.09.202661</t>
+  </si>
+  <si>
+    <t>16.09.202662</t>
+  </si>
+  <si>
+    <t>16.09.202663</t>
+  </si>
+  <si>
+    <t>16.09.202664</t>
+  </si>
+  <si>
+    <t>16.09.202665</t>
+  </si>
+  <si>
+    <t>16.09.202666</t>
+  </si>
+  <si>
+    <t>16.09.202667</t>
+  </si>
+  <si>
+    <t>16.09.202668</t>
+  </si>
+  <si>
+    <t>16.09.202669</t>
+  </si>
+  <si>
+    <t>16.09.202670</t>
+  </si>
+  <si>
+    <t>16.09.202671</t>
+  </si>
+  <si>
+    <t>16.09.202672</t>
+  </si>
+  <si>
+    <t>16.09.202673</t>
+  </si>
+  <si>
+    <t>16.09.202674</t>
+  </si>
+  <si>
+    <t>16.09.202675</t>
+  </si>
+  <si>
+    <t>16.09.202676</t>
+  </si>
+  <si>
+    <t>16.09.202677</t>
+  </si>
+  <si>
+    <t>16.09.202678</t>
+  </si>
+  <si>
+    <t>16.09.202679</t>
+  </si>
+  <si>
+    <t>16.09.202680</t>
+  </si>
+  <si>
+    <t>16.09.202681</t>
+  </si>
+  <si>
+    <t>16.09.202682</t>
+  </si>
+  <si>
+    <t>16.09.202683</t>
+  </si>
+  <si>
+    <t>16.09.202684</t>
+  </si>
+  <si>
+    <t>16.09.202685</t>
+  </si>
+  <si>
+    <t>16.09.202686</t>
+  </si>
+  <si>
+    <t>16.09.202687</t>
+  </si>
+  <si>
+    <t>16.09.202688</t>
+  </si>
+  <si>
+    <t>16.09.202689</t>
+  </si>
+  <si>
+    <t>16.09.202690</t>
+  </si>
+  <si>
+    <t>16.09.202691</t>
+  </si>
+  <si>
+    <t>16.09.202692</t>
+  </si>
+  <si>
+    <t>16.09.202693</t>
+  </si>
+  <si>
+    <t>16.09.202694</t>
+  </si>
+  <si>
+    <t>16.09.202695</t>
+  </si>
+  <si>
+    <t>16.09.202696</t>
+  </si>
+  <si>
+    <t>17.09.20261</t>
+  </si>
+  <si>
+    <t>17.09.20262</t>
+  </si>
+  <si>
+    <t>17.09.20263</t>
+  </si>
+  <si>
+    <t>17.09.20264</t>
+  </si>
+  <si>
+    <t>17.09.20265</t>
+  </si>
+  <si>
+    <t>17.09.20266</t>
+  </si>
+  <si>
+    <t>17.09.20267</t>
+  </si>
+  <si>
+    <t>17.09.20268</t>
+  </si>
+  <si>
+    <t>17.09.20269</t>
+  </si>
+  <si>
+    <t>17.09.202610</t>
+  </si>
+  <si>
+    <t>17.09.202611</t>
+  </si>
+  <si>
+    <t>17.09.202612</t>
+  </si>
+  <si>
+    <t>17.09.202613</t>
+  </si>
+  <si>
+    <t>17.09.202614</t>
+  </si>
+  <si>
+    <t>17.09.202615</t>
+  </si>
+  <si>
+    <t>17.09.202616</t>
+  </si>
+  <si>
+    <t>17.09.202617</t>
+  </si>
+  <si>
+    <t>17.09.202618</t>
+  </si>
+  <si>
+    <t>17.09.202619</t>
+  </si>
+  <si>
+    <t>17.09.202620</t>
+  </si>
+  <si>
+    <t>17.09.202621</t>
+  </si>
+  <si>
+    <t>17.09.202622</t>
+  </si>
+  <si>
+    <t>17.09.202623</t>
+  </si>
+  <si>
+    <t>17.09.202624</t>
+  </si>
+  <si>
+    <t>17.09.202625</t>
+  </si>
+  <si>
+    <t>17.09.202626</t>
+  </si>
+  <si>
+    <t>17.09.202627</t>
+  </si>
+  <si>
+    <t>17.09.202628</t>
+  </si>
+  <si>
+    <t>17.09.202629</t>
+  </si>
+  <si>
+    <t>17.09.202630</t>
+  </si>
+  <si>
+    <t>17.09.202631</t>
+  </si>
+  <si>
+    <t>17.09.202632</t>
+  </si>
+  <si>
+    <t>17.09.202633</t>
+  </si>
+  <si>
+    <t>17.09.202634</t>
+  </si>
+  <si>
+    <t>17.09.202635</t>
+  </si>
+  <si>
+    <t>17.09.202636</t>
+  </si>
+  <si>
+    <t>17.09.202637</t>
+  </si>
+  <si>
+    <t>17.09.202638</t>
+  </si>
+  <si>
+    <t>17.09.202639</t>
+  </si>
+  <si>
+    <t>17.09.202640</t>
+  </si>
+  <si>
+    <t>17.09.202641</t>
+  </si>
+  <si>
+    <t>17.09.202642</t>
+  </si>
+  <si>
+    <t>17.09.202643</t>
+  </si>
+  <si>
+    <t>17.09.202644</t>
+  </si>
+  <si>
+    <t>17.09.202645</t>
+  </si>
+  <si>
+    <t>17.09.202646</t>
+  </si>
+  <si>
+    <t>17.09.202647</t>
+  </si>
+  <si>
+    <t>17.09.202648</t>
+  </si>
+  <si>
+    <t>17.09.202649</t>
+  </si>
+  <si>
+    <t>17.09.202650</t>
+  </si>
+  <si>
+    <t>17.09.202651</t>
+  </si>
+  <si>
+    <t>17.09.202652</t>
+  </si>
+  <si>
+    <t>17.09.202653</t>
+  </si>
+  <si>
+    <t>17.09.202654</t>
+  </si>
+  <si>
+    <t>17.09.202655</t>
+  </si>
+  <si>
+    <t>17.09.202656</t>
+  </si>
+  <si>
+    <t>17.09.202657</t>
+  </si>
+  <si>
+    <t>17.09.202658</t>
+  </si>
+  <si>
+    <t>17.09.202659</t>
+  </si>
+  <si>
+    <t>17.09.202660</t>
+  </si>
+  <si>
+    <t>17.09.202661</t>
+  </si>
+  <si>
+    <t>17.09.202662</t>
+  </si>
+  <si>
+    <t>17.09.202663</t>
+  </si>
+  <si>
+    <t>17.09.202664</t>
+  </si>
+  <si>
+    <t>17.09.202665</t>
+  </si>
+  <si>
+    <t>17.09.202666</t>
+  </si>
+  <si>
+    <t>17.09.202667</t>
+  </si>
+  <si>
+    <t>17.09.202668</t>
+  </si>
+  <si>
+    <t>17.09.202669</t>
+  </si>
+  <si>
+    <t>17.09.202670</t>
+  </si>
+  <si>
+    <t>17.09.202671</t>
+  </si>
+  <si>
+    <t>17.09.202672</t>
+  </si>
+  <si>
+    <t>17.09.202673</t>
+  </si>
+  <si>
+    <t>17.09.202674</t>
+  </si>
+  <si>
+    <t>17.09.202675</t>
+  </si>
+  <si>
+    <t>17.09.202676</t>
+  </si>
+  <si>
+    <t>17.09.202677</t>
+  </si>
+  <si>
+    <t>17.09.202678</t>
+  </si>
+  <si>
+    <t>17.09.202679</t>
+  </si>
+  <si>
+    <t>17.09.202680</t>
+  </si>
+  <si>
+    <t>17.09.202681</t>
+  </si>
+  <si>
+    <t>17.09.202682</t>
+  </si>
+  <si>
+    <t>17.09.202683</t>
+  </si>
+  <si>
+    <t>17.09.202684</t>
+  </si>
+  <si>
+    <t>17.09.202685</t>
+  </si>
+  <si>
+    <t>17.09.202686</t>
+  </si>
+  <si>
+    <t>17.09.202687</t>
+  </si>
+  <si>
+    <t>17.09.202688</t>
+  </si>
+  <si>
+    <t>17.09.202689</t>
+  </si>
+  <si>
+    <t>17.09.202690</t>
+  </si>
+  <si>
+    <t>17.09.202691</t>
+  </si>
+  <si>
+    <t>17.09.202692</t>
+  </si>
+  <si>
+    <t>17.09.202693</t>
+  </si>
+  <si>
+    <t>17.09.202694</t>
+  </si>
+  <si>
+    <t>17.09.202695</t>
+  </si>
+  <si>
+    <t>17.09.202696</t>
+  </si>
+  <si>
+    <t>18.09.20261</t>
+  </si>
+  <si>
+    <t>18.09.20262</t>
+  </si>
+  <si>
+    <t>18.09.20263</t>
+  </si>
+  <si>
+    <t>18.09.20264</t>
+  </si>
+  <si>
+    <t>18.09.20265</t>
+  </si>
+  <si>
+    <t>18.09.20266</t>
+  </si>
+  <si>
+    <t>18.09.20267</t>
+  </si>
+  <si>
+    <t>18.09.20268</t>
+  </si>
+  <si>
+    <t>18.09.20269</t>
+  </si>
+  <si>
+    <t>18.09.202610</t>
+  </si>
+  <si>
+    <t>18.09.202611</t>
+  </si>
+  <si>
+    <t>18.09.202612</t>
+  </si>
+  <si>
+    <t>18.09.202613</t>
+  </si>
+  <si>
+    <t>18.09.202614</t>
+  </si>
+  <si>
+    <t>18.09.202615</t>
+  </si>
+  <si>
+    <t>18.09.202616</t>
+  </si>
+  <si>
+    <t>18.09.202617</t>
+  </si>
+  <si>
+    <t>18.09.202618</t>
+  </si>
+  <si>
+    <t>18.09.202619</t>
+  </si>
+  <si>
+    <t>18.09.202620</t>
+  </si>
+  <si>
+    <t>18.09.202621</t>
+  </si>
+  <si>
+    <t>18.09.202622</t>
+  </si>
+  <si>
+    <t>18.09.202623</t>
+  </si>
+  <si>
+    <t>18.09.202624</t>
+  </si>
+  <si>
+    <t>18.09.202625</t>
+  </si>
+  <si>
+    <t>18.09.202626</t>
+  </si>
+  <si>
+    <t>18.09.202627</t>
+  </si>
+  <si>
+    <t>18.09.202628</t>
+  </si>
+  <si>
+    <t>18.09.202629</t>
+  </si>
+  <si>
+    <t>18.09.202630</t>
+  </si>
+  <si>
+    <t>18.09.202631</t>
+  </si>
+  <si>
+    <t>18.09.202632</t>
+  </si>
+  <si>
+    <t>18.09.202633</t>
+  </si>
+  <si>
+    <t>18.09.202634</t>
+  </si>
+  <si>
+    <t>18.09.202635</t>
+  </si>
+  <si>
+    <t>18.09.202636</t>
+  </si>
+  <si>
+    <t>18.09.202637</t>
+  </si>
+  <si>
+    <t>18.09.202638</t>
+  </si>
+  <si>
+    <t>18.09.202639</t>
+  </si>
+  <si>
+    <t>18.09.202640</t>
   </si>
 </sst>
 </file>
@@ -777,7 +1947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D521"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -796,10 +1966,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B2">
-        <v>5329</v>
+        <v>4781</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -810,10 +1980,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46277.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
       <c r="B3">
-        <v>5284</v>
+        <v>4681</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -824,10 +1994,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46277.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
       <c r="B4">
-        <v>5279</v>
+        <v>4650</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -838,10 +2008,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46277.03125</v>
+        <v>46278.03125</v>
       </c>
       <c r="B5">
-        <v>5235</v>
+        <v>4592</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -852,10 +2022,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46277.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="B6">
-        <v>5180</v>
+        <v>4580</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -866,10 +2036,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46277.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
       <c r="B7">
-        <v>5126</v>
+        <v>4617</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -880,10 +2050,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46277.0625</v>
+        <v>46278.0625</v>
       </c>
       <c r="B8">
-        <v>5190</v>
+        <v>4539</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -894,10 +2064,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46277.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
       <c r="B9">
-        <v>5158</v>
+        <v>4567</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -908,10 +2078,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46277.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="B10">
-        <v>5061</v>
+        <v>4447</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -922,10 +2092,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46277.09375</v>
+        <v>46278.09375</v>
       </c>
       <c r="B11">
-        <v>5020</v>
+        <v>4422</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -936,10 +2106,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46277.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
       <c r="B12">
-        <v>5020</v>
+        <v>4402</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -950,10 +2120,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46277.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
       <c r="B13">
-        <v>5023</v>
+        <v>4398</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -964,10 +2134,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46277.125</v>
+        <v>46278.125</v>
       </c>
       <c r="B14">
-        <v>5032</v>
+        <v>4368</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -978,10 +2148,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46277.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
       <c r="B15">
-        <v>5011</v>
+        <v>4395</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -992,10 +2162,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46277.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
       <c r="B16">
-        <v>5065</v>
+        <v>4413</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1006,10 +2176,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46277.15625</v>
+        <v>46278.15625</v>
       </c>
       <c r="B17">
-        <v>5037</v>
+        <v>4450</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1020,10 +2190,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46277.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
       <c r="B18">
-        <v>5075</v>
+        <v>4504</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1034,10 +2204,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46277.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
       <c r="B19">
-        <v>5059</v>
+        <v>4558</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1048,10 +2218,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46277.1875</v>
+        <v>46278.1875</v>
       </c>
       <c r="B20">
-        <v>5091</v>
+        <v>4541</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1062,10 +2232,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46277.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
       <c r="B21">
-        <v>5079</v>
+        <v>4574</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1076,10 +2246,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46277.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
       <c r="B22">
-        <v>5184</v>
+        <v>4563</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1090,10 +2260,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46277.21875</v>
+        <v>46278.21875</v>
       </c>
       <c r="B23">
-        <v>5189</v>
+        <v>4594</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1104,10 +2274,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46277.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
       <c r="B24">
-        <v>5148</v>
+        <v>4635</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1118,10 +2288,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46277.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
       <c r="B25">
-        <v>5130</v>
+        <v>4653</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1132,10 +2302,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46277.25</v>
+        <v>46278.25</v>
       </c>
       <c r="B26">
-        <v>5303</v>
+        <v>4699</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1146,10 +2316,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46277.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
       <c r="B27">
-        <v>5311</v>
+        <v>4671</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1160,10 +2330,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46277.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
       <c r="B28">
-        <v>5431</v>
+        <v>4750</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1174,10 +2344,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46277.28125</v>
+        <v>46278.28125</v>
       </c>
       <c r="B29">
-        <v>5455</v>
+        <v>4759</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1188,10 +2358,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46277.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
       <c r="B30">
-        <v>5393</v>
+        <v>4809</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1202,10 +2372,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46277.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
       <c r="B31">
-        <v>5438</v>
+        <v>4789</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1216,10 +2386,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46277.3125</v>
+        <v>46278.3125</v>
       </c>
       <c r="B32">
-        <v>5464</v>
+        <v>4688</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1230,10 +2400,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46277.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
       <c r="B33">
-        <v>5517</v>
+        <v>4721</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1244,10 +2414,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46277.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
       <c r="B34">
-        <v>5424</v>
+        <v>4692</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1258,10 +2428,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46277.34375</v>
+        <v>46278.34375</v>
       </c>
       <c r="B35">
-        <v>5435</v>
+        <v>4631</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1272,10 +2442,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46277.35416666666</v>
+        <v>46278.35416666666</v>
       </c>
       <c r="B36">
-        <v>5383</v>
+        <v>4568</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1286,10 +2456,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46277.36458333334</v>
+        <v>46278.36458333334</v>
       </c>
       <c r="B37">
-        <v>5361</v>
+        <v>4519</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1300,10 +2470,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46277.375</v>
+        <v>46278.375</v>
       </c>
       <c r="B38">
-        <v>5302</v>
+        <v>4422</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1314,10 +2484,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46277.38541666666</v>
+        <v>46278.38541666666</v>
       </c>
       <c r="B39">
-        <v>5349</v>
+        <v>4426</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1328,10 +2498,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46277.39583333334</v>
+        <v>46278.39583333334</v>
       </c>
       <c r="B40">
-        <v>5235</v>
+        <v>4322</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1342,10 +2512,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46277.40625</v>
+        <v>46278.40625</v>
       </c>
       <c r="B41">
-        <v>5188</v>
+        <v>4152</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1356,10 +2526,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46277.41666666666</v>
+        <v>46278.41666666666</v>
       </c>
       <c r="B42">
-        <v>5138</v>
+        <v>4067</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1370,10 +2540,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46277.42708333334</v>
+        <v>46278.42708333334</v>
       </c>
       <c r="B43">
-        <v>5100</v>
+        <v>4014</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1384,10 +2554,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46277.4375</v>
+        <v>46278.4375</v>
       </c>
       <c r="B44">
-        <v>5155</v>
+        <v>3947</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1398,10 +2568,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46277.44791666666</v>
+        <v>46278.44791666666</v>
       </c>
       <c r="B45">
-        <v>5208</v>
+        <v>3930</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1412,10 +2582,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46277.45833333334</v>
+        <v>46278.45833333334</v>
       </c>
       <c r="B46">
-        <v>5242</v>
+        <v>3915</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1426,10 +2596,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46277.46875</v>
+        <v>46278.46875</v>
       </c>
       <c r="B47">
-        <v>5307</v>
+        <v>3769</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1440,10 +2610,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46277.47916666666</v>
+        <v>46278.47916666666</v>
       </c>
       <c r="B48">
-        <v>5325</v>
+        <v>3762</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1454,10 +2624,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46277.48958333334</v>
+        <v>46278.48958333334</v>
       </c>
       <c r="B49">
-        <v>5441</v>
+        <v>3878</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1468,10 +2638,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46277.5</v>
+        <v>46278.5</v>
       </c>
       <c r="B50">
-        <v>5490</v>
+        <v>3981</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1482,10 +2652,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46277.51041666666</v>
+        <v>46278.51041666666</v>
       </c>
       <c r="B51">
-        <v>5519</v>
+        <v>4055</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1496,10 +2666,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46277.52083333334</v>
+        <v>46278.52083333334</v>
       </c>
       <c r="B52">
-        <v>5572</v>
+        <v>4066</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1510,10 +2680,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46277.53125</v>
+        <v>46278.53125</v>
       </c>
       <c r="B53">
-        <v>5520</v>
+        <v>4038</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1524,10 +2694,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46277.54166666666</v>
+        <v>46278.54166666666</v>
       </c>
       <c r="B54">
-        <v>5496</v>
+        <v>4138</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1538,10 +2708,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46277.55208333334</v>
+        <v>46278.55208333334</v>
       </c>
       <c r="B55">
-        <v>5482</v>
+        <v>4145</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1552,10 +2722,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46277.5625</v>
+        <v>46278.5625</v>
       </c>
       <c r="B56">
-        <v>5479</v>
+        <v>4163</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1566,10 +2736,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46277.57291666666</v>
+        <v>46278.57291666666</v>
       </c>
       <c r="B57">
-        <v>5480</v>
+        <v>4169</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1580,10 +2750,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46277.58333333334</v>
+        <v>46278.58333333334</v>
       </c>
       <c r="B58">
-        <v>5469</v>
+        <v>4322</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1594,10 +2764,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46277.59375</v>
+        <v>46278.59375</v>
       </c>
       <c r="B59">
-        <v>5391</v>
+        <v>4314</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1608,10 +2778,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46277.60416666666</v>
+        <v>46278.60416666666</v>
       </c>
       <c r="B60">
-        <v>5283</v>
+        <v>4382</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1622,10 +2792,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46277.61458333334</v>
+        <v>46278.61458333334</v>
       </c>
       <c r="B61">
-        <v>5306</v>
+        <v>4283</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1636,10 +2806,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46277.625</v>
+        <v>46278.625</v>
       </c>
       <c r="B62">
-        <v>5300</v>
+        <v>4329</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1650,10 +2820,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46277.63541666666</v>
+        <v>46278.63541666666</v>
       </c>
       <c r="B63">
-        <v>5285</v>
+        <v>4344</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1664,10 +2834,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46277.64583333334</v>
+        <v>46278.64583333334</v>
       </c>
       <c r="B64">
-        <v>5305</v>
+        <v>4432</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1678,10 +2848,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46277.65625</v>
+        <v>46278.65625</v>
       </c>
       <c r="B65">
-        <v>5418</v>
+        <v>4526</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1692,10 +2862,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46277.66666666666</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="B66">
-        <v>5464</v>
+        <v>4525</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1706,10 +2876,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46277.67708333334</v>
+        <v>46278.67708333334</v>
       </c>
       <c r="B67">
-        <v>5524</v>
+        <v>4661</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1720,10 +2890,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46277.6875</v>
+        <v>46278.6875</v>
       </c>
       <c r="B68">
-        <v>5682</v>
+        <v>4782</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1734,10 +2904,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46277.69791666666</v>
+        <v>46278.69791666666</v>
       </c>
       <c r="B69">
-        <v>5750</v>
+        <v>4852</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1748,10 +2918,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46277.70833333334</v>
+        <v>46278.70833333334</v>
       </c>
       <c r="B70">
-        <v>5860</v>
+        <v>4951</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1762,10 +2932,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46277.71875</v>
+        <v>46278.71875</v>
       </c>
       <c r="B71">
-        <v>5889</v>
+        <v>5055</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1776,10 +2946,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46277.72916666666</v>
+        <v>46278.72916666666</v>
       </c>
       <c r="B72">
-        <v>5931</v>
+        <v>5195</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1790,10 +2960,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46277.73958333334</v>
+        <v>46278.73958333334</v>
       </c>
       <c r="B73">
-        <v>5960</v>
+        <v>5212</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1804,10 +2974,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46277.75</v>
+        <v>46278.75</v>
       </c>
       <c r="B74">
-        <v>5933</v>
+        <v>5322</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -1818,10 +2988,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46277.76041666666</v>
+        <v>46278.76041666666</v>
       </c>
       <c r="B75">
-        <v>5999</v>
+        <v>5420</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -1832,10 +3002,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46277.77083333334</v>
+        <v>46278.77083333334</v>
       </c>
       <c r="B76">
-        <v>6127</v>
+        <v>5597</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -1846,10 +3016,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46277.78125</v>
+        <v>46278.78125</v>
       </c>
       <c r="B77">
-        <v>6227</v>
+        <v>5687</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -1860,10 +3030,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46277.79166666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="B78">
-        <v>6298</v>
+        <v>5842</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -1874,10 +3044,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46277.80208333334</v>
+        <v>46278.80208333334</v>
       </c>
       <c r="B79">
-        <v>6324</v>
+        <v>5865</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -1888,10 +3058,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46277.8125</v>
+        <v>46278.8125</v>
       </c>
       <c r="B80">
-        <v>6282</v>
+        <v>5892</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -1902,10 +3072,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46277.82291666666</v>
+        <v>46278.82291666666</v>
       </c>
       <c r="B81">
-        <v>6251</v>
+        <v>5818</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -1916,10 +3086,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46277.83333333334</v>
+        <v>46278.83333333334</v>
       </c>
       <c r="B82">
-        <v>6142</v>
+        <v>5827</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -1930,10 +3100,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46277.84375</v>
+        <v>46278.84375</v>
       </c>
       <c r="B83">
-        <v>6101</v>
+        <v>5725</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -1944,10 +3114,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46277.85416666666</v>
+        <v>46278.85416666666</v>
       </c>
       <c r="B84">
-        <v>5996</v>
+        <v>5641</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -1958,10 +3128,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46277.86458333334</v>
+        <v>46278.86458333334</v>
       </c>
       <c r="B85">
-        <v>5921</v>
+        <v>5472</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -1972,10 +3142,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46277.875</v>
+        <v>46278.875</v>
       </c>
       <c r="B86">
-        <v>5711</v>
+        <v>5362</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -1986,10 +3156,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46277.88541666666</v>
+        <v>46278.88541666666</v>
       </c>
       <c r="B87">
-        <v>5609</v>
+        <v>5266</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2000,10 +3170,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46277.89583333334</v>
+        <v>46278.89583333334</v>
       </c>
       <c r="B88">
-        <v>5536</v>
+        <v>5170</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2014,10 +3184,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46277.90625</v>
+        <v>46278.90625</v>
       </c>
       <c r="B89">
-        <v>5442</v>
+        <v>5065</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2028,10 +3198,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46277.91666666666</v>
+        <v>46278.91666666666</v>
       </c>
       <c r="B90">
-        <v>5413</v>
+        <v>5027</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2042,10 +3212,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46277.92708333334</v>
+        <v>46278.92708333334</v>
       </c>
       <c r="B91">
-        <v>5277</v>
+        <v>5011</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2056,10 +3226,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46277.9375</v>
+        <v>46278.9375</v>
       </c>
       <c r="B92">
-        <v>5219</v>
+        <v>4966</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2070,10 +3240,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46277.94791666666</v>
+        <v>46278.94791666666</v>
       </c>
       <c r="B93">
-        <v>5139</v>
+        <v>4957</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2084,10 +3254,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46277.95833333334</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="B94">
-        <v>4989</v>
+        <v>4823</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2098,10 +3268,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46277.96875</v>
+        <v>46278.96875</v>
       </c>
       <c r="B95">
-        <v>4904</v>
+        <v>4798</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2112,10 +3282,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46277.97916666666</v>
+        <v>46278.97916666666</v>
       </c>
       <c r="B96">
-        <v>4890</v>
+        <v>4710</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2126,10 +3296,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46277.98958333334</v>
+        <v>46278.98958333334</v>
       </c>
       <c r="B97">
-        <v>4829</v>
+        <v>4672</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2140,10 +3310,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B98">
-        <v>4781</v>
+        <v>4515</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2154,10 +3324,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46278.01041666666</v>
+        <v>46279.01041666666</v>
       </c>
       <c r="B99">
-        <v>4681</v>
+        <v>4490</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2168,10 +3338,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46278.02083333334</v>
+        <v>46279.02083333334</v>
       </c>
       <c r="B100">
-        <v>4650</v>
+        <v>4408</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2182,10 +3352,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46278.03125</v>
+        <v>46279.03125</v>
       </c>
       <c r="B101">
-        <v>4592</v>
+        <v>4431</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2196,10 +3366,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46278.04166666666</v>
+        <v>46279.04166666666</v>
       </c>
       <c r="B102">
-        <v>4580</v>
+        <v>4447</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2210,10 +3380,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46278.05208333334</v>
+        <v>46279.05208333334</v>
       </c>
       <c r="B103">
-        <v>4617</v>
+        <v>4439</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2224,10 +3394,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46278.0625</v>
+        <v>46279.0625</v>
       </c>
       <c r="B104">
-        <v>4539</v>
+        <v>4437</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2238,10 +3408,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46278.07291666666</v>
+        <v>46279.07291666666</v>
       </c>
       <c r="B105">
-        <v>4567</v>
+        <v>4545</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2252,10 +3422,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46278.08333333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="B106">
-        <v>4447</v>
+        <v>4514</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2266,10 +3436,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46278.09375</v>
+        <v>46279.09375</v>
       </c>
       <c r="B107">
-        <v>4422</v>
+        <v>4477</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2280,10 +3450,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46278.10416666666</v>
+        <v>46279.10416666666</v>
       </c>
       <c r="B108">
-        <v>4402</v>
+        <v>4489</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2294,10 +3464,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46278.11458333334</v>
+        <v>46279.11458333334</v>
       </c>
       <c r="B109">
-        <v>4398</v>
+        <v>4540</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2308,10 +3478,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46278.125</v>
+        <v>46279.125</v>
       </c>
       <c r="B110">
-        <v>4368</v>
+        <v>4516</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2322,10 +3492,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46278.13541666666</v>
+        <v>46279.13541666666</v>
       </c>
       <c r="B111">
-        <v>4395</v>
+        <v>4541</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2336,10 +3506,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46278.14583333334</v>
+        <v>46279.14583333334</v>
       </c>
       <c r="B112">
-        <v>4413</v>
+        <v>4587</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2350,10 +3520,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46278.15625</v>
+        <v>46279.15625</v>
       </c>
       <c r="B113">
-        <v>4450</v>
+        <v>4723</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2364,10 +3534,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46278.16666666666</v>
+        <v>46279.16666666666</v>
       </c>
       <c r="B114">
-        <v>4504</v>
+        <v>4760</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2378,10 +3548,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46278.17708333334</v>
+        <v>46279.17708333334</v>
       </c>
       <c r="B115">
-        <v>4558</v>
+        <v>4670</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2392,10 +3562,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46278.1875</v>
+        <v>46279.1875</v>
       </c>
       <c r="B116">
-        <v>4541</v>
+        <v>4726</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2406,10 +3576,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46278.19791666666</v>
+        <v>46279.19791666666</v>
       </c>
       <c r="B117">
-        <v>4574</v>
+        <v>4871</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2420,10 +3590,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46278.20833333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="B118">
-        <v>4563</v>
+        <v>4947</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2434,10 +3604,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46278.21875</v>
+        <v>46279.21875</v>
       </c>
       <c r="B119">
-        <v>4594</v>
+        <v>5044</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2448,10 +3618,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46278.22916666666</v>
+        <v>46279.22916666666</v>
       </c>
       <c r="B120">
-        <v>4635</v>
+        <v>5174</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2462,10 +3632,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46278.23958333334</v>
+        <v>46279.23958333334</v>
       </c>
       <c r="B121">
-        <v>4653</v>
+        <v>5325</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2476,10 +3646,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46278.25</v>
+        <v>46279.25</v>
       </c>
       <c r="B122">
-        <v>4699</v>
+        <v>5566</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2490,10 +3660,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46278.26041666666</v>
+        <v>46279.26041666666</v>
       </c>
       <c r="B123">
-        <v>4671</v>
+        <v>5680</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2504,10 +3674,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46278.27083333334</v>
+        <v>46279.27083333334</v>
       </c>
       <c r="B124">
-        <v>4750</v>
+        <v>5718</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2518,10 +3688,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46278.28125</v>
+        <v>46279.28125</v>
       </c>
       <c r="B125">
-        <v>4759</v>
+        <v>5712</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2532,10 +3702,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46278.29166666666</v>
+        <v>46279.29166666666</v>
       </c>
       <c r="B126">
-        <v>4809</v>
+        <v>5789</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2546,10 +3716,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46278.30208333334</v>
+        <v>46279.30208333334</v>
       </c>
       <c r="B127">
-        <v>4789</v>
+        <v>5697</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2560,10 +3730,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46278.3125</v>
+        <v>46279.3125</v>
       </c>
       <c r="B128">
-        <v>4688</v>
+        <v>5634</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2574,10 +3744,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46278.32291666666</v>
+        <v>46279.32291666666</v>
       </c>
       <c r="B129">
-        <v>4721</v>
+        <v>5570</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2588,10 +3758,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46278.33333333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="B130">
-        <v>4692</v>
+        <v>5540</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2602,16 +3772,5476 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46278.34375</v>
+        <v>46279.34375</v>
       </c>
       <c r="B131">
-        <v>4631</v>
+        <v>5503</v>
       </c>
       <c r="C131">
         <v>34</v>
       </c>
       <c r="D131" t="s">
         <v>133</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="2">
+        <v>46279.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>5371</v>
+      </c>
+      <c r="C132">
+        <v>35</v>
+      </c>
+      <c r="D132" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="2">
+        <v>46279.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>5293</v>
+      </c>
+      <c r="C133">
+        <v>36</v>
+      </c>
+      <c r="D133" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="2">
+        <v>46279.375</v>
+      </c>
+      <c r="B134">
+        <v>5071</v>
+      </c>
+      <c r="C134">
+        <v>37</v>
+      </c>
+      <c r="D134" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="2">
+        <v>46279.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>4945</v>
+      </c>
+      <c r="C135">
+        <v>38</v>
+      </c>
+      <c r="D135" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="2">
+        <v>46279.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>4845</v>
+      </c>
+      <c r="C136">
+        <v>39</v>
+      </c>
+      <c r="D136" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="2">
+        <v>46279.40625</v>
+      </c>
+      <c r="B137">
+        <v>4762</v>
+      </c>
+      <c r="C137">
+        <v>40</v>
+      </c>
+      <c r="D137" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="2">
+        <v>46279.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>4749</v>
+      </c>
+      <c r="C138">
+        <v>41</v>
+      </c>
+      <c r="D138" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="2">
+        <v>46279.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>4672</v>
+      </c>
+      <c r="C139">
+        <v>42</v>
+      </c>
+      <c r="D139" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="2">
+        <v>46279.4375</v>
+      </c>
+      <c r="B140">
+        <v>4621</v>
+      </c>
+      <c r="C140">
+        <v>43</v>
+      </c>
+      <c r="D140" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="2">
+        <v>46279.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>4512</v>
+      </c>
+      <c r="C141">
+        <v>44</v>
+      </c>
+      <c r="D141" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="2">
+        <v>46279.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>4492</v>
+      </c>
+      <c r="C142">
+        <v>45</v>
+      </c>
+      <c r="D142" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="2">
+        <v>46279.46875</v>
+      </c>
+      <c r="B143">
+        <v>4375</v>
+      </c>
+      <c r="C143">
+        <v>46</v>
+      </c>
+      <c r="D143" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="2">
+        <v>46279.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>4467</v>
+      </c>
+      <c r="C144">
+        <v>47</v>
+      </c>
+      <c r="D144" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="2">
+        <v>46279.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>4356</v>
+      </c>
+      <c r="C145">
+        <v>48</v>
+      </c>
+      <c r="D145" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="2">
+        <v>46279.5</v>
+      </c>
+      <c r="B146">
+        <v>4498</v>
+      </c>
+      <c r="C146">
+        <v>49</v>
+      </c>
+      <c r="D146" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="2">
+        <v>46279.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>4603</v>
+      </c>
+      <c r="C147">
+        <v>50</v>
+      </c>
+      <c r="D147" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="2">
+        <v>46279.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>4685</v>
+      </c>
+      <c r="C148">
+        <v>51</v>
+      </c>
+      <c r="D148" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="2">
+        <v>46279.53125</v>
+      </c>
+      <c r="B149">
+        <v>4721</v>
+      </c>
+      <c r="C149">
+        <v>52</v>
+      </c>
+      <c r="D149" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="2">
+        <v>46279.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>4788</v>
+      </c>
+      <c r="C150">
+        <v>53</v>
+      </c>
+      <c r="D150" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="2">
+        <v>46279.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>4871</v>
+      </c>
+      <c r="C151">
+        <v>54</v>
+      </c>
+      <c r="D151" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="2">
+        <v>46279.5625</v>
+      </c>
+      <c r="B152">
+        <v>5039</v>
+      </c>
+      <c r="C152">
+        <v>55</v>
+      </c>
+      <c r="D152" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="2">
+        <v>46279.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>5157</v>
+      </c>
+      <c r="C153">
+        <v>56</v>
+      </c>
+      <c r="D153" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="2">
+        <v>46279.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>5252</v>
+      </c>
+      <c r="C154">
+        <v>57</v>
+      </c>
+      <c r="D154" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="2">
+        <v>46279.59375</v>
+      </c>
+      <c r="B155">
+        <v>5106</v>
+      </c>
+      <c r="C155">
+        <v>58</v>
+      </c>
+      <c r="D155" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" s="2">
+        <v>46279.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>5026</v>
+      </c>
+      <c r="C156">
+        <v>59</v>
+      </c>
+      <c r="D156" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" s="2">
+        <v>46279.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>5138</v>
+      </c>
+      <c r="C157">
+        <v>60</v>
+      </c>
+      <c r="D157" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" s="2">
+        <v>46279.625</v>
+      </c>
+      <c r="B158">
+        <v>5283</v>
+      </c>
+      <c r="C158">
+        <v>61</v>
+      </c>
+      <c r="D158" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" s="2">
+        <v>46279.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>5390</v>
+      </c>
+      <c r="C159">
+        <v>62</v>
+      </c>
+      <c r="D159" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="2">
+        <v>46279.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>5459</v>
+      </c>
+      <c r="C160">
+        <v>63</v>
+      </c>
+      <c r="D160" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" s="2">
+        <v>46279.65625</v>
+      </c>
+      <c r="B161">
+        <v>5483</v>
+      </c>
+      <c r="C161">
+        <v>64</v>
+      </c>
+      <c r="D161" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" s="2">
+        <v>46279.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>5593</v>
+      </c>
+      <c r="C162">
+        <v>65</v>
+      </c>
+      <c r="D162" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" s="2">
+        <v>46279.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>5688</v>
+      </c>
+      <c r="C163">
+        <v>66</v>
+      </c>
+      <c r="D163" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" s="2">
+        <v>46279.6875</v>
+      </c>
+      <c r="B164">
+        <v>5765</v>
+      </c>
+      <c r="C164">
+        <v>67</v>
+      </c>
+      <c r="D164" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" s="2">
+        <v>46279.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>5873</v>
+      </c>
+      <c r="C165">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" s="2">
+        <v>46279.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>5831</v>
+      </c>
+      <c r="C166">
+        <v>69</v>
+      </c>
+      <c r="D166" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" s="2">
+        <v>46279.71875</v>
+      </c>
+      <c r="B167">
+        <v>5978</v>
+      </c>
+      <c r="C167">
+        <v>70</v>
+      </c>
+      <c r="D167" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" s="2">
+        <v>46279.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>6063</v>
+      </c>
+      <c r="C168">
+        <v>71</v>
+      </c>
+      <c r="D168" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" s="2">
+        <v>46279.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>6104</v>
+      </c>
+      <c r="C169">
+        <v>72</v>
+      </c>
+      <c r="D169" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" s="2">
+        <v>46279.75</v>
+      </c>
+      <c r="B170">
+        <v>6161</v>
+      </c>
+      <c r="C170">
+        <v>73</v>
+      </c>
+      <c r="D170" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" s="2">
+        <v>46279.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>6304</v>
+      </c>
+      <c r="C171">
+        <v>74</v>
+      </c>
+      <c r="D171" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" s="2">
+        <v>46279.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>6383</v>
+      </c>
+      <c r="C172">
+        <v>75</v>
+      </c>
+      <c r="D172" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" s="2">
+        <v>46279.78125</v>
+      </c>
+      <c r="B173">
+        <v>6541</v>
+      </c>
+      <c r="C173">
+        <v>76</v>
+      </c>
+      <c r="D173" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" s="2">
+        <v>46279.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>6620</v>
+      </c>
+      <c r="C174">
+        <v>77</v>
+      </c>
+      <c r="D174" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" s="2">
+        <v>46279.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>6641</v>
+      </c>
+      <c r="C175">
+        <v>78</v>
+      </c>
+      <c r="D175" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" s="2">
+        <v>46279.8125</v>
+      </c>
+      <c r="B176">
+        <v>6656</v>
+      </c>
+      <c r="C176">
+        <v>79</v>
+      </c>
+      <c r="D176" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" s="2">
+        <v>46279.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>6536</v>
+      </c>
+      <c r="C177">
+        <v>80</v>
+      </c>
+      <c r="D177" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" s="2">
+        <v>46279.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>6485</v>
+      </c>
+      <c r="C178">
+        <v>81</v>
+      </c>
+      <c r="D178" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" s="2">
+        <v>46279.84375</v>
+      </c>
+      <c r="B179">
+        <v>6378</v>
+      </c>
+      <c r="C179">
+        <v>82</v>
+      </c>
+      <c r="D179" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" s="2">
+        <v>46279.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>6301</v>
+      </c>
+      <c r="C180">
+        <v>83</v>
+      </c>
+      <c r="D180" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" s="2">
+        <v>46279.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>6125</v>
+      </c>
+      <c r="C181">
+        <v>84</v>
+      </c>
+      <c r="D181" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" s="2">
+        <v>46279.875</v>
+      </c>
+      <c r="B182">
+        <v>5969</v>
+      </c>
+      <c r="C182">
+        <v>85</v>
+      </c>
+      <c r="D182" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" s="2">
+        <v>46279.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>5845</v>
+      </c>
+      <c r="C183">
+        <v>86</v>
+      </c>
+      <c r="D183" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184" s="2">
+        <v>46279.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>5734</v>
+      </c>
+      <c r="C184">
+        <v>87</v>
+      </c>
+      <c r="D184" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="A185" s="2">
+        <v>46279.90625</v>
+      </c>
+      <c r="B185">
+        <v>5598</v>
+      </c>
+      <c r="C185">
+        <v>88</v>
+      </c>
+      <c r="D185" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="A186" s="2">
+        <v>46279.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>5511</v>
+      </c>
+      <c r="C186">
+        <v>89</v>
+      </c>
+      <c r="D186" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="A187" s="2">
+        <v>46279.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>5425</v>
+      </c>
+      <c r="C187">
+        <v>90</v>
+      </c>
+      <c r="D187" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188" s="2">
+        <v>46279.9375</v>
+      </c>
+      <c r="B188">
+        <v>5344</v>
+      </c>
+      <c r="C188">
+        <v>91</v>
+      </c>
+      <c r="D188" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" s="2">
+        <v>46279.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>5258</v>
+      </c>
+      <c r="C189">
+        <v>92</v>
+      </c>
+      <c r="D189" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190" s="2">
+        <v>46279.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>5162</v>
+      </c>
+      <c r="C190">
+        <v>93</v>
+      </c>
+      <c r="D190" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" s="2">
+        <v>46279.96875</v>
+      </c>
+      <c r="B191">
+        <v>5171</v>
+      </c>
+      <c r="C191">
+        <v>94</v>
+      </c>
+      <c r="D191" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192" s="2">
+        <v>46279.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>5037</v>
+      </c>
+      <c r="C192">
+        <v>95</v>
+      </c>
+      <c r="D192" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193" s="2">
+        <v>46279.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>5006</v>
+      </c>
+      <c r="C193">
+        <v>96</v>
+      </c>
+      <c r="D193" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B194">
+        <v>5017</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" s="2">
+        <v>46280.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>4999</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+      <c r="D195" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" s="2">
+        <v>46280.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>4911</v>
+      </c>
+      <c r="C196">
+        <v>3</v>
+      </c>
+      <c r="D196" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" s="2">
+        <v>46280.03125</v>
+      </c>
+      <c r="B197">
+        <v>4942</v>
+      </c>
+      <c r="C197">
+        <v>4</v>
+      </c>
+      <c r="D197" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" s="2">
+        <v>46280.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>4878</v>
+      </c>
+      <c r="C198">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" s="2">
+        <v>46280.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>4798</v>
+      </c>
+      <c r="C199">
+        <v>6</v>
+      </c>
+      <c r="D199" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" s="2">
+        <v>46280.0625</v>
+      </c>
+      <c r="B200">
+        <v>4866</v>
+      </c>
+      <c r="C200">
+        <v>7</v>
+      </c>
+      <c r="D200" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" s="2">
+        <v>46280.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>4967</v>
+      </c>
+      <c r="C201">
+        <v>8</v>
+      </c>
+      <c r="D201" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" s="2">
+        <v>46280.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>5104</v>
+      </c>
+      <c r="C202">
+        <v>9</v>
+      </c>
+      <c r="D202" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" s="2">
+        <v>46280.09375</v>
+      </c>
+      <c r="B203">
+        <v>4994</v>
+      </c>
+      <c r="C203">
+        <v>10</v>
+      </c>
+      <c r="D203" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" s="2">
+        <v>46280.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>5022</v>
+      </c>
+      <c r="C204">
+        <v>11</v>
+      </c>
+      <c r="D204" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" s="2">
+        <v>46280.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>5005</v>
+      </c>
+      <c r="C205">
+        <v>12</v>
+      </c>
+      <c r="D205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" s="2">
+        <v>46280.125</v>
+      </c>
+      <c r="B206">
+        <v>5100</v>
+      </c>
+      <c r="C206">
+        <v>13</v>
+      </c>
+      <c r="D206" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" s="2">
+        <v>46280.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>5071</v>
+      </c>
+      <c r="C207">
+        <v>14</v>
+      </c>
+      <c r="D207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="2">
+        <v>46280.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>5140</v>
+      </c>
+      <c r="C208">
+        <v>15</v>
+      </c>
+      <c r="D208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="2">
+        <v>46280.15625</v>
+      </c>
+      <c r="B209">
+        <v>5183</v>
+      </c>
+      <c r="C209">
+        <v>16</v>
+      </c>
+      <c r="D209" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="2">
+        <v>46280.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>5164</v>
+      </c>
+      <c r="C210">
+        <v>17</v>
+      </c>
+      <c r="D210" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="2">
+        <v>46280.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>5119</v>
+      </c>
+      <c r="C211">
+        <v>18</v>
+      </c>
+      <c r="D211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="2">
+        <v>46280.1875</v>
+      </c>
+      <c r="B212">
+        <v>5219</v>
+      </c>
+      <c r="C212">
+        <v>19</v>
+      </c>
+      <c r="D212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="2">
+        <v>46280.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>5341</v>
+      </c>
+      <c r="C213">
+        <v>20</v>
+      </c>
+      <c r="D213" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="2">
+        <v>46280.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>5379</v>
+      </c>
+      <c r="C214">
+        <v>21</v>
+      </c>
+      <c r="D214" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="2">
+        <v>46280.21875</v>
+      </c>
+      <c r="B215">
+        <v>5446</v>
+      </c>
+      <c r="C215">
+        <v>22</v>
+      </c>
+      <c r="D215" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="2">
+        <v>46280.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>5549</v>
+      </c>
+      <c r="C216">
+        <v>23</v>
+      </c>
+      <c r="D216" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" s="2">
+        <v>46280.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>5699</v>
+      </c>
+      <c r="C217">
+        <v>24</v>
+      </c>
+      <c r="D217" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" s="2">
+        <v>46280.25</v>
+      </c>
+      <c r="B218">
+        <v>5940</v>
+      </c>
+      <c r="C218">
+        <v>25</v>
+      </c>
+      <c r="D218" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" s="2">
+        <v>46280.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>6027</v>
+      </c>
+      <c r="C219">
+        <v>26</v>
+      </c>
+      <c r="D219" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="2">
+        <v>46280.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>6062</v>
+      </c>
+      <c r="C220">
+        <v>27</v>
+      </c>
+      <c r="D220" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" s="2">
+        <v>46280.28125</v>
+      </c>
+      <c r="B221">
+        <v>6109</v>
+      </c>
+      <c r="C221">
+        <v>28</v>
+      </c>
+      <c r="D221" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" s="2">
+        <v>46280.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>6117</v>
+      </c>
+      <c r="C222">
+        <v>29</v>
+      </c>
+      <c r="D222" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" s="2">
+        <v>46280.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>6121</v>
+      </c>
+      <c r="C223">
+        <v>30</v>
+      </c>
+      <c r="D223" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="2">
+        <v>46280.3125</v>
+      </c>
+      <c r="B224">
+        <v>6036</v>
+      </c>
+      <c r="C224">
+        <v>31</v>
+      </c>
+      <c r="D224" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="2">
+        <v>46280.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>6021</v>
+      </c>
+      <c r="C225">
+        <v>32</v>
+      </c>
+      <c r="D225" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="2">
+        <v>46280.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>5923</v>
+      </c>
+      <c r="C226">
+        <v>33</v>
+      </c>
+      <c r="D226" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="2">
+        <v>46280.34375</v>
+      </c>
+      <c r="B227">
+        <v>5763</v>
+      </c>
+      <c r="C227">
+        <v>34</v>
+      </c>
+      <c r="D227" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="2">
+        <v>46280.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>5624</v>
+      </c>
+      <c r="C228">
+        <v>35</v>
+      </c>
+      <c r="D228" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="2">
+        <v>46280.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>5557</v>
+      </c>
+      <c r="C229">
+        <v>36</v>
+      </c>
+      <c r="D229" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="2">
+        <v>46280.375</v>
+      </c>
+      <c r="B230">
+        <v>5349</v>
+      </c>
+      <c r="C230">
+        <v>37</v>
+      </c>
+      <c r="D230" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="2">
+        <v>46280.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>5247</v>
+      </c>
+      <c r="C231">
+        <v>38</v>
+      </c>
+      <c r="D231" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="2">
+        <v>46280.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>5153</v>
+      </c>
+      <c r="C232">
+        <v>39</v>
+      </c>
+      <c r="D232" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" s="2">
+        <v>46280.40625</v>
+      </c>
+      <c r="B233">
+        <v>5031</v>
+      </c>
+      <c r="C233">
+        <v>40</v>
+      </c>
+      <c r="D233" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" s="2">
+        <v>46280.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>4882</v>
+      </c>
+      <c r="C234">
+        <v>41</v>
+      </c>
+      <c r="D234" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="2">
+        <v>46280.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>4696</v>
+      </c>
+      <c r="C235">
+        <v>42</v>
+      </c>
+      <c r="D235" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="2">
+        <v>46280.4375</v>
+      </c>
+      <c r="B236">
+        <v>4586</v>
+      </c>
+      <c r="C236">
+        <v>43</v>
+      </c>
+      <c r="D236" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="2">
+        <v>46280.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>4489</v>
+      </c>
+      <c r="C237">
+        <v>44</v>
+      </c>
+      <c r="D237" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="2">
+        <v>46280.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>4359</v>
+      </c>
+      <c r="C238">
+        <v>45</v>
+      </c>
+      <c r="D238" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="2">
+        <v>46280.46875</v>
+      </c>
+      <c r="B239">
+        <v>4364</v>
+      </c>
+      <c r="C239">
+        <v>46</v>
+      </c>
+      <c r="D239" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="2">
+        <v>46280.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>4367</v>
+      </c>
+      <c r="C240">
+        <v>47</v>
+      </c>
+      <c r="D240" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" s="2">
+        <v>46280.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>4458</v>
+      </c>
+      <c r="C241">
+        <v>48</v>
+      </c>
+      <c r="D241" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" s="2">
+        <v>46280.5</v>
+      </c>
+      <c r="B242">
+        <v>4489</v>
+      </c>
+      <c r="C242">
+        <v>49</v>
+      </c>
+      <c r="D242" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" s="2">
+        <v>46280.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>4539</v>
+      </c>
+      <c r="C243">
+        <v>50</v>
+      </c>
+      <c r="D243" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" s="2">
+        <v>46280.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>4480</v>
+      </c>
+      <c r="C244">
+        <v>51</v>
+      </c>
+      <c r="D244" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="2">
+        <v>46280.53125</v>
+      </c>
+      <c r="B245">
+        <v>4580</v>
+      </c>
+      <c r="C245">
+        <v>52</v>
+      </c>
+      <c r="D245" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="2">
+        <v>46280.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>4566</v>
+      </c>
+      <c r="C246">
+        <v>53</v>
+      </c>
+      <c r="D246" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" s="2">
+        <v>46280.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>4761</v>
+      </c>
+      <c r="C247">
+        <v>54</v>
+      </c>
+      <c r="D247" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="2">
+        <v>46280.5625</v>
+      </c>
+      <c r="B248">
+        <v>4714</v>
+      </c>
+      <c r="C248">
+        <v>55</v>
+      </c>
+      <c r="D248" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" s="2">
+        <v>46280.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>4673</v>
+      </c>
+      <c r="C249">
+        <v>56</v>
+      </c>
+      <c r="D249" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" s="2">
+        <v>46280.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>4651</v>
+      </c>
+      <c r="C250">
+        <v>57</v>
+      </c>
+      <c r="D250" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" s="2">
+        <v>46280.59375</v>
+      </c>
+      <c r="B251">
+        <v>4722</v>
+      </c>
+      <c r="C251">
+        <v>58</v>
+      </c>
+      <c r="D251" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" s="2">
+        <v>46280.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>4824</v>
+      </c>
+      <c r="C252">
+        <v>59</v>
+      </c>
+      <c r="D252" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" s="2">
+        <v>46280.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>5008</v>
+      </c>
+      <c r="C253">
+        <v>60</v>
+      </c>
+      <c r="D253" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" s="2">
+        <v>46280.625</v>
+      </c>
+      <c r="B254">
+        <v>5101</v>
+      </c>
+      <c r="C254">
+        <v>61</v>
+      </c>
+      <c r="D254" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" s="2">
+        <v>46280.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>5173</v>
+      </c>
+      <c r="C255">
+        <v>62</v>
+      </c>
+      <c r="D255" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" s="2">
+        <v>46280.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>5318</v>
+      </c>
+      <c r="C256">
+        <v>63</v>
+      </c>
+      <c r="D256" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="2">
+        <v>46280.65625</v>
+      </c>
+      <c r="B257">
+        <v>5563</v>
+      </c>
+      <c r="C257">
+        <v>64</v>
+      </c>
+      <c r="D257" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" s="2">
+        <v>46280.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>5651</v>
+      </c>
+      <c r="C258">
+        <v>65</v>
+      </c>
+      <c r="D258" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" s="2">
+        <v>46280.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>5833</v>
+      </c>
+      <c r="C259">
+        <v>66</v>
+      </c>
+      <c r="D259" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" s="2">
+        <v>46280.6875</v>
+      </c>
+      <c r="B260">
+        <v>5977</v>
+      </c>
+      <c r="C260">
+        <v>67</v>
+      </c>
+      <c r="D260" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" s="2">
+        <v>46280.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>6105</v>
+      </c>
+      <c r="C261">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" s="2">
+        <v>46280.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>6198</v>
+      </c>
+      <c r="C262">
+        <v>69</v>
+      </c>
+      <c r="D262" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" s="2">
+        <v>46280.71875</v>
+      </c>
+      <c r="B263">
+        <v>6297</v>
+      </c>
+      <c r="C263">
+        <v>70</v>
+      </c>
+      <c r="D263" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" s="2">
+        <v>46280.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>6416</v>
+      </c>
+      <c r="C264">
+        <v>71</v>
+      </c>
+      <c r="D264" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" s="2">
+        <v>46280.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>6441</v>
+      </c>
+      <c r="C265">
+        <v>72</v>
+      </c>
+      <c r="D265" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="2">
+        <v>46280.75</v>
+      </c>
+      <c r="B266">
+        <v>6483</v>
+      </c>
+      <c r="C266">
+        <v>73</v>
+      </c>
+      <c r="D266" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="2">
+        <v>46280.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>6516</v>
+      </c>
+      <c r="C267">
+        <v>74</v>
+      </c>
+      <c r="D267" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="2">
+        <v>46280.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>6724</v>
+      </c>
+      <c r="C268">
+        <v>75</v>
+      </c>
+      <c r="D268" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="2">
+        <v>46280.78125</v>
+      </c>
+      <c r="B269">
+        <v>6831</v>
+      </c>
+      <c r="C269">
+        <v>76</v>
+      </c>
+      <c r="D269" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="2">
+        <v>46280.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>6903</v>
+      </c>
+      <c r="C270">
+        <v>77</v>
+      </c>
+      <c r="D270" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="2">
+        <v>46280.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>6898</v>
+      </c>
+      <c r="C271">
+        <v>78</v>
+      </c>
+      <c r="D271" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="2">
+        <v>46280.8125</v>
+      </c>
+      <c r="B272">
+        <v>6938</v>
+      </c>
+      <c r="C272">
+        <v>79</v>
+      </c>
+      <c r="D272" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="2">
+        <v>46280.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>6861</v>
+      </c>
+      <c r="C273">
+        <v>80</v>
+      </c>
+      <c r="D273" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="2">
+        <v>46280.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>6767</v>
+      </c>
+      <c r="C274">
+        <v>81</v>
+      </c>
+      <c r="D274" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="2">
+        <v>46280.84375</v>
+      </c>
+      <c r="B275">
+        <v>6625</v>
+      </c>
+      <c r="C275">
+        <v>82</v>
+      </c>
+      <c r="D275" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="2">
+        <v>46280.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>6541</v>
+      </c>
+      <c r="C276">
+        <v>83</v>
+      </c>
+      <c r="D276" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="2">
+        <v>46280.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>6393</v>
+      </c>
+      <c r="C277">
+        <v>84</v>
+      </c>
+      <c r="D277" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="2">
+        <v>46280.875</v>
+      </c>
+      <c r="B278">
+        <v>6201</v>
+      </c>
+      <c r="C278">
+        <v>85</v>
+      </c>
+      <c r="D278" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" s="2">
+        <v>46280.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>6079</v>
+      </c>
+      <c r="C279">
+        <v>86</v>
+      </c>
+      <c r="D279" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" s="2">
+        <v>46280.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>5977</v>
+      </c>
+      <c r="C280">
+        <v>87</v>
+      </c>
+      <c r="D280" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="2">
+        <v>46280.90625</v>
+      </c>
+      <c r="B281">
+        <v>5842</v>
+      </c>
+      <c r="C281">
+        <v>88</v>
+      </c>
+      <c r="D281" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" s="2">
+        <v>46280.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>5771</v>
+      </c>
+      <c r="C282">
+        <v>89</v>
+      </c>
+      <c r="D282" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="2">
+        <v>46280.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>5638</v>
+      </c>
+      <c r="C283">
+        <v>90</v>
+      </c>
+      <c r="D283" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" s="2">
+        <v>46280.9375</v>
+      </c>
+      <c r="B284">
+        <v>5522</v>
+      </c>
+      <c r="C284">
+        <v>91</v>
+      </c>
+      <c r="D284" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" s="2">
+        <v>46280.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>5441</v>
+      </c>
+      <c r="C285">
+        <v>92</v>
+      </c>
+      <c r="D285" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" s="2">
+        <v>46280.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>5321</v>
+      </c>
+      <c r="C286">
+        <v>93</v>
+      </c>
+      <c r="D286" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" s="2">
+        <v>46280.96875</v>
+      </c>
+      <c r="B287">
+        <v>5193</v>
+      </c>
+      <c r="C287">
+        <v>94</v>
+      </c>
+      <c r="D287" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" s="2">
+        <v>46280.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>5106</v>
+      </c>
+      <c r="C288">
+        <v>95</v>
+      </c>
+      <c r="D288" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" s="2">
+        <v>46280.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>5123</v>
+      </c>
+      <c r="C289">
+        <v>96</v>
+      </c>
+      <c r="D289" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B290">
+        <v>5084</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="D290" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" s="2">
+        <v>46281.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>5007</v>
+      </c>
+      <c r="C291">
+        <v>2</v>
+      </c>
+      <c r="D291" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="2">
+        <v>46281.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>4971</v>
+      </c>
+      <c r="C292">
+        <v>3</v>
+      </c>
+      <c r="D292" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" s="2">
+        <v>46281.03125</v>
+      </c>
+      <c r="B293">
+        <v>4971</v>
+      </c>
+      <c r="C293">
+        <v>4</v>
+      </c>
+      <c r="D293" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="2">
+        <v>46281.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>4990</v>
+      </c>
+      <c r="C294">
+        <v>5</v>
+      </c>
+      <c r="D294" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" s="2">
+        <v>46281.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>4979</v>
+      </c>
+      <c r="C295">
+        <v>6</v>
+      </c>
+      <c r="D295" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" s="2">
+        <v>46281.0625</v>
+      </c>
+      <c r="B296">
+        <v>4972</v>
+      </c>
+      <c r="C296">
+        <v>7</v>
+      </c>
+      <c r="D296" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" s="2">
+        <v>46281.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>5089</v>
+      </c>
+      <c r="C297">
+        <v>8</v>
+      </c>
+      <c r="D297" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" s="2">
+        <v>46281.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>5142</v>
+      </c>
+      <c r="C298">
+        <v>9</v>
+      </c>
+      <c r="D298" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" s="2">
+        <v>46281.09375</v>
+      </c>
+      <c r="B299">
+        <v>5142</v>
+      </c>
+      <c r="C299">
+        <v>10</v>
+      </c>
+      <c r="D299" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" s="2">
+        <v>46281.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>5221</v>
+      </c>
+      <c r="C300">
+        <v>11</v>
+      </c>
+      <c r="D300" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" s="2">
+        <v>46281.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>5247</v>
+      </c>
+      <c r="C301">
+        <v>12</v>
+      </c>
+      <c r="D301" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" s="2">
+        <v>46281.125</v>
+      </c>
+      <c r="B302">
+        <v>5111</v>
+      </c>
+      <c r="C302">
+        <v>13</v>
+      </c>
+      <c r="D302" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" s="2">
+        <v>46281.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>5143</v>
+      </c>
+      <c r="C303">
+        <v>14</v>
+      </c>
+      <c r="D303" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" s="2">
+        <v>46281.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>5179</v>
+      </c>
+      <c r="C304">
+        <v>15</v>
+      </c>
+      <c r="D304" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" s="2">
+        <v>46281.15625</v>
+      </c>
+      <c r="B305">
+        <v>5141</v>
+      </c>
+      <c r="C305">
+        <v>16</v>
+      </c>
+      <c r="D305" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306" s="2">
+        <v>46281.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>5294</v>
+      </c>
+      <c r="C306">
+        <v>17</v>
+      </c>
+      <c r="D306" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307" s="2">
+        <v>46281.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>5303</v>
+      </c>
+      <c r="C307">
+        <v>18</v>
+      </c>
+      <c r="D307" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" s="2">
+        <v>46281.1875</v>
+      </c>
+      <c r="B308">
+        <v>5265</v>
+      </c>
+      <c r="C308">
+        <v>19</v>
+      </c>
+      <c r="D308" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309" s="2">
+        <v>46281.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>5236</v>
+      </c>
+      <c r="C309">
+        <v>20</v>
+      </c>
+      <c r="D309" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" s="2">
+        <v>46281.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>5364</v>
+      </c>
+      <c r="C310">
+        <v>21</v>
+      </c>
+      <c r="D310" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" s="2">
+        <v>46281.21875</v>
+      </c>
+      <c r="B311">
+        <v>5493</v>
+      </c>
+      <c r="C311">
+        <v>22</v>
+      </c>
+      <c r="D311" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" s="2">
+        <v>46281.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>5631</v>
+      </c>
+      <c r="C312">
+        <v>23</v>
+      </c>
+      <c r="D312" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" s="2">
+        <v>46281.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>5649</v>
+      </c>
+      <c r="C313">
+        <v>24</v>
+      </c>
+      <c r="D313" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314" s="2">
+        <v>46281.25</v>
+      </c>
+      <c r="B314">
+        <v>5911</v>
+      </c>
+      <c r="C314">
+        <v>25</v>
+      </c>
+      <c r="D314" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315" s="2">
+        <v>46281.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>6009</v>
+      </c>
+      <c r="C315">
+        <v>26</v>
+      </c>
+      <c r="D315" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316" s="2">
+        <v>46281.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>6031</v>
+      </c>
+      <c r="C316">
+        <v>27</v>
+      </c>
+      <c r="D316" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" s="2">
+        <v>46281.28125</v>
+      </c>
+      <c r="B317">
+        <v>6001</v>
+      </c>
+      <c r="C317">
+        <v>28</v>
+      </c>
+      <c r="D317" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" s="2">
+        <v>46281.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>5994</v>
+      </c>
+      <c r="C318">
+        <v>29</v>
+      </c>
+      <c r="D318" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" s="2">
+        <v>46281.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>5989</v>
+      </c>
+      <c r="C319">
+        <v>30</v>
+      </c>
+      <c r="D319" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" s="2">
+        <v>46281.3125</v>
+      </c>
+      <c r="B320">
+        <v>5832</v>
+      </c>
+      <c r="C320">
+        <v>31</v>
+      </c>
+      <c r="D320" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" s="2">
+        <v>46281.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>5739</v>
+      </c>
+      <c r="C321">
+        <v>32</v>
+      </c>
+      <c r="D321" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" s="2">
+        <v>46281.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>5553</v>
+      </c>
+      <c r="C322">
+        <v>33</v>
+      </c>
+      <c r="D322" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" s="2">
+        <v>46281.34375</v>
+      </c>
+      <c r="B323">
+        <v>5441</v>
+      </c>
+      <c r="C323">
+        <v>34</v>
+      </c>
+      <c r="D323" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" s="2">
+        <v>46281.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>5283</v>
+      </c>
+      <c r="C324">
+        <v>35</v>
+      </c>
+      <c r="D324" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325" s="2">
+        <v>46281.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>5193</v>
+      </c>
+      <c r="C325">
+        <v>36</v>
+      </c>
+      <c r="D325" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" s="2">
+        <v>46281.375</v>
+      </c>
+      <c r="B326">
+        <v>4935</v>
+      </c>
+      <c r="C326">
+        <v>37</v>
+      </c>
+      <c r="D326" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327" s="2">
+        <v>46281.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>4738</v>
+      </c>
+      <c r="C327">
+        <v>38</v>
+      </c>
+      <c r="D327" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328" s="2">
+        <v>46281.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>4653</v>
+      </c>
+      <c r="C328">
+        <v>39</v>
+      </c>
+      <c r="D328" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" s="2">
+        <v>46281.40625</v>
+      </c>
+      <c r="B329">
+        <v>4481</v>
+      </c>
+      <c r="C329">
+        <v>40</v>
+      </c>
+      <c r="D329" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330" s="2">
+        <v>46281.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>4339</v>
+      </c>
+      <c r="C330">
+        <v>41</v>
+      </c>
+      <c r="D330" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331" s="2">
+        <v>46281.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>4186</v>
+      </c>
+      <c r="C331">
+        <v>42</v>
+      </c>
+      <c r="D331" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" s="2">
+        <v>46281.4375</v>
+      </c>
+      <c r="B332">
+        <v>4164</v>
+      </c>
+      <c r="C332">
+        <v>43</v>
+      </c>
+      <c r="D332" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333" s="2">
+        <v>46281.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>4101</v>
+      </c>
+      <c r="C333">
+        <v>44</v>
+      </c>
+      <c r="D333" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334" s="2">
+        <v>46281.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>4145</v>
+      </c>
+      <c r="C334">
+        <v>45</v>
+      </c>
+      <c r="D334" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" s="2">
+        <v>46281.46875</v>
+      </c>
+      <c r="B335">
+        <v>4103</v>
+      </c>
+      <c r="C335">
+        <v>46</v>
+      </c>
+      <c r="D335" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" s="2">
+        <v>46281.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>4121</v>
+      </c>
+      <c r="C336">
+        <v>47</v>
+      </c>
+      <c r="D336" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337" s="2">
+        <v>46281.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>4204</v>
+      </c>
+      <c r="C337">
+        <v>48</v>
+      </c>
+      <c r="D337" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338" s="2">
+        <v>46281.5</v>
+      </c>
+      <c r="B338">
+        <v>4322</v>
+      </c>
+      <c r="C338">
+        <v>49</v>
+      </c>
+      <c r="D338" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
+      <c r="A339" s="2">
+        <v>46281.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>4316</v>
+      </c>
+      <c r="C339">
+        <v>50</v>
+      </c>
+      <c r="D339" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340" s="2">
+        <v>46281.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>4347</v>
+      </c>
+      <c r="C340">
+        <v>51</v>
+      </c>
+      <c r="D340" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341" s="2">
+        <v>46281.53125</v>
+      </c>
+      <c r="B341">
+        <v>4338</v>
+      </c>
+      <c r="C341">
+        <v>52</v>
+      </c>
+      <c r="D341" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
+      <c r="A342" s="2">
+        <v>46281.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>4469</v>
+      </c>
+      <c r="C342">
+        <v>53</v>
+      </c>
+      <c r="D342" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343" s="2">
+        <v>46281.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>4473</v>
+      </c>
+      <c r="C343">
+        <v>54</v>
+      </c>
+      <c r="D343" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
+      <c r="A344" s="2">
+        <v>46281.5625</v>
+      </c>
+      <c r="B344">
+        <v>4523</v>
+      </c>
+      <c r="C344">
+        <v>55</v>
+      </c>
+      <c r="D344" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
+      <c r="A345" s="2">
+        <v>46281.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>4548</v>
+      </c>
+      <c r="C345">
+        <v>56</v>
+      </c>
+      <c r="D345" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
+      <c r="A346" s="2">
+        <v>46281.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>4596</v>
+      </c>
+      <c r="C346">
+        <v>57</v>
+      </c>
+      <c r="D346" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
+      <c r="A347" s="2">
+        <v>46281.59375</v>
+      </c>
+      <c r="B347">
+        <v>4569</v>
+      </c>
+      <c r="C347">
+        <v>58</v>
+      </c>
+      <c r="D347" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
+      <c r="A348" s="2">
+        <v>46281.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>4550</v>
+      </c>
+      <c r="C348">
+        <v>59</v>
+      </c>
+      <c r="D348" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349" s="2">
+        <v>46281.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>4660</v>
+      </c>
+      <c r="C349">
+        <v>60</v>
+      </c>
+      <c r="D349" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350" s="2">
+        <v>46281.625</v>
+      </c>
+      <c r="B350">
+        <v>4792</v>
+      </c>
+      <c r="C350">
+        <v>61</v>
+      </c>
+      <c r="D350" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351" s="2">
+        <v>46281.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>4922</v>
+      </c>
+      <c r="C351">
+        <v>62</v>
+      </c>
+      <c r="D351" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
+      <c r="A352" s="2">
+        <v>46281.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>4988</v>
+      </c>
+      <c r="C352">
+        <v>63</v>
+      </c>
+      <c r="D352" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
+      <c r="A353" s="2">
+        <v>46281.65625</v>
+      </c>
+      <c r="B353">
+        <v>5204</v>
+      </c>
+      <c r="C353">
+        <v>64</v>
+      </c>
+      <c r="D353" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
+      <c r="A354" s="2">
+        <v>46281.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>5348</v>
+      </c>
+      <c r="C354">
+        <v>65</v>
+      </c>
+      <c r="D354" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
+      <c r="A355" s="2">
+        <v>46281.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>5519</v>
+      </c>
+      <c r="C355">
+        <v>66</v>
+      </c>
+      <c r="D355" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
+      <c r="A356" s="2">
+        <v>46281.6875</v>
+      </c>
+      <c r="B356">
+        <v>5668</v>
+      </c>
+      <c r="C356">
+        <v>67</v>
+      </c>
+      <c r="D356" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
+      <c r="A357" s="2">
+        <v>46281.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>5858</v>
+      </c>
+      <c r="C357">
+        <v>68</v>
+      </c>
+      <c r="D357" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
+      <c r="A358" s="2">
+        <v>46281.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>6001</v>
+      </c>
+      <c r="C358">
+        <v>69</v>
+      </c>
+      <c r="D358" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
+      <c r="A359" s="2">
+        <v>46281.71875</v>
+      </c>
+      <c r="B359">
+        <v>6216</v>
+      </c>
+      <c r="C359">
+        <v>70</v>
+      </c>
+      <c r="D359" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
+      <c r="A360" s="2">
+        <v>46281.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>6312</v>
+      </c>
+      <c r="C360">
+        <v>71</v>
+      </c>
+      <c r="D360" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
+      <c r="A361" s="2">
+        <v>46281.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>6435</v>
+      </c>
+      <c r="C361">
+        <v>72</v>
+      </c>
+      <c r="D361" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
+      <c r="A362" s="2">
+        <v>46281.75</v>
+      </c>
+      <c r="B362">
+        <v>6437</v>
+      </c>
+      <c r="C362">
+        <v>73</v>
+      </c>
+      <c r="D362" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
+      <c r="A363" s="2">
+        <v>46281.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>6561</v>
+      </c>
+      <c r="C363">
+        <v>74</v>
+      </c>
+      <c r="D363" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364" s="2">
+        <v>46281.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>6668</v>
+      </c>
+      <c r="C364">
+        <v>75</v>
+      </c>
+      <c r="D364" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365" s="2">
+        <v>46281.78125</v>
+      </c>
+      <c r="B365">
+        <v>6765</v>
+      </c>
+      <c r="C365">
+        <v>76</v>
+      </c>
+      <c r="D365" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366" s="2">
+        <v>46281.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>6880</v>
+      </c>
+      <c r="C366">
+        <v>77</v>
+      </c>
+      <c r="D366" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367" s="2">
+        <v>46281.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>6900</v>
+      </c>
+      <c r="C367">
+        <v>78</v>
+      </c>
+      <c r="D367" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
+      <c r="A368" s="2">
+        <v>46281.8125</v>
+      </c>
+      <c r="B368">
+        <v>6913</v>
+      </c>
+      <c r="C368">
+        <v>79</v>
+      </c>
+      <c r="D368" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369" s="2">
+        <v>46281.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>6862</v>
+      </c>
+      <c r="C369">
+        <v>80</v>
+      </c>
+      <c r="D369" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
+      <c r="A370" s="2">
+        <v>46281.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>6710</v>
+      </c>
+      <c r="C370">
+        <v>81</v>
+      </c>
+      <c r="D370" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371" s="2">
+        <v>46281.84375</v>
+      </c>
+      <c r="B371">
+        <v>6640</v>
+      </c>
+      <c r="C371">
+        <v>82</v>
+      </c>
+      <c r="D371" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
+      <c r="A372" s="2">
+        <v>46281.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>6489</v>
+      </c>
+      <c r="C372">
+        <v>83</v>
+      </c>
+      <c r="D372" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373" s="2">
+        <v>46281.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>6378</v>
+      </c>
+      <c r="C373">
+        <v>84</v>
+      </c>
+      <c r="D373" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374" s="2">
+        <v>46281.875</v>
+      </c>
+      <c r="B374">
+        <v>6171</v>
+      </c>
+      <c r="C374">
+        <v>85</v>
+      </c>
+      <c r="D374" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
+      <c r="A375" s="2">
+        <v>46281.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>6021</v>
+      </c>
+      <c r="C375">
+        <v>86</v>
+      </c>
+      <c r="D375" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
+      <c r="A376" s="2">
+        <v>46281.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>5868</v>
+      </c>
+      <c r="C376">
+        <v>87</v>
+      </c>
+      <c r="D376" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
+      <c r="A377" s="2">
+        <v>46281.90625</v>
+      </c>
+      <c r="B377">
+        <v>5784</v>
+      </c>
+      <c r="C377">
+        <v>88</v>
+      </c>
+      <c r="D377" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
+      <c r="A378" s="2">
+        <v>46281.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>5657</v>
+      </c>
+      <c r="C378">
+        <v>89</v>
+      </c>
+      <c r="D378" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
+      <c r="A379" s="2">
+        <v>46281.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>5544</v>
+      </c>
+      <c r="C379">
+        <v>90</v>
+      </c>
+      <c r="D379" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
+      <c r="A380" s="2">
+        <v>46281.9375</v>
+      </c>
+      <c r="B380">
+        <v>5424</v>
+      </c>
+      <c r="C380">
+        <v>91</v>
+      </c>
+      <c r="D380" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
+      <c r="A381" s="2">
+        <v>46281.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>5347</v>
+      </c>
+      <c r="C381">
+        <v>92</v>
+      </c>
+      <c r="D381" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
+      <c r="A382" s="2">
+        <v>46281.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>5253</v>
+      </c>
+      <c r="C382">
+        <v>93</v>
+      </c>
+      <c r="D382" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
+      <c r="A383" s="2">
+        <v>46281.96875</v>
+      </c>
+      <c r="B383">
+        <v>5168</v>
+      </c>
+      <c r="C383">
+        <v>94</v>
+      </c>
+      <c r="D383" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
+      <c r="A384" s="2">
+        <v>46281.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>5097</v>
+      </c>
+      <c r="C384">
+        <v>95</v>
+      </c>
+      <c r="D384" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
+      <c r="A385" s="2">
+        <v>46281.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>5070</v>
+      </c>
+      <c r="C385">
+        <v>96</v>
+      </c>
+      <c r="D385" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4">
+      <c r="A386" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B386">
+        <v>5023</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+      <c r="D386" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4">
+      <c r="A387" s="2">
+        <v>46282.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>5005</v>
+      </c>
+      <c r="C387">
+        <v>2</v>
+      </c>
+      <c r="D387" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4">
+      <c r="A388" s="2">
+        <v>46282.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>4945</v>
+      </c>
+      <c r="C388">
+        <v>3</v>
+      </c>
+      <c r="D388" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4">
+      <c r="A389" s="2">
+        <v>46282.03125</v>
+      </c>
+      <c r="B389">
+        <v>4931</v>
+      </c>
+      <c r="C389">
+        <v>4</v>
+      </c>
+      <c r="D389" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4">
+      <c r="A390" s="2">
+        <v>46282.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>4875</v>
+      </c>
+      <c r="C390">
+        <v>5</v>
+      </c>
+      <c r="D390" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4">
+      <c r="A391" s="2">
+        <v>46282.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>4912</v>
+      </c>
+      <c r="C391">
+        <v>6</v>
+      </c>
+      <c r="D391" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4">
+      <c r="A392" s="2">
+        <v>46282.0625</v>
+      </c>
+      <c r="B392">
+        <v>4874</v>
+      </c>
+      <c r="C392">
+        <v>7</v>
+      </c>
+      <c r="D392" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4">
+      <c r="A393" s="2">
+        <v>46282.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>4975</v>
+      </c>
+      <c r="C393">
+        <v>8</v>
+      </c>
+      <c r="D393" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4">
+      <c r="A394" s="2">
+        <v>46282.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>4999</v>
+      </c>
+      <c r="C394">
+        <v>9</v>
+      </c>
+      <c r="D394" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4">
+      <c r="A395" s="2">
+        <v>46282.09375</v>
+      </c>
+      <c r="B395">
+        <v>5073</v>
+      </c>
+      <c r="C395">
+        <v>10</v>
+      </c>
+      <c r="D395" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4">
+      <c r="A396" s="2">
+        <v>46282.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>5104</v>
+      </c>
+      <c r="C396">
+        <v>11</v>
+      </c>
+      <c r="D396" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4">
+      <c r="A397" s="2">
+        <v>46282.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>5157</v>
+      </c>
+      <c r="C397">
+        <v>12</v>
+      </c>
+      <c r="D397" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4">
+      <c r="A398" s="2">
+        <v>46282.125</v>
+      </c>
+      <c r="B398">
+        <v>5160</v>
+      </c>
+      <c r="C398">
+        <v>13</v>
+      </c>
+      <c r="D398" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4">
+      <c r="A399" s="2">
+        <v>46282.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>5186</v>
+      </c>
+      <c r="C399">
+        <v>14</v>
+      </c>
+      <c r="D399" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4">
+      <c r="A400" s="2">
+        <v>46282.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>5220</v>
+      </c>
+      <c r="C400">
+        <v>15</v>
+      </c>
+      <c r="D400" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4">
+      <c r="A401" s="2">
+        <v>46282.15625</v>
+      </c>
+      <c r="B401">
+        <v>5203</v>
+      </c>
+      <c r="C401">
+        <v>16</v>
+      </c>
+      <c r="D401" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4">
+      <c r="A402" s="2">
+        <v>46282.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>5286</v>
+      </c>
+      <c r="C402">
+        <v>17</v>
+      </c>
+      <c r="D402" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4">
+      <c r="A403" s="2">
+        <v>46282.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>5208</v>
+      </c>
+      <c r="C403">
+        <v>18</v>
+      </c>
+      <c r="D403" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4">
+      <c r="A404" s="2">
+        <v>46282.1875</v>
+      </c>
+      <c r="B404">
+        <v>5261</v>
+      </c>
+      <c r="C404">
+        <v>19</v>
+      </c>
+      <c r="D404" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4">
+      <c r="A405" s="2">
+        <v>46282.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>5298</v>
+      </c>
+      <c r="C405">
+        <v>20</v>
+      </c>
+      <c r="D405" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4">
+      <c r="A406" s="2">
+        <v>46282.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>5381</v>
+      </c>
+      <c r="C406">
+        <v>21</v>
+      </c>
+      <c r="D406" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4">
+      <c r="A407" s="2">
+        <v>46282.21875</v>
+      </c>
+      <c r="B407">
+        <v>5483</v>
+      </c>
+      <c r="C407">
+        <v>22</v>
+      </c>
+      <c r="D407" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4">
+      <c r="A408" s="2">
+        <v>46282.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>5583</v>
+      </c>
+      <c r="C408">
+        <v>23</v>
+      </c>
+      <c r="D408" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4">
+      <c r="A409" s="2">
+        <v>46282.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>5693</v>
+      </c>
+      <c r="C409">
+        <v>24</v>
+      </c>
+      <c r="D409" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4">
+      <c r="A410" s="2">
+        <v>46282.25</v>
+      </c>
+      <c r="B410">
+        <v>5909</v>
+      </c>
+      <c r="C410">
+        <v>25</v>
+      </c>
+      <c r="D410" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4">
+      <c r="A411" s="2">
+        <v>46282.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>5985</v>
+      </c>
+      <c r="C411">
+        <v>26</v>
+      </c>
+      <c r="D411" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4">
+      <c r="A412" s="2">
+        <v>46282.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>6039</v>
+      </c>
+      <c r="C412">
+        <v>27</v>
+      </c>
+      <c r="D412" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4">
+      <c r="A413" s="2">
+        <v>46282.28125</v>
+      </c>
+      <c r="B413">
+        <v>6025</v>
+      </c>
+      <c r="C413">
+        <v>28</v>
+      </c>
+      <c r="D413" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4">
+      <c r="A414" s="2">
+        <v>46282.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>6075</v>
+      </c>
+      <c r="C414">
+        <v>29</v>
+      </c>
+      <c r="D414" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4">
+      <c r="A415" s="2">
+        <v>46282.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>5987</v>
+      </c>
+      <c r="C415">
+        <v>30</v>
+      </c>
+      <c r="D415" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4">
+      <c r="A416" s="2">
+        <v>46282.3125</v>
+      </c>
+      <c r="B416">
+        <v>5934</v>
+      </c>
+      <c r="C416">
+        <v>31</v>
+      </c>
+      <c r="D416" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4">
+      <c r="A417" s="2">
+        <v>46282.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>5853</v>
+      </c>
+      <c r="C417">
+        <v>32</v>
+      </c>
+      <c r="D417" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4">
+      <c r="A418" s="2">
+        <v>46282.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>5624</v>
+      </c>
+      <c r="C418">
+        <v>33</v>
+      </c>
+      <c r="D418" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4">
+      <c r="A419" s="2">
+        <v>46282.34375</v>
+      </c>
+      <c r="B419">
+        <v>5496</v>
+      </c>
+      <c r="C419">
+        <v>34</v>
+      </c>
+      <c r="D419" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4">
+      <c r="A420" s="2">
+        <v>46282.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>5344</v>
+      </c>
+      <c r="C420">
+        <v>35</v>
+      </c>
+      <c r="D420" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4">
+      <c r="A421" s="2">
+        <v>46282.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>5275</v>
+      </c>
+      <c r="C421">
+        <v>36</v>
+      </c>
+      <c r="D421" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4">
+      <c r="A422" s="2">
+        <v>46282.375</v>
+      </c>
+      <c r="B422">
+        <v>4987</v>
+      </c>
+      <c r="C422">
+        <v>37</v>
+      </c>
+      <c r="D422" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4">
+      <c r="A423" s="2">
+        <v>46282.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>4791</v>
+      </c>
+      <c r="C423">
+        <v>38</v>
+      </c>
+      <c r="D423" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4">
+      <c r="A424" s="2">
+        <v>46282.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>4704</v>
+      </c>
+      <c r="C424">
+        <v>39</v>
+      </c>
+      <c r="D424" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4">
+      <c r="A425" s="2">
+        <v>46282.40625</v>
+      </c>
+      <c r="B425">
+        <v>4615</v>
+      </c>
+      <c r="C425">
+        <v>40</v>
+      </c>
+      <c r="D425" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4">
+      <c r="A426" s="2">
+        <v>46282.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>4495</v>
+      </c>
+      <c r="C426">
+        <v>41</v>
+      </c>
+      <c r="D426" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4">
+      <c r="A427" s="2">
+        <v>46282.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>4369</v>
+      </c>
+      <c r="C427">
+        <v>42</v>
+      </c>
+      <c r="D427" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4">
+      <c r="A428" s="2">
+        <v>46282.4375</v>
+      </c>
+      <c r="B428">
+        <v>4324</v>
+      </c>
+      <c r="C428">
+        <v>43</v>
+      </c>
+      <c r="D428" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4">
+      <c r="A429" s="2">
+        <v>46282.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>4249</v>
+      </c>
+      <c r="C429">
+        <v>44</v>
+      </c>
+      <c r="D429" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4">
+      <c r="A430" s="2">
+        <v>46282.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>4169</v>
+      </c>
+      <c r="C430">
+        <v>45</v>
+      </c>
+      <c r="D430" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4">
+      <c r="A431" s="2">
+        <v>46282.46875</v>
+      </c>
+      <c r="B431">
+        <v>4165</v>
+      </c>
+      <c r="C431">
+        <v>46</v>
+      </c>
+      <c r="D431" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4">
+      <c r="A432" s="2">
+        <v>46282.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>4181</v>
+      </c>
+      <c r="C432">
+        <v>47</v>
+      </c>
+      <c r="D432" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4">
+      <c r="A433" s="2">
+        <v>46282.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>4217</v>
+      </c>
+      <c r="C433">
+        <v>48</v>
+      </c>
+      <c r="D433" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4">
+      <c r="A434" s="2">
+        <v>46282.5</v>
+      </c>
+      <c r="B434">
+        <v>4295</v>
+      </c>
+      <c r="C434">
+        <v>49</v>
+      </c>
+      <c r="D434" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4">
+      <c r="A435" s="2">
+        <v>46282.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>4327</v>
+      </c>
+      <c r="C435">
+        <v>50</v>
+      </c>
+      <c r="D435" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4">
+      <c r="A436" s="2">
+        <v>46282.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>4307</v>
+      </c>
+      <c r="C436">
+        <v>51</v>
+      </c>
+      <c r="D436" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4">
+      <c r="A437" s="2">
+        <v>46282.53125</v>
+      </c>
+      <c r="B437">
+        <v>4321</v>
+      </c>
+      <c r="C437">
+        <v>52</v>
+      </c>
+      <c r="D437" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4">
+      <c r="A438" s="2">
+        <v>46282.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>4311</v>
+      </c>
+      <c r="C438">
+        <v>53</v>
+      </c>
+      <c r="D438" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4">
+      <c r="A439" s="2">
+        <v>46282.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>4343</v>
+      </c>
+      <c r="C439">
+        <v>54</v>
+      </c>
+      <c r="D439" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4">
+      <c r="A440" s="2">
+        <v>46282.5625</v>
+      </c>
+      <c r="B440">
+        <v>4347</v>
+      </c>
+      <c r="C440">
+        <v>55</v>
+      </c>
+      <c r="D440" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4">
+      <c r="A441" s="2">
+        <v>46282.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>4337</v>
+      </c>
+      <c r="C441">
+        <v>56</v>
+      </c>
+      <c r="D441" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4">
+      <c r="A442" s="2">
+        <v>46282.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>4338</v>
+      </c>
+      <c r="C442">
+        <v>57</v>
+      </c>
+      <c r="D442" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4">
+      <c r="A443" s="2">
+        <v>46282.59375</v>
+      </c>
+      <c r="B443">
+        <v>4367</v>
+      </c>
+      <c r="C443">
+        <v>58</v>
+      </c>
+      <c r="D443" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4">
+      <c r="A444" s="2">
+        <v>46282.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>4394</v>
+      </c>
+      <c r="C444">
+        <v>59</v>
+      </c>
+      <c r="D444" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4">
+      <c r="A445" s="2">
+        <v>46282.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>4521</v>
+      </c>
+      <c r="C445">
+        <v>60</v>
+      </c>
+      <c r="D445" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4">
+      <c r="A446" s="2">
+        <v>46282.625</v>
+      </c>
+      <c r="B446">
+        <v>4648</v>
+      </c>
+      <c r="C446">
+        <v>61</v>
+      </c>
+      <c r="D446" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4">
+      <c r="A447" s="2">
+        <v>46282.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>4817</v>
+      </c>
+      <c r="C447">
+        <v>62</v>
+      </c>
+      <c r="D447" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4">
+      <c r="A448" s="2">
+        <v>46282.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>4962</v>
+      </c>
+      <c r="C448">
+        <v>63</v>
+      </c>
+      <c r="D448" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4">
+      <c r="A449" s="2">
+        <v>46282.65625</v>
+      </c>
+      <c r="B449">
+        <v>5125</v>
+      </c>
+      <c r="C449">
+        <v>64</v>
+      </c>
+      <c r="D449" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4">
+      <c r="A450" s="2">
+        <v>46282.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>5222</v>
+      </c>
+      <c r="C450">
+        <v>65</v>
+      </c>
+      <c r="D450" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4">
+      <c r="A451" s="2">
+        <v>46282.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>5447</v>
+      </c>
+      <c r="C451">
+        <v>66</v>
+      </c>
+      <c r="D451" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4">
+      <c r="A452" s="2">
+        <v>46282.6875</v>
+      </c>
+      <c r="B452">
+        <v>5623</v>
+      </c>
+      <c r="C452">
+        <v>67</v>
+      </c>
+      <c r="D452" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4">
+      <c r="A453" s="2">
+        <v>46282.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>5773</v>
+      </c>
+      <c r="C453">
+        <v>68</v>
+      </c>
+      <c r="D453" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4">
+      <c r="A454" s="2">
+        <v>46282.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>5949</v>
+      </c>
+      <c r="C454">
+        <v>69</v>
+      </c>
+      <c r="D454" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4">
+      <c r="A455" s="2">
+        <v>46282.71875</v>
+      </c>
+      <c r="B455">
+        <v>6140</v>
+      </c>
+      <c r="C455">
+        <v>70</v>
+      </c>
+      <c r="D455" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4">
+      <c r="A456" s="2">
+        <v>46282.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>6318</v>
+      </c>
+      <c r="C456">
+        <v>71</v>
+      </c>
+      <c r="D456" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4">
+      <c r="A457" s="2">
+        <v>46282.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>6521</v>
+      </c>
+      <c r="C457">
+        <v>72</v>
+      </c>
+      <c r="D457" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4">
+      <c r="A458" s="2">
+        <v>46282.75</v>
+      </c>
+      <c r="B458">
+        <v>6442</v>
+      </c>
+      <c r="C458">
+        <v>73</v>
+      </c>
+      <c r="D458" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4">
+      <c r="A459" s="2">
+        <v>46282.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>6515</v>
+      </c>
+      <c r="C459">
+        <v>74</v>
+      </c>
+      <c r="D459" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4">
+      <c r="A460" s="2">
+        <v>46282.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>6661</v>
+      </c>
+      <c r="C460">
+        <v>75</v>
+      </c>
+      <c r="D460" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4">
+      <c r="A461" s="2">
+        <v>46282.78125</v>
+      </c>
+      <c r="B461">
+        <v>6780</v>
+      </c>
+      <c r="C461">
+        <v>76</v>
+      </c>
+      <c r="D461" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4">
+      <c r="A462" s="2">
+        <v>46282.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>6860</v>
+      </c>
+      <c r="C462">
+        <v>77</v>
+      </c>
+      <c r="D462" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4">
+      <c r="A463" s="2">
+        <v>46282.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>6843</v>
+      </c>
+      <c r="C463">
+        <v>78</v>
+      </c>
+      <c r="D463" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4">
+      <c r="A464" s="2">
+        <v>46282.8125</v>
+      </c>
+      <c r="B464">
+        <v>6823</v>
+      </c>
+      <c r="C464">
+        <v>79</v>
+      </c>
+      <c r="D464" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4">
+      <c r="A465" s="2">
+        <v>46282.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>6762</v>
+      </c>
+      <c r="C465">
+        <v>80</v>
+      </c>
+      <c r="D465" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4">
+      <c r="A466" s="2">
+        <v>46282.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>6652</v>
+      </c>
+      <c r="C466">
+        <v>81</v>
+      </c>
+      <c r="D466" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4">
+      <c r="A467" s="2">
+        <v>46282.84375</v>
+      </c>
+      <c r="B467">
+        <v>6568</v>
+      </c>
+      <c r="C467">
+        <v>82</v>
+      </c>
+      <c r="D467" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4">
+      <c r="A468" s="2">
+        <v>46282.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>6465</v>
+      </c>
+      <c r="C468">
+        <v>83</v>
+      </c>
+      <c r="D468" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4">
+      <c r="A469" s="2">
+        <v>46282.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>6325</v>
+      </c>
+      <c r="C469">
+        <v>84</v>
+      </c>
+      <c r="D469" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4">
+      <c r="A470" s="2">
+        <v>46282.875</v>
+      </c>
+      <c r="B470">
+        <v>6177</v>
+      </c>
+      <c r="C470">
+        <v>85</v>
+      </c>
+      <c r="D470" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4">
+      <c r="A471" s="2">
+        <v>46282.88541666666</v>
+      </c>
+      <c r="B471">
+        <v>6032</v>
+      </c>
+      <c r="C471">
+        <v>86</v>
+      </c>
+      <c r="D471" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4">
+      <c r="A472" s="2">
+        <v>46282.89583333334</v>
+      </c>
+      <c r="B472">
+        <v>5901</v>
+      </c>
+      <c r="C472">
+        <v>87</v>
+      </c>
+      <c r="D472" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4">
+      <c r="A473" s="2">
+        <v>46282.90625</v>
+      </c>
+      <c r="B473">
+        <v>5754</v>
+      </c>
+      <c r="C473">
+        <v>88</v>
+      </c>
+      <c r="D473" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4">
+      <c r="A474" s="2">
+        <v>46282.91666666666</v>
+      </c>
+      <c r="B474">
+        <v>5636</v>
+      </c>
+      <c r="C474">
+        <v>89</v>
+      </c>
+      <c r="D474" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4">
+      <c r="A475" s="2">
+        <v>46282.92708333334</v>
+      </c>
+      <c r="B475">
+        <v>5500</v>
+      </c>
+      <c r="C475">
+        <v>90</v>
+      </c>
+      <c r="D475" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4">
+      <c r="A476" s="2">
+        <v>46282.9375</v>
+      </c>
+      <c r="B476">
+        <v>5424</v>
+      </c>
+      <c r="C476">
+        <v>91</v>
+      </c>
+      <c r="D476" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4">
+      <c r="A477" s="2">
+        <v>46282.94791666666</v>
+      </c>
+      <c r="B477">
+        <v>5332</v>
+      </c>
+      <c r="C477">
+        <v>92</v>
+      </c>
+      <c r="D477" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4">
+      <c r="A478" s="2">
+        <v>46282.95833333334</v>
+      </c>
+      <c r="B478">
+        <v>5257</v>
+      </c>
+      <c r="C478">
+        <v>93</v>
+      </c>
+      <c r="D478" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4">
+      <c r="A479" s="2">
+        <v>46282.96875</v>
+      </c>
+      <c r="B479">
+        <v>5161</v>
+      </c>
+      <c r="C479">
+        <v>94</v>
+      </c>
+      <c r="D479" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4">
+      <c r="A480" s="2">
+        <v>46282.97916666666</v>
+      </c>
+      <c r="B480">
+        <v>5106</v>
+      </c>
+      <c r="C480">
+        <v>95</v>
+      </c>
+      <c r="D480" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4">
+      <c r="A481" s="2">
+        <v>46282.98958333334</v>
+      </c>
+      <c r="B481">
+        <v>5066</v>
+      </c>
+      <c r="C481">
+        <v>96</v>
+      </c>
+      <c r="D481" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4">
+      <c r="A482" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B482">
+        <v>5025</v>
+      </c>
+      <c r="C482">
+        <v>1</v>
+      </c>
+      <c r="D482" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4">
+      <c r="A483" s="2">
+        <v>46283.01041666666</v>
+      </c>
+      <c r="B483">
+        <v>5000</v>
+      </c>
+      <c r="C483">
+        <v>2</v>
+      </c>
+      <c r="D483" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4">
+      <c r="A484" s="2">
+        <v>46283.02083333334</v>
+      </c>
+      <c r="B484">
+        <v>4953</v>
+      </c>
+      <c r="C484">
+        <v>3</v>
+      </c>
+      <c r="D484" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4">
+      <c r="A485" s="2">
+        <v>46283.03125</v>
+      </c>
+      <c r="B485">
+        <v>4926</v>
+      </c>
+      <c r="C485">
+        <v>4</v>
+      </c>
+      <c r="D485" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4">
+      <c r="A486" s="2">
+        <v>46283.04166666666</v>
+      </c>
+      <c r="B486">
+        <v>4875</v>
+      </c>
+      <c r="C486">
+        <v>5</v>
+      </c>
+      <c r="D486" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4">
+      <c r="A487" s="2">
+        <v>46283.05208333334</v>
+      </c>
+      <c r="B487">
+        <v>4833</v>
+      </c>
+      <c r="C487">
+        <v>6</v>
+      </c>
+      <c r="D487" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4">
+      <c r="A488" s="2">
+        <v>46283.0625</v>
+      </c>
+      <c r="B488">
+        <v>4846</v>
+      </c>
+      <c r="C488">
+        <v>7</v>
+      </c>
+      <c r="D488" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4">
+      <c r="A489" s="2">
+        <v>46283.07291666666</v>
+      </c>
+      <c r="B489">
+        <v>4807</v>
+      </c>
+      <c r="C489">
+        <v>8</v>
+      </c>
+      <c r="D489" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4">
+      <c r="A490" s="2">
+        <v>46283.08333333334</v>
+      </c>
+      <c r="B490">
+        <v>4814</v>
+      </c>
+      <c r="C490">
+        <v>9</v>
+      </c>
+      <c r="D490" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4">
+      <c r="A491" s="2">
+        <v>46283.09375</v>
+      </c>
+      <c r="B491">
+        <v>4882</v>
+      </c>
+      <c r="C491">
+        <v>10</v>
+      </c>
+      <c r="D491" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4">
+      <c r="A492" s="2">
+        <v>46283.10416666666</v>
+      </c>
+      <c r="B492">
+        <v>4895</v>
+      </c>
+      <c r="C492">
+        <v>11</v>
+      </c>
+      <c r="D492" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4">
+      <c r="A493" s="2">
+        <v>46283.11458333334</v>
+      </c>
+      <c r="B493">
+        <v>4879</v>
+      </c>
+      <c r="C493">
+        <v>12</v>
+      </c>
+      <c r="D493" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4">
+      <c r="A494" s="2">
+        <v>46283.125</v>
+      </c>
+      <c r="B494">
+        <v>4900</v>
+      </c>
+      <c r="C494">
+        <v>13</v>
+      </c>
+      <c r="D494" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4">
+      <c r="A495" s="2">
+        <v>46283.13541666666</v>
+      </c>
+      <c r="B495">
+        <v>4922</v>
+      </c>
+      <c r="C495">
+        <v>14</v>
+      </c>
+      <c r="D495" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4">
+      <c r="A496" s="2">
+        <v>46283.14583333334</v>
+      </c>
+      <c r="B496">
+        <v>4946</v>
+      </c>
+      <c r="C496">
+        <v>15</v>
+      </c>
+      <c r="D496" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4">
+      <c r="A497" s="2">
+        <v>46283.15625</v>
+      </c>
+      <c r="B497">
+        <v>4969</v>
+      </c>
+      <c r="C497">
+        <v>16</v>
+      </c>
+      <c r="D497" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4">
+      <c r="A498" s="2">
+        <v>46283.16666666666</v>
+      </c>
+      <c r="B498">
+        <v>5106</v>
+      </c>
+      <c r="C498">
+        <v>17</v>
+      </c>
+      <c r="D498" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4">
+      <c r="A499" s="2">
+        <v>46283.17708333334</v>
+      </c>
+      <c r="B499">
+        <v>5132</v>
+      </c>
+      <c r="C499">
+        <v>18</v>
+      </c>
+      <c r="D499" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4">
+      <c r="A500" s="2">
+        <v>46283.1875</v>
+      </c>
+      <c r="B500">
+        <v>5091</v>
+      </c>
+      <c r="C500">
+        <v>19</v>
+      </c>
+      <c r="D500" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4">
+      <c r="A501" s="2">
+        <v>46283.19791666666</v>
+      </c>
+      <c r="B501">
+        <v>5117</v>
+      </c>
+      <c r="C501">
+        <v>20</v>
+      </c>
+      <c r="D501" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4">
+      <c r="A502" s="2">
+        <v>46283.20833333334</v>
+      </c>
+      <c r="B502">
+        <v>5299</v>
+      </c>
+      <c r="C502">
+        <v>21</v>
+      </c>
+      <c r="D502" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4">
+      <c r="A503" s="2">
+        <v>46283.21875</v>
+      </c>
+      <c r="B503">
+        <v>5404</v>
+      </c>
+      <c r="C503">
+        <v>22</v>
+      </c>
+      <c r="D503" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4">
+      <c r="A504" s="2">
+        <v>46283.22916666666</v>
+      </c>
+      <c r="B504">
+        <v>5532</v>
+      </c>
+      <c r="C504">
+        <v>23</v>
+      </c>
+      <c r="D504" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4">
+      <c r="A505" s="2">
+        <v>46283.23958333334</v>
+      </c>
+      <c r="B505">
+        <v>5601</v>
+      </c>
+      <c r="C505">
+        <v>24</v>
+      </c>
+      <c r="D505" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4">
+      <c r="A506" s="2">
+        <v>46283.25</v>
+      </c>
+      <c r="B506">
+        <v>5811</v>
+      </c>
+      <c r="C506">
+        <v>25</v>
+      </c>
+      <c r="D506" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4">
+      <c r="A507" s="2">
+        <v>46283.26041666666</v>
+      </c>
+      <c r="B507">
+        <v>5936</v>
+      </c>
+      <c r="C507">
+        <v>26</v>
+      </c>
+      <c r="D507" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4">
+      <c r="A508" s="2">
+        <v>46283.27083333334</v>
+      </c>
+      <c r="B508">
+        <v>5954</v>
+      </c>
+      <c r="C508">
+        <v>27</v>
+      </c>
+      <c r="D508" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4">
+      <c r="A509" s="2">
+        <v>46283.28125</v>
+      </c>
+      <c r="B509">
+        <v>5872</v>
+      </c>
+      <c r="C509">
+        <v>28</v>
+      </c>
+      <c r="D509" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4">
+      <c r="A510" s="2">
+        <v>46283.29166666666</v>
+      </c>
+      <c r="B510">
+        <v>5978</v>
+      </c>
+      <c r="C510">
+        <v>29</v>
+      </c>
+      <c r="D510" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4">
+      <c r="A511" s="2">
+        <v>46283.30208333334</v>
+      </c>
+      <c r="B511">
+        <v>6008</v>
+      </c>
+      <c r="C511">
+        <v>30</v>
+      </c>
+      <c r="D511" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4">
+      <c r="A512" s="2">
+        <v>46283.3125</v>
+      </c>
+      <c r="B512">
+        <v>6008</v>
+      </c>
+      <c r="C512">
+        <v>31</v>
+      </c>
+      <c r="D512" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4">
+      <c r="A513" s="2">
+        <v>46283.32291666666</v>
+      </c>
+      <c r="B513">
+        <v>6008</v>
+      </c>
+      <c r="C513">
+        <v>32</v>
+      </c>
+      <c r="D513" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4">
+      <c r="A514" s="2">
+        <v>46283.33333333334</v>
+      </c>
+      <c r="B514">
+        <v>6008</v>
+      </c>
+      <c r="C514">
+        <v>33</v>
+      </c>
+      <c r="D514" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4">
+      <c r="A515" s="2">
+        <v>46283.34375</v>
+      </c>
+      <c r="B515">
+        <v>6008</v>
+      </c>
+      <c r="C515">
+        <v>34</v>
+      </c>
+      <c r="D515" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4">
+      <c r="A516" s="2">
+        <v>46283.35416666666</v>
+      </c>
+      <c r="B516">
+        <v>5646</v>
+      </c>
+      <c r="C516">
+        <v>35</v>
+      </c>
+      <c r="D516" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4">
+      <c r="A517" s="2">
+        <v>46283.36458333334</v>
+      </c>
+      <c r="B517">
+        <v>5719</v>
+      </c>
+      <c r="C517">
+        <v>36</v>
+      </c>
+      <c r="D517" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4">
+      <c r="A518" s="2">
+        <v>46283.375</v>
+      </c>
+      <c r="B518">
+        <v>5387</v>
+      </c>
+      <c r="C518">
+        <v>37</v>
+      </c>
+      <c r="D518" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4">
+      <c r="A519" s="2">
+        <v>46283.38541666666</v>
+      </c>
+      <c r="B519">
+        <v>5299</v>
+      </c>
+      <c r="C519">
+        <v>38</v>
+      </c>
+      <c r="D519" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4">
+      <c r="A520" s="2">
+        <v>46283.39583333334</v>
+      </c>
+      <c r="B520">
+        <v>5211</v>
+      </c>
+      <c r="C520">
+        <v>39</v>
+      </c>
+      <c r="D520" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4">
+      <c r="A521" s="2">
+        <v>46283.40625</v>
+      </c>
+      <c r="B521">
+        <v>5092</v>
+      </c>
+      <c r="C521">
+        <v>40</v>
+      </c>
+      <c r="D521" t="s">
+        <v>523</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,691 +28,697 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>18.09.20261</t>
-  </si>
-  <si>
-    <t>18.09.20262</t>
-  </si>
-  <si>
-    <t>18.09.20263</t>
-  </si>
-  <si>
-    <t>18.09.20264</t>
-  </si>
-  <si>
-    <t>18.09.20265</t>
-  </si>
-  <si>
-    <t>18.09.20266</t>
-  </si>
-  <si>
-    <t>18.09.20267</t>
-  </si>
-  <si>
-    <t>18.09.20268</t>
-  </si>
-  <si>
-    <t>18.09.20269</t>
-  </si>
-  <si>
-    <t>18.09.202610</t>
-  </si>
-  <si>
-    <t>18.09.202611</t>
-  </si>
-  <si>
-    <t>18.09.202612</t>
-  </si>
-  <si>
-    <t>18.09.202613</t>
-  </si>
-  <si>
-    <t>18.09.202614</t>
-  </si>
-  <si>
-    <t>18.09.202615</t>
-  </si>
-  <si>
-    <t>18.09.202616</t>
-  </si>
-  <si>
-    <t>18.09.202617</t>
-  </si>
-  <si>
-    <t>18.09.202618</t>
-  </si>
-  <si>
-    <t>18.09.202619</t>
-  </si>
-  <si>
-    <t>18.09.202620</t>
-  </si>
-  <si>
-    <t>18.09.202621</t>
-  </si>
-  <si>
-    <t>18.09.202622</t>
-  </si>
-  <si>
-    <t>18.09.202623</t>
-  </si>
-  <si>
-    <t>18.09.202624</t>
-  </si>
-  <si>
-    <t>18.09.202625</t>
-  </si>
-  <si>
-    <t>18.09.202626</t>
-  </si>
-  <si>
-    <t>18.09.202627</t>
-  </si>
-  <si>
-    <t>18.09.202628</t>
-  </si>
-  <si>
-    <t>18.09.202629</t>
-  </si>
-  <si>
-    <t>18.09.202630</t>
-  </si>
-  <si>
-    <t>18.09.202631</t>
-  </si>
-  <si>
-    <t>18.09.202632</t>
-  </si>
-  <si>
-    <t>18.09.202633</t>
-  </si>
-  <si>
-    <t>18.09.202634</t>
-  </si>
-  <si>
-    <t>18.09.202635</t>
-  </si>
-  <si>
-    <t>18.09.202636</t>
-  </si>
-  <si>
-    <t>18.09.202637</t>
-  </si>
-  <si>
-    <t>18.09.202638</t>
-  </si>
-  <si>
-    <t>18.09.202639</t>
-  </si>
-  <si>
-    <t>18.09.202640</t>
-  </si>
-  <si>
-    <t>18.09.202641</t>
-  </si>
-  <si>
-    <t>18.09.202642</t>
-  </si>
-  <si>
-    <t>18.09.202643</t>
-  </si>
-  <si>
-    <t>18.09.202644</t>
-  </si>
-  <si>
-    <t>18.09.202645</t>
-  </si>
-  <si>
-    <t>18.09.202646</t>
-  </si>
-  <si>
-    <t>18.09.202647</t>
-  </si>
-  <si>
-    <t>18.09.202648</t>
-  </si>
-  <si>
-    <t>18.09.202649</t>
-  </si>
-  <si>
-    <t>18.09.202650</t>
-  </si>
-  <si>
-    <t>18.09.202651</t>
-  </si>
-  <si>
-    <t>18.09.202652</t>
-  </si>
-  <si>
-    <t>18.09.202653</t>
-  </si>
-  <si>
-    <t>18.09.202654</t>
-  </si>
-  <si>
-    <t>18.09.202655</t>
-  </si>
-  <si>
-    <t>18.09.202656</t>
-  </si>
-  <si>
-    <t>18.09.202657</t>
-  </si>
-  <si>
-    <t>18.09.202658</t>
-  </si>
-  <si>
-    <t>18.09.202659</t>
-  </si>
-  <si>
-    <t>18.09.202660</t>
-  </si>
-  <si>
-    <t>18.09.202661</t>
-  </si>
-  <si>
-    <t>18.09.202662</t>
-  </si>
-  <si>
-    <t>18.09.202663</t>
-  </si>
-  <si>
-    <t>18.09.202664</t>
-  </si>
-  <si>
-    <t>18.09.202665</t>
-  </si>
-  <si>
-    <t>18.09.202666</t>
-  </si>
-  <si>
-    <t>18.09.202667</t>
-  </si>
-  <si>
-    <t>18.09.202668</t>
-  </si>
-  <si>
-    <t>18.09.202669</t>
-  </si>
-  <si>
-    <t>18.09.202670</t>
-  </si>
-  <si>
-    <t>18.09.202671</t>
-  </si>
-  <si>
-    <t>18.09.202672</t>
-  </si>
-  <si>
-    <t>18.09.202673</t>
-  </si>
-  <si>
-    <t>18.09.202674</t>
-  </si>
-  <si>
-    <t>18.09.202675</t>
-  </si>
-  <si>
-    <t>18.09.202676</t>
-  </si>
-  <si>
-    <t>18.09.202677</t>
-  </si>
-  <si>
-    <t>18.09.202678</t>
-  </si>
-  <si>
-    <t>18.09.202679</t>
-  </si>
-  <si>
-    <t>18.09.202680</t>
-  </si>
-  <si>
-    <t>18.09.202681</t>
-  </si>
-  <si>
-    <t>18.09.202682</t>
-  </si>
-  <si>
-    <t>18.09.202683</t>
-  </si>
-  <si>
-    <t>18.09.202684</t>
-  </si>
-  <si>
-    <t>18.09.202685</t>
-  </si>
-  <si>
-    <t>18.09.202686</t>
-  </si>
-  <si>
-    <t>18.09.202687</t>
-  </si>
-  <si>
-    <t>18.09.202688</t>
-  </si>
-  <si>
-    <t>18.09.202689</t>
-  </si>
-  <si>
-    <t>18.09.202690</t>
-  </si>
-  <si>
-    <t>18.09.202691</t>
-  </si>
-  <si>
-    <t>18.09.202692</t>
-  </si>
-  <si>
-    <t>18.09.202693</t>
-  </si>
-  <si>
-    <t>18.09.202694</t>
-  </si>
-  <si>
-    <t>18.09.202695</t>
-  </si>
-  <si>
-    <t>18.09.202696</t>
-  </si>
-  <si>
-    <t>19.09.20261</t>
-  </si>
-  <si>
-    <t>19.09.20262</t>
-  </si>
-  <si>
-    <t>19.09.20263</t>
-  </si>
-  <si>
-    <t>19.09.20264</t>
-  </si>
-  <si>
-    <t>19.09.20265</t>
-  </si>
-  <si>
-    <t>19.09.20266</t>
-  </si>
-  <si>
-    <t>19.09.20267</t>
-  </si>
-  <si>
-    <t>19.09.20268</t>
-  </si>
-  <si>
-    <t>19.09.20269</t>
-  </si>
-  <si>
-    <t>19.09.202610</t>
-  </si>
-  <si>
-    <t>19.09.202611</t>
-  </si>
-  <si>
-    <t>19.09.202612</t>
-  </si>
-  <si>
-    <t>19.09.202613</t>
-  </si>
-  <si>
-    <t>19.09.202614</t>
-  </si>
-  <si>
-    <t>19.09.202615</t>
-  </si>
-  <si>
-    <t>19.09.202616</t>
-  </si>
-  <si>
-    <t>19.09.202617</t>
-  </si>
-  <si>
-    <t>19.09.202618</t>
-  </si>
-  <si>
-    <t>19.09.202619</t>
-  </si>
-  <si>
-    <t>19.09.202620</t>
-  </si>
-  <si>
-    <t>19.09.202621</t>
-  </si>
-  <si>
-    <t>19.09.202622</t>
-  </si>
-  <si>
-    <t>19.09.202623</t>
-  </si>
-  <si>
-    <t>19.09.202624</t>
-  </si>
-  <si>
-    <t>19.09.202625</t>
-  </si>
-  <si>
-    <t>19.09.202626</t>
-  </si>
-  <si>
-    <t>19.09.202627</t>
-  </si>
-  <si>
-    <t>19.09.202628</t>
-  </si>
-  <si>
-    <t>19.09.202629</t>
-  </si>
-  <si>
-    <t>19.09.202630</t>
-  </si>
-  <si>
-    <t>19.09.202631</t>
-  </si>
-  <si>
-    <t>19.09.202632</t>
-  </si>
-  <si>
-    <t>19.09.202633</t>
-  </si>
-  <si>
-    <t>19.09.202634</t>
-  </si>
-  <si>
-    <t>19.09.202635</t>
-  </si>
-  <si>
-    <t>19.09.202636</t>
-  </si>
-  <si>
-    <t>19.09.202637</t>
-  </si>
-  <si>
-    <t>19.09.202638</t>
-  </si>
-  <si>
-    <t>19.09.202639</t>
-  </si>
-  <si>
-    <t>19.09.202640</t>
-  </si>
-  <si>
-    <t>19.09.202641</t>
-  </si>
-  <si>
-    <t>19.09.202642</t>
-  </si>
-  <si>
-    <t>19.09.202643</t>
-  </si>
-  <si>
-    <t>19.09.202644</t>
-  </si>
-  <si>
-    <t>19.09.202645</t>
-  </si>
-  <si>
-    <t>19.09.202646</t>
-  </si>
-  <si>
-    <t>19.09.202647</t>
-  </si>
-  <si>
-    <t>19.09.202648</t>
-  </si>
-  <si>
-    <t>19.09.202649</t>
-  </si>
-  <si>
-    <t>19.09.202650</t>
-  </si>
-  <si>
-    <t>19.09.202651</t>
-  </si>
-  <si>
-    <t>19.09.202652</t>
-  </si>
-  <si>
-    <t>19.09.202653</t>
-  </si>
-  <si>
-    <t>19.09.202654</t>
-  </si>
-  <si>
-    <t>19.09.202655</t>
-  </si>
-  <si>
-    <t>19.09.202656</t>
-  </si>
-  <si>
-    <t>19.09.202657</t>
-  </si>
-  <si>
-    <t>19.09.202658</t>
-  </si>
-  <si>
-    <t>19.09.202659</t>
-  </si>
-  <si>
-    <t>19.09.202660</t>
-  </si>
-  <si>
-    <t>19.09.202661</t>
-  </si>
-  <si>
-    <t>19.09.202662</t>
-  </si>
-  <si>
-    <t>19.09.202663</t>
-  </si>
-  <si>
-    <t>19.09.202664</t>
-  </si>
-  <si>
-    <t>19.09.202665</t>
-  </si>
-  <si>
-    <t>19.09.202666</t>
-  </si>
-  <si>
-    <t>19.09.202667</t>
-  </si>
-  <si>
-    <t>19.09.202668</t>
-  </si>
-  <si>
-    <t>19.09.202669</t>
-  </si>
-  <si>
-    <t>19.09.202670</t>
-  </si>
-  <si>
-    <t>19.09.202671</t>
-  </si>
-  <si>
-    <t>19.09.202672</t>
-  </si>
-  <si>
-    <t>19.09.202673</t>
-  </si>
-  <si>
-    <t>19.09.202674</t>
-  </si>
-  <si>
-    <t>19.09.202675</t>
-  </si>
-  <si>
-    <t>19.09.202676</t>
-  </si>
-  <si>
-    <t>19.09.202677</t>
-  </si>
-  <si>
-    <t>19.09.202678</t>
-  </si>
-  <si>
-    <t>19.09.202679</t>
-  </si>
-  <si>
-    <t>19.09.202680</t>
-  </si>
-  <si>
-    <t>19.09.202681</t>
-  </si>
-  <si>
-    <t>19.09.202682</t>
-  </si>
-  <si>
-    <t>19.09.202683</t>
-  </si>
-  <si>
-    <t>19.09.202684</t>
-  </si>
-  <si>
-    <t>19.09.202685</t>
-  </si>
-  <si>
-    <t>19.09.202686</t>
-  </si>
-  <si>
-    <t>19.09.202687</t>
-  </si>
-  <si>
-    <t>19.09.202688</t>
-  </si>
-  <si>
-    <t>19.09.202689</t>
-  </si>
-  <si>
-    <t>19.09.202690</t>
-  </si>
-  <si>
-    <t>19.09.202691</t>
-  </si>
-  <si>
-    <t>19.09.202692</t>
-  </si>
-  <si>
-    <t>19.09.202693</t>
-  </si>
-  <si>
-    <t>19.09.202694</t>
-  </si>
-  <si>
-    <t>19.09.202695</t>
-  </si>
-  <si>
-    <t>19.09.202696</t>
-  </si>
-  <si>
-    <t>20.09.20261</t>
-  </si>
-  <si>
-    <t>20.09.20262</t>
-  </si>
-  <si>
-    <t>20.09.20263</t>
-  </si>
-  <si>
-    <t>20.09.20264</t>
-  </si>
-  <si>
-    <t>20.09.20265</t>
-  </si>
-  <si>
-    <t>20.09.20266</t>
-  </si>
-  <si>
-    <t>20.09.20267</t>
-  </si>
-  <si>
-    <t>20.09.20268</t>
-  </si>
-  <si>
-    <t>20.09.20269</t>
-  </si>
-  <si>
-    <t>20.09.202610</t>
-  </si>
-  <si>
-    <t>20.09.202611</t>
-  </si>
-  <si>
-    <t>20.09.202612</t>
-  </si>
-  <si>
-    <t>20.09.202613</t>
-  </si>
-  <si>
-    <t>20.09.202614</t>
-  </si>
-  <si>
-    <t>20.09.202615</t>
-  </si>
-  <si>
-    <t>20.09.202616</t>
-  </si>
-  <si>
-    <t>20.09.202617</t>
-  </si>
-  <si>
-    <t>20.09.202618</t>
-  </si>
-  <si>
-    <t>20.09.202619</t>
-  </si>
-  <si>
-    <t>20.09.202620</t>
-  </si>
-  <si>
-    <t>20.09.202621</t>
-  </si>
-  <si>
-    <t>20.09.202622</t>
-  </si>
-  <si>
-    <t>20.09.202623</t>
-  </si>
-  <si>
-    <t>20.09.202624</t>
-  </si>
-  <si>
-    <t>20.09.202625</t>
-  </si>
-  <si>
-    <t>20.09.202626</t>
-  </si>
-  <si>
-    <t>20.09.202627</t>
-  </si>
-  <si>
-    <t>20.09.202628</t>
-  </si>
-  <si>
-    <t>20.09.202629</t>
-  </si>
-  <si>
-    <t>20.09.202630</t>
-  </si>
-  <si>
-    <t>20.09.202631</t>
-  </si>
-  <si>
-    <t>20.09.202632</t>
-  </si>
-  <si>
-    <t>20.09.202633</t>
-  </si>
-  <si>
-    <t>20.09.202634</t>
-  </si>
-  <si>
-    <t>20.09.202635</t>
-  </si>
-  <si>
-    <t>20.09.202636</t>
-  </si>
-  <si>
-    <t>20.09.202637</t>
+    <t>28.09.20261</t>
+  </si>
+  <si>
+    <t>28.09.20262</t>
+  </si>
+  <si>
+    <t>28.09.20263</t>
+  </si>
+  <si>
+    <t>28.09.20264</t>
+  </si>
+  <si>
+    <t>28.09.20265</t>
+  </si>
+  <si>
+    <t>28.09.20266</t>
+  </si>
+  <si>
+    <t>28.09.20267</t>
+  </si>
+  <si>
+    <t>28.09.20268</t>
+  </si>
+  <si>
+    <t>28.09.20269</t>
+  </si>
+  <si>
+    <t>28.09.202610</t>
+  </si>
+  <si>
+    <t>28.09.202611</t>
+  </si>
+  <si>
+    <t>28.09.202612</t>
+  </si>
+  <si>
+    <t>28.09.202613</t>
+  </si>
+  <si>
+    <t>28.09.202614</t>
+  </si>
+  <si>
+    <t>28.09.202615</t>
+  </si>
+  <si>
+    <t>28.09.202616</t>
+  </si>
+  <si>
+    <t>28.09.202617</t>
+  </si>
+  <si>
+    <t>28.09.202618</t>
+  </si>
+  <si>
+    <t>28.09.202619</t>
+  </si>
+  <si>
+    <t>28.09.202620</t>
+  </si>
+  <si>
+    <t>28.09.202621</t>
+  </si>
+  <si>
+    <t>28.09.202622</t>
+  </si>
+  <si>
+    <t>28.09.202623</t>
+  </si>
+  <si>
+    <t>28.09.202624</t>
+  </si>
+  <si>
+    <t>28.09.202625</t>
+  </si>
+  <si>
+    <t>28.09.202626</t>
+  </si>
+  <si>
+    <t>28.09.202627</t>
+  </si>
+  <si>
+    <t>28.09.202628</t>
+  </si>
+  <si>
+    <t>28.09.202629</t>
+  </si>
+  <si>
+    <t>28.09.202630</t>
+  </si>
+  <si>
+    <t>28.09.202631</t>
+  </si>
+  <si>
+    <t>28.09.202632</t>
+  </si>
+  <si>
+    <t>28.09.202633</t>
+  </si>
+  <si>
+    <t>28.09.202634</t>
+  </si>
+  <si>
+    <t>28.09.202635</t>
+  </si>
+  <si>
+    <t>28.09.202636</t>
+  </si>
+  <si>
+    <t>28.09.202637</t>
+  </si>
+  <si>
+    <t>28.09.202638</t>
+  </si>
+  <si>
+    <t>28.09.202639</t>
+  </si>
+  <si>
+    <t>28.09.202640</t>
+  </si>
+  <si>
+    <t>28.09.202641</t>
+  </si>
+  <si>
+    <t>28.09.202642</t>
+  </si>
+  <si>
+    <t>28.09.202643</t>
+  </si>
+  <si>
+    <t>28.09.202644</t>
+  </si>
+  <si>
+    <t>28.09.202645</t>
+  </si>
+  <si>
+    <t>28.09.202646</t>
+  </si>
+  <si>
+    <t>28.09.202647</t>
+  </si>
+  <si>
+    <t>28.09.202648</t>
+  </si>
+  <si>
+    <t>28.09.202649</t>
+  </si>
+  <si>
+    <t>28.09.202650</t>
+  </si>
+  <si>
+    <t>28.09.202651</t>
+  </si>
+  <si>
+    <t>28.09.202652</t>
+  </si>
+  <si>
+    <t>28.09.202653</t>
+  </si>
+  <si>
+    <t>28.09.202654</t>
+  </si>
+  <si>
+    <t>28.09.202655</t>
+  </si>
+  <si>
+    <t>28.09.202656</t>
+  </si>
+  <si>
+    <t>28.09.202657</t>
+  </si>
+  <si>
+    <t>28.09.202658</t>
+  </si>
+  <si>
+    <t>28.09.202659</t>
+  </si>
+  <si>
+    <t>28.09.202660</t>
+  </si>
+  <si>
+    <t>28.09.202661</t>
+  </si>
+  <si>
+    <t>28.09.202662</t>
+  </si>
+  <si>
+    <t>28.09.202663</t>
+  </si>
+  <si>
+    <t>28.09.202664</t>
+  </si>
+  <si>
+    <t>28.09.202665</t>
+  </si>
+  <si>
+    <t>28.09.202666</t>
+  </si>
+  <si>
+    <t>28.09.202667</t>
+  </si>
+  <si>
+    <t>28.09.202668</t>
+  </si>
+  <si>
+    <t>28.09.202669</t>
+  </si>
+  <si>
+    <t>28.09.202670</t>
+  </si>
+  <si>
+    <t>28.09.202671</t>
+  </si>
+  <si>
+    <t>28.09.202672</t>
+  </si>
+  <si>
+    <t>28.09.202673</t>
+  </si>
+  <si>
+    <t>28.09.202674</t>
+  </si>
+  <si>
+    <t>28.09.202675</t>
+  </si>
+  <si>
+    <t>28.09.202676</t>
+  </si>
+  <si>
+    <t>28.09.202677</t>
+  </si>
+  <si>
+    <t>28.09.202678</t>
+  </si>
+  <si>
+    <t>28.09.202679</t>
+  </si>
+  <si>
+    <t>28.09.202680</t>
+  </si>
+  <si>
+    <t>28.09.202681</t>
+  </si>
+  <si>
+    <t>28.09.202682</t>
+  </si>
+  <si>
+    <t>28.09.202683</t>
+  </si>
+  <si>
+    <t>28.09.202684</t>
+  </si>
+  <si>
+    <t>28.09.202685</t>
+  </si>
+  <si>
+    <t>28.09.202686</t>
+  </si>
+  <si>
+    <t>28.09.202687</t>
+  </si>
+  <si>
+    <t>28.09.202688</t>
+  </si>
+  <si>
+    <t>28.09.202689</t>
+  </si>
+  <si>
+    <t>28.09.202690</t>
+  </si>
+  <si>
+    <t>28.09.202691</t>
+  </si>
+  <si>
+    <t>28.09.202692</t>
+  </si>
+  <si>
+    <t>28.09.202693</t>
+  </si>
+  <si>
+    <t>28.09.202694</t>
+  </si>
+  <si>
+    <t>28.09.202695</t>
+  </si>
+  <si>
+    <t>28.09.202696</t>
+  </si>
+  <si>
+    <t>29.09.20261</t>
+  </si>
+  <si>
+    <t>29.09.20262</t>
+  </si>
+  <si>
+    <t>29.09.20263</t>
+  </si>
+  <si>
+    <t>29.09.20264</t>
+  </si>
+  <si>
+    <t>29.09.20265</t>
+  </si>
+  <si>
+    <t>29.09.20266</t>
+  </si>
+  <si>
+    <t>29.09.20267</t>
+  </si>
+  <si>
+    <t>29.09.20268</t>
+  </si>
+  <si>
+    <t>29.09.20269</t>
+  </si>
+  <si>
+    <t>29.09.202610</t>
+  </si>
+  <si>
+    <t>29.09.202611</t>
+  </si>
+  <si>
+    <t>29.09.202612</t>
+  </si>
+  <si>
+    <t>29.09.202613</t>
+  </si>
+  <si>
+    <t>29.09.202614</t>
+  </si>
+  <si>
+    <t>29.09.202615</t>
+  </si>
+  <si>
+    <t>29.09.202616</t>
+  </si>
+  <si>
+    <t>29.09.202617</t>
+  </si>
+  <si>
+    <t>29.09.202618</t>
+  </si>
+  <si>
+    <t>29.09.202619</t>
+  </si>
+  <si>
+    <t>29.09.202620</t>
+  </si>
+  <si>
+    <t>29.09.202621</t>
+  </si>
+  <si>
+    <t>29.09.202622</t>
+  </si>
+  <si>
+    <t>29.09.202623</t>
+  </si>
+  <si>
+    <t>29.09.202624</t>
+  </si>
+  <si>
+    <t>29.09.202625</t>
+  </si>
+  <si>
+    <t>29.09.202626</t>
+  </si>
+  <si>
+    <t>29.09.202627</t>
+  </si>
+  <si>
+    <t>29.09.202628</t>
+  </si>
+  <si>
+    <t>29.09.202629</t>
+  </si>
+  <si>
+    <t>29.09.202630</t>
+  </si>
+  <si>
+    <t>29.09.202631</t>
+  </si>
+  <si>
+    <t>29.09.202632</t>
+  </si>
+  <si>
+    <t>29.09.202633</t>
+  </si>
+  <si>
+    <t>29.09.202634</t>
+  </si>
+  <si>
+    <t>29.09.202635</t>
+  </si>
+  <si>
+    <t>29.09.202636</t>
+  </si>
+  <si>
+    <t>29.09.202637</t>
+  </si>
+  <si>
+    <t>29.09.202638</t>
+  </si>
+  <si>
+    <t>29.09.202639</t>
+  </si>
+  <si>
+    <t>29.09.202640</t>
+  </si>
+  <si>
+    <t>29.09.202641</t>
+  </si>
+  <si>
+    <t>29.09.202642</t>
+  </si>
+  <si>
+    <t>29.09.202643</t>
+  </si>
+  <si>
+    <t>29.09.202644</t>
+  </si>
+  <si>
+    <t>29.09.202645</t>
+  </si>
+  <si>
+    <t>29.09.202646</t>
+  </si>
+  <si>
+    <t>29.09.202647</t>
+  </si>
+  <si>
+    <t>29.09.202648</t>
+  </si>
+  <si>
+    <t>29.09.202649</t>
+  </si>
+  <si>
+    <t>29.09.202650</t>
+  </si>
+  <si>
+    <t>29.09.202651</t>
+  </si>
+  <si>
+    <t>29.09.202652</t>
+  </si>
+  <si>
+    <t>29.09.202653</t>
+  </si>
+  <si>
+    <t>29.09.202654</t>
+  </si>
+  <si>
+    <t>29.09.202655</t>
+  </si>
+  <si>
+    <t>29.09.202656</t>
+  </si>
+  <si>
+    <t>29.09.202657</t>
+  </si>
+  <si>
+    <t>29.09.202658</t>
+  </si>
+  <si>
+    <t>29.09.202659</t>
+  </si>
+  <si>
+    <t>29.09.202660</t>
+  </si>
+  <si>
+    <t>29.09.202661</t>
+  </si>
+  <si>
+    <t>29.09.202662</t>
+  </si>
+  <si>
+    <t>29.09.202663</t>
+  </si>
+  <si>
+    <t>29.09.202664</t>
+  </si>
+  <si>
+    <t>29.09.202665</t>
+  </si>
+  <si>
+    <t>29.09.202666</t>
+  </si>
+  <si>
+    <t>29.09.202667</t>
+  </si>
+  <si>
+    <t>29.09.202668</t>
+  </si>
+  <si>
+    <t>29.09.202669</t>
+  </si>
+  <si>
+    <t>29.09.202670</t>
+  </si>
+  <si>
+    <t>29.09.202671</t>
+  </si>
+  <si>
+    <t>29.09.202672</t>
+  </si>
+  <si>
+    <t>29.09.202673</t>
+  </si>
+  <si>
+    <t>29.09.202674</t>
+  </si>
+  <si>
+    <t>29.09.202675</t>
+  </si>
+  <si>
+    <t>29.09.202676</t>
+  </si>
+  <si>
+    <t>29.09.202677</t>
+  </si>
+  <si>
+    <t>29.09.202678</t>
+  </si>
+  <si>
+    <t>29.09.202679</t>
+  </si>
+  <si>
+    <t>29.09.202680</t>
+  </si>
+  <si>
+    <t>29.09.202681</t>
+  </si>
+  <si>
+    <t>29.09.202682</t>
+  </si>
+  <si>
+    <t>29.09.202683</t>
+  </si>
+  <si>
+    <t>29.09.202684</t>
+  </si>
+  <si>
+    <t>29.09.202685</t>
+  </si>
+  <si>
+    <t>29.09.202686</t>
+  </si>
+  <si>
+    <t>29.09.202687</t>
+  </si>
+  <si>
+    <t>29.09.202688</t>
+  </si>
+  <si>
+    <t>29.09.202689</t>
+  </si>
+  <si>
+    <t>29.09.202690</t>
+  </si>
+  <si>
+    <t>29.09.202691</t>
+  </si>
+  <si>
+    <t>29.09.202692</t>
+  </si>
+  <si>
+    <t>29.09.202693</t>
+  </si>
+  <si>
+    <t>29.09.202694</t>
+  </si>
+  <si>
+    <t>29.09.202695</t>
+  </si>
+  <si>
+    <t>29.09.202696</t>
+  </si>
+  <si>
+    <t>30.09.20261</t>
+  </si>
+  <si>
+    <t>30.09.20262</t>
+  </si>
+  <si>
+    <t>30.09.20263</t>
+  </si>
+  <si>
+    <t>30.09.20264</t>
+  </si>
+  <si>
+    <t>30.09.20265</t>
+  </si>
+  <si>
+    <t>30.09.20266</t>
+  </si>
+  <si>
+    <t>30.09.20267</t>
+  </si>
+  <si>
+    <t>30.09.20268</t>
+  </si>
+  <si>
+    <t>30.09.20269</t>
+  </si>
+  <si>
+    <t>30.09.202610</t>
+  </si>
+  <si>
+    <t>30.09.202611</t>
+  </si>
+  <si>
+    <t>30.09.202612</t>
+  </si>
+  <si>
+    <t>30.09.202613</t>
+  </si>
+  <si>
+    <t>30.09.202614</t>
+  </si>
+  <si>
+    <t>30.09.202615</t>
+  </si>
+  <si>
+    <t>30.09.202616</t>
+  </si>
+  <si>
+    <t>30.09.202617</t>
+  </si>
+  <si>
+    <t>30.09.202618</t>
+  </si>
+  <si>
+    <t>30.09.202619</t>
+  </si>
+  <si>
+    <t>30.09.202620</t>
+  </si>
+  <si>
+    <t>30.09.202621</t>
+  </si>
+  <si>
+    <t>30.09.202622</t>
+  </si>
+  <si>
+    <t>30.09.202623</t>
+  </si>
+  <si>
+    <t>30.09.202624</t>
+  </si>
+  <si>
+    <t>30.09.202625</t>
+  </si>
+  <si>
+    <t>30.09.202626</t>
+  </si>
+  <si>
+    <t>30.09.202627</t>
+  </si>
+  <si>
+    <t>30.09.202628</t>
+  </si>
+  <si>
+    <t>30.09.202629</t>
+  </si>
+  <si>
+    <t>30.09.202630</t>
+  </si>
+  <si>
+    <t>30.09.202631</t>
+  </si>
+  <si>
+    <t>30.09.202632</t>
+  </si>
+  <si>
+    <t>30.09.202633</t>
+  </si>
+  <si>
+    <t>30.09.202634</t>
+  </si>
+  <si>
+    <t>30.09.202635</t>
+  </si>
+  <si>
+    <t>30.09.202636</t>
+  </si>
+  <si>
+    <t>30.09.202637</t>
+  </si>
+  <si>
+    <t>30.09.202638</t>
+  </si>
+  <si>
+    <t>30.09.202639</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D230"/>
+  <dimension ref="A1:D232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1093,10 +1099,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="B2">
-        <v>5025</v>
+        <v>4485</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1107,10 +1113,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46283.01041666666</v>
+        <v>46293.01041666666</v>
       </c>
       <c r="B3">
-        <v>5000</v>
+        <v>4473</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1121,10 +1127,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46283.02083333334</v>
+        <v>46293.02083333334</v>
       </c>
       <c r="B4">
-        <v>4953</v>
+        <v>4400</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1135,10 +1141,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46283.03125</v>
+        <v>46293.03125</v>
       </c>
       <c r="B5">
-        <v>4926</v>
+        <v>4555</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1149,10 +1155,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46283.04166666666</v>
+        <v>46293.04166666666</v>
       </c>
       <c r="B6">
-        <v>4875</v>
+        <v>4640</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1163,10 +1169,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46283.05208333334</v>
+        <v>46293.05208333334</v>
       </c>
       <c r="B7">
-        <v>4833</v>
+        <v>4646</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1177,10 +1183,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46283.0625</v>
+        <v>46293.0625</v>
       </c>
       <c r="B8">
-        <v>4846</v>
+        <v>4527</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1191,10 +1197,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46283.07291666666</v>
+        <v>46293.07291666666</v>
       </c>
       <c r="B9">
-        <v>4807</v>
+        <v>4429</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1205,10 +1211,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46283.08333333334</v>
+        <v>46293.08333333334</v>
       </c>
       <c r="B10">
-        <v>4814</v>
+        <v>4454</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1219,10 +1225,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46283.09375</v>
+        <v>46293.09375</v>
       </c>
       <c r="B11">
-        <v>4882</v>
+        <v>4447</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1233,10 +1239,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46283.10416666666</v>
+        <v>46293.10416666666</v>
       </c>
       <c r="B12">
-        <v>4895</v>
+        <v>4493</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1247,10 +1253,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46283.11458333334</v>
+        <v>46293.11458333334</v>
       </c>
       <c r="B13">
-        <v>4879</v>
+        <v>4488</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1261,10 +1267,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46283.125</v>
+        <v>46293.125</v>
       </c>
       <c r="B14">
-        <v>4900</v>
+        <v>4433</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1275,10 +1281,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46283.13541666666</v>
+        <v>46293.13541666666</v>
       </c>
       <c r="B15">
-        <v>4922</v>
+        <v>4457</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1289,10 +1295,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46283.14583333334</v>
+        <v>46293.14583333334</v>
       </c>
       <c r="B16">
-        <v>4946</v>
+        <v>4493</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1303,10 +1309,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46283.15625</v>
+        <v>46293.15625</v>
       </c>
       <c r="B17">
-        <v>4969</v>
+        <v>4504</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1317,10 +1323,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46283.16666666666</v>
+        <v>46293.16666666666</v>
       </c>
       <c r="B18">
-        <v>5106</v>
+        <v>4497</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1331,10 +1337,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46283.17708333334</v>
+        <v>46293.17708333334</v>
       </c>
       <c r="B19">
-        <v>5132</v>
+        <v>4647</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1345,10 +1351,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46283.1875</v>
+        <v>46293.1875</v>
       </c>
       <c r="B20">
-        <v>5091</v>
+        <v>4707</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1359,10 +1365,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46283.19791666666</v>
+        <v>46293.19791666666</v>
       </c>
       <c r="B21">
-        <v>5117</v>
+        <v>4832</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1373,10 +1379,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46283.20833333334</v>
+        <v>46293.20833333334</v>
       </c>
       <c r="B22">
-        <v>5299</v>
+        <v>5045</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1387,10 +1393,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46283.21875</v>
+        <v>46293.21875</v>
       </c>
       <c r="B23">
-        <v>5404</v>
+        <v>5251</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1401,10 +1407,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46283.22916666666</v>
+        <v>46293.22916666666</v>
       </c>
       <c r="B24">
-        <v>5532</v>
+        <v>5397</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1415,10 +1421,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46283.23958333334</v>
+        <v>46293.23958333334</v>
       </c>
       <c r="B25">
-        <v>5601</v>
+        <v>5562</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1429,10 +1435,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46283.25</v>
+        <v>46293.25</v>
       </c>
       <c r="B26">
-        <v>5811</v>
+        <v>5846</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1443,10 +1449,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46283.26041666666</v>
+        <v>46293.26041666666</v>
       </c>
       <c r="B27">
-        <v>5936</v>
+        <v>6030</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1457,10 +1463,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46283.27083333334</v>
+        <v>46293.27083333334</v>
       </c>
       <c r="B28">
-        <v>5954</v>
+        <v>6083</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1471,10 +1477,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46283.28125</v>
+        <v>46293.28125</v>
       </c>
       <c r="B29">
-        <v>5872</v>
+        <v>6086</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1485,10 +1491,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46283.29166666666</v>
+        <v>46293.29166666666</v>
       </c>
       <c r="B30">
-        <v>5978</v>
+        <v>6198</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1499,10 +1505,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46283.30208333334</v>
+        <v>46293.30208333334</v>
       </c>
       <c r="B31">
-        <v>6008</v>
+        <v>6135</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1513,10 +1519,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46283.3125</v>
+        <v>46293.3125</v>
       </c>
       <c r="B32">
-        <v>5959</v>
+        <v>6115</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1527,10 +1533,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46283.32291666666</v>
+        <v>46293.32291666666</v>
       </c>
       <c r="B33">
-        <v>5870</v>
+        <v>5953</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1541,10 +1547,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46283.33333333334</v>
+        <v>46293.33333333334</v>
       </c>
       <c r="B34">
-        <v>5806</v>
+        <v>5872</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1555,10 +1561,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46283.34375</v>
+        <v>46293.34375</v>
       </c>
       <c r="B35">
-        <v>5714</v>
+        <v>5810</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1569,10 +1575,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46283.35416666666</v>
+        <v>46293.35416666666</v>
       </c>
       <c r="B36">
-        <v>5646</v>
+        <v>5684</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1583,10 +1589,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46283.36458333334</v>
+        <v>46293.36458333334</v>
       </c>
       <c r="B37">
-        <v>5719</v>
+        <v>5408</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1597,10 +1603,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46283.375</v>
+        <v>46293.375</v>
       </c>
       <c r="B38">
-        <v>5387</v>
+        <v>5274</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1611,10 +1617,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46283.38541666666</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="B39">
-        <v>5299</v>
+        <v>5175</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1625,10 +1631,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46283.39583333334</v>
+        <v>46293.39583333334</v>
       </c>
       <c r="B40">
-        <v>5211</v>
+        <v>5033</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1639,10 +1645,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46283.40625</v>
+        <v>46293.40625</v>
       </c>
       <c r="B41">
-        <v>5092</v>
+        <v>4886</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1653,10 +1659,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46283.41666666666</v>
+        <v>46293.41666666666</v>
       </c>
       <c r="B42">
-        <v>5000</v>
+        <v>4694</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1667,10 +1673,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46283.42708333334</v>
+        <v>46293.42708333334</v>
       </c>
       <c r="B43">
-        <v>4852</v>
+        <v>4613</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1681,10 +1687,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46283.4375</v>
+        <v>46293.4375</v>
       </c>
       <c r="B44">
-        <v>4811</v>
+        <v>4528</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1695,10 +1701,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46283.44791666666</v>
+        <v>46293.44791666666</v>
       </c>
       <c r="B45">
-        <v>4860</v>
+        <v>4438</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1709,10 +1715,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46283.45833333334</v>
+        <v>46293.45833333334</v>
       </c>
       <c r="B46">
-        <v>4776</v>
+        <v>4468</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1723,10 +1729,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46283.46875</v>
+        <v>46293.46875</v>
       </c>
       <c r="B47">
-        <v>4863</v>
+        <v>4473</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1737,10 +1743,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46283.47916666666</v>
+        <v>46293.47916666666</v>
       </c>
       <c r="B48">
-        <v>4927</v>
+        <v>4488</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1751,10 +1757,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46283.48958333334</v>
+        <v>46293.48958333334</v>
       </c>
       <c r="B49">
-        <v>4940</v>
+        <v>4478</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1765,10 +1771,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46283.5</v>
+        <v>46293.5</v>
       </c>
       <c r="B50">
-        <v>5006</v>
+        <v>4427</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1779,10 +1785,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46283.51041666666</v>
+        <v>46293.51041666666</v>
       </c>
       <c r="B51">
-        <v>5044</v>
+        <v>4523</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1793,10 +1799,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46283.52083333334</v>
+        <v>46293.52083333334</v>
       </c>
       <c r="B52">
-        <v>5100</v>
+        <v>4560</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1807,10 +1813,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46283.53125</v>
+        <v>46293.53125</v>
       </c>
       <c r="B53">
-        <v>5027</v>
+        <v>4648</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1821,10 +1827,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46283.54166666666</v>
+        <v>46293.54166666666</v>
       </c>
       <c r="B54">
-        <v>4832</v>
+        <v>4589</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1835,10 +1841,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46283.55208333334</v>
+        <v>46293.55208333334</v>
       </c>
       <c r="B55">
-        <v>4681</v>
+        <v>4674</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1849,10 +1855,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46283.5625</v>
+        <v>46293.5625</v>
       </c>
       <c r="B56">
-        <v>4745</v>
+        <v>4739</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1863,10 +1869,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46283.57291666666</v>
+        <v>46293.57291666666</v>
       </c>
       <c r="B57">
-        <v>4678</v>
+        <v>4779</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1877,10 +1883,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46283.58333333334</v>
+        <v>46293.58333333334</v>
       </c>
       <c r="B58">
-        <v>4701</v>
+        <v>4779</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1891,10 +1897,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46283.59375</v>
+        <v>46293.59375</v>
       </c>
       <c r="B59">
-        <v>4726</v>
+        <v>4851</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1905,10 +1911,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46283.60416666666</v>
+        <v>46293.60416666666</v>
       </c>
       <c r="B60">
-        <v>4818</v>
+        <v>4930</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1919,10 +1925,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46283.61458333334</v>
+        <v>46293.61458333334</v>
       </c>
       <c r="B61">
-        <v>4911</v>
+        <v>4973</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1933,10 +1939,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46283.625</v>
+        <v>46293.625</v>
       </c>
       <c r="B62">
-        <v>5003</v>
+        <v>5229</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1947,10 +1953,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46283.63541666666</v>
+        <v>46293.63541666666</v>
       </c>
       <c r="B63">
-        <v>5158</v>
+        <v>5346</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1961,10 +1967,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46283.64583333334</v>
+        <v>46293.64583333334</v>
       </c>
       <c r="B64">
-        <v>5260</v>
+        <v>5468</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1975,10 +1981,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46283.65625</v>
+        <v>46293.65625</v>
       </c>
       <c r="B65">
-        <v>5347</v>
+        <v>5509</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1989,10 +1995,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46283.66666666666</v>
+        <v>46293.66666666666</v>
       </c>
       <c r="B66">
-        <v>5657</v>
+        <v>5605</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -2003,10 +2009,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46283.67708333334</v>
+        <v>46293.67708333334</v>
       </c>
       <c r="B67">
-        <v>5780</v>
+        <v>5862</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -2017,10 +2023,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46283.6875</v>
+        <v>46293.6875</v>
       </c>
       <c r="B68">
-        <v>5786</v>
+        <v>6066</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -2031,10 +2037,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46283.69791666666</v>
+        <v>46293.69791666666</v>
       </c>
       <c r="B69">
-        <v>5914</v>
+        <v>6215</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -2045,10 +2051,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46283.70833333334</v>
+        <v>46293.70833333334</v>
       </c>
       <c r="B70">
-        <v>6066</v>
+        <v>6241</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -2059,10 +2065,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46283.71875</v>
+        <v>46293.71875</v>
       </c>
       <c r="B71">
-        <v>6183</v>
+        <v>6379</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -2073,10 +2079,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46283.72916666666</v>
+        <v>46293.72916666666</v>
       </c>
       <c r="B72">
-        <v>6257</v>
+        <v>6576</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -2087,10 +2093,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46283.73958333334</v>
+        <v>46293.73958333334</v>
       </c>
       <c r="B73">
-        <v>6389</v>
+        <v>6538</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -2101,10 +2107,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46283.75</v>
+        <v>46293.75</v>
       </c>
       <c r="B74">
-        <v>6451</v>
+        <v>6558</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2115,10 +2121,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46283.76041666666</v>
+        <v>46293.76041666666</v>
       </c>
       <c r="B75">
-        <v>6493</v>
+        <v>6760</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2129,10 +2135,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46283.77083333334</v>
+        <v>46293.77083333334</v>
       </c>
       <c r="B76">
-        <v>6656</v>
+        <v>6760</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2143,10 +2149,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46283.78125</v>
+        <v>46293.78125</v>
       </c>
       <c r="B77">
-        <v>6732</v>
+        <v>6981</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2157,10 +2163,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46283.79166666666</v>
+        <v>46293.79166666666</v>
       </c>
       <c r="B78">
-        <v>6772</v>
+        <v>6906</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2171,10 +2177,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46283.80208333334</v>
+        <v>46293.80208333334</v>
       </c>
       <c r="B79">
-        <v>6770</v>
+        <v>6936</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2185,10 +2191,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46283.8125</v>
+        <v>46293.8125</v>
       </c>
       <c r="B80">
-        <v>6692</v>
+        <v>6867</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2199,10 +2205,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46283.82291666666</v>
+        <v>46293.82291666666</v>
       </c>
       <c r="B81">
-        <v>6648</v>
+        <v>6810</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2213,10 +2219,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46283.83333333334</v>
+        <v>46293.83333333334</v>
       </c>
       <c r="B82">
-        <v>6554</v>
+        <v>6709</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2227,10 +2233,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46283.84375</v>
+        <v>46293.84375</v>
       </c>
       <c r="B83">
-        <v>6468</v>
+        <v>6592</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2241,10 +2247,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46283.85416666666</v>
+        <v>46293.85416666666</v>
       </c>
       <c r="B84">
-        <v>6361</v>
+        <v>6448</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2255,10 +2261,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46283.86458333334</v>
+        <v>46293.86458333334</v>
       </c>
       <c r="B85">
-        <v>6202</v>
+        <v>6342</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2269,10 +2275,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46283.875</v>
+        <v>46293.875</v>
       </c>
       <c r="B86">
-        <v>6012</v>
+        <v>6170</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2283,10 +2289,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46283.88541666666</v>
+        <v>46293.88541666666</v>
       </c>
       <c r="B87">
-        <v>5902</v>
+        <v>6006</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2297,10 +2303,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46283.89583333334</v>
+        <v>46293.89583333334</v>
       </c>
       <c r="B88">
-        <v>5795</v>
+        <v>5830</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2311,10 +2317,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46283.90625</v>
+        <v>46293.90625</v>
       </c>
       <c r="B89">
-        <v>5701</v>
+        <v>5766</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2325,10 +2331,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46283.91666666666</v>
+        <v>46293.91666666666</v>
       </c>
       <c r="B90">
-        <v>5539</v>
+        <v>5725</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2339,10 +2345,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46283.92708333334</v>
+        <v>46293.92708333334</v>
       </c>
       <c r="B91">
-        <v>5443</v>
+        <v>5663</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2353,10 +2359,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46283.9375</v>
+        <v>46293.9375</v>
       </c>
       <c r="B92">
-        <v>5385</v>
+        <v>5556</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2367,10 +2373,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46283.94791666666</v>
+        <v>46293.94791666666</v>
       </c>
       <c r="B93">
-        <v>5295</v>
+        <v>5486</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2381,10 +2387,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46283.95833333334</v>
+        <v>46293.95833333334</v>
       </c>
       <c r="B94">
-        <v>5234</v>
+        <v>5314</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2395,10 +2401,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46283.96875</v>
+        <v>46293.96875</v>
       </c>
       <c r="B95">
-        <v>5112</v>
+        <v>5222</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2409,10 +2415,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46283.97916666666</v>
+        <v>46293.97916666666</v>
       </c>
       <c r="B96">
-        <v>5066</v>
+        <v>5130</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2423,10 +2429,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46283.98958333334</v>
+        <v>46293.98958333334</v>
       </c>
       <c r="B97">
-        <v>5029</v>
+        <v>5109</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2437,10 +2443,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46284</v>
+        <v>46294</v>
       </c>
       <c r="B98">
-        <v>5085</v>
+        <v>5046</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2451,10 +2457,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46284.01041666666</v>
+        <v>46294.01041666666</v>
       </c>
       <c r="B99">
-        <v>5060</v>
+        <v>5034</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2465,10 +2471,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46284.02083333334</v>
+        <v>46294.02083333334</v>
       </c>
       <c r="B100">
-        <v>5056</v>
+        <v>4970</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2479,10 +2485,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46284.03125</v>
+        <v>46294.03125</v>
       </c>
       <c r="B101">
-        <v>4978</v>
+        <v>4913</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2493,10 +2499,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46284.04166666666</v>
+        <v>46294.04166666666</v>
       </c>
       <c r="B102">
-        <v>4978</v>
+        <v>4874</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2507,10 +2513,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46284.05208333334</v>
+        <v>46294.05208333334</v>
       </c>
       <c r="B103">
-        <v>4987</v>
+        <v>4993</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2521,10 +2527,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46284.0625</v>
+        <v>46294.0625</v>
       </c>
       <c r="B104">
-        <v>4933</v>
+        <v>5074</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2535,10 +2541,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46284.07291666666</v>
+        <v>46294.07291666666</v>
       </c>
       <c r="B105">
-        <v>4952</v>
+        <v>5048</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2549,10 +2555,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46284.08333333334</v>
+        <v>46294.08333333334</v>
       </c>
       <c r="B106">
-        <v>4774</v>
+        <v>5067</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2563,10 +2569,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46284.09375</v>
+        <v>46294.09375</v>
       </c>
       <c r="B107">
-        <v>4788</v>
+        <v>5047</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2577,10 +2583,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46284.10416666666</v>
+        <v>46294.10416666666</v>
       </c>
       <c r="B108">
-        <v>4791</v>
+        <v>5061</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2591,10 +2597,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46284.11458333334</v>
+        <v>46294.11458333334</v>
       </c>
       <c r="B109">
-        <v>4797</v>
+        <v>5084</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2605,10 +2611,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46284.125</v>
+        <v>46294.125</v>
       </c>
       <c r="B110">
-        <v>4771</v>
+        <v>5076</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2619,10 +2625,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46284.13541666666</v>
+        <v>46294.13541666666</v>
       </c>
       <c r="B111">
-        <v>4770</v>
+        <v>5080</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2633,10 +2639,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46284.14583333334</v>
+        <v>46294.14583333334</v>
       </c>
       <c r="B112">
-        <v>4766</v>
+        <v>5124</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2647,10 +2653,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46284.15625</v>
+        <v>46294.15625</v>
       </c>
       <c r="B113">
-        <v>4758</v>
+        <v>5083</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2661,10 +2667,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46284.16666666666</v>
+        <v>46294.16666666666</v>
       </c>
       <c r="B114">
-        <v>4818</v>
+        <v>5123</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2675,10 +2681,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46284.17708333334</v>
+        <v>46294.17708333334</v>
       </c>
       <c r="B115">
-        <v>4794</v>
+        <v>5101</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2689,10 +2695,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46284.1875</v>
+        <v>46294.1875</v>
       </c>
       <c r="B116">
-        <v>4840</v>
+        <v>5196</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2703,10 +2709,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46284.19791666666</v>
+        <v>46294.19791666666</v>
       </c>
       <c r="B117">
-        <v>4851</v>
+        <v>5204</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2717,10 +2723,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46284.20833333334</v>
+        <v>46294.20833333334</v>
       </c>
       <c r="B118">
-        <v>4894</v>
+        <v>5395</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2731,10 +2737,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46284.21875</v>
+        <v>46294.21875</v>
       </c>
       <c r="B119">
-        <v>4968</v>
+        <v>5558</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2745,10 +2751,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46284.22916666666</v>
+        <v>46294.22916666666</v>
       </c>
       <c r="B120">
-        <v>4923</v>
+        <v>5712</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2759,10 +2765,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46284.23958333334</v>
+        <v>46294.23958333334</v>
       </c>
       <c r="B121">
-        <v>4925</v>
+        <v>5793</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2773,10 +2779,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46284.25</v>
+        <v>46294.25</v>
       </c>
       <c r="B122">
-        <v>4974</v>
+        <v>6052</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2787,10 +2793,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46284.26041666666</v>
+        <v>46294.26041666666</v>
       </c>
       <c r="B123">
-        <v>4994</v>
+        <v>6217</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2801,10 +2807,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46284.27083333334</v>
+        <v>46294.27083333334</v>
       </c>
       <c r="B124">
-        <v>5060</v>
+        <v>6319</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2815,10 +2821,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46284.28125</v>
+        <v>46294.28125</v>
       </c>
       <c r="B125">
-        <v>5065</v>
+        <v>6363</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2829,10 +2835,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46284.29166666666</v>
+        <v>46294.29166666666</v>
       </c>
       <c r="B126">
-        <v>5055</v>
+        <v>6381</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2843,10 +2849,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46284.30208333334</v>
+        <v>46294.30208333334</v>
       </c>
       <c r="B127">
-        <v>5051</v>
+        <v>6358</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2857,10 +2863,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46284.3125</v>
+        <v>46294.3125</v>
       </c>
       <c r="B128">
-        <v>4940</v>
+        <v>6287</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2871,10 +2877,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46284.32291666666</v>
+        <v>46294.32291666666</v>
       </c>
       <c r="B129">
-        <v>4903</v>
+        <v>6198</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2885,10 +2891,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46284.33333333334</v>
+        <v>46294.33333333334</v>
       </c>
       <c r="B130">
-        <v>4838</v>
+        <v>6020</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2899,10 +2905,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46284.34375</v>
+        <v>46294.34375</v>
       </c>
       <c r="B131">
-        <v>4696</v>
+        <v>6004</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2913,10 +2919,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46284.35416666666</v>
+        <v>46294.35416666666</v>
       </c>
       <c r="B132">
-        <v>4620</v>
+        <v>5855</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2927,10 +2933,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46284.36458333334</v>
+        <v>46294.36458333334</v>
       </c>
       <c r="B133">
-        <v>4556</v>
+        <v>5689</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2941,10 +2947,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46284.375</v>
+        <v>46294.375</v>
       </c>
       <c r="B134">
-        <v>4345</v>
+        <v>5458</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2955,10 +2961,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46284.38541666666</v>
+        <v>46294.38541666666</v>
       </c>
       <c r="B135">
-        <v>4335</v>
+        <v>5278</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2969,10 +2975,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46284.39583333334</v>
+        <v>46294.39583333334</v>
       </c>
       <c r="B136">
-        <v>4135</v>
+        <v>5127</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2983,10 +2989,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46284.40625</v>
+        <v>46294.40625</v>
       </c>
       <c r="B137">
-        <v>4009</v>
+        <v>4872</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2997,10 +3003,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46284.41666666666</v>
+        <v>46294.41666666666</v>
       </c>
       <c r="B138">
-        <v>4052</v>
+        <v>4785</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -3011,10 +3017,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46284.42708333334</v>
+        <v>46294.42708333334</v>
       </c>
       <c r="B139">
-        <v>3954</v>
+        <v>4666</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -3025,10 +3031,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46284.4375</v>
+        <v>46294.4375</v>
       </c>
       <c r="B140">
-        <v>3898</v>
+        <v>4604</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -3039,10 +3045,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46284.44791666666</v>
+        <v>46294.44791666666</v>
       </c>
       <c r="B141">
-        <v>3751</v>
+        <v>4608</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -3053,10 +3059,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46284.45833333334</v>
+        <v>46294.45833333334</v>
       </c>
       <c r="B142">
-        <v>3639</v>
+        <v>4460</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -3067,10 +3073,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46284.46875</v>
+        <v>46294.46875</v>
       </c>
       <c r="B143">
-        <v>3702</v>
+        <v>4454</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -3081,10 +3087,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46284.47916666666</v>
+        <v>46294.47916666666</v>
       </c>
       <c r="B144">
-        <v>3653</v>
+        <v>4438</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -3095,10 +3101,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46284.48958333334</v>
+        <v>46294.48958333334</v>
       </c>
       <c r="B145">
-        <v>3645</v>
+        <v>4427</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -3109,10 +3115,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46284.5</v>
+        <v>46294.5</v>
       </c>
       <c r="B146">
-        <v>3686</v>
+        <v>4550</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3123,10 +3129,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46284.51041666666</v>
+        <v>46294.51041666666</v>
       </c>
       <c r="B147">
-        <v>3673</v>
+        <v>4618</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3137,10 +3143,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46284.52083333334</v>
+        <v>46294.52083333334</v>
       </c>
       <c r="B148">
-        <v>3685</v>
+        <v>4495</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3151,10 +3157,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46284.53125</v>
+        <v>46294.53125</v>
       </c>
       <c r="B149">
-        <v>3728</v>
+        <v>4601</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3165,10 +3171,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46284.54166666666</v>
+        <v>46294.54166666666</v>
       </c>
       <c r="B150">
-        <v>3774</v>
+        <v>4671</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3179,10 +3185,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46284.55208333334</v>
+        <v>46294.55208333334</v>
       </c>
       <c r="B151">
-        <v>3808</v>
+        <v>4696</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3193,10 +3199,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46284.5625</v>
+        <v>46294.5625</v>
       </c>
       <c r="B152">
-        <v>3798</v>
+        <v>4699</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3207,10 +3213,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46284.57291666666</v>
+        <v>46294.57291666666</v>
       </c>
       <c r="B153">
-        <v>3849</v>
+        <v>4837</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3221,10 +3227,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46284.58333333334</v>
+        <v>46294.58333333334</v>
       </c>
       <c r="B154">
-        <v>4114</v>
+        <v>5034</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3235,10 +3241,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46284.59375</v>
+        <v>46294.59375</v>
       </c>
       <c r="B155">
-        <v>4111</v>
+        <v>4869</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3249,10 +3255,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46284.60416666666</v>
+        <v>46294.60416666666</v>
       </c>
       <c r="B156">
-        <v>4206</v>
+        <v>4903</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3263,10 +3269,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46284.61458333334</v>
+        <v>46294.61458333334</v>
       </c>
       <c r="B157">
-        <v>4301</v>
+        <v>5027</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3277,10 +3283,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46284.625</v>
+        <v>46294.625</v>
       </c>
       <c r="B158">
-        <v>4274</v>
+        <v>5102</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3291,10 +3297,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46284.63541666666</v>
+        <v>46294.63541666666</v>
       </c>
       <c r="B159">
-        <v>4467</v>
+        <v>5227</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3305,10 +3311,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46284.64583333334</v>
+        <v>46294.64583333334</v>
       </c>
       <c r="B160">
-        <v>4625</v>
+        <v>5283</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3319,10 +3325,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46284.65625</v>
+        <v>46294.65625</v>
       </c>
       <c r="B161">
-        <v>4764</v>
+        <v>5451</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3333,10 +3339,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46284.66666666666</v>
+        <v>46294.66666666666</v>
       </c>
       <c r="B162">
-        <v>4907</v>
+        <v>5604</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3347,10 +3353,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46284.67708333334</v>
+        <v>46294.67708333334</v>
       </c>
       <c r="B163">
-        <v>4984</v>
+        <v>5759</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3361,10 +3367,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46284.6875</v>
+        <v>46294.6875</v>
       </c>
       <c r="B164">
-        <v>5160</v>
+        <v>5893</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3375,10 +3381,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46284.69791666666</v>
+        <v>46294.69791666666</v>
       </c>
       <c r="B165">
-        <v>5390</v>
+        <v>6012</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3389,10 +3395,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46284.70833333334</v>
+        <v>46294.70833333334</v>
       </c>
       <c r="B166">
-        <v>5421</v>
+        <v>6081</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3403,10 +3409,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46284.71875</v>
+        <v>46294.71875</v>
       </c>
       <c r="B167">
-        <v>5566</v>
+        <v>6275</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3417,10 +3423,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46284.72916666666</v>
+        <v>46294.72916666666</v>
       </c>
       <c r="B168">
-        <v>5719</v>
+        <v>6432</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3431,10 +3437,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46284.73958333334</v>
+        <v>46294.73958333334</v>
       </c>
       <c r="B169">
-        <v>5760</v>
+        <v>6712</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3445,10 +3451,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46284.75</v>
+        <v>46294.75</v>
       </c>
       <c r="B170">
-        <v>5822</v>
+        <v>6649</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3459,10 +3465,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46284.76041666666</v>
+        <v>46294.76041666666</v>
       </c>
       <c r="B171">
-        <v>5961</v>
+        <v>6787</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3473,10 +3479,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46284.77083333334</v>
+        <v>46294.77083333334</v>
       </c>
       <c r="B172">
-        <v>6080</v>
+        <v>6953</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3487,10 +3493,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46284.78125</v>
+        <v>46294.78125</v>
       </c>
       <c r="B173">
-        <v>6256</v>
+        <v>6995</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3501,10 +3507,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46284.79166666666</v>
+        <v>46294.79166666666</v>
       </c>
       <c r="B174">
-        <v>6302</v>
+        <v>6991</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3515,10 +3521,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46284.80208333334</v>
+        <v>46294.80208333334</v>
       </c>
       <c r="B175">
-        <v>6247</v>
+        <v>6944</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3529,10 +3535,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46284.8125</v>
+        <v>46294.8125</v>
       </c>
       <c r="B176">
-        <v>6216</v>
+        <v>6894</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3543,10 +3549,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46284.82291666666</v>
+        <v>46294.82291666666</v>
       </c>
       <c r="B177">
-        <v>6193</v>
+        <v>6879</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -3557,10 +3563,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46284.83333333334</v>
+        <v>46294.83333333334</v>
       </c>
       <c r="B178">
-        <v>6085</v>
+        <v>6690</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -3571,10 +3577,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46284.84375</v>
+        <v>46294.84375</v>
       </c>
       <c r="B179">
-        <v>5972</v>
+        <v>6555</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3585,10 +3591,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46284.85416666666</v>
+        <v>46294.85416666666</v>
       </c>
       <c r="B180">
-        <v>5893</v>
+        <v>6432</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3599,10 +3605,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46284.86458333334</v>
+        <v>46294.86458333334</v>
       </c>
       <c r="B181">
-        <v>5777</v>
+        <v>6430</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -3613,10 +3619,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46284.875</v>
+        <v>46294.875</v>
       </c>
       <c r="B182">
-        <v>5626</v>
+        <v>6241</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3627,10 +3633,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46284.88541666666</v>
+        <v>46294.88541666666</v>
       </c>
       <c r="B183">
-        <v>5507</v>
+        <v>6102</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3641,10 +3647,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46284.89583333334</v>
+        <v>46294.89583333334</v>
       </c>
       <c r="B184">
-        <v>5420</v>
+        <v>5930</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3655,10 +3661,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46284.90625</v>
+        <v>46294.90625</v>
       </c>
       <c r="B185">
-        <v>5343</v>
+        <v>5759</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3669,10 +3675,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46284.91666666666</v>
+        <v>46294.91666666666</v>
       </c>
       <c r="B186">
-        <v>5336</v>
+        <v>5709</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3683,10 +3689,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46284.92708333334</v>
+        <v>46294.92708333334</v>
       </c>
       <c r="B187">
-        <v>5201</v>
+        <v>5574</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3697,10 +3703,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46284.9375</v>
+        <v>46294.9375</v>
       </c>
       <c r="B188">
-        <v>5088</v>
+        <v>5490</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -3711,10 +3717,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46284.94791666666</v>
+        <v>46294.94791666666</v>
       </c>
       <c r="B189">
-        <v>5009</v>
+        <v>5370</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3725,10 +3731,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46284.95833333334</v>
+        <v>46294.95833333334</v>
       </c>
       <c r="B190">
-        <v>4861</v>
+        <v>5272</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3739,10 +3745,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46284.96875</v>
+        <v>46294.96875</v>
       </c>
       <c r="B191">
-        <v>4802</v>
+        <v>5203</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3753,10 +3759,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46284.97916666666</v>
+        <v>46294.97916666666</v>
       </c>
       <c r="B192">
-        <v>4745</v>
+        <v>5163</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -3767,10 +3773,10 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46284.98958333334</v>
+        <v>46294.98958333334</v>
       </c>
       <c r="B193">
-        <v>4678</v>
+        <v>5121</v>
       </c>
       <c r="C193">
         <v>96</v>
@@ -3781,10 +3787,10 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="2">
-        <v>46285</v>
+        <v>46295</v>
       </c>
       <c r="B194">
-        <v>4610</v>
+        <v>5019</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -3795,10 +3801,10 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="2">
-        <v>46285.01041666666</v>
+        <v>46295.01041666666</v>
       </c>
       <c r="B195">
-        <v>4614</v>
+        <v>4994</v>
       </c>
       <c r="C195">
         <v>2</v>
@@ -3809,10 +3815,10 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="2">
-        <v>46285.02083333334</v>
+        <v>46295.02083333334</v>
       </c>
       <c r="B196">
-        <v>4640</v>
+        <v>4979</v>
       </c>
       <c r="C196">
         <v>3</v>
@@ -3823,10 +3829,10 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="2">
-        <v>46285.03125</v>
+        <v>46295.03125</v>
       </c>
       <c r="B197">
-        <v>4588</v>
+        <v>4931</v>
       </c>
       <c r="C197">
         <v>4</v>
@@ -3837,10 +3843,10 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="2">
-        <v>46285.04166666666</v>
+        <v>46295.04166666666</v>
       </c>
       <c r="B198">
-        <v>4648</v>
+        <v>4987</v>
       </c>
       <c r="C198">
         <v>5</v>
@@ -3851,10 +3857,10 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="2">
-        <v>46285.05208333334</v>
+        <v>46295.05208333334</v>
       </c>
       <c r="B199">
-        <v>4583</v>
+        <v>4907</v>
       </c>
       <c r="C199">
         <v>6</v>
@@ -3865,10 +3871,10 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="2">
-        <v>46285.0625</v>
+        <v>46295.0625</v>
       </c>
       <c r="B200">
-        <v>4545</v>
+        <v>4944</v>
       </c>
       <c r="C200">
         <v>7</v>
@@ -3879,10 +3885,10 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="2">
-        <v>46285.07291666666</v>
+        <v>46295.07291666666</v>
       </c>
       <c r="B201">
-        <v>4529</v>
+        <v>4940</v>
       </c>
       <c r="C201">
         <v>8</v>
@@ -3893,10 +3899,10 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="2">
-        <v>46285.08333333334</v>
+        <v>46295.08333333334</v>
       </c>
       <c r="B202">
-        <v>4402</v>
+        <v>4967</v>
       </c>
       <c r="C202">
         <v>9</v>
@@ -3907,10 +3913,10 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="2">
-        <v>46285.09375</v>
+        <v>46295.09375</v>
       </c>
       <c r="B203">
-        <v>4399</v>
+        <v>4934</v>
       </c>
       <c r="C203">
         <v>10</v>
@@ -3921,10 +3927,10 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="2">
-        <v>46285.10416666666</v>
+        <v>46295.10416666666</v>
       </c>
       <c r="B204">
-        <v>4357</v>
+        <v>5145</v>
       </c>
       <c r="C204">
         <v>11</v>
@@ -3935,10 +3941,10 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="2">
-        <v>46285.11458333334</v>
+        <v>46295.11458333334</v>
       </c>
       <c r="B205">
-        <v>4352</v>
+        <v>5103</v>
       </c>
       <c r="C205">
         <v>12</v>
@@ -3949,10 +3955,10 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="2">
-        <v>46285.125</v>
+        <v>46295.125</v>
       </c>
       <c r="B206">
-        <v>4354</v>
+        <v>5062</v>
       </c>
       <c r="C206">
         <v>13</v>
@@ -3963,10 +3969,10 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="2">
-        <v>46285.13541666666</v>
+        <v>46295.13541666666</v>
       </c>
       <c r="B207">
-        <v>4365</v>
+        <v>5040</v>
       </c>
       <c r="C207">
         <v>14</v>
@@ -3977,10 +3983,10 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="2">
-        <v>46285.14583333334</v>
+        <v>46295.14583333334</v>
       </c>
       <c r="B208">
-        <v>4353</v>
+        <v>5127</v>
       </c>
       <c r="C208">
         <v>15</v>
@@ -3991,10 +3997,10 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="2">
-        <v>46285.15625</v>
+        <v>46295.15625</v>
       </c>
       <c r="B209">
-        <v>4401</v>
+        <v>5242</v>
       </c>
       <c r="C209">
         <v>16</v>
@@ -4005,10 +4011,10 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="2">
-        <v>46285.16666666666</v>
+        <v>46295.16666666666</v>
       </c>
       <c r="B210">
-        <v>4377</v>
+        <v>5201</v>
       </c>
       <c r="C210">
         <v>17</v>
@@ -4019,10 +4025,10 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="2">
-        <v>46285.17708333334</v>
+        <v>46295.17708333334</v>
       </c>
       <c r="B211">
-        <v>4354</v>
+        <v>5228</v>
       </c>
       <c r="C211">
         <v>18</v>
@@ -4033,10 +4039,10 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="2">
-        <v>46285.1875</v>
+        <v>46295.1875</v>
       </c>
       <c r="B212">
-        <v>4377</v>
+        <v>5350</v>
       </c>
       <c r="C212">
         <v>19</v>
@@ -4047,10 +4053,10 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="2">
-        <v>46285.19791666666</v>
+        <v>46295.19791666666</v>
       </c>
       <c r="B213">
-        <v>4391</v>
+        <v>5433</v>
       </c>
       <c r="C213">
         <v>20</v>
@@ -4061,10 +4067,10 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="2">
-        <v>46285.20833333334</v>
+        <v>46295.20833333334</v>
       </c>
       <c r="B214">
-        <v>4440</v>
+        <v>5625</v>
       </c>
       <c r="C214">
         <v>21</v>
@@ -4075,10 +4081,10 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="2">
-        <v>46285.21875</v>
+        <v>46295.21875</v>
       </c>
       <c r="B215">
-        <v>4458</v>
+        <v>5618</v>
       </c>
       <c r="C215">
         <v>22</v>
@@ -4089,10 +4095,10 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" s="2">
-        <v>46285.22916666666</v>
+        <v>46295.22916666666</v>
       </c>
       <c r="B216">
-        <v>4449</v>
+        <v>5745</v>
       </c>
       <c r="C216">
         <v>23</v>
@@ -4103,10 +4109,10 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="2">
-        <v>46285.23958333334</v>
+        <v>46295.23958333334</v>
       </c>
       <c r="B217">
-        <v>4412</v>
+        <v>5917</v>
       </c>
       <c r="C217">
         <v>24</v>
@@ -4117,10 +4123,10 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="2">
-        <v>46285.25</v>
+        <v>46295.25</v>
       </c>
       <c r="B218">
-        <v>4417</v>
+        <v>6064</v>
       </c>
       <c r="C218">
         <v>25</v>
@@ -4131,10 +4137,10 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="2">
-        <v>46285.26041666666</v>
+        <v>46295.26041666666</v>
       </c>
       <c r="B219">
-        <v>4429</v>
+        <v>6231</v>
       </c>
       <c r="C219">
         <v>26</v>
@@ -4145,10 +4151,10 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="2">
-        <v>46285.27083333334</v>
+        <v>46295.27083333334</v>
       </c>
       <c r="B220">
-        <v>4420</v>
+        <v>6312</v>
       </c>
       <c r="C220">
         <v>27</v>
@@ -4159,10 +4165,10 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="2">
-        <v>46285.28125</v>
+        <v>46295.28125</v>
       </c>
       <c r="B221">
-        <v>4325</v>
+        <v>6300</v>
       </c>
       <c r="C221">
         <v>28</v>
@@ -4173,10 +4179,10 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="2">
-        <v>46285.29166666666</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="B222">
-        <v>4302</v>
+        <v>6278</v>
       </c>
       <c r="C222">
         <v>29</v>
@@ -4187,10 +4193,10 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="2">
-        <v>46285.30208333334</v>
+        <v>46295.30208333334</v>
       </c>
       <c r="B223">
-        <v>4305</v>
+        <v>6324</v>
       </c>
       <c r="C223">
         <v>30</v>
@@ -4201,10 +4207,10 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="2">
-        <v>46285.3125</v>
+        <v>46295.3125</v>
       </c>
       <c r="B224">
-        <v>4231</v>
+        <v>6224</v>
       </c>
       <c r="C224">
         <v>31</v>
@@ -4215,10 +4221,10 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="2">
-        <v>46285.32291666666</v>
+        <v>46295.32291666666</v>
       </c>
       <c r="B225">
-        <v>4114</v>
+        <v>6112</v>
       </c>
       <c r="C225">
         <v>32</v>
@@ -4229,10 +4235,10 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="2">
-        <v>46285.33333333334</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="B226">
-        <v>4039</v>
+        <v>5868</v>
       </c>
       <c r="C226">
         <v>33</v>
@@ -4243,10 +4249,10 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="2">
-        <v>46285.34375</v>
+        <v>46295.34375</v>
       </c>
       <c r="B227">
-        <v>3903</v>
+        <v>5770</v>
       </c>
       <c r="C227">
         <v>34</v>
@@ -4257,10 +4263,10 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="2">
-        <v>46285.35416666666</v>
+        <v>46295.35416666666</v>
       </c>
       <c r="B228">
-        <v>3785</v>
+        <v>5641</v>
       </c>
       <c r="C228">
         <v>35</v>
@@ -4271,10 +4277,10 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="2">
-        <v>46285.36458333334</v>
+        <v>46295.36458333334</v>
       </c>
       <c r="B229">
-        <v>3649</v>
+        <v>5505</v>
       </c>
       <c r="C229">
         <v>36</v>
@@ -4285,16 +4291,44 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="2">
-        <v>46285.375</v>
+        <v>46295.375</v>
       </c>
       <c r="B230">
-        <v>3540</v>
+        <v>5199</v>
       </c>
       <c r="C230">
         <v>37</v>
       </c>
       <c r="D230" t="s">
         <v>232</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="2">
+        <v>46295.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>5088</v>
+      </c>
+      <c r="C231">
+        <v>38</v>
+      </c>
+      <c r="D231" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="2">
+        <v>46295.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>5110</v>
+      </c>
+      <c r="C232">
+        <v>39</v>
+      </c>
+      <c r="D232" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="428">
   <si>
     <t>Timestamp</t>
   </si>
@@ -26,12 +26,1287 @@
   </si>
   <si>
     <t>Lookup</t>
+  </si>
+  <si>
+    <t>03.10.20261</t>
+  </si>
+  <si>
+    <t>03.10.20262</t>
+  </si>
+  <si>
+    <t>03.10.20263</t>
+  </si>
+  <si>
+    <t>03.10.20264</t>
+  </si>
+  <si>
+    <t>03.10.20265</t>
+  </si>
+  <si>
+    <t>03.10.20266</t>
+  </si>
+  <si>
+    <t>03.10.20267</t>
+  </si>
+  <si>
+    <t>03.10.20268</t>
+  </si>
+  <si>
+    <t>03.10.20269</t>
+  </si>
+  <si>
+    <t>03.10.202610</t>
+  </si>
+  <si>
+    <t>03.10.202611</t>
+  </si>
+  <si>
+    <t>03.10.202612</t>
+  </si>
+  <si>
+    <t>03.10.202613</t>
+  </si>
+  <si>
+    <t>03.10.202614</t>
+  </si>
+  <si>
+    <t>03.10.202615</t>
+  </si>
+  <si>
+    <t>03.10.202616</t>
+  </si>
+  <si>
+    <t>03.10.202617</t>
+  </si>
+  <si>
+    <t>03.10.202618</t>
+  </si>
+  <si>
+    <t>03.10.202619</t>
+  </si>
+  <si>
+    <t>03.10.202620</t>
+  </si>
+  <si>
+    <t>03.10.202621</t>
+  </si>
+  <si>
+    <t>03.10.202622</t>
+  </si>
+  <si>
+    <t>03.10.202623</t>
+  </si>
+  <si>
+    <t>03.10.202624</t>
+  </si>
+  <si>
+    <t>03.10.202625</t>
+  </si>
+  <si>
+    <t>03.10.202626</t>
+  </si>
+  <si>
+    <t>03.10.202627</t>
+  </si>
+  <si>
+    <t>03.10.202628</t>
+  </si>
+  <si>
+    <t>03.10.202629</t>
+  </si>
+  <si>
+    <t>03.10.202630</t>
+  </si>
+  <si>
+    <t>03.10.202631</t>
+  </si>
+  <si>
+    <t>03.10.202632</t>
+  </si>
+  <si>
+    <t>03.10.202633</t>
+  </si>
+  <si>
+    <t>03.10.202634</t>
+  </si>
+  <si>
+    <t>03.10.202635</t>
+  </si>
+  <si>
+    <t>03.10.202636</t>
+  </si>
+  <si>
+    <t>03.10.202637</t>
+  </si>
+  <si>
+    <t>03.10.202638</t>
+  </si>
+  <si>
+    <t>03.10.202639</t>
+  </si>
+  <si>
+    <t>03.10.202640</t>
+  </si>
+  <si>
+    <t>03.10.202641</t>
+  </si>
+  <si>
+    <t>03.10.202642</t>
+  </si>
+  <si>
+    <t>03.10.202643</t>
+  </si>
+  <si>
+    <t>03.10.202644</t>
+  </si>
+  <si>
+    <t>03.10.202645</t>
+  </si>
+  <si>
+    <t>03.10.202646</t>
+  </si>
+  <si>
+    <t>03.10.202647</t>
+  </si>
+  <si>
+    <t>03.10.202648</t>
+  </si>
+  <si>
+    <t>03.10.202649</t>
+  </si>
+  <si>
+    <t>03.10.202650</t>
+  </si>
+  <si>
+    <t>03.10.202651</t>
+  </si>
+  <si>
+    <t>03.10.202652</t>
+  </si>
+  <si>
+    <t>03.10.202653</t>
+  </si>
+  <si>
+    <t>03.10.202654</t>
+  </si>
+  <si>
+    <t>03.10.202655</t>
+  </si>
+  <si>
+    <t>03.10.202656</t>
+  </si>
+  <si>
+    <t>03.10.202657</t>
+  </si>
+  <si>
+    <t>03.10.202658</t>
+  </si>
+  <si>
+    <t>03.10.202659</t>
+  </si>
+  <si>
+    <t>03.10.202660</t>
+  </si>
+  <si>
+    <t>03.10.202661</t>
+  </si>
+  <si>
+    <t>03.10.202662</t>
+  </si>
+  <si>
+    <t>03.10.202663</t>
+  </si>
+  <si>
+    <t>03.10.202664</t>
+  </si>
+  <si>
+    <t>03.10.202665</t>
+  </si>
+  <si>
+    <t>03.10.202666</t>
+  </si>
+  <si>
+    <t>03.10.202667</t>
+  </si>
+  <si>
+    <t>03.10.202668</t>
+  </si>
+  <si>
+    <t>03.10.202669</t>
+  </si>
+  <si>
+    <t>03.10.202670</t>
+  </si>
+  <si>
+    <t>03.10.202671</t>
+  </si>
+  <si>
+    <t>03.10.202672</t>
+  </si>
+  <si>
+    <t>03.10.202673</t>
+  </si>
+  <si>
+    <t>03.10.202674</t>
+  </si>
+  <si>
+    <t>03.10.202675</t>
+  </si>
+  <si>
+    <t>03.10.202676</t>
+  </si>
+  <si>
+    <t>03.10.202677</t>
+  </si>
+  <si>
+    <t>03.10.202678</t>
+  </si>
+  <si>
+    <t>03.10.202679</t>
+  </si>
+  <si>
+    <t>03.10.202680</t>
+  </si>
+  <si>
+    <t>03.10.202681</t>
+  </si>
+  <si>
+    <t>03.10.202682</t>
+  </si>
+  <si>
+    <t>03.10.202683</t>
+  </si>
+  <si>
+    <t>03.10.202684</t>
+  </si>
+  <si>
+    <t>03.10.202685</t>
+  </si>
+  <si>
+    <t>03.10.202686</t>
+  </si>
+  <si>
+    <t>03.10.202687</t>
+  </si>
+  <si>
+    <t>03.10.202688</t>
+  </si>
+  <si>
+    <t>03.10.202689</t>
+  </si>
+  <si>
+    <t>03.10.202690</t>
+  </si>
+  <si>
+    <t>03.10.202691</t>
+  </si>
+  <si>
+    <t>03.10.202692</t>
+  </si>
+  <si>
+    <t>03.10.202693</t>
+  </si>
+  <si>
+    <t>03.10.202694</t>
+  </si>
+  <si>
+    <t>03.10.202695</t>
+  </si>
+  <si>
+    <t>03.10.202696</t>
+  </si>
+  <si>
+    <t>04.10.20261</t>
+  </si>
+  <si>
+    <t>04.10.20262</t>
+  </si>
+  <si>
+    <t>04.10.20263</t>
+  </si>
+  <si>
+    <t>04.10.20264</t>
+  </si>
+  <si>
+    <t>04.10.20265</t>
+  </si>
+  <si>
+    <t>04.10.20266</t>
+  </si>
+  <si>
+    <t>04.10.20267</t>
+  </si>
+  <si>
+    <t>04.10.20268</t>
+  </si>
+  <si>
+    <t>04.10.20269</t>
+  </si>
+  <si>
+    <t>04.10.202610</t>
+  </si>
+  <si>
+    <t>04.10.202611</t>
+  </si>
+  <si>
+    <t>04.10.202612</t>
+  </si>
+  <si>
+    <t>04.10.202613</t>
+  </si>
+  <si>
+    <t>04.10.202614</t>
+  </si>
+  <si>
+    <t>04.10.202615</t>
+  </si>
+  <si>
+    <t>04.10.202616</t>
+  </si>
+  <si>
+    <t>04.10.202617</t>
+  </si>
+  <si>
+    <t>04.10.202618</t>
+  </si>
+  <si>
+    <t>04.10.202619</t>
+  </si>
+  <si>
+    <t>04.10.202620</t>
+  </si>
+  <si>
+    <t>04.10.202621</t>
+  </si>
+  <si>
+    <t>04.10.202622</t>
+  </si>
+  <si>
+    <t>04.10.202623</t>
+  </si>
+  <si>
+    <t>04.10.202624</t>
+  </si>
+  <si>
+    <t>04.10.202625</t>
+  </si>
+  <si>
+    <t>04.10.202626</t>
+  </si>
+  <si>
+    <t>04.10.202627</t>
+  </si>
+  <si>
+    <t>04.10.202628</t>
+  </si>
+  <si>
+    <t>04.10.202629</t>
+  </si>
+  <si>
+    <t>04.10.202630</t>
+  </si>
+  <si>
+    <t>04.10.202631</t>
+  </si>
+  <si>
+    <t>04.10.202632</t>
+  </si>
+  <si>
+    <t>04.10.202633</t>
+  </si>
+  <si>
+    <t>04.10.202634</t>
+  </si>
+  <si>
+    <t>04.10.202635</t>
+  </si>
+  <si>
+    <t>04.10.202636</t>
+  </si>
+  <si>
+    <t>04.10.202637</t>
+  </si>
+  <si>
+    <t>04.10.202638</t>
+  </si>
+  <si>
+    <t>04.10.202639</t>
+  </si>
+  <si>
+    <t>04.10.202640</t>
+  </si>
+  <si>
+    <t>04.10.202641</t>
+  </si>
+  <si>
+    <t>04.10.202642</t>
+  </si>
+  <si>
+    <t>04.10.202643</t>
+  </si>
+  <si>
+    <t>04.10.202644</t>
+  </si>
+  <si>
+    <t>04.10.202645</t>
+  </si>
+  <si>
+    <t>04.10.202646</t>
+  </si>
+  <si>
+    <t>04.10.202647</t>
+  </si>
+  <si>
+    <t>04.10.202648</t>
+  </si>
+  <si>
+    <t>04.10.202649</t>
+  </si>
+  <si>
+    <t>04.10.202650</t>
+  </si>
+  <si>
+    <t>04.10.202651</t>
+  </si>
+  <si>
+    <t>04.10.202652</t>
+  </si>
+  <si>
+    <t>04.10.202653</t>
+  </si>
+  <si>
+    <t>04.10.202654</t>
+  </si>
+  <si>
+    <t>04.10.202655</t>
+  </si>
+  <si>
+    <t>04.10.202656</t>
+  </si>
+  <si>
+    <t>04.10.202657</t>
+  </si>
+  <si>
+    <t>04.10.202658</t>
+  </si>
+  <si>
+    <t>04.10.202659</t>
+  </si>
+  <si>
+    <t>04.10.202660</t>
+  </si>
+  <si>
+    <t>04.10.202661</t>
+  </si>
+  <si>
+    <t>04.10.202662</t>
+  </si>
+  <si>
+    <t>04.10.202663</t>
+  </si>
+  <si>
+    <t>04.10.202664</t>
+  </si>
+  <si>
+    <t>04.10.202665</t>
+  </si>
+  <si>
+    <t>04.10.202666</t>
+  </si>
+  <si>
+    <t>04.10.202667</t>
+  </si>
+  <si>
+    <t>04.10.202668</t>
+  </si>
+  <si>
+    <t>04.10.202669</t>
+  </si>
+  <si>
+    <t>04.10.202670</t>
+  </si>
+  <si>
+    <t>04.10.202671</t>
+  </si>
+  <si>
+    <t>04.10.202672</t>
+  </si>
+  <si>
+    <t>04.10.202673</t>
+  </si>
+  <si>
+    <t>04.10.202674</t>
+  </si>
+  <si>
+    <t>04.10.202675</t>
+  </si>
+  <si>
+    <t>04.10.202676</t>
+  </si>
+  <si>
+    <t>04.10.202677</t>
+  </si>
+  <si>
+    <t>04.10.202678</t>
+  </si>
+  <si>
+    <t>04.10.202679</t>
+  </si>
+  <si>
+    <t>04.10.202680</t>
+  </si>
+  <si>
+    <t>04.10.202681</t>
+  </si>
+  <si>
+    <t>04.10.202682</t>
+  </si>
+  <si>
+    <t>04.10.202683</t>
+  </si>
+  <si>
+    <t>04.10.202684</t>
+  </si>
+  <si>
+    <t>04.10.202685</t>
+  </si>
+  <si>
+    <t>04.10.202686</t>
+  </si>
+  <si>
+    <t>04.10.202687</t>
+  </si>
+  <si>
+    <t>04.10.202688</t>
+  </si>
+  <si>
+    <t>04.10.202689</t>
+  </si>
+  <si>
+    <t>04.10.202690</t>
+  </si>
+  <si>
+    <t>04.10.202691</t>
+  </si>
+  <si>
+    <t>04.10.202692</t>
+  </si>
+  <si>
+    <t>04.10.202693</t>
+  </si>
+  <si>
+    <t>04.10.202694</t>
+  </si>
+  <si>
+    <t>04.10.202695</t>
+  </si>
+  <si>
+    <t>04.10.202696</t>
+  </si>
+  <si>
+    <t>05.10.20261</t>
+  </si>
+  <si>
+    <t>05.10.20262</t>
+  </si>
+  <si>
+    <t>05.10.20263</t>
+  </si>
+  <si>
+    <t>05.10.20264</t>
+  </si>
+  <si>
+    <t>05.10.20265</t>
+  </si>
+  <si>
+    <t>05.10.20266</t>
+  </si>
+  <si>
+    <t>05.10.20267</t>
+  </si>
+  <si>
+    <t>05.10.20268</t>
+  </si>
+  <si>
+    <t>05.10.20269</t>
+  </si>
+  <si>
+    <t>05.10.202610</t>
+  </si>
+  <si>
+    <t>05.10.202611</t>
+  </si>
+  <si>
+    <t>05.10.202612</t>
+  </si>
+  <si>
+    <t>05.10.202613</t>
+  </si>
+  <si>
+    <t>05.10.202614</t>
+  </si>
+  <si>
+    <t>05.10.202615</t>
+  </si>
+  <si>
+    <t>05.10.202616</t>
+  </si>
+  <si>
+    <t>05.10.202617</t>
+  </si>
+  <si>
+    <t>05.10.202618</t>
+  </si>
+  <si>
+    <t>05.10.202619</t>
+  </si>
+  <si>
+    <t>05.10.202620</t>
+  </si>
+  <si>
+    <t>05.10.202621</t>
+  </si>
+  <si>
+    <t>05.10.202622</t>
+  </si>
+  <si>
+    <t>05.10.202623</t>
+  </si>
+  <si>
+    <t>05.10.202624</t>
+  </si>
+  <si>
+    <t>05.10.202625</t>
+  </si>
+  <si>
+    <t>05.10.202626</t>
+  </si>
+  <si>
+    <t>05.10.202627</t>
+  </si>
+  <si>
+    <t>05.10.202628</t>
+  </si>
+  <si>
+    <t>05.10.202629</t>
+  </si>
+  <si>
+    <t>05.10.202630</t>
+  </si>
+  <si>
+    <t>05.10.202631</t>
+  </si>
+  <si>
+    <t>05.10.202632</t>
+  </si>
+  <si>
+    <t>05.10.202633</t>
+  </si>
+  <si>
+    <t>05.10.202634</t>
+  </si>
+  <si>
+    <t>05.10.202635</t>
+  </si>
+  <si>
+    <t>05.10.202636</t>
+  </si>
+  <si>
+    <t>05.10.202637</t>
+  </si>
+  <si>
+    <t>05.10.202638</t>
+  </si>
+  <si>
+    <t>05.10.202639</t>
+  </si>
+  <si>
+    <t>05.10.202640</t>
+  </si>
+  <si>
+    <t>05.10.202641</t>
+  </si>
+  <si>
+    <t>05.10.202642</t>
+  </si>
+  <si>
+    <t>05.10.202643</t>
+  </si>
+  <si>
+    <t>05.10.202644</t>
+  </si>
+  <si>
+    <t>05.10.202645</t>
+  </si>
+  <si>
+    <t>05.10.202646</t>
+  </si>
+  <si>
+    <t>05.10.202647</t>
+  </si>
+  <si>
+    <t>05.10.202648</t>
+  </si>
+  <si>
+    <t>05.10.202649</t>
+  </si>
+  <si>
+    <t>05.10.202650</t>
+  </si>
+  <si>
+    <t>05.10.202651</t>
+  </si>
+  <si>
+    <t>05.10.202652</t>
+  </si>
+  <si>
+    <t>05.10.202653</t>
+  </si>
+  <si>
+    <t>05.10.202654</t>
+  </si>
+  <si>
+    <t>05.10.202655</t>
+  </si>
+  <si>
+    <t>05.10.202656</t>
+  </si>
+  <si>
+    <t>05.10.202657</t>
+  </si>
+  <si>
+    <t>05.10.202658</t>
+  </si>
+  <si>
+    <t>05.10.202659</t>
+  </si>
+  <si>
+    <t>05.10.202660</t>
+  </si>
+  <si>
+    <t>05.10.202661</t>
+  </si>
+  <si>
+    <t>05.10.202662</t>
+  </si>
+  <si>
+    <t>05.10.202663</t>
+  </si>
+  <si>
+    <t>05.10.202664</t>
+  </si>
+  <si>
+    <t>05.10.202665</t>
+  </si>
+  <si>
+    <t>05.10.202666</t>
+  </si>
+  <si>
+    <t>05.10.202667</t>
+  </si>
+  <si>
+    <t>05.10.202668</t>
+  </si>
+  <si>
+    <t>05.10.202669</t>
+  </si>
+  <si>
+    <t>05.10.202670</t>
+  </si>
+  <si>
+    <t>05.10.202671</t>
+  </si>
+  <si>
+    <t>05.10.202672</t>
+  </si>
+  <si>
+    <t>05.10.202673</t>
+  </si>
+  <si>
+    <t>05.10.202674</t>
+  </si>
+  <si>
+    <t>05.10.202675</t>
+  </si>
+  <si>
+    <t>05.10.202676</t>
+  </si>
+  <si>
+    <t>05.10.202677</t>
+  </si>
+  <si>
+    <t>05.10.202678</t>
+  </si>
+  <si>
+    <t>05.10.202679</t>
+  </si>
+  <si>
+    <t>05.10.202680</t>
+  </si>
+  <si>
+    <t>05.10.202681</t>
+  </si>
+  <si>
+    <t>05.10.202682</t>
+  </si>
+  <si>
+    <t>05.10.202683</t>
+  </si>
+  <si>
+    <t>05.10.202684</t>
+  </si>
+  <si>
+    <t>05.10.202685</t>
+  </si>
+  <si>
+    <t>05.10.202686</t>
+  </si>
+  <si>
+    <t>05.10.202687</t>
+  </si>
+  <si>
+    <t>05.10.202688</t>
+  </si>
+  <si>
+    <t>05.10.202689</t>
+  </si>
+  <si>
+    <t>05.10.202690</t>
+  </si>
+  <si>
+    <t>05.10.202691</t>
+  </si>
+  <si>
+    <t>05.10.202692</t>
+  </si>
+  <si>
+    <t>05.10.202693</t>
+  </si>
+  <si>
+    <t>05.10.202694</t>
+  </si>
+  <si>
+    <t>05.10.202695</t>
+  </si>
+  <si>
+    <t>05.10.202696</t>
+  </si>
+  <si>
+    <t>06.10.20261</t>
+  </si>
+  <si>
+    <t>06.10.20262</t>
+  </si>
+  <si>
+    <t>06.10.20263</t>
+  </si>
+  <si>
+    <t>06.10.20264</t>
+  </si>
+  <si>
+    <t>06.10.20265</t>
+  </si>
+  <si>
+    <t>06.10.20266</t>
+  </si>
+  <si>
+    <t>06.10.20267</t>
+  </si>
+  <si>
+    <t>06.10.20268</t>
+  </si>
+  <si>
+    <t>06.10.20269</t>
+  </si>
+  <si>
+    <t>06.10.202610</t>
+  </si>
+  <si>
+    <t>06.10.202611</t>
+  </si>
+  <si>
+    <t>06.10.202612</t>
+  </si>
+  <si>
+    <t>06.10.202613</t>
+  </si>
+  <si>
+    <t>06.10.202614</t>
+  </si>
+  <si>
+    <t>06.10.202615</t>
+  </si>
+  <si>
+    <t>06.10.202616</t>
+  </si>
+  <si>
+    <t>06.10.202617</t>
+  </si>
+  <si>
+    <t>06.10.202618</t>
+  </si>
+  <si>
+    <t>06.10.202619</t>
+  </si>
+  <si>
+    <t>06.10.202620</t>
+  </si>
+  <si>
+    <t>06.10.202621</t>
+  </si>
+  <si>
+    <t>06.10.202622</t>
+  </si>
+  <si>
+    <t>06.10.202623</t>
+  </si>
+  <si>
+    <t>06.10.202624</t>
+  </si>
+  <si>
+    <t>06.10.202625</t>
+  </si>
+  <si>
+    <t>06.10.202626</t>
+  </si>
+  <si>
+    <t>06.10.202627</t>
+  </si>
+  <si>
+    <t>06.10.202628</t>
+  </si>
+  <si>
+    <t>06.10.202629</t>
+  </si>
+  <si>
+    <t>06.10.202630</t>
+  </si>
+  <si>
+    <t>06.10.202631</t>
+  </si>
+  <si>
+    <t>06.10.202632</t>
+  </si>
+  <si>
+    <t>06.10.202633</t>
+  </si>
+  <si>
+    <t>06.10.202634</t>
+  </si>
+  <si>
+    <t>06.10.202635</t>
+  </si>
+  <si>
+    <t>06.10.202636</t>
+  </si>
+  <si>
+    <t>06.10.202637</t>
+  </si>
+  <si>
+    <t>06.10.202638</t>
+  </si>
+  <si>
+    <t>06.10.202639</t>
+  </si>
+  <si>
+    <t>06.10.202640</t>
+  </si>
+  <si>
+    <t>06.10.202641</t>
+  </si>
+  <si>
+    <t>06.10.202642</t>
+  </si>
+  <si>
+    <t>06.10.202643</t>
+  </si>
+  <si>
+    <t>06.10.202644</t>
+  </si>
+  <si>
+    <t>06.10.202645</t>
+  </si>
+  <si>
+    <t>06.10.202646</t>
+  </si>
+  <si>
+    <t>06.10.202647</t>
+  </si>
+  <si>
+    <t>06.10.202648</t>
+  </si>
+  <si>
+    <t>06.10.202649</t>
+  </si>
+  <si>
+    <t>06.10.202650</t>
+  </si>
+  <si>
+    <t>06.10.202651</t>
+  </si>
+  <si>
+    <t>06.10.202652</t>
+  </si>
+  <si>
+    <t>06.10.202653</t>
+  </si>
+  <si>
+    <t>06.10.202654</t>
+  </si>
+  <si>
+    <t>06.10.202655</t>
+  </si>
+  <si>
+    <t>06.10.202656</t>
+  </si>
+  <si>
+    <t>06.10.202657</t>
+  </si>
+  <si>
+    <t>06.10.202658</t>
+  </si>
+  <si>
+    <t>06.10.202659</t>
+  </si>
+  <si>
+    <t>06.10.202660</t>
+  </si>
+  <si>
+    <t>06.10.202661</t>
+  </si>
+  <si>
+    <t>06.10.202662</t>
+  </si>
+  <si>
+    <t>06.10.202663</t>
+  </si>
+  <si>
+    <t>06.10.202664</t>
+  </si>
+  <si>
+    <t>06.10.202665</t>
+  </si>
+  <si>
+    <t>06.10.202666</t>
+  </si>
+  <si>
+    <t>06.10.202667</t>
+  </si>
+  <si>
+    <t>06.10.202668</t>
+  </si>
+  <si>
+    <t>06.10.202669</t>
+  </si>
+  <si>
+    <t>06.10.202670</t>
+  </si>
+  <si>
+    <t>06.10.202671</t>
+  </si>
+  <si>
+    <t>06.10.202672</t>
+  </si>
+  <si>
+    <t>06.10.202673</t>
+  </si>
+  <si>
+    <t>06.10.202674</t>
+  </si>
+  <si>
+    <t>06.10.202675</t>
+  </si>
+  <si>
+    <t>06.10.202676</t>
+  </si>
+  <si>
+    <t>06.10.202677</t>
+  </si>
+  <si>
+    <t>06.10.202678</t>
+  </si>
+  <si>
+    <t>06.10.202679</t>
+  </si>
+  <si>
+    <t>06.10.202680</t>
+  </si>
+  <si>
+    <t>06.10.202681</t>
+  </si>
+  <si>
+    <t>06.10.202682</t>
+  </si>
+  <si>
+    <t>06.10.202683</t>
+  </si>
+  <si>
+    <t>06.10.202684</t>
+  </si>
+  <si>
+    <t>06.10.202685</t>
+  </si>
+  <si>
+    <t>06.10.202686</t>
+  </si>
+  <si>
+    <t>06.10.202687</t>
+  </si>
+  <si>
+    <t>06.10.202688</t>
+  </si>
+  <si>
+    <t>06.10.202689</t>
+  </si>
+  <si>
+    <t>06.10.202690</t>
+  </si>
+  <si>
+    <t>06.10.202691</t>
+  </si>
+  <si>
+    <t>06.10.202692</t>
+  </si>
+  <si>
+    <t>06.10.202693</t>
+  </si>
+  <si>
+    <t>06.10.202694</t>
+  </si>
+  <si>
+    <t>06.10.202695</t>
+  </si>
+  <si>
+    <t>06.10.202696</t>
+  </si>
+  <si>
+    <t>07.10.20261</t>
+  </si>
+  <si>
+    <t>07.10.20262</t>
+  </si>
+  <si>
+    <t>07.10.20263</t>
+  </si>
+  <si>
+    <t>07.10.20264</t>
+  </si>
+  <si>
+    <t>07.10.20265</t>
+  </si>
+  <si>
+    <t>07.10.20266</t>
+  </si>
+  <si>
+    <t>07.10.20267</t>
+  </si>
+  <si>
+    <t>07.10.20268</t>
+  </si>
+  <si>
+    <t>07.10.20269</t>
+  </si>
+  <si>
+    <t>07.10.202610</t>
+  </si>
+  <si>
+    <t>07.10.202611</t>
+  </si>
+  <si>
+    <t>07.10.202612</t>
+  </si>
+  <si>
+    <t>07.10.202613</t>
+  </si>
+  <si>
+    <t>07.10.202614</t>
+  </si>
+  <si>
+    <t>07.10.202615</t>
+  </si>
+  <si>
+    <t>07.10.202616</t>
+  </si>
+  <si>
+    <t>07.10.202617</t>
+  </si>
+  <si>
+    <t>07.10.202618</t>
+  </si>
+  <si>
+    <t>07.10.202619</t>
+  </si>
+  <si>
+    <t>07.10.202620</t>
+  </si>
+  <si>
+    <t>07.10.202621</t>
+  </si>
+  <si>
+    <t>07.10.202622</t>
+  </si>
+  <si>
+    <t>07.10.202623</t>
+  </si>
+  <si>
+    <t>07.10.202624</t>
+  </si>
+  <si>
+    <t>07.10.202625</t>
+  </si>
+  <si>
+    <t>07.10.202626</t>
+  </si>
+  <si>
+    <t>07.10.202627</t>
+  </si>
+  <si>
+    <t>07.10.202628</t>
+  </si>
+  <si>
+    <t>07.10.202629</t>
+  </si>
+  <si>
+    <t>07.10.202630</t>
+  </si>
+  <si>
+    <t>07.10.202631</t>
+  </si>
+  <si>
+    <t>07.10.202632</t>
+  </si>
+  <si>
+    <t>07.10.202633</t>
+  </si>
+  <si>
+    <t>07.10.202634</t>
+  </si>
+  <si>
+    <t>07.10.202635</t>
+  </si>
+  <si>
+    <t>07.10.202636</t>
+  </si>
+  <si>
+    <t>07.10.202637</t>
+  </si>
+  <si>
+    <t>07.10.202638</t>
+  </si>
+  <si>
+    <t>07.10.202639</t>
+  </si>
+  <si>
+    <t>07.10.202640</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -84,11 +1359,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -383,7 +1659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D425"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -400,6 +1676,5942 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2">
+        <v>46298.01041666666</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2">
+        <v>46298.02083333334</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2">
+        <v>46298.03125</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2">
+        <v>46298.04166666666</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2">
+        <v>46298.05208333334</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2">
+        <v>46298.0625</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2">
+        <v>46298.07291666666</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2">
+        <v>46298.08333333334</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2">
+        <v>46298.09375</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2">
+        <v>46298.10416666666</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2">
+        <v>46298.11458333334</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2">
+        <v>46298.125</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2">
+        <v>46298.13541666666</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2">
+        <v>46298.14583333334</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2">
+        <v>46298.15625</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2">
+        <v>46298.16666666666</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2">
+        <v>46298.17708333334</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2">
+        <v>46298.1875</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2">
+        <v>46298.19791666666</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2">
+        <v>46298.20833333334</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2">
+        <v>46298.21875</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>22</v>
+      </c>
+      <c r="D23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2">
+        <v>46298.22916666666</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>23</v>
+      </c>
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2">
+        <v>46298.23958333334</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>24</v>
+      </c>
+      <c r="D25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2">
+        <v>46298.25</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>25</v>
+      </c>
+      <c r="D26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2">
+        <v>46298.26041666666</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>26</v>
+      </c>
+      <c r="D27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2">
+        <v>46298.27083333334</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>27</v>
+      </c>
+      <c r="D28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2">
+        <v>46298.28125</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>28</v>
+      </c>
+      <c r="D29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2">
+        <v>46298.29166666666</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>29</v>
+      </c>
+      <c r="D30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2">
+        <v>46298.30208333334</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>30</v>
+      </c>
+      <c r="D31" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2">
+        <v>46298.3125</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <v>31</v>
+      </c>
+      <c r="D32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="2">
+        <v>46298.32291666666</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <v>32</v>
+      </c>
+      <c r="D33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="2">
+        <v>46298.33333333334</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <v>33</v>
+      </c>
+      <c r="D34" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="2">
+        <v>46298.34375</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>34</v>
+      </c>
+      <c r="D35" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="2">
+        <v>46298.35416666666</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>35</v>
+      </c>
+      <c r="D36" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="2">
+        <v>46298.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>36</v>
+      </c>
+      <c r="D37" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="2">
+        <v>46298.375</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>37</v>
+      </c>
+      <c r="D38" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="2">
+        <v>46298.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>38</v>
+      </c>
+      <c r="D39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="2">
+        <v>46298.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <v>39</v>
+      </c>
+      <c r="D40" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="2">
+        <v>46298.40625</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
+        <v>40</v>
+      </c>
+      <c r="D41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="2">
+        <v>46298.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>41</v>
+      </c>
+      <c r="D42" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="2">
+        <v>46298.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>42</v>
+      </c>
+      <c r="D43" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="2">
+        <v>46298.4375</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>43</v>
+      </c>
+      <c r="D44" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="2">
+        <v>46298.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>44</v>
+      </c>
+      <c r="D45" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="2">
+        <v>46298.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>45</v>
+      </c>
+      <c r="D46" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="2">
+        <v>46298.46875</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>46</v>
+      </c>
+      <c r="D47" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="2">
+        <v>46298.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>47</v>
+      </c>
+      <c r="D48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="2">
+        <v>46298.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>48</v>
+      </c>
+      <c r="D49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="2">
+        <v>46298.5</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>49</v>
+      </c>
+      <c r="D50" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="2">
+        <v>46298.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
+        <v>50</v>
+      </c>
+      <c r="D51" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="2">
+        <v>46298.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>51</v>
+      </c>
+      <c r="D52" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="2">
+        <v>46298.53125</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>52</v>
+      </c>
+      <c r="D53" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="2">
+        <v>46298.54166666666</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <v>53</v>
+      </c>
+      <c r="D54" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="2">
+        <v>46298.55208333334</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>54</v>
+      </c>
+      <c r="D55" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="2">
+        <v>46298.5625</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56">
+        <v>55</v>
+      </c>
+      <c r="D56" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="2">
+        <v>46298.57291666666</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57">
+        <v>56</v>
+      </c>
+      <c r="D57" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="2">
+        <v>46298.58333333334</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58">
+        <v>57</v>
+      </c>
+      <c r="D58" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="2">
+        <v>46298.59375</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="C59">
+        <v>58</v>
+      </c>
+      <c r="D59" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="2">
+        <v>46298.60416666666</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
+        <v>59</v>
+      </c>
+      <c r="D60" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="2">
+        <v>46298.61458333334</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <v>60</v>
+      </c>
+      <c r="D61" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="2">
+        <v>46298.625</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
+        <v>61</v>
+      </c>
+      <c r="D62" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="2">
+        <v>46298.63541666666</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <v>62</v>
+      </c>
+      <c r="D63" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="2">
+        <v>46298.64583333334</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
+        <v>63</v>
+      </c>
+      <c r="D64" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="2">
+        <v>46298.65625</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <v>64</v>
+      </c>
+      <c r="D65" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="2">
+        <v>46298.66666666666</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <v>65</v>
+      </c>
+      <c r="D66" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="2">
+        <v>46298.67708333334</v>
+      </c>
+      <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67">
+        <v>66</v>
+      </c>
+      <c r="D67" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="2">
+        <v>46298.6875</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <v>67</v>
+      </c>
+      <c r="D68" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="2">
+        <v>46298.69791666666</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>68</v>
+      </c>
+      <c r="D69" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="2">
+        <v>46298.70833333334</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <v>69</v>
+      </c>
+      <c r="D70" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="2">
+        <v>46298.71875</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <v>70</v>
+      </c>
+      <c r="D71" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="2">
+        <v>46298.72916666666</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <v>71</v>
+      </c>
+      <c r="D72" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="2">
+        <v>46298.73958333334</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>72</v>
+      </c>
+      <c r="D73" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="2">
+        <v>46298.75</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>73</v>
+      </c>
+      <c r="D74" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="2">
+        <v>46298.76041666666</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
+        <v>74</v>
+      </c>
+      <c r="D75" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="2">
+        <v>46298.77083333334</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76">
+        <v>75</v>
+      </c>
+      <c r="D76" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="2">
+        <v>46298.78125</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+      <c r="C77">
+        <v>76</v>
+      </c>
+      <c r="D77" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="2">
+        <v>46298.79166666666</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
+        <v>77</v>
+      </c>
+      <c r="D78" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="2">
+        <v>46298.80208333334</v>
+      </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+      <c r="C79">
+        <v>78</v>
+      </c>
+      <c r="D79" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="2">
+        <v>46298.8125</v>
+      </c>
+      <c r="B80">
+        <v>0</v>
+      </c>
+      <c r="C80">
+        <v>79</v>
+      </c>
+      <c r="D80" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="2">
+        <v>46298.82291666666</v>
+      </c>
+      <c r="B81">
+        <v>0</v>
+      </c>
+      <c r="C81">
+        <v>80</v>
+      </c>
+      <c r="D81" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="2">
+        <v>46298.83333333334</v>
+      </c>
+      <c r="B82">
+        <v>0</v>
+      </c>
+      <c r="C82">
+        <v>81</v>
+      </c>
+      <c r="D82" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="2">
+        <v>46298.84375</v>
+      </c>
+      <c r="B83">
+        <v>0</v>
+      </c>
+      <c r="C83">
+        <v>82</v>
+      </c>
+      <c r="D83" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="2">
+        <v>46298.85416666666</v>
+      </c>
+      <c r="B84">
+        <v>0</v>
+      </c>
+      <c r="C84">
+        <v>83</v>
+      </c>
+      <c r="D84" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="2">
+        <v>46298.86458333334</v>
+      </c>
+      <c r="B85">
+        <v>0</v>
+      </c>
+      <c r="C85">
+        <v>84</v>
+      </c>
+      <c r="D85" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="2">
+        <v>46298.875</v>
+      </c>
+      <c r="B86">
+        <v>0</v>
+      </c>
+      <c r="C86">
+        <v>85</v>
+      </c>
+      <c r="D86" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="2">
+        <v>46298.88541666666</v>
+      </c>
+      <c r="B87">
+        <v>0</v>
+      </c>
+      <c r="C87">
+        <v>86</v>
+      </c>
+      <c r="D87" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="2">
+        <v>46298.89583333334</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+      <c r="C88">
+        <v>87</v>
+      </c>
+      <c r="D88" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="2">
+        <v>46298.90625</v>
+      </c>
+      <c r="B89">
+        <v>0</v>
+      </c>
+      <c r="C89">
+        <v>88</v>
+      </c>
+      <c r="D89" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="2">
+        <v>46298.91666666666</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+      <c r="C90">
+        <v>89</v>
+      </c>
+      <c r="D90" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="2">
+        <v>46298.92708333334</v>
+      </c>
+      <c r="B91">
+        <v>0</v>
+      </c>
+      <c r="C91">
+        <v>90</v>
+      </c>
+      <c r="D91" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="2">
+        <v>46298.9375</v>
+      </c>
+      <c r="B92">
+        <v>0</v>
+      </c>
+      <c r="C92">
+        <v>91</v>
+      </c>
+      <c r="D92" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="2">
+        <v>46298.94791666666</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+      <c r="C93">
+        <v>92</v>
+      </c>
+      <c r="D93" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="2">
+        <v>46298.95833333334</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+      <c r="C94">
+        <v>93</v>
+      </c>
+      <c r="D94" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="2">
+        <v>46298.96875</v>
+      </c>
+      <c r="B95">
+        <v>0</v>
+      </c>
+      <c r="C95">
+        <v>94</v>
+      </c>
+      <c r="D95" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="2">
+        <v>46298.97916666666</v>
+      </c>
+      <c r="B96">
+        <v>0</v>
+      </c>
+      <c r="C96">
+        <v>95</v>
+      </c>
+      <c r="D96" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="2">
+        <v>46298.98958333334</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+      <c r="C97">
+        <v>96</v>
+      </c>
+      <c r="D97" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="2">
+        <v>46299.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="D99" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="2">
+        <v>46299.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+      <c r="C100">
+        <v>3</v>
+      </c>
+      <c r="D100" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="2">
+        <v>46299.03125</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+      <c r="C101">
+        <v>4</v>
+      </c>
+      <c r="D101" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="2">
+        <v>46299.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+      <c r="C102">
+        <v>5</v>
+      </c>
+      <c r="D102" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="2">
+        <v>46299.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+      <c r="C103">
+        <v>6</v>
+      </c>
+      <c r="D103" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="2">
+        <v>46299.0625</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+      <c r="C104">
+        <v>7</v>
+      </c>
+      <c r="D104" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="2">
+        <v>46299.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+      <c r="C105">
+        <v>8</v>
+      </c>
+      <c r="D105" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="2">
+        <v>46299.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+      <c r="C106">
+        <v>9</v>
+      </c>
+      <c r="D106" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="2">
+        <v>46299.09375</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+      <c r="C107">
+        <v>10</v>
+      </c>
+      <c r="D107" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="2">
+        <v>46299.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+      <c r="C108">
+        <v>11</v>
+      </c>
+      <c r="D108" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="2">
+        <v>46299.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+      <c r="C109">
+        <v>12</v>
+      </c>
+      <c r="D109" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="2">
+        <v>46299.125</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+      <c r="C110">
+        <v>13</v>
+      </c>
+      <c r="D110" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="2">
+        <v>46299.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+      <c r="C111">
+        <v>14</v>
+      </c>
+      <c r="D111" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="2">
+        <v>46299.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+      <c r="C112">
+        <v>15</v>
+      </c>
+      <c r="D112" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="2">
+        <v>46299.15625</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+      <c r="C113">
+        <v>16</v>
+      </c>
+      <c r="D113" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="2">
+        <v>46299.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>0</v>
+      </c>
+      <c r="C114">
+        <v>17</v>
+      </c>
+      <c r="D114" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="2">
+        <v>46299.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>0</v>
+      </c>
+      <c r="C115">
+        <v>18</v>
+      </c>
+      <c r="D115" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="2">
+        <v>46299.1875</v>
+      </c>
+      <c r="B116">
+        <v>0</v>
+      </c>
+      <c r="C116">
+        <v>19</v>
+      </c>
+      <c r="D116" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="2">
+        <v>46299.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+      <c r="C117">
+        <v>20</v>
+      </c>
+      <c r="D117" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="2">
+        <v>46299.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>0</v>
+      </c>
+      <c r="C118">
+        <v>21</v>
+      </c>
+      <c r="D118" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="2">
+        <v>46299.21875</v>
+      </c>
+      <c r="B119">
+        <v>0</v>
+      </c>
+      <c r="C119">
+        <v>22</v>
+      </c>
+      <c r="D119" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="2">
+        <v>46299.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>0</v>
+      </c>
+      <c r="C120">
+        <v>23</v>
+      </c>
+      <c r="D120" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="2">
+        <v>46299.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>0</v>
+      </c>
+      <c r="C121">
+        <v>24</v>
+      </c>
+      <c r="D121" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="2">
+        <v>46299.25</v>
+      </c>
+      <c r="B122">
+        <v>0</v>
+      </c>
+      <c r="C122">
+        <v>25</v>
+      </c>
+      <c r="D122" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="2">
+        <v>46299.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>0</v>
+      </c>
+      <c r="C123">
+        <v>26</v>
+      </c>
+      <c r="D123" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="2">
+        <v>46299.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>0</v>
+      </c>
+      <c r="C124">
+        <v>27</v>
+      </c>
+      <c r="D124" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="2">
+        <v>46299.28125</v>
+      </c>
+      <c r="B125">
+        <v>0</v>
+      </c>
+      <c r="C125">
+        <v>28</v>
+      </c>
+      <c r="D125" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="2">
+        <v>46299.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+      <c r="C126">
+        <v>29</v>
+      </c>
+      <c r="D126" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="2">
+        <v>46299.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>0</v>
+      </c>
+      <c r="C127">
+        <v>30</v>
+      </c>
+      <c r="D127" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="2">
+        <v>46299.3125</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128">
+        <v>31</v>
+      </c>
+      <c r="D128" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" s="2">
+        <v>46299.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+      <c r="C129">
+        <v>32</v>
+      </c>
+      <c r="D129" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="2">
+        <v>46299.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>0</v>
+      </c>
+      <c r="C130">
+        <v>33</v>
+      </c>
+      <c r="D130" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="2">
+        <v>46299.34375</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+      <c r="C131">
+        <v>34</v>
+      </c>
+      <c r="D131" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="2">
+        <v>46299.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+      <c r="C132">
+        <v>35</v>
+      </c>
+      <c r="D132" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="2">
+        <v>46299.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+      <c r="C133">
+        <v>36</v>
+      </c>
+      <c r="D133" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="2">
+        <v>46299.375</v>
+      </c>
+      <c r="B134">
+        <v>0</v>
+      </c>
+      <c r="C134">
+        <v>37</v>
+      </c>
+      <c r="D134" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="2">
+        <v>46299.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+      <c r="C135">
+        <v>38</v>
+      </c>
+      <c r="D135" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="2">
+        <v>46299.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+      <c r="C136">
+        <v>39</v>
+      </c>
+      <c r="D136" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="2">
+        <v>46299.40625</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+      <c r="C137">
+        <v>40</v>
+      </c>
+      <c r="D137" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="2">
+        <v>46299.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+      <c r="C138">
+        <v>41</v>
+      </c>
+      <c r="D138" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="2">
+        <v>46299.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+      <c r="C139">
+        <v>42</v>
+      </c>
+      <c r="D139" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="2">
+        <v>46299.4375</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+      <c r="C140">
+        <v>43</v>
+      </c>
+      <c r="D140" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="2">
+        <v>46299.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+      <c r="C141">
+        <v>44</v>
+      </c>
+      <c r="D141" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="2">
+        <v>46299.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+      <c r="C142">
+        <v>45</v>
+      </c>
+      <c r="D142" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="2">
+        <v>46299.46875</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+      <c r="C143">
+        <v>46</v>
+      </c>
+      <c r="D143" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="2">
+        <v>46299.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+      <c r="C144">
+        <v>47</v>
+      </c>
+      <c r="D144" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="2">
+        <v>46299.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+      <c r="C145">
+        <v>48</v>
+      </c>
+      <c r="D145" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="2">
+        <v>46299.5</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+      <c r="C146">
+        <v>49</v>
+      </c>
+      <c r="D146" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="2">
+        <v>46299.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+      <c r="C147">
+        <v>50</v>
+      </c>
+      <c r="D147" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="2">
+        <v>46299.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+      <c r="C148">
+        <v>51</v>
+      </c>
+      <c r="D148" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="2">
+        <v>46299.53125</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+      <c r="C149">
+        <v>52</v>
+      </c>
+      <c r="D149" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="2">
+        <v>46299.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+      <c r="C150">
+        <v>53</v>
+      </c>
+      <c r="D150" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="2">
+        <v>46299.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>0</v>
+      </c>
+      <c r="C151">
+        <v>54</v>
+      </c>
+      <c r="D151" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="2">
+        <v>46299.5625</v>
+      </c>
+      <c r="B152">
+        <v>0</v>
+      </c>
+      <c r="C152">
+        <v>55</v>
+      </c>
+      <c r="D152" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="2">
+        <v>46299.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+      <c r="C153">
+        <v>56</v>
+      </c>
+      <c r="D153" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="2">
+        <v>46299.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+      <c r="C154">
+        <v>57</v>
+      </c>
+      <c r="D154" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="2">
+        <v>46299.59375</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+      <c r="C155">
+        <v>58</v>
+      </c>
+      <c r="D155" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" s="2">
+        <v>46299.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+      <c r="C156">
+        <v>59</v>
+      </c>
+      <c r="D156" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" s="2">
+        <v>46299.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>0</v>
+      </c>
+      <c r="C157">
+        <v>60</v>
+      </c>
+      <c r="D157" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" s="2">
+        <v>46299.625</v>
+      </c>
+      <c r="B158">
+        <v>0</v>
+      </c>
+      <c r="C158">
+        <v>61</v>
+      </c>
+      <c r="D158" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" s="2">
+        <v>46299.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+      <c r="C159">
+        <v>62</v>
+      </c>
+      <c r="D159" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="2">
+        <v>46299.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>0</v>
+      </c>
+      <c r="C160">
+        <v>63</v>
+      </c>
+      <c r="D160" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" s="2">
+        <v>46299.65625</v>
+      </c>
+      <c r="B161">
+        <v>0</v>
+      </c>
+      <c r="C161">
+        <v>64</v>
+      </c>
+      <c r="D161" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" s="2">
+        <v>46299.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>0</v>
+      </c>
+      <c r="C162">
+        <v>65</v>
+      </c>
+      <c r="D162" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" s="2">
+        <v>46299.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>0</v>
+      </c>
+      <c r="C163">
+        <v>66</v>
+      </c>
+      <c r="D163" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" s="2">
+        <v>46299.6875</v>
+      </c>
+      <c r="B164">
+        <v>0</v>
+      </c>
+      <c r="C164">
+        <v>67</v>
+      </c>
+      <c r="D164" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" s="2">
+        <v>46299.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>0</v>
+      </c>
+      <c r="C165">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" s="2">
+        <v>46299.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>0</v>
+      </c>
+      <c r="C166">
+        <v>69</v>
+      </c>
+      <c r="D166" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" s="2">
+        <v>46299.71875</v>
+      </c>
+      <c r="B167">
+        <v>0</v>
+      </c>
+      <c r="C167">
+        <v>70</v>
+      </c>
+      <c r="D167" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" s="2">
+        <v>46299.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>0</v>
+      </c>
+      <c r="C168">
+        <v>71</v>
+      </c>
+      <c r="D168" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" s="2">
+        <v>46299.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>0</v>
+      </c>
+      <c r="C169">
+        <v>72</v>
+      </c>
+      <c r="D169" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" s="2">
+        <v>46299.75</v>
+      </c>
+      <c r="B170">
+        <v>0</v>
+      </c>
+      <c r="C170">
+        <v>73</v>
+      </c>
+      <c r="D170" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" s="2">
+        <v>46299.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+      <c r="C171">
+        <v>74</v>
+      </c>
+      <c r="D171" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" s="2">
+        <v>46299.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>0</v>
+      </c>
+      <c r="C172">
+        <v>75</v>
+      </c>
+      <c r="D172" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" s="2">
+        <v>46299.78125</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+      <c r="C173">
+        <v>76</v>
+      </c>
+      <c r="D173" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" s="2">
+        <v>46299.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>0</v>
+      </c>
+      <c r="C174">
+        <v>77</v>
+      </c>
+      <c r="D174" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" s="2">
+        <v>46299.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>0</v>
+      </c>
+      <c r="C175">
+        <v>78</v>
+      </c>
+      <c r="D175" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" s="2">
+        <v>46299.8125</v>
+      </c>
+      <c r="B176">
+        <v>0</v>
+      </c>
+      <c r="C176">
+        <v>79</v>
+      </c>
+      <c r="D176" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" s="2">
+        <v>46299.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>0</v>
+      </c>
+      <c r="C177">
+        <v>80</v>
+      </c>
+      <c r="D177" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" s="2">
+        <v>46299.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>0</v>
+      </c>
+      <c r="C178">
+        <v>81</v>
+      </c>
+      <c r="D178" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" s="2">
+        <v>46299.84375</v>
+      </c>
+      <c r="B179">
+        <v>0</v>
+      </c>
+      <c r="C179">
+        <v>82</v>
+      </c>
+      <c r="D179" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" s="2">
+        <v>46299.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>0</v>
+      </c>
+      <c r="C180">
+        <v>83</v>
+      </c>
+      <c r="D180" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" s="2">
+        <v>46299.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>0</v>
+      </c>
+      <c r="C181">
+        <v>84</v>
+      </c>
+      <c r="D181" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" s="2">
+        <v>46299.875</v>
+      </c>
+      <c r="B182">
+        <v>0</v>
+      </c>
+      <c r="C182">
+        <v>85</v>
+      </c>
+      <c r="D182" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" s="2">
+        <v>46299.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+      <c r="C183">
+        <v>86</v>
+      </c>
+      <c r="D183" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184" s="2">
+        <v>46299.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+      <c r="C184">
+        <v>87</v>
+      </c>
+      <c r="D184" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="A185" s="2">
+        <v>46299.90625</v>
+      </c>
+      <c r="B185">
+        <v>0</v>
+      </c>
+      <c r="C185">
+        <v>88</v>
+      </c>
+      <c r="D185" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="A186" s="2">
+        <v>46299.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>0</v>
+      </c>
+      <c r="C186">
+        <v>89</v>
+      </c>
+      <c r="D186" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="A187" s="2">
+        <v>46299.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>0</v>
+      </c>
+      <c r="C187">
+        <v>90</v>
+      </c>
+      <c r="D187" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188" s="2">
+        <v>46299.9375</v>
+      </c>
+      <c r="B188">
+        <v>0</v>
+      </c>
+      <c r="C188">
+        <v>91</v>
+      </c>
+      <c r="D188" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" s="2">
+        <v>46299.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>0</v>
+      </c>
+      <c r="C189">
+        <v>92</v>
+      </c>
+      <c r="D189" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190" s="2">
+        <v>46299.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+      <c r="C190">
+        <v>93</v>
+      </c>
+      <c r="D190" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" s="2">
+        <v>46299.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+      <c r="C191">
+        <v>94</v>
+      </c>
+      <c r="D191" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192" s="2">
+        <v>46299.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+      <c r="C192">
+        <v>95</v>
+      </c>
+      <c r="D192" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193" s="2">
+        <v>46299.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>0</v>
+      </c>
+      <c r="C193">
+        <v>96</v>
+      </c>
+      <c r="D193" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B194">
+        <v>0</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" s="2">
+        <v>46300.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+      <c r="D195" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" s="2">
+        <v>46300.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+      <c r="C196">
+        <v>3</v>
+      </c>
+      <c r="D196" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" s="2">
+        <v>46300.03125</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+      <c r="C197">
+        <v>4</v>
+      </c>
+      <c r="D197" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" s="2">
+        <v>46300.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+      <c r="C198">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" s="2">
+        <v>46300.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+      <c r="C199">
+        <v>6</v>
+      </c>
+      <c r="D199" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" s="2">
+        <v>46300.0625</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+      <c r="C200">
+        <v>7</v>
+      </c>
+      <c r="D200" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" s="2">
+        <v>46300.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+      <c r="C201">
+        <v>8</v>
+      </c>
+      <c r="D201" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" s="2">
+        <v>46300.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+      <c r="C202">
+        <v>9</v>
+      </c>
+      <c r="D202" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" s="2">
+        <v>46300.09375</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+      <c r="C203">
+        <v>10</v>
+      </c>
+      <c r="D203" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" s="2">
+        <v>46300.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+      <c r="C204">
+        <v>11</v>
+      </c>
+      <c r="D204" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" s="2">
+        <v>46300.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+      <c r="C205">
+        <v>12</v>
+      </c>
+      <c r="D205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" s="2">
+        <v>46300.125</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+      <c r="C206">
+        <v>13</v>
+      </c>
+      <c r="D206" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" s="2">
+        <v>46300.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+      <c r="C207">
+        <v>14</v>
+      </c>
+      <c r="D207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="2">
+        <v>46300.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+      <c r="C208">
+        <v>15</v>
+      </c>
+      <c r="D208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="2">
+        <v>46300.15625</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+      <c r="C209">
+        <v>16</v>
+      </c>
+      <c r="D209" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="2">
+        <v>46300.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>0</v>
+      </c>
+      <c r="C210">
+        <v>17</v>
+      </c>
+      <c r="D210" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="2">
+        <v>46300.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+      <c r="C211">
+        <v>18</v>
+      </c>
+      <c r="D211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="2">
+        <v>46300.1875</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+      <c r="C212">
+        <v>19</v>
+      </c>
+      <c r="D212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="2">
+        <v>46300.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+      <c r="C213">
+        <v>20</v>
+      </c>
+      <c r="D213" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="2">
+        <v>46300.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>0</v>
+      </c>
+      <c r="C214">
+        <v>21</v>
+      </c>
+      <c r="D214" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="2">
+        <v>46300.21875</v>
+      </c>
+      <c r="B215">
+        <v>0</v>
+      </c>
+      <c r="C215">
+        <v>22</v>
+      </c>
+      <c r="D215" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="2">
+        <v>46300.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+      <c r="C216">
+        <v>23</v>
+      </c>
+      <c r="D216" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" s="2">
+        <v>46300.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>0</v>
+      </c>
+      <c r="C217">
+        <v>24</v>
+      </c>
+      <c r="D217" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" s="2">
+        <v>46300.25</v>
+      </c>
+      <c r="B218">
+        <v>0</v>
+      </c>
+      <c r="C218">
+        <v>25</v>
+      </c>
+      <c r="D218" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" s="2">
+        <v>46300.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+      <c r="C219">
+        <v>26</v>
+      </c>
+      <c r="D219" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="2">
+        <v>46300.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>0</v>
+      </c>
+      <c r="C220">
+        <v>27</v>
+      </c>
+      <c r="D220" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" s="2">
+        <v>46300.28125</v>
+      </c>
+      <c r="B221">
+        <v>0</v>
+      </c>
+      <c r="C221">
+        <v>28</v>
+      </c>
+      <c r="D221" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" s="2">
+        <v>46300.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>0</v>
+      </c>
+      <c r="C222">
+        <v>29</v>
+      </c>
+      <c r="D222" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" s="2">
+        <v>46300.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>0</v>
+      </c>
+      <c r="C223">
+        <v>30</v>
+      </c>
+      <c r="D223" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="2">
+        <v>46300.3125</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+      <c r="C224">
+        <v>31</v>
+      </c>
+      <c r="D224" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="2">
+        <v>46300.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+      <c r="C225">
+        <v>32</v>
+      </c>
+      <c r="D225" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="2">
+        <v>46300.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+      <c r="C226">
+        <v>33</v>
+      </c>
+      <c r="D226" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="2">
+        <v>46300.34375</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+      <c r="C227">
+        <v>34</v>
+      </c>
+      <c r="D227" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="2">
+        <v>46300.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+      <c r="C228">
+        <v>35</v>
+      </c>
+      <c r="D228" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="2">
+        <v>46300.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+      <c r="C229">
+        <v>36</v>
+      </c>
+      <c r="D229" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="2">
+        <v>46300.375</v>
+      </c>
+      <c r="B230">
+        <v>0</v>
+      </c>
+      <c r="C230">
+        <v>37</v>
+      </c>
+      <c r="D230" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="2">
+        <v>46300.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>0</v>
+      </c>
+      <c r="C231">
+        <v>38</v>
+      </c>
+      <c r="D231" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="2">
+        <v>46300.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>0</v>
+      </c>
+      <c r="C232">
+        <v>39</v>
+      </c>
+      <c r="D232" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" s="2">
+        <v>46300.40625</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+      <c r="C233">
+        <v>40</v>
+      </c>
+      <c r="D233" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" s="2">
+        <v>46300.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+      <c r="C234">
+        <v>41</v>
+      </c>
+      <c r="D234" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="2">
+        <v>46300.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>0</v>
+      </c>
+      <c r="C235">
+        <v>42</v>
+      </c>
+      <c r="D235" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="2">
+        <v>46300.4375</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+      <c r="C236">
+        <v>43</v>
+      </c>
+      <c r="D236" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="2">
+        <v>46300.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+      <c r="C237">
+        <v>44</v>
+      </c>
+      <c r="D237" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="2">
+        <v>46300.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>0</v>
+      </c>
+      <c r="C238">
+        <v>45</v>
+      </c>
+      <c r="D238" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="2">
+        <v>46300.46875</v>
+      </c>
+      <c r="B239">
+        <v>0</v>
+      </c>
+      <c r="C239">
+        <v>46</v>
+      </c>
+      <c r="D239" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="2">
+        <v>46300.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>0</v>
+      </c>
+      <c r="C240">
+        <v>47</v>
+      </c>
+      <c r="D240" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" s="2">
+        <v>46300.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>0</v>
+      </c>
+      <c r="C241">
+        <v>48</v>
+      </c>
+      <c r="D241" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" s="2">
+        <v>46300.5</v>
+      </c>
+      <c r="B242">
+        <v>0</v>
+      </c>
+      <c r="C242">
+        <v>49</v>
+      </c>
+      <c r="D242" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" s="2">
+        <v>46300.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>0</v>
+      </c>
+      <c r="C243">
+        <v>50</v>
+      </c>
+      <c r="D243" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" s="2">
+        <v>46300.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+      <c r="C244">
+        <v>51</v>
+      </c>
+      <c r="D244" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="2">
+        <v>46300.53125</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+      <c r="C245">
+        <v>52</v>
+      </c>
+      <c r="D245" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="2">
+        <v>46300.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>0</v>
+      </c>
+      <c r="C246">
+        <v>53</v>
+      </c>
+      <c r="D246" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" s="2">
+        <v>46300.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+      <c r="C247">
+        <v>54</v>
+      </c>
+      <c r="D247" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="2">
+        <v>46300.5625</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
+      <c r="C248">
+        <v>55</v>
+      </c>
+      <c r="D248" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" s="2">
+        <v>46300.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>0</v>
+      </c>
+      <c r="C249">
+        <v>56</v>
+      </c>
+      <c r="D249" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" s="2">
+        <v>46300.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>0</v>
+      </c>
+      <c r="C250">
+        <v>57</v>
+      </c>
+      <c r="D250" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" s="2">
+        <v>46300.59375</v>
+      </c>
+      <c r="B251">
+        <v>0</v>
+      </c>
+      <c r="C251">
+        <v>58</v>
+      </c>
+      <c r="D251" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" s="2">
+        <v>46300.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
+      <c r="C252">
+        <v>59</v>
+      </c>
+      <c r="D252" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" s="2">
+        <v>46300.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>0</v>
+      </c>
+      <c r="C253">
+        <v>60</v>
+      </c>
+      <c r="D253" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" s="2">
+        <v>46300.625</v>
+      </c>
+      <c r="B254">
+        <v>0</v>
+      </c>
+      <c r="C254">
+        <v>61</v>
+      </c>
+      <c r="D254" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" s="2">
+        <v>46300.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>0</v>
+      </c>
+      <c r="C255">
+        <v>62</v>
+      </c>
+      <c r="D255" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" s="2">
+        <v>46300.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>0</v>
+      </c>
+      <c r="C256">
+        <v>63</v>
+      </c>
+      <c r="D256" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="2">
+        <v>46300.65625</v>
+      </c>
+      <c r="B257">
+        <v>0</v>
+      </c>
+      <c r="C257">
+        <v>64</v>
+      </c>
+      <c r="D257" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" s="2">
+        <v>46300.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>0</v>
+      </c>
+      <c r="C258">
+        <v>65</v>
+      </c>
+      <c r="D258" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" s="2">
+        <v>46300.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>0</v>
+      </c>
+      <c r="C259">
+        <v>66</v>
+      </c>
+      <c r="D259" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" s="2">
+        <v>46300.6875</v>
+      </c>
+      <c r="B260">
+        <v>0</v>
+      </c>
+      <c r="C260">
+        <v>67</v>
+      </c>
+      <c r="D260" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" s="2">
+        <v>46300.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>0</v>
+      </c>
+      <c r="C261">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" s="2">
+        <v>46300.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>0</v>
+      </c>
+      <c r="C262">
+        <v>69</v>
+      </c>
+      <c r="D262" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" s="2">
+        <v>46300.71875</v>
+      </c>
+      <c r="B263">
+        <v>0</v>
+      </c>
+      <c r="C263">
+        <v>70</v>
+      </c>
+      <c r="D263" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" s="2">
+        <v>46300.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+      <c r="C264">
+        <v>71</v>
+      </c>
+      <c r="D264" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" s="2">
+        <v>46300.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+      <c r="C265">
+        <v>72</v>
+      </c>
+      <c r="D265" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="2">
+        <v>46300.75</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+      <c r="C266">
+        <v>73</v>
+      </c>
+      <c r="D266" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="2">
+        <v>46300.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>0</v>
+      </c>
+      <c r="C267">
+        <v>74</v>
+      </c>
+      <c r="D267" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="2">
+        <v>46300.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+      <c r="C268">
+        <v>75</v>
+      </c>
+      <c r="D268" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="2">
+        <v>46300.78125</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+      <c r="C269">
+        <v>76</v>
+      </c>
+      <c r="D269" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="2">
+        <v>46300.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>0</v>
+      </c>
+      <c r="C270">
+        <v>77</v>
+      </c>
+      <c r="D270" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="2">
+        <v>46300.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>0</v>
+      </c>
+      <c r="C271">
+        <v>78</v>
+      </c>
+      <c r="D271" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="2">
+        <v>46300.8125</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+      <c r="C272">
+        <v>79</v>
+      </c>
+      <c r="D272" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="2">
+        <v>46300.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+      <c r="C273">
+        <v>80</v>
+      </c>
+      <c r="D273" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="2">
+        <v>46300.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>0</v>
+      </c>
+      <c r="C274">
+        <v>81</v>
+      </c>
+      <c r="D274" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="2">
+        <v>46300.84375</v>
+      </c>
+      <c r="B275">
+        <v>0</v>
+      </c>
+      <c r="C275">
+        <v>82</v>
+      </c>
+      <c r="D275" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="2">
+        <v>46300.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+      <c r="C276">
+        <v>83</v>
+      </c>
+      <c r="D276" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="2">
+        <v>46300.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>0</v>
+      </c>
+      <c r="C277">
+        <v>84</v>
+      </c>
+      <c r="D277" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="2">
+        <v>46300.875</v>
+      </c>
+      <c r="B278">
+        <v>0</v>
+      </c>
+      <c r="C278">
+        <v>85</v>
+      </c>
+      <c r="D278" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" s="2">
+        <v>46300.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+      <c r="C279">
+        <v>86</v>
+      </c>
+      <c r="D279" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" s="2">
+        <v>46300.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+      <c r="C280">
+        <v>87</v>
+      </c>
+      <c r="D280" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="2">
+        <v>46300.90625</v>
+      </c>
+      <c r="B281">
+        <v>0</v>
+      </c>
+      <c r="C281">
+        <v>88</v>
+      </c>
+      <c r="D281" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" s="2">
+        <v>46300.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>0</v>
+      </c>
+      <c r="C282">
+        <v>89</v>
+      </c>
+      <c r="D282" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="2">
+        <v>46300.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>0</v>
+      </c>
+      <c r="C283">
+        <v>90</v>
+      </c>
+      <c r="D283" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" s="2">
+        <v>46300.9375</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+      <c r="C284">
+        <v>91</v>
+      </c>
+      <c r="D284" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" s="2">
+        <v>46300.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>0</v>
+      </c>
+      <c r="C285">
+        <v>92</v>
+      </c>
+      <c r="D285" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" s="2">
+        <v>46300.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>0</v>
+      </c>
+      <c r="C286">
+        <v>93</v>
+      </c>
+      <c r="D286" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" s="2">
+        <v>46300.96875</v>
+      </c>
+      <c r="B287">
+        <v>0</v>
+      </c>
+      <c r="C287">
+        <v>94</v>
+      </c>
+      <c r="D287" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" s="2">
+        <v>46300.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>0</v>
+      </c>
+      <c r="C288">
+        <v>95</v>
+      </c>
+      <c r="D288" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" s="2">
+        <v>46300.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>0</v>
+      </c>
+      <c r="C289">
+        <v>96</v>
+      </c>
+      <c r="D289" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="D290" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" s="2">
+        <v>46301.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+      <c r="C291">
+        <v>2</v>
+      </c>
+      <c r="D291" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="2">
+        <v>46301.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+      <c r="C292">
+        <v>3</v>
+      </c>
+      <c r="D292" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" s="2">
+        <v>46301.03125</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>4</v>
+      </c>
+      <c r="D293" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="2">
+        <v>46301.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>5</v>
+      </c>
+      <c r="D294" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" s="2">
+        <v>46301.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>6</v>
+      </c>
+      <c r="D295" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" s="2">
+        <v>46301.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>7</v>
+      </c>
+      <c r="D296" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" s="2">
+        <v>46301.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297">
+        <v>8</v>
+      </c>
+      <c r="D297" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" s="2">
+        <v>46301.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>9</v>
+      </c>
+      <c r="D298" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" s="2">
+        <v>46301.09375</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>10</v>
+      </c>
+      <c r="D299" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" s="2">
+        <v>46301.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+      <c r="C300">
+        <v>11</v>
+      </c>
+      <c r="D300" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" s="2">
+        <v>46301.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>12</v>
+      </c>
+      <c r="D301" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" s="2">
+        <v>46301.125</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+      <c r="C302">
+        <v>13</v>
+      </c>
+      <c r="D302" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" s="2">
+        <v>46301.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>14</v>
+      </c>
+      <c r="D303" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" s="2">
+        <v>46301.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>15</v>
+      </c>
+      <c r="D304" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" s="2">
+        <v>46301.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>16</v>
+      </c>
+      <c r="D305" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306" s="2">
+        <v>46301.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>0</v>
+      </c>
+      <c r="C306">
+        <v>17</v>
+      </c>
+      <c r="D306" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307" s="2">
+        <v>46301.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+      <c r="C307">
+        <v>18</v>
+      </c>
+      <c r="D307" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" s="2">
+        <v>46301.1875</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+      <c r="C308">
+        <v>19</v>
+      </c>
+      <c r="D308" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309" s="2">
+        <v>46301.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>0</v>
+      </c>
+      <c r="C309">
+        <v>20</v>
+      </c>
+      <c r="D309" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" s="2">
+        <v>46301.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
+      <c r="C310">
+        <v>21</v>
+      </c>
+      <c r="D310" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" s="2">
+        <v>46301.21875</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+      <c r="C311">
+        <v>22</v>
+      </c>
+      <c r="D311" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" s="2">
+        <v>46301.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>0</v>
+      </c>
+      <c r="C312">
+        <v>23</v>
+      </c>
+      <c r="D312" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" s="2">
+        <v>46301.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>0</v>
+      </c>
+      <c r="C313">
+        <v>24</v>
+      </c>
+      <c r="D313" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314" s="2">
+        <v>46301.25</v>
+      </c>
+      <c r="B314">
+        <v>0</v>
+      </c>
+      <c r="C314">
+        <v>25</v>
+      </c>
+      <c r="D314" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315" s="2">
+        <v>46301.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+      <c r="C315">
+        <v>26</v>
+      </c>
+      <c r="D315" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316" s="2">
+        <v>46301.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>0</v>
+      </c>
+      <c r="C316">
+        <v>27</v>
+      </c>
+      <c r="D316" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" s="2">
+        <v>46301.28125</v>
+      </c>
+      <c r="B317">
+        <v>0</v>
+      </c>
+      <c r="C317">
+        <v>28</v>
+      </c>
+      <c r="D317" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" s="2">
+        <v>46301.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+      <c r="C318">
+        <v>29</v>
+      </c>
+      <c r="D318" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" s="2">
+        <v>46301.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>0</v>
+      </c>
+      <c r="C319">
+        <v>30</v>
+      </c>
+      <c r="D319" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" s="2">
+        <v>46301.3125</v>
+      </c>
+      <c r="B320">
+        <v>0</v>
+      </c>
+      <c r="C320">
+        <v>31</v>
+      </c>
+      <c r="D320" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" s="2">
+        <v>46301.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+      <c r="C321">
+        <v>32</v>
+      </c>
+      <c r="D321" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" s="2">
+        <v>46301.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+      <c r="C322">
+        <v>33</v>
+      </c>
+      <c r="D322" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" s="2">
+        <v>46301.34375</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+      <c r="C323">
+        <v>34</v>
+      </c>
+      <c r="D323" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" s="2">
+        <v>46301.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+      <c r="C324">
+        <v>35</v>
+      </c>
+      <c r="D324" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325" s="2">
+        <v>46301.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>36</v>
+      </c>
+      <c r="D325" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" s="2">
+        <v>46301.375</v>
+      </c>
+      <c r="B326">
+        <v>5460</v>
+      </c>
+      <c r="C326">
+        <v>37</v>
+      </c>
+      <c r="D326" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327" s="2">
+        <v>46301.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>5243</v>
+      </c>
+      <c r="C327">
+        <v>38</v>
+      </c>
+      <c r="D327" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328" s="2">
+        <v>46301.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>5099</v>
+      </c>
+      <c r="C328">
+        <v>39</v>
+      </c>
+      <c r="D328" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" s="2">
+        <v>46301.40625</v>
+      </c>
+      <c r="B329">
+        <v>4884</v>
+      </c>
+      <c r="C329">
+        <v>40</v>
+      </c>
+      <c r="D329" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330" s="2">
+        <v>46301.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>4687</v>
+      </c>
+      <c r="C330">
+        <v>41</v>
+      </c>
+      <c r="D330" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331" s="2">
+        <v>46301.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>4570</v>
+      </c>
+      <c r="C331">
+        <v>42</v>
+      </c>
+      <c r="D331" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" s="2">
+        <v>46301.4375</v>
+      </c>
+      <c r="B332">
+        <v>4510</v>
+      </c>
+      <c r="C332">
+        <v>43</v>
+      </c>
+      <c r="D332" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333" s="2">
+        <v>46301.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>4366</v>
+      </c>
+      <c r="C333">
+        <v>44</v>
+      </c>
+      <c r="D333" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334" s="2">
+        <v>46301.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>4341</v>
+      </c>
+      <c r="C334">
+        <v>45</v>
+      </c>
+      <c r="D334" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" s="2">
+        <v>46301.46875</v>
+      </c>
+      <c r="B335">
+        <v>4307</v>
+      </c>
+      <c r="C335">
+        <v>46</v>
+      </c>
+      <c r="D335" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" s="2">
+        <v>46301.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>4374</v>
+      </c>
+      <c r="C336">
+        <v>47</v>
+      </c>
+      <c r="D336" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337" s="2">
+        <v>46301.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>4329</v>
+      </c>
+      <c r="C337">
+        <v>48</v>
+      </c>
+      <c r="D337" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338" s="2">
+        <v>46301.5</v>
+      </c>
+      <c r="B338">
+        <v>4438</v>
+      </c>
+      <c r="C338">
+        <v>49</v>
+      </c>
+      <c r="D338" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
+      <c r="A339" s="2">
+        <v>46301.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>4490</v>
+      </c>
+      <c r="C339">
+        <v>50</v>
+      </c>
+      <c r="D339" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340" s="2">
+        <v>46301.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>4465</v>
+      </c>
+      <c r="C340">
+        <v>51</v>
+      </c>
+      <c r="D340" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341" s="2">
+        <v>46301.53125</v>
+      </c>
+      <c r="B341">
+        <v>4474</v>
+      </c>
+      <c r="C341">
+        <v>52</v>
+      </c>
+      <c r="D341" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
+      <c r="A342" s="2">
+        <v>46301.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>4440</v>
+      </c>
+      <c r="C342">
+        <v>53</v>
+      </c>
+      <c r="D342" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343" s="2">
+        <v>46301.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>4479</v>
+      </c>
+      <c r="C343">
+        <v>54</v>
+      </c>
+      <c r="D343" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
+      <c r="A344" s="2">
+        <v>46301.5625</v>
+      </c>
+      <c r="B344">
+        <v>4501</v>
+      </c>
+      <c r="C344">
+        <v>55</v>
+      </c>
+      <c r="D344" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
+      <c r="A345" s="2">
+        <v>46301.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>4458</v>
+      </c>
+      <c r="C345">
+        <v>56</v>
+      </c>
+      <c r="D345" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
+      <c r="A346" s="2">
+        <v>46301.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>4544</v>
+      </c>
+      <c r="C346">
+        <v>57</v>
+      </c>
+      <c r="D346" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
+      <c r="A347" s="2">
+        <v>46301.59375</v>
+      </c>
+      <c r="B347">
+        <v>4628</v>
+      </c>
+      <c r="C347">
+        <v>58</v>
+      </c>
+      <c r="D347" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
+      <c r="A348" s="2">
+        <v>46301.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>4652</v>
+      </c>
+      <c r="C348">
+        <v>59</v>
+      </c>
+      <c r="D348" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349" s="2">
+        <v>46301.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>4784</v>
+      </c>
+      <c r="C349">
+        <v>60</v>
+      </c>
+      <c r="D349" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350" s="2">
+        <v>46301.625</v>
+      </c>
+      <c r="B350">
+        <v>4954</v>
+      </c>
+      <c r="C350">
+        <v>61</v>
+      </c>
+      <c r="D350" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351" s="2">
+        <v>46301.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>5016</v>
+      </c>
+      <c r="C351">
+        <v>62</v>
+      </c>
+      <c r="D351" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
+      <c r="A352" s="2">
+        <v>46301.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>5193</v>
+      </c>
+      <c r="C352">
+        <v>63</v>
+      </c>
+      <c r="D352" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
+      <c r="A353" s="2">
+        <v>46301.65625</v>
+      </c>
+      <c r="B353">
+        <v>5348</v>
+      </c>
+      <c r="C353">
+        <v>64</v>
+      </c>
+      <c r="D353" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
+      <c r="A354" s="2">
+        <v>46301.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>5499</v>
+      </c>
+      <c r="C354">
+        <v>65</v>
+      </c>
+      <c r="D354" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
+      <c r="A355" s="2">
+        <v>46301.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>5701</v>
+      </c>
+      <c r="C355">
+        <v>66</v>
+      </c>
+      <c r="D355" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
+      <c r="A356" s="2">
+        <v>46301.6875</v>
+      </c>
+      <c r="B356">
+        <v>5853</v>
+      </c>
+      <c r="C356">
+        <v>67</v>
+      </c>
+      <c r="D356" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
+      <c r="A357" s="2">
+        <v>46301.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>6139</v>
+      </c>
+      <c r="C357">
+        <v>68</v>
+      </c>
+      <c r="D357" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
+      <c r="A358" s="2">
+        <v>46301.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>6164</v>
+      </c>
+      <c r="C358">
+        <v>69</v>
+      </c>
+      <c r="D358" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
+      <c r="A359" s="2">
+        <v>46301.71875</v>
+      </c>
+      <c r="B359">
+        <v>6333</v>
+      </c>
+      <c r="C359">
+        <v>70</v>
+      </c>
+      <c r="D359" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
+      <c r="A360" s="2">
+        <v>46301.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>6464</v>
+      </c>
+      <c r="C360">
+        <v>71</v>
+      </c>
+      <c r="D360" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
+      <c r="A361" s="2">
+        <v>46301.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>6522</v>
+      </c>
+      <c r="C361">
+        <v>72</v>
+      </c>
+      <c r="D361" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
+      <c r="A362" s="2">
+        <v>46301.75</v>
+      </c>
+      <c r="B362">
+        <v>6751</v>
+      </c>
+      <c r="C362">
+        <v>73</v>
+      </c>
+      <c r="D362" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
+      <c r="A363" s="2">
+        <v>46301.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>6886</v>
+      </c>
+      <c r="C363">
+        <v>74</v>
+      </c>
+      <c r="D363" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364" s="2">
+        <v>46301.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>7019</v>
+      </c>
+      <c r="C364">
+        <v>75</v>
+      </c>
+      <c r="D364" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365" s="2">
+        <v>46301.78125</v>
+      </c>
+      <c r="B365">
+        <v>7050</v>
+      </c>
+      <c r="C365">
+        <v>76</v>
+      </c>
+      <c r="D365" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366" s="2">
+        <v>46301.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>6974</v>
+      </c>
+      <c r="C366">
+        <v>77</v>
+      </c>
+      <c r="D366" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367" s="2">
+        <v>46301.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>6959</v>
+      </c>
+      <c r="C367">
+        <v>78</v>
+      </c>
+      <c r="D367" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
+      <c r="A368" s="2">
+        <v>46301.8125</v>
+      </c>
+      <c r="B368">
+        <v>6888</v>
+      </c>
+      <c r="C368">
+        <v>79</v>
+      </c>
+      <c r="D368" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369" s="2">
+        <v>46301.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>6812</v>
+      </c>
+      <c r="C369">
+        <v>80</v>
+      </c>
+      <c r="D369" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
+      <c r="A370" s="2">
+        <v>46301.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>6716</v>
+      </c>
+      <c r="C370">
+        <v>81</v>
+      </c>
+      <c r="D370" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371" s="2">
+        <v>46301.84375</v>
+      </c>
+      <c r="B371">
+        <v>6599</v>
+      </c>
+      <c r="C371">
+        <v>82</v>
+      </c>
+      <c r="D371" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
+      <c r="A372" s="2">
+        <v>46301.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>6475</v>
+      </c>
+      <c r="C372">
+        <v>83</v>
+      </c>
+      <c r="D372" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373" s="2">
+        <v>46301.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>6354</v>
+      </c>
+      <c r="C373">
+        <v>84</v>
+      </c>
+      <c r="D373" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374" s="2">
+        <v>46301.875</v>
+      </c>
+      <c r="B374">
+        <v>6210</v>
+      </c>
+      <c r="C374">
+        <v>85</v>
+      </c>
+      <c r="D374" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
+      <c r="A375" s="2">
+        <v>46301.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>5985</v>
+      </c>
+      <c r="C375">
+        <v>86</v>
+      </c>
+      <c r="D375" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
+      <c r="A376" s="2">
+        <v>46301.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>5867</v>
+      </c>
+      <c r="C376">
+        <v>87</v>
+      </c>
+      <c r="D376" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
+      <c r="A377" s="2">
+        <v>46301.90625</v>
+      </c>
+      <c r="B377">
+        <v>5746</v>
+      </c>
+      <c r="C377">
+        <v>88</v>
+      </c>
+      <c r="D377" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
+      <c r="A378" s="2">
+        <v>46301.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>5602</v>
+      </c>
+      <c r="C378">
+        <v>89</v>
+      </c>
+      <c r="D378" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
+      <c r="A379" s="2">
+        <v>46301.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>5533</v>
+      </c>
+      <c r="C379">
+        <v>90</v>
+      </c>
+      <c r="D379" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
+      <c r="A380" s="2">
+        <v>46301.9375</v>
+      </c>
+      <c r="B380">
+        <v>5442</v>
+      </c>
+      <c r="C380">
+        <v>91</v>
+      </c>
+      <c r="D380" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
+      <c r="A381" s="2">
+        <v>46301.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>5324</v>
+      </c>
+      <c r="C381">
+        <v>92</v>
+      </c>
+      <c r="D381" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
+      <c r="A382" s="2">
+        <v>46301.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>5297</v>
+      </c>
+      <c r="C382">
+        <v>93</v>
+      </c>
+      <c r="D382" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
+      <c r="A383" s="2">
+        <v>46301.96875</v>
+      </c>
+      <c r="B383">
+        <v>5162</v>
+      </c>
+      <c r="C383">
+        <v>94</v>
+      </c>
+      <c r="D383" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
+      <c r="A384" s="2">
+        <v>46301.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>5117</v>
+      </c>
+      <c r="C384">
+        <v>95</v>
+      </c>
+      <c r="D384" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
+      <c r="A385" s="2">
+        <v>46301.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>5046</v>
+      </c>
+      <c r="C385">
+        <v>96</v>
+      </c>
+      <c r="D385" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4">
+      <c r="A386" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B386">
+        <v>5054</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+      <c r="D386" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4">
+      <c r="A387" s="2">
+        <v>46302.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>5026</v>
+      </c>
+      <c r="C387">
+        <v>2</v>
+      </c>
+      <c r="D387" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4">
+      <c r="A388" s="2">
+        <v>46302.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>5130</v>
+      </c>
+      <c r="C388">
+        <v>3</v>
+      </c>
+      <c r="D388" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4">
+      <c r="A389" s="2">
+        <v>46302.03125</v>
+      </c>
+      <c r="B389">
+        <v>5132</v>
+      </c>
+      <c r="C389">
+        <v>4</v>
+      </c>
+      <c r="D389" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4">
+      <c r="A390" s="2">
+        <v>46302.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>5181</v>
+      </c>
+      <c r="C390">
+        <v>5</v>
+      </c>
+      <c r="D390" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4">
+      <c r="A391" s="2">
+        <v>46302.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>5094</v>
+      </c>
+      <c r="C391">
+        <v>6</v>
+      </c>
+      <c r="D391" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4">
+      <c r="A392" s="2">
+        <v>46302.0625</v>
+      </c>
+      <c r="B392">
+        <v>5123</v>
+      </c>
+      <c r="C392">
+        <v>7</v>
+      </c>
+      <c r="D392" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4">
+      <c r="A393" s="2">
+        <v>46302.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>5094</v>
+      </c>
+      <c r="C393">
+        <v>8</v>
+      </c>
+      <c r="D393" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4">
+      <c r="A394" s="2">
+        <v>46302.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>5156</v>
+      </c>
+      <c r="C394">
+        <v>9</v>
+      </c>
+      <c r="D394" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4">
+      <c r="A395" s="2">
+        <v>46302.09375</v>
+      </c>
+      <c r="B395">
+        <v>5204</v>
+      </c>
+      <c r="C395">
+        <v>10</v>
+      </c>
+      <c r="D395" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4">
+      <c r="A396" s="2">
+        <v>46302.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>5124</v>
+      </c>
+      <c r="C396">
+        <v>11</v>
+      </c>
+      <c r="D396" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4">
+      <c r="A397" s="2">
+        <v>46302.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>5125</v>
+      </c>
+      <c r="C397">
+        <v>12</v>
+      </c>
+      <c r="D397" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4">
+      <c r="A398" s="2">
+        <v>46302.125</v>
+      </c>
+      <c r="B398">
+        <v>5158</v>
+      </c>
+      <c r="C398">
+        <v>13</v>
+      </c>
+      <c r="D398" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4">
+      <c r="A399" s="2">
+        <v>46302.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>5209</v>
+      </c>
+      <c r="C399">
+        <v>14</v>
+      </c>
+      <c r="D399" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4">
+      <c r="A400" s="2">
+        <v>46302.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>5175</v>
+      </c>
+      <c r="C400">
+        <v>15</v>
+      </c>
+      <c r="D400" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4">
+      <c r="A401" s="2">
+        <v>46302.15625</v>
+      </c>
+      <c r="B401">
+        <v>5096</v>
+      </c>
+      <c r="C401">
+        <v>16</v>
+      </c>
+      <c r="D401" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4">
+      <c r="A402" s="2">
+        <v>46302.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>5014</v>
+      </c>
+      <c r="C402">
+        <v>17</v>
+      </c>
+      <c r="D402" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4">
+      <c r="A403" s="2">
+        <v>46302.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>5139</v>
+      </c>
+      <c r="C403">
+        <v>18</v>
+      </c>
+      <c r="D403" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4">
+      <c r="A404" s="2">
+        <v>46302.1875</v>
+      </c>
+      <c r="B404">
+        <v>5153</v>
+      </c>
+      <c r="C404">
+        <v>19</v>
+      </c>
+      <c r="D404" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4">
+      <c r="A405" s="2">
+        <v>46302.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>5287</v>
+      </c>
+      <c r="C405">
+        <v>20</v>
+      </c>
+      <c r="D405" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4">
+      <c r="A406" s="2">
+        <v>46302.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>5552</v>
+      </c>
+      <c r="C406">
+        <v>21</v>
+      </c>
+      <c r="D406" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4">
+      <c r="A407" s="2">
+        <v>46302.21875</v>
+      </c>
+      <c r="B407">
+        <v>5647</v>
+      </c>
+      <c r="C407">
+        <v>22</v>
+      </c>
+      <c r="D407" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4">
+      <c r="A408" s="2">
+        <v>46302.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>5849</v>
+      </c>
+      <c r="C408">
+        <v>23</v>
+      </c>
+      <c r="D408" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4">
+      <c r="A409" s="2">
+        <v>46302.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>5982</v>
+      </c>
+      <c r="C409">
+        <v>24</v>
+      </c>
+      <c r="D409" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4">
+      <c r="A410" s="2">
+        <v>46302.25</v>
+      </c>
+      <c r="B410">
+        <v>6202</v>
+      </c>
+      <c r="C410">
+        <v>25</v>
+      </c>
+      <c r="D410" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4">
+      <c r="A411" s="2">
+        <v>46302.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>6350</v>
+      </c>
+      <c r="C411">
+        <v>26</v>
+      </c>
+      <c r="D411" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4">
+      <c r="A412" s="2">
+        <v>46302.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>6371</v>
+      </c>
+      <c r="C412">
+        <v>27</v>
+      </c>
+      <c r="D412" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4">
+      <c r="A413" s="2">
+        <v>46302.28125</v>
+      </c>
+      <c r="B413">
+        <v>6374</v>
+      </c>
+      <c r="C413">
+        <v>28</v>
+      </c>
+      <c r="D413" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4">
+      <c r="A414" s="2">
+        <v>46302.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>6469</v>
+      </c>
+      <c r="C414">
+        <v>29</v>
+      </c>
+      <c r="D414" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4">
+      <c r="A415" s="2">
+        <v>46302.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>6447</v>
+      </c>
+      <c r="C415">
+        <v>30</v>
+      </c>
+      <c r="D415" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4">
+      <c r="A416" s="2">
+        <v>46302.3125</v>
+      </c>
+      <c r="B416">
+        <v>6409</v>
+      </c>
+      <c r="C416">
+        <v>31</v>
+      </c>
+      <c r="D416" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4">
+      <c r="A417" s="2">
+        <v>46302.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>6363</v>
+      </c>
+      <c r="C417">
+        <v>32</v>
+      </c>
+      <c r="D417" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4">
+      <c r="A418" s="2">
+        <v>46302.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>6167</v>
+      </c>
+      <c r="C418">
+        <v>33</v>
+      </c>
+      <c r="D418" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4">
+      <c r="A419" s="2">
+        <v>46302.34375</v>
+      </c>
+      <c r="B419">
+        <v>6062</v>
+      </c>
+      <c r="C419">
+        <v>34</v>
+      </c>
+      <c r="D419" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4">
+      <c r="A420" s="2">
+        <v>46302.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>6006</v>
+      </c>
+      <c r="C420">
+        <v>35</v>
+      </c>
+      <c r="D420" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4">
+      <c r="A421" s="2">
+        <v>46302.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>5880</v>
+      </c>
+      <c r="C421">
+        <v>36</v>
+      </c>
+      <c r="D421" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4">
+      <c r="A422" s="2">
+        <v>46302.375</v>
+      </c>
+      <c r="B422">
+        <v>5500</v>
+      </c>
+      <c r="C422">
+        <v>37</v>
+      </c>
+      <c r="D422" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4">
+      <c r="A423" s="2">
+        <v>46302.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>5232</v>
+      </c>
+      <c r="C423">
+        <v>38</v>
+      </c>
+      <c r="D423" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4">
+      <c r="A424" s="2">
+        <v>46302.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>5100</v>
+      </c>
+      <c r="C424">
+        <v>39</v>
+      </c>
+      <c r="D424" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4">
+      <c r="A425" s="2">
+        <v>46302.40625</v>
+      </c>
+      <c r="B425">
+        <v>4966</v>
+      </c>
+      <c r="C425">
+        <v>40</v>
+      </c>
+      <c r="D425" t="s">
+        <v>427</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>07.10.20261</t>
-  </si>
-  <si>
-    <t>07.10.20262</t>
-  </si>
-  <si>
-    <t>07.10.20263</t>
-  </si>
-  <si>
-    <t>07.10.20264</t>
-  </si>
-  <si>
-    <t>07.10.20265</t>
-  </si>
-  <si>
-    <t>07.10.20266</t>
-  </si>
-  <si>
-    <t>07.10.20267</t>
-  </si>
-  <si>
-    <t>07.10.20268</t>
-  </si>
-  <si>
-    <t>07.10.20269</t>
-  </si>
-  <si>
-    <t>07.10.202610</t>
-  </si>
-  <si>
-    <t>07.10.202611</t>
-  </si>
-  <si>
-    <t>07.10.202612</t>
-  </si>
-  <si>
-    <t>07.10.202613</t>
-  </si>
-  <si>
-    <t>07.10.202614</t>
-  </si>
-  <si>
-    <t>07.10.202615</t>
-  </si>
-  <si>
-    <t>07.10.202616</t>
-  </si>
-  <si>
-    <t>07.10.202617</t>
-  </si>
-  <si>
-    <t>07.10.202618</t>
-  </si>
-  <si>
-    <t>07.10.202619</t>
-  </si>
-  <si>
-    <t>07.10.202620</t>
-  </si>
-  <si>
-    <t>07.10.202621</t>
-  </si>
-  <si>
-    <t>07.10.202622</t>
-  </si>
-  <si>
-    <t>07.10.202623</t>
-  </si>
-  <si>
-    <t>07.10.202624</t>
-  </si>
-  <si>
-    <t>07.10.202625</t>
-  </si>
-  <si>
-    <t>07.10.202626</t>
-  </si>
-  <si>
-    <t>07.10.202627</t>
-  </si>
-  <si>
-    <t>07.10.202628</t>
-  </si>
-  <si>
-    <t>07.10.202629</t>
-  </si>
-  <si>
-    <t>07.10.202630</t>
-  </si>
-  <si>
-    <t>07.10.202631</t>
-  </si>
-  <si>
-    <t>07.10.202632</t>
-  </si>
-  <si>
-    <t>07.10.202633</t>
-  </si>
-  <si>
-    <t>07.10.202634</t>
-  </si>
-  <si>
-    <t>07.10.202635</t>
-  </si>
-  <si>
-    <t>07.10.202636</t>
-  </si>
-  <si>
-    <t>07.10.202637</t>
-  </si>
-  <si>
-    <t>07.10.202638</t>
-  </si>
-  <si>
-    <t>07.10.202639</t>
-  </si>
-  <si>
-    <t>07.10.202640</t>
-  </si>
-  <si>
-    <t>07.10.202641</t>
-  </si>
-  <si>
-    <t>07.10.202642</t>
-  </si>
-  <si>
-    <t>07.10.202643</t>
-  </si>
-  <si>
-    <t>07.10.202644</t>
-  </si>
-  <si>
-    <t>07.10.202645</t>
-  </si>
-  <si>
-    <t>07.10.202646</t>
-  </si>
-  <si>
-    <t>07.10.202647</t>
-  </si>
-  <si>
-    <t>07.10.202648</t>
-  </si>
-  <si>
-    <t>07.10.202649</t>
-  </si>
-  <si>
-    <t>07.10.202650</t>
-  </si>
-  <si>
-    <t>07.10.202651</t>
-  </si>
-  <si>
-    <t>07.10.202652</t>
-  </si>
-  <si>
-    <t>07.10.202653</t>
-  </si>
-  <si>
-    <t>07.10.202654</t>
-  </si>
-  <si>
-    <t>07.10.202655</t>
-  </si>
-  <si>
-    <t>07.10.202656</t>
-  </si>
-  <si>
-    <t>07.10.202657</t>
-  </si>
-  <si>
-    <t>07.10.202658</t>
-  </si>
-  <si>
-    <t>07.10.202659</t>
-  </si>
-  <si>
-    <t>07.10.202660</t>
-  </si>
-  <si>
-    <t>07.10.202661</t>
-  </si>
-  <si>
-    <t>07.10.202662</t>
-  </si>
-  <si>
-    <t>07.10.202663</t>
-  </si>
-  <si>
-    <t>07.10.202664</t>
-  </si>
-  <si>
-    <t>07.10.202665</t>
-  </si>
-  <si>
-    <t>07.10.202666</t>
-  </si>
-  <si>
-    <t>07.10.202667</t>
-  </si>
-  <si>
-    <t>07.10.202668</t>
-  </si>
-  <si>
-    <t>07.10.202669</t>
-  </si>
-  <si>
-    <t>07.10.202670</t>
-  </si>
-  <si>
-    <t>07.10.202671</t>
-  </si>
-  <si>
-    <t>07.10.202672</t>
-  </si>
-  <si>
-    <t>07.10.202673</t>
-  </si>
-  <si>
-    <t>07.10.202674</t>
-  </si>
-  <si>
-    <t>07.10.202675</t>
-  </si>
-  <si>
-    <t>07.10.202676</t>
-  </si>
-  <si>
-    <t>07.10.202677</t>
-  </si>
-  <si>
-    <t>07.10.202678</t>
-  </si>
-  <si>
-    <t>07.10.202679</t>
-  </si>
-  <si>
-    <t>07.10.202680</t>
-  </si>
-  <si>
-    <t>07.10.202681</t>
-  </si>
-  <si>
-    <t>07.10.202682</t>
-  </si>
-  <si>
-    <t>07.10.202683</t>
-  </si>
-  <si>
-    <t>07.10.202684</t>
-  </si>
-  <si>
-    <t>07.10.202685</t>
-  </si>
-  <si>
-    <t>07.10.202686</t>
-  </si>
-  <si>
-    <t>07.10.202687</t>
-  </si>
-  <si>
-    <t>07.10.202688</t>
-  </si>
-  <si>
-    <t>07.10.202689</t>
-  </si>
-  <si>
-    <t>07.10.202690</t>
-  </si>
-  <si>
-    <t>07.10.202691</t>
-  </si>
-  <si>
-    <t>07.10.202692</t>
-  </si>
-  <si>
-    <t>07.10.202693</t>
-  </si>
-  <si>
-    <t>07.10.202694</t>
-  </si>
-  <si>
-    <t>07.10.202695</t>
-  </si>
-  <si>
-    <t>07.10.202696</t>
-  </si>
-  <si>
     <t>08.10.20261</t>
   </si>
   <si>
@@ -419,6 +131,294 @@
   </si>
   <si>
     <t>08.10.202635</t>
+  </si>
+  <si>
+    <t>08.10.202636</t>
+  </si>
+  <si>
+    <t>08.10.202637</t>
+  </si>
+  <si>
+    <t>08.10.202638</t>
+  </si>
+  <si>
+    <t>08.10.202639</t>
+  </si>
+  <si>
+    <t>08.10.202640</t>
+  </si>
+  <si>
+    <t>08.10.202641</t>
+  </si>
+  <si>
+    <t>08.10.202642</t>
+  </si>
+  <si>
+    <t>08.10.202643</t>
+  </si>
+  <si>
+    <t>08.10.202644</t>
+  </si>
+  <si>
+    <t>08.10.202645</t>
+  </si>
+  <si>
+    <t>08.10.202646</t>
+  </si>
+  <si>
+    <t>08.10.202647</t>
+  </si>
+  <si>
+    <t>08.10.202648</t>
+  </si>
+  <si>
+    <t>08.10.202649</t>
+  </si>
+  <si>
+    <t>08.10.202650</t>
+  </si>
+  <si>
+    <t>08.10.202651</t>
+  </si>
+  <si>
+    <t>08.10.202652</t>
+  </si>
+  <si>
+    <t>08.10.202653</t>
+  </si>
+  <si>
+    <t>08.10.202654</t>
+  </si>
+  <si>
+    <t>08.10.202655</t>
+  </si>
+  <si>
+    <t>08.10.202656</t>
+  </si>
+  <si>
+    <t>08.10.202657</t>
+  </si>
+  <si>
+    <t>08.10.202658</t>
+  </si>
+  <si>
+    <t>08.10.202659</t>
+  </si>
+  <si>
+    <t>08.10.202660</t>
+  </si>
+  <si>
+    <t>08.10.202661</t>
+  </si>
+  <si>
+    <t>08.10.202662</t>
+  </si>
+  <si>
+    <t>08.10.202663</t>
+  </si>
+  <si>
+    <t>08.10.202664</t>
+  </si>
+  <si>
+    <t>08.10.202665</t>
+  </si>
+  <si>
+    <t>08.10.202666</t>
+  </si>
+  <si>
+    <t>08.10.202667</t>
+  </si>
+  <si>
+    <t>08.10.202668</t>
+  </si>
+  <si>
+    <t>08.10.202669</t>
+  </si>
+  <si>
+    <t>08.10.202670</t>
+  </si>
+  <si>
+    <t>08.10.202671</t>
+  </si>
+  <si>
+    <t>08.10.202672</t>
+  </si>
+  <si>
+    <t>08.10.202673</t>
+  </si>
+  <si>
+    <t>08.10.202674</t>
+  </si>
+  <si>
+    <t>08.10.202675</t>
+  </si>
+  <si>
+    <t>08.10.202676</t>
+  </si>
+  <si>
+    <t>08.10.202677</t>
+  </si>
+  <si>
+    <t>08.10.202678</t>
+  </si>
+  <si>
+    <t>08.10.202679</t>
+  </si>
+  <si>
+    <t>08.10.202680</t>
+  </si>
+  <si>
+    <t>08.10.202681</t>
+  </si>
+  <si>
+    <t>08.10.202682</t>
+  </si>
+  <si>
+    <t>08.10.202683</t>
+  </si>
+  <si>
+    <t>08.10.202684</t>
+  </si>
+  <si>
+    <t>08.10.202685</t>
+  </si>
+  <si>
+    <t>08.10.202686</t>
+  </si>
+  <si>
+    <t>08.10.202687</t>
+  </si>
+  <si>
+    <t>08.10.202688</t>
+  </si>
+  <si>
+    <t>08.10.202689</t>
+  </si>
+  <si>
+    <t>08.10.202690</t>
+  </si>
+  <si>
+    <t>08.10.202691</t>
+  </si>
+  <si>
+    <t>08.10.202692</t>
+  </si>
+  <si>
+    <t>08.10.202693</t>
+  </si>
+  <si>
+    <t>08.10.202694</t>
+  </si>
+  <si>
+    <t>08.10.202695</t>
+  </si>
+  <si>
+    <t>08.10.202696</t>
+  </si>
+  <si>
+    <t>09.10.20261</t>
+  </si>
+  <si>
+    <t>09.10.20262</t>
+  </si>
+  <si>
+    <t>09.10.20263</t>
+  </si>
+  <si>
+    <t>09.10.20264</t>
+  </si>
+  <si>
+    <t>09.10.20265</t>
+  </si>
+  <si>
+    <t>09.10.20266</t>
+  </si>
+  <si>
+    <t>09.10.20267</t>
+  </si>
+  <si>
+    <t>09.10.20268</t>
+  </si>
+  <si>
+    <t>09.10.20269</t>
+  </si>
+  <si>
+    <t>09.10.202610</t>
+  </si>
+  <si>
+    <t>09.10.202611</t>
+  </si>
+  <si>
+    <t>09.10.202612</t>
+  </si>
+  <si>
+    <t>09.10.202613</t>
+  </si>
+  <si>
+    <t>09.10.202614</t>
+  </si>
+  <si>
+    <t>09.10.202615</t>
+  </si>
+  <si>
+    <t>09.10.202616</t>
+  </si>
+  <si>
+    <t>09.10.202617</t>
+  </si>
+  <si>
+    <t>09.10.202618</t>
+  </si>
+  <si>
+    <t>09.10.202619</t>
+  </si>
+  <si>
+    <t>09.10.202620</t>
+  </si>
+  <si>
+    <t>09.10.202621</t>
+  </si>
+  <si>
+    <t>09.10.202622</t>
+  </si>
+  <si>
+    <t>09.10.202623</t>
+  </si>
+  <si>
+    <t>09.10.202624</t>
+  </si>
+  <si>
+    <t>09.10.202625</t>
+  </si>
+  <si>
+    <t>09.10.202626</t>
+  </si>
+  <si>
+    <t>09.10.202627</t>
+  </si>
+  <si>
+    <t>09.10.202628</t>
+  </si>
+  <si>
+    <t>09.10.202629</t>
+  </si>
+  <si>
+    <t>09.10.202630</t>
+  </si>
+  <si>
+    <t>09.10.202631</t>
+  </si>
+  <si>
+    <t>09.10.202632</t>
+  </si>
+  <si>
+    <t>09.10.202633</t>
+  </si>
+  <si>
+    <t>09.10.202634</t>
+  </si>
+  <si>
+    <t>09.10.202635</t>
   </si>
 </sst>
 </file>
@@ -799,10 +799,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2">
-        <v>5054</v>
+        <v>5194</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -813,10 +813,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46302.01041666666</v>
+        <v>46303.01041666666</v>
       </c>
       <c r="B3">
-        <v>5026</v>
+        <v>5121</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -827,10 +827,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46302.02083333334</v>
+        <v>46303.02083333334</v>
       </c>
       <c r="B4">
-        <v>5130</v>
+        <v>5131</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46302.03125</v>
+        <v>46303.03125</v>
       </c>
       <c r="B5">
-        <v>5132</v>
+        <v>5081</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -855,10 +855,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46302.04166666666</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="B6">
-        <v>5181</v>
+        <v>4949</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46302.05208333334</v>
+        <v>46303.05208333334</v>
       </c>
       <c r="B7">
-        <v>5094</v>
+        <v>4935</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -883,10 +883,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46302.0625</v>
+        <v>46303.0625</v>
       </c>
       <c r="B8">
-        <v>5123</v>
+        <v>4998</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46302.07291666666</v>
+        <v>46303.07291666666</v>
       </c>
       <c r="B9">
-        <v>5094</v>
+        <v>5103</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -911,10 +911,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46302.08333333334</v>
+        <v>46303.08333333334</v>
       </c>
       <c r="B10">
-        <v>5156</v>
+        <v>5118</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -925,10 +925,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46302.09375</v>
+        <v>46303.09375</v>
       </c>
       <c r="B11">
-        <v>5204</v>
+        <v>5142</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -939,10 +939,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46302.10416666666</v>
+        <v>46303.10416666666</v>
       </c>
       <c r="B12">
-        <v>5124</v>
+        <v>5076</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -953,10 +953,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46302.11458333334</v>
+        <v>46303.11458333334</v>
       </c>
       <c r="B13">
-        <v>5125</v>
+        <v>5052</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -967,10 +967,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46302.125</v>
+        <v>46303.125</v>
       </c>
       <c r="B14">
-        <v>5158</v>
+        <v>5006</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46302.13541666666</v>
+        <v>46303.13541666666</v>
       </c>
       <c r="B15">
-        <v>5209</v>
+        <v>5030</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46302.14583333334</v>
+        <v>46303.14583333334</v>
       </c>
       <c r="B16">
-        <v>5175</v>
+        <v>4996</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46302.15625</v>
+        <v>46303.15625</v>
       </c>
       <c r="B17">
-        <v>5096</v>
+        <v>5047</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46302.16666666666</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="B18">
-        <v>5014</v>
+        <v>5229</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1037,10 +1037,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46302.17708333334</v>
+        <v>46303.17708333334</v>
       </c>
       <c r="B19">
-        <v>5139</v>
+        <v>5151</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1051,10 +1051,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46302.1875</v>
+        <v>46303.1875</v>
       </c>
       <c r="B20">
-        <v>5153</v>
+        <v>5235</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1065,7 +1065,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46302.19791666666</v>
+        <v>46303.19791666666</v>
       </c>
       <c r="B21">
         <v>5287</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46302.20833333334</v>
+        <v>46303.20833333334</v>
       </c>
       <c r="B22">
-        <v>5552</v>
+        <v>5488</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46302.21875</v>
+        <v>46303.21875</v>
       </c>
       <c r="B23">
-        <v>5647</v>
+        <v>5562</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46302.22916666666</v>
+        <v>46303.22916666666</v>
       </c>
       <c r="B24">
-        <v>5849</v>
+        <v>5740</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46302.23958333334</v>
+        <v>46303.23958333334</v>
       </c>
       <c r="B25">
-        <v>5982</v>
+        <v>5884</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="B26">
-        <v>6202</v>
+        <v>6176</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46302.26041666666</v>
+        <v>46303.26041666666</v>
       </c>
       <c r="B27">
-        <v>6350</v>
+        <v>6318</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1163,10 +1163,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46302.27083333334</v>
+        <v>46303.27083333334</v>
       </c>
       <c r="B28">
-        <v>6371</v>
+        <v>6352</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46302.28125</v>
+        <v>46303.28125</v>
       </c>
       <c r="B29">
-        <v>6374</v>
+        <v>6387</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1191,10 +1191,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46302.29166666666</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="B30">
-        <v>6469</v>
+        <v>6461</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46302.30208333334</v>
+        <v>46303.30208333334</v>
       </c>
       <c r="B31">
-        <v>6447</v>
+        <v>6469</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1219,10 +1219,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46302.3125</v>
+        <v>46303.3125</v>
       </c>
       <c r="B32">
-        <v>6409</v>
+        <v>6384</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46302.32291666666</v>
+        <v>46303.32291666666</v>
       </c>
       <c r="B33">
-        <v>6363</v>
+        <v>6319</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1247,10 +1247,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46302.33333333334</v>
+        <v>46303.33333333334</v>
       </c>
       <c r="B34">
-        <v>6167</v>
+        <v>6073</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46302.34375</v>
+        <v>46303.34375</v>
       </c>
       <c r="B35">
-        <v>6062</v>
+        <v>5958</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1275,10 +1275,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46302.35416666666</v>
+        <v>46303.35416666666</v>
       </c>
       <c r="B36">
-        <v>6006</v>
+        <v>5816</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46302.36458333334</v>
+        <v>46303.36458333334</v>
       </c>
       <c r="B37">
-        <v>5880</v>
+        <v>5816</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1303,10 +1303,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46302.375</v>
+        <v>46303.375</v>
       </c>
       <c r="B38">
-        <v>5500</v>
+        <v>5421</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46302.38541666666</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="B39">
-        <v>5232</v>
+        <v>5244</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46302.39583333334</v>
+        <v>46303.39583333334</v>
       </c>
       <c r="B40">
-        <v>5100</v>
+        <v>5101</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46302.40625</v>
+        <v>46303.40625</v>
       </c>
       <c r="B41">
-        <v>4966</v>
+        <v>4952</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46302.41666666666</v>
+        <v>46303.41666666666</v>
       </c>
       <c r="B42">
-        <v>4782</v>
+        <v>4705</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1373,10 +1373,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46302.42708333334</v>
+        <v>46303.42708333334</v>
       </c>
       <c r="B43">
-        <v>4594</v>
+        <v>4588</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1387,10 +1387,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46302.4375</v>
+        <v>46303.4375</v>
       </c>
       <c r="B44">
-        <v>4583</v>
+        <v>4505</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46302.44791666666</v>
+        <v>46303.44791666666</v>
       </c>
       <c r="B45">
-        <v>4470</v>
+        <v>4397</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46302.45833333334</v>
+        <v>46303.45833333334</v>
       </c>
       <c r="B46">
-        <v>4504</v>
+        <v>4354</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46302.46875</v>
+        <v>46303.46875</v>
       </c>
       <c r="B47">
-        <v>4399</v>
+        <v>4427</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1443,10 +1443,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46302.47916666666</v>
+        <v>46303.47916666666</v>
       </c>
       <c r="B48">
-        <v>4390</v>
+        <v>4449</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46302.48958333334</v>
+        <v>46303.48958333334</v>
       </c>
       <c r="B49">
-        <v>4552</v>
+        <v>4446</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46302.5</v>
+        <v>46303.5</v>
       </c>
       <c r="B50">
-        <v>4628</v>
+        <v>4551</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46302.51041666666</v>
+        <v>46303.51041666666</v>
       </c>
       <c r="B51">
-        <v>4672</v>
+        <v>4553</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46302.52083333334</v>
+        <v>46303.52083333334</v>
       </c>
       <c r="B52">
-        <v>4655</v>
+        <v>4575</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46302.53125</v>
+        <v>46303.53125</v>
       </c>
       <c r="B53">
-        <v>4734</v>
+        <v>4578</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1527,10 +1527,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46302.54166666666</v>
+        <v>46303.54166666666</v>
       </c>
       <c r="B54">
-        <v>4607</v>
+        <v>4464</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46302.55208333334</v>
+        <v>46303.55208333334</v>
       </c>
       <c r="B55">
-        <v>4619</v>
+        <v>4456</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46302.5625</v>
+        <v>46303.5625</v>
       </c>
       <c r="B56">
-        <v>4653</v>
+        <v>4481</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46302.57291666666</v>
+        <v>46303.57291666666</v>
       </c>
       <c r="B57">
-        <v>4702</v>
+        <v>4493</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1583,10 +1583,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46302.58333333334</v>
+        <v>46303.58333333334</v>
       </c>
       <c r="B58">
-        <v>4636</v>
+        <v>4497</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46302.59375</v>
+        <v>46303.59375</v>
       </c>
       <c r="B59">
-        <v>4628</v>
+        <v>4590</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46302.60416666666</v>
+        <v>46303.60416666666</v>
       </c>
       <c r="B60">
-        <v>4890</v>
+        <v>4653</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1625,10 +1625,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46302.61458333334</v>
+        <v>46303.61458333334</v>
       </c>
       <c r="B61">
-        <v>5059</v>
+        <v>4910</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46302.625</v>
+        <v>46303.625</v>
       </c>
       <c r="B62">
-        <v>5142</v>
+        <v>4926</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46302.63541666666</v>
+        <v>46303.63541666666</v>
       </c>
       <c r="B63">
-        <v>5214</v>
+        <v>5109</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1667,10 +1667,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46302.64583333334</v>
+        <v>46303.64583333334</v>
       </c>
       <c r="B64">
-        <v>5369</v>
+        <v>5317</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1681,10 +1681,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46302.65625</v>
+        <v>46303.65625</v>
       </c>
       <c r="B65">
-        <v>5505</v>
+        <v>5437</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46302.66666666666</v>
+        <v>46303.66666666666</v>
       </c>
       <c r="B66">
-        <v>5787</v>
+        <v>5608</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46302.67708333334</v>
+        <v>46303.67708333334</v>
       </c>
       <c r="B67">
-        <v>5845</v>
+        <v>5801</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46302.6875</v>
+        <v>46303.6875</v>
       </c>
       <c r="B68">
-        <v>6039</v>
+        <v>6027</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1737,10 +1737,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46302.69791666666</v>
+        <v>46303.69791666666</v>
       </c>
       <c r="B69">
-        <v>6189</v>
+        <v>6180</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46302.70833333334</v>
+        <v>46303.70833333334</v>
       </c>
       <c r="B70">
-        <v>6268</v>
+        <v>6287</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46302.71875</v>
+        <v>46303.71875</v>
       </c>
       <c r="B71">
-        <v>6412</v>
+        <v>6425</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46302.72916666666</v>
+        <v>46303.72916666666</v>
       </c>
       <c r="B72">
-        <v>6510</v>
+        <v>6474</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1793,10 +1793,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46302.73958333334</v>
+        <v>46303.73958333334</v>
       </c>
       <c r="B73">
-        <v>6643</v>
+        <v>6650</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46302.75</v>
+        <v>46303.75</v>
       </c>
       <c r="B74">
-        <v>6788</v>
+        <v>6779</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -1821,10 +1821,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46302.76041666666</v>
+        <v>46303.76041666666</v>
       </c>
       <c r="B75">
-        <v>6961</v>
+        <v>6948</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -1835,10 +1835,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46302.77083333334</v>
+        <v>46303.77083333334</v>
       </c>
       <c r="B76">
-        <v>7053</v>
+        <v>7045</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46302.78125</v>
+        <v>46303.78125</v>
       </c>
       <c r="B77">
-        <v>7111</v>
+        <v>7076</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46302.79166666666</v>
+        <v>46303.79166666666</v>
       </c>
       <c r="B78">
-        <v>7092</v>
+        <v>7017</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46302.80208333334</v>
+        <v>46303.80208333334</v>
       </c>
       <c r="B79">
-        <v>7023</v>
+        <v>6977</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46302.8125</v>
+        <v>46303.8125</v>
       </c>
       <c r="B80">
-        <v>6929</v>
+        <v>6937</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -1905,10 +1905,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46302.82291666666</v>
+        <v>46303.82291666666</v>
       </c>
       <c r="B81">
-        <v>6886</v>
+        <v>6809</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46302.83333333334</v>
+        <v>46303.83333333334</v>
       </c>
       <c r="B82">
-        <v>6763</v>
+        <v>6772</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46302.84375</v>
+        <v>46303.84375</v>
       </c>
       <c r="B83">
-        <v>6668</v>
+        <v>6664</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46302.85416666666</v>
+        <v>46303.85416666666</v>
       </c>
       <c r="B84">
-        <v>6504</v>
+        <v>6492</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -1961,10 +1961,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46302.86458333334</v>
+        <v>46303.86458333334</v>
       </c>
       <c r="B85">
-        <v>6342</v>
+        <v>6346</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46302.875</v>
+        <v>46303.875</v>
       </c>
       <c r="B86">
-        <v>6199</v>
+        <v>6144</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -1989,10 +1989,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46302.88541666666</v>
+        <v>46303.88541666666</v>
       </c>
       <c r="B87">
-        <v>6036</v>
+        <v>6014</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2003,10 +2003,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46302.89583333334</v>
+        <v>46303.89583333334</v>
       </c>
       <c r="B88">
-        <v>5920</v>
+        <v>5866</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46302.90625</v>
+        <v>46303.90625</v>
       </c>
       <c r="B89">
-        <v>5810</v>
+        <v>5719</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46302.91666666666</v>
+        <v>46303.91666666666</v>
       </c>
       <c r="B90">
-        <v>5651</v>
+        <v>5617</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46302.92708333334</v>
+        <v>46303.92708333334</v>
       </c>
       <c r="B91">
-        <v>5560</v>
+        <v>5550</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2059,10 +2059,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46302.9375</v>
+        <v>46303.9375</v>
       </c>
       <c r="B92">
-        <v>5473</v>
+        <v>5466</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46302.94791666666</v>
+        <v>46303.94791666666</v>
       </c>
       <c r="B93">
-        <v>5401</v>
+        <v>5384</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2087,10 +2087,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46302.95833333334</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="B94">
-        <v>5281</v>
+        <v>5335</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2101,10 +2101,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46302.96875</v>
+        <v>46303.96875</v>
       </c>
       <c r="B95">
-        <v>5196</v>
+        <v>5246</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2115,10 +2115,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46302.97916666666</v>
+        <v>46303.97916666666</v>
       </c>
       <c r="B96">
-        <v>5167</v>
+        <v>5152</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2129,10 +2129,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46302.98958333334</v>
+        <v>46303.98958333334</v>
       </c>
       <c r="B97">
-        <v>5125</v>
+        <v>5138</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B98">
-        <v>5194</v>
+        <v>5147</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2157,10 +2157,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B99">
-        <v>5121</v>
+        <v>5091</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B100">
-        <v>5131</v>
+        <v>5031</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B101">
-        <v>5081</v>
+        <v>5025</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2199,10 +2199,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B102">
-        <v>4949</v>
+        <v>5210</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2213,10 +2213,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B103">
-        <v>4935</v>
+        <v>5172</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B104">
-        <v>4998</v>
+        <v>5187</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B105">
-        <v>5103</v>
+        <v>5135</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B106">
-        <v>5118</v>
+        <v>5128</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B107">
-        <v>5142</v>
+        <v>5129</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2283,10 +2283,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B108">
-        <v>5076</v>
+        <v>5064</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2297,10 +2297,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B109">
-        <v>5052</v>
+        <v>5094</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2311,10 +2311,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B110">
-        <v>5006</v>
+        <v>5135</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2325,10 +2325,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B111">
-        <v>5030</v>
+        <v>5169</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B112">
-        <v>4996</v>
+        <v>5015</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B113">
-        <v>5047</v>
+        <v>5121</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B114">
-        <v>5229</v>
+        <v>5106</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2381,10 +2381,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B115">
-        <v>5151</v>
+        <v>5137</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B116">
-        <v>5235</v>
+        <v>5164</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B117">
         <v>5287</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B118">
-        <v>5488</v>
+        <v>5628</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2437,10 +2437,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B119">
-        <v>5562</v>
+        <v>5765</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B120">
-        <v>5740</v>
+        <v>5799</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B121">
-        <v>5884</v>
+        <v>5980</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B122">
-        <v>6176</v>
+        <v>6174</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B123">
-        <v>6318</v>
+        <v>6248</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2507,10 +2507,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B124">
-        <v>6352</v>
+        <v>6266</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2521,10 +2521,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B125">
-        <v>6387</v>
+        <v>6334</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B126">
-        <v>6461</v>
+        <v>6437</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B127">
-        <v>6469</v>
+        <v>6484</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2563,10 +2563,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B128">
-        <v>6384</v>
+        <v>6401</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B129">
-        <v>6319</v>
+        <v>6361</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B130">
-        <v>6073</v>
+        <v>6247</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2605,10 +2605,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B131">
-        <v>5958</v>
+        <v>6207</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B132">
-        <v>5816</v>
+        <v>6041</v>
       </c>
       <c r="C132">
         <v>35</v>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="330">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>08.10.20261</t>
-  </si>
-  <si>
-    <t>08.10.20262</t>
-  </si>
-  <si>
-    <t>08.10.20263</t>
-  </si>
-  <si>
-    <t>08.10.20264</t>
-  </si>
-  <si>
-    <t>08.10.20265</t>
-  </si>
-  <si>
-    <t>08.10.20266</t>
-  </si>
-  <si>
-    <t>08.10.20267</t>
-  </si>
-  <si>
-    <t>08.10.20268</t>
-  </si>
-  <si>
-    <t>08.10.20269</t>
-  </si>
-  <si>
-    <t>08.10.202610</t>
-  </si>
-  <si>
-    <t>08.10.202611</t>
-  </si>
-  <si>
-    <t>08.10.202612</t>
-  </si>
-  <si>
-    <t>08.10.202613</t>
-  </si>
-  <si>
-    <t>08.10.202614</t>
-  </si>
-  <si>
-    <t>08.10.202615</t>
-  </si>
-  <si>
-    <t>08.10.202616</t>
-  </si>
-  <si>
-    <t>08.10.202617</t>
-  </si>
-  <si>
-    <t>08.10.202618</t>
-  </si>
-  <si>
-    <t>08.10.202619</t>
-  </si>
-  <si>
-    <t>08.10.202620</t>
-  </si>
-  <si>
-    <t>08.10.202621</t>
-  </si>
-  <si>
-    <t>08.10.202622</t>
-  </si>
-  <si>
-    <t>08.10.202623</t>
-  </si>
-  <si>
-    <t>08.10.202624</t>
-  </si>
-  <si>
-    <t>08.10.202625</t>
-  </si>
-  <si>
-    <t>08.10.202626</t>
-  </si>
-  <si>
-    <t>08.10.202627</t>
-  </si>
-  <si>
-    <t>08.10.202628</t>
-  </si>
-  <si>
-    <t>08.10.202629</t>
-  </si>
-  <si>
-    <t>08.10.202630</t>
-  </si>
-  <si>
-    <t>08.10.202631</t>
-  </si>
-  <si>
-    <t>08.10.202632</t>
-  </si>
-  <si>
-    <t>08.10.202633</t>
-  </si>
-  <si>
-    <t>08.10.202634</t>
-  </si>
-  <si>
-    <t>08.10.202635</t>
-  </si>
-  <si>
-    <t>08.10.202636</t>
-  </si>
-  <si>
-    <t>08.10.202637</t>
-  </si>
-  <si>
-    <t>08.10.202638</t>
-  </si>
-  <si>
-    <t>08.10.202639</t>
-  </si>
-  <si>
-    <t>08.10.202640</t>
-  </si>
-  <si>
-    <t>08.10.202641</t>
-  </si>
-  <si>
-    <t>08.10.202642</t>
-  </si>
-  <si>
-    <t>08.10.202643</t>
-  </si>
-  <si>
-    <t>08.10.202644</t>
-  </si>
-  <si>
-    <t>08.10.202645</t>
-  </si>
-  <si>
-    <t>08.10.202646</t>
-  </si>
-  <si>
-    <t>08.10.202647</t>
-  </si>
-  <si>
-    <t>08.10.202648</t>
-  </si>
-  <si>
-    <t>08.10.202649</t>
-  </si>
-  <si>
-    <t>08.10.202650</t>
-  </si>
-  <si>
-    <t>08.10.202651</t>
-  </si>
-  <si>
-    <t>08.10.202652</t>
-  </si>
-  <si>
-    <t>08.10.202653</t>
-  </si>
-  <si>
-    <t>08.10.202654</t>
-  </si>
-  <si>
-    <t>08.10.202655</t>
-  </si>
-  <si>
-    <t>08.10.202656</t>
-  </si>
-  <si>
-    <t>08.10.202657</t>
-  </si>
-  <si>
-    <t>08.10.202658</t>
-  </si>
-  <si>
-    <t>08.10.202659</t>
-  </si>
-  <si>
-    <t>08.10.202660</t>
-  </si>
-  <si>
-    <t>08.10.202661</t>
-  </si>
-  <si>
-    <t>08.10.202662</t>
-  </si>
-  <si>
-    <t>08.10.202663</t>
-  </si>
-  <si>
-    <t>08.10.202664</t>
-  </si>
-  <si>
-    <t>08.10.202665</t>
-  </si>
-  <si>
-    <t>08.10.202666</t>
-  </si>
-  <si>
-    <t>08.10.202667</t>
-  </si>
-  <si>
-    <t>08.10.202668</t>
-  </si>
-  <si>
-    <t>08.10.202669</t>
-  </si>
-  <si>
-    <t>08.10.202670</t>
-  </si>
-  <si>
-    <t>08.10.202671</t>
-  </si>
-  <si>
-    <t>08.10.202672</t>
-  </si>
-  <si>
-    <t>08.10.202673</t>
-  </si>
-  <si>
-    <t>08.10.202674</t>
-  </si>
-  <si>
-    <t>08.10.202675</t>
-  </si>
-  <si>
-    <t>08.10.202676</t>
-  </si>
-  <si>
-    <t>08.10.202677</t>
-  </si>
-  <si>
-    <t>08.10.202678</t>
-  </si>
-  <si>
-    <t>08.10.202679</t>
-  </si>
-  <si>
-    <t>08.10.202680</t>
-  </si>
-  <si>
-    <t>08.10.202681</t>
-  </si>
-  <si>
-    <t>08.10.202682</t>
-  </si>
-  <si>
-    <t>08.10.202683</t>
-  </si>
-  <si>
-    <t>08.10.202684</t>
-  </si>
-  <si>
-    <t>08.10.202685</t>
-  </si>
-  <si>
-    <t>08.10.202686</t>
-  </si>
-  <si>
-    <t>08.10.202687</t>
-  </si>
-  <si>
-    <t>08.10.202688</t>
-  </si>
-  <si>
-    <t>08.10.202689</t>
-  </si>
-  <si>
-    <t>08.10.202690</t>
-  </si>
-  <si>
-    <t>08.10.202691</t>
-  </si>
-  <si>
-    <t>08.10.202692</t>
-  </si>
-  <si>
-    <t>08.10.202693</t>
-  </si>
-  <si>
-    <t>08.10.202694</t>
-  </si>
-  <si>
-    <t>08.10.202695</t>
-  </si>
-  <si>
-    <t>08.10.202696</t>
-  </si>
-  <si>
     <t>09.10.20261</t>
   </si>
   <si>
@@ -419,6 +131,879 @@
   </si>
   <si>
     <t>09.10.202635</t>
+  </si>
+  <si>
+    <t>09.10.202636</t>
+  </si>
+  <si>
+    <t>09.10.202637</t>
+  </si>
+  <si>
+    <t>09.10.202638</t>
+  </si>
+  <si>
+    <t>09.10.202639</t>
+  </si>
+  <si>
+    <t>09.10.202640</t>
+  </si>
+  <si>
+    <t>09.10.202641</t>
+  </si>
+  <si>
+    <t>09.10.202642</t>
+  </si>
+  <si>
+    <t>09.10.202643</t>
+  </si>
+  <si>
+    <t>09.10.202644</t>
+  </si>
+  <si>
+    <t>09.10.202645</t>
+  </si>
+  <si>
+    <t>09.10.202646</t>
+  </si>
+  <si>
+    <t>09.10.202647</t>
+  </si>
+  <si>
+    <t>09.10.202648</t>
+  </si>
+  <si>
+    <t>09.10.202649</t>
+  </si>
+  <si>
+    <t>09.10.202650</t>
+  </si>
+  <si>
+    <t>09.10.202651</t>
+  </si>
+  <si>
+    <t>09.10.202652</t>
+  </si>
+  <si>
+    <t>09.10.202653</t>
+  </si>
+  <si>
+    <t>09.10.202654</t>
+  </si>
+  <si>
+    <t>09.10.202655</t>
+  </si>
+  <si>
+    <t>09.10.202656</t>
+  </si>
+  <si>
+    <t>09.10.202657</t>
+  </si>
+  <si>
+    <t>09.10.202658</t>
+  </si>
+  <si>
+    <t>09.10.202659</t>
+  </si>
+  <si>
+    <t>09.10.202660</t>
+  </si>
+  <si>
+    <t>09.10.202661</t>
+  </si>
+  <si>
+    <t>09.10.202662</t>
+  </si>
+  <si>
+    <t>09.10.202663</t>
+  </si>
+  <si>
+    <t>09.10.202664</t>
+  </si>
+  <si>
+    <t>09.10.202665</t>
+  </si>
+  <si>
+    <t>09.10.202666</t>
+  </si>
+  <si>
+    <t>09.10.202667</t>
+  </si>
+  <si>
+    <t>09.10.202668</t>
+  </si>
+  <si>
+    <t>09.10.202669</t>
+  </si>
+  <si>
+    <t>09.10.202670</t>
+  </si>
+  <si>
+    <t>09.10.202671</t>
+  </si>
+  <si>
+    <t>09.10.202672</t>
+  </si>
+  <si>
+    <t>09.10.202673</t>
+  </si>
+  <si>
+    <t>09.10.202674</t>
+  </si>
+  <si>
+    <t>09.10.202675</t>
+  </si>
+  <si>
+    <t>09.10.202676</t>
+  </si>
+  <si>
+    <t>09.10.202677</t>
+  </si>
+  <si>
+    <t>09.10.202678</t>
+  </si>
+  <si>
+    <t>09.10.202679</t>
+  </si>
+  <si>
+    <t>09.10.202680</t>
+  </si>
+  <si>
+    <t>09.10.202681</t>
+  </si>
+  <si>
+    <t>09.10.202682</t>
+  </si>
+  <si>
+    <t>09.10.202683</t>
+  </si>
+  <si>
+    <t>09.10.202684</t>
+  </si>
+  <si>
+    <t>09.10.202685</t>
+  </si>
+  <si>
+    <t>09.10.202686</t>
+  </si>
+  <si>
+    <t>09.10.202687</t>
+  </si>
+  <si>
+    <t>09.10.202688</t>
+  </si>
+  <si>
+    <t>09.10.202689</t>
+  </si>
+  <si>
+    <t>09.10.202690</t>
+  </si>
+  <si>
+    <t>09.10.202691</t>
+  </si>
+  <si>
+    <t>09.10.202692</t>
+  </si>
+  <si>
+    <t>09.10.202693</t>
+  </si>
+  <si>
+    <t>09.10.202694</t>
+  </si>
+  <si>
+    <t>09.10.202695</t>
+  </si>
+  <si>
+    <t>09.10.202696</t>
+  </si>
+  <si>
+    <t>10.10.20261</t>
+  </si>
+  <si>
+    <t>10.10.20262</t>
+  </si>
+  <si>
+    <t>10.10.20263</t>
+  </si>
+  <si>
+    <t>10.10.20264</t>
+  </si>
+  <si>
+    <t>10.10.20265</t>
+  </si>
+  <si>
+    <t>10.10.20266</t>
+  </si>
+  <si>
+    <t>10.10.20267</t>
+  </si>
+  <si>
+    <t>10.10.20268</t>
+  </si>
+  <si>
+    <t>10.10.20269</t>
+  </si>
+  <si>
+    <t>10.10.202610</t>
+  </si>
+  <si>
+    <t>10.10.202611</t>
+  </si>
+  <si>
+    <t>10.10.202612</t>
+  </si>
+  <si>
+    <t>10.10.202613</t>
+  </si>
+  <si>
+    <t>10.10.202614</t>
+  </si>
+  <si>
+    <t>10.10.202615</t>
+  </si>
+  <si>
+    <t>10.10.202616</t>
+  </si>
+  <si>
+    <t>10.10.202617</t>
+  </si>
+  <si>
+    <t>10.10.202618</t>
+  </si>
+  <si>
+    <t>10.10.202619</t>
+  </si>
+  <si>
+    <t>10.10.202620</t>
+  </si>
+  <si>
+    <t>10.10.202621</t>
+  </si>
+  <si>
+    <t>10.10.202622</t>
+  </si>
+  <si>
+    <t>10.10.202623</t>
+  </si>
+  <si>
+    <t>10.10.202624</t>
+  </si>
+  <si>
+    <t>10.10.202625</t>
+  </si>
+  <si>
+    <t>10.10.202626</t>
+  </si>
+  <si>
+    <t>10.10.202627</t>
+  </si>
+  <si>
+    <t>10.10.202628</t>
+  </si>
+  <si>
+    <t>10.10.202629</t>
+  </si>
+  <si>
+    <t>10.10.202630</t>
+  </si>
+  <si>
+    <t>10.10.202631</t>
+  </si>
+  <si>
+    <t>10.10.202632</t>
+  </si>
+  <si>
+    <t>10.10.202633</t>
+  </si>
+  <si>
+    <t>10.10.202634</t>
+  </si>
+  <si>
+    <t>10.10.202635</t>
+  </si>
+  <si>
+    <t>10.10.202636</t>
+  </si>
+  <si>
+    <t>10.10.202637</t>
+  </si>
+  <si>
+    <t>10.10.202638</t>
+  </si>
+  <si>
+    <t>10.10.202639</t>
+  </si>
+  <si>
+    <t>10.10.202640</t>
+  </si>
+  <si>
+    <t>10.10.202641</t>
+  </si>
+  <si>
+    <t>10.10.202642</t>
+  </si>
+  <si>
+    <t>10.10.202643</t>
+  </si>
+  <si>
+    <t>10.10.202644</t>
+  </si>
+  <si>
+    <t>10.10.202645</t>
+  </si>
+  <si>
+    <t>10.10.202646</t>
+  </si>
+  <si>
+    <t>10.10.202647</t>
+  </si>
+  <si>
+    <t>10.10.202648</t>
+  </si>
+  <si>
+    <t>10.10.202649</t>
+  </si>
+  <si>
+    <t>10.10.202650</t>
+  </si>
+  <si>
+    <t>10.10.202651</t>
+  </si>
+  <si>
+    <t>10.10.202652</t>
+  </si>
+  <si>
+    <t>10.10.202653</t>
+  </si>
+  <si>
+    <t>10.10.202654</t>
+  </si>
+  <si>
+    <t>10.10.202655</t>
+  </si>
+  <si>
+    <t>10.10.202656</t>
+  </si>
+  <si>
+    <t>10.10.202657</t>
+  </si>
+  <si>
+    <t>10.10.202658</t>
+  </si>
+  <si>
+    <t>10.10.202659</t>
+  </si>
+  <si>
+    <t>10.10.202660</t>
+  </si>
+  <si>
+    <t>10.10.202661</t>
+  </si>
+  <si>
+    <t>10.10.202662</t>
+  </si>
+  <si>
+    <t>10.10.202663</t>
+  </si>
+  <si>
+    <t>10.10.202664</t>
+  </si>
+  <si>
+    <t>10.10.202665</t>
+  </si>
+  <si>
+    <t>10.10.202666</t>
+  </si>
+  <si>
+    <t>10.10.202667</t>
+  </si>
+  <si>
+    <t>10.10.202668</t>
+  </si>
+  <si>
+    <t>10.10.202669</t>
+  </si>
+  <si>
+    <t>10.10.202670</t>
+  </si>
+  <si>
+    <t>10.10.202671</t>
+  </si>
+  <si>
+    <t>10.10.202672</t>
+  </si>
+  <si>
+    <t>10.10.202673</t>
+  </si>
+  <si>
+    <t>10.10.202674</t>
+  </si>
+  <si>
+    <t>10.10.202675</t>
+  </si>
+  <si>
+    <t>10.10.202676</t>
+  </si>
+  <si>
+    <t>10.10.202677</t>
+  </si>
+  <si>
+    <t>10.10.202678</t>
+  </si>
+  <si>
+    <t>10.10.202679</t>
+  </si>
+  <si>
+    <t>10.10.202680</t>
+  </si>
+  <si>
+    <t>10.10.202681</t>
+  </si>
+  <si>
+    <t>10.10.202682</t>
+  </si>
+  <si>
+    <t>10.10.202683</t>
+  </si>
+  <si>
+    <t>10.10.202684</t>
+  </si>
+  <si>
+    <t>10.10.202685</t>
+  </si>
+  <si>
+    <t>10.10.202686</t>
+  </si>
+  <si>
+    <t>10.10.202687</t>
+  </si>
+  <si>
+    <t>10.10.202688</t>
+  </si>
+  <si>
+    <t>10.10.202689</t>
+  </si>
+  <si>
+    <t>10.10.202690</t>
+  </si>
+  <si>
+    <t>10.10.202691</t>
+  </si>
+  <si>
+    <t>10.10.202692</t>
+  </si>
+  <si>
+    <t>10.10.202693</t>
+  </si>
+  <si>
+    <t>10.10.202694</t>
+  </si>
+  <si>
+    <t>10.10.202695</t>
+  </si>
+  <si>
+    <t>10.10.202696</t>
+  </si>
+  <si>
+    <t>11.10.20261</t>
+  </si>
+  <si>
+    <t>11.10.20262</t>
+  </si>
+  <si>
+    <t>11.10.20263</t>
+  </si>
+  <si>
+    <t>11.10.20264</t>
+  </si>
+  <si>
+    <t>11.10.20265</t>
+  </si>
+  <si>
+    <t>11.10.20266</t>
+  </si>
+  <si>
+    <t>11.10.20267</t>
+  </si>
+  <si>
+    <t>11.10.20268</t>
+  </si>
+  <si>
+    <t>11.10.20269</t>
+  </si>
+  <si>
+    <t>11.10.202610</t>
+  </si>
+  <si>
+    <t>11.10.202611</t>
+  </si>
+  <si>
+    <t>11.10.202612</t>
+  </si>
+  <si>
+    <t>11.10.202613</t>
+  </si>
+  <si>
+    <t>11.10.202614</t>
+  </si>
+  <si>
+    <t>11.10.202615</t>
+  </si>
+  <si>
+    <t>11.10.202616</t>
+  </si>
+  <si>
+    <t>11.10.202617</t>
+  </si>
+  <si>
+    <t>11.10.202618</t>
+  </si>
+  <si>
+    <t>11.10.202619</t>
+  </si>
+  <si>
+    <t>11.10.202620</t>
+  </si>
+  <si>
+    <t>11.10.202621</t>
+  </si>
+  <si>
+    <t>11.10.202622</t>
+  </si>
+  <si>
+    <t>11.10.202623</t>
+  </si>
+  <si>
+    <t>11.10.202624</t>
+  </si>
+  <si>
+    <t>11.10.202625</t>
+  </si>
+  <si>
+    <t>11.10.202626</t>
+  </si>
+  <si>
+    <t>11.10.202627</t>
+  </si>
+  <si>
+    <t>11.10.202628</t>
+  </si>
+  <si>
+    <t>11.10.202629</t>
+  </si>
+  <si>
+    <t>11.10.202630</t>
+  </si>
+  <si>
+    <t>11.10.202631</t>
+  </si>
+  <si>
+    <t>11.10.202632</t>
+  </si>
+  <si>
+    <t>11.10.202633</t>
+  </si>
+  <si>
+    <t>11.10.202634</t>
+  </si>
+  <si>
+    <t>11.10.202635</t>
+  </si>
+  <si>
+    <t>11.10.202636</t>
+  </si>
+  <si>
+    <t>11.10.202637</t>
+  </si>
+  <si>
+    <t>11.10.202638</t>
+  </si>
+  <si>
+    <t>11.10.202639</t>
+  </si>
+  <si>
+    <t>11.10.202640</t>
+  </si>
+  <si>
+    <t>11.10.202641</t>
+  </si>
+  <si>
+    <t>11.10.202642</t>
+  </si>
+  <si>
+    <t>11.10.202643</t>
+  </si>
+  <si>
+    <t>11.10.202644</t>
+  </si>
+  <si>
+    <t>11.10.202645</t>
+  </si>
+  <si>
+    <t>11.10.202646</t>
+  </si>
+  <si>
+    <t>11.10.202647</t>
+  </si>
+  <si>
+    <t>11.10.202648</t>
+  </si>
+  <si>
+    <t>11.10.202649</t>
+  </si>
+  <si>
+    <t>11.10.202650</t>
+  </si>
+  <si>
+    <t>11.10.202651</t>
+  </si>
+  <si>
+    <t>11.10.202652</t>
+  </si>
+  <si>
+    <t>11.10.202653</t>
+  </si>
+  <si>
+    <t>11.10.202654</t>
+  </si>
+  <si>
+    <t>11.10.202655</t>
+  </si>
+  <si>
+    <t>11.10.202656</t>
+  </si>
+  <si>
+    <t>11.10.202657</t>
+  </si>
+  <si>
+    <t>11.10.202658</t>
+  </si>
+  <si>
+    <t>11.10.202659</t>
+  </si>
+  <si>
+    <t>11.10.202660</t>
+  </si>
+  <si>
+    <t>11.10.202661</t>
+  </si>
+  <si>
+    <t>11.10.202662</t>
+  </si>
+  <si>
+    <t>11.10.202663</t>
+  </si>
+  <si>
+    <t>11.10.202664</t>
+  </si>
+  <si>
+    <t>11.10.202665</t>
+  </si>
+  <si>
+    <t>11.10.202666</t>
+  </si>
+  <si>
+    <t>11.10.202667</t>
+  </si>
+  <si>
+    <t>11.10.202668</t>
+  </si>
+  <si>
+    <t>11.10.202669</t>
+  </si>
+  <si>
+    <t>11.10.202670</t>
+  </si>
+  <si>
+    <t>11.10.202671</t>
+  </si>
+  <si>
+    <t>11.10.202672</t>
+  </si>
+  <si>
+    <t>11.10.202673</t>
+  </si>
+  <si>
+    <t>11.10.202674</t>
+  </si>
+  <si>
+    <t>11.10.202675</t>
+  </si>
+  <si>
+    <t>11.10.202676</t>
+  </si>
+  <si>
+    <t>11.10.202677</t>
+  </si>
+  <si>
+    <t>11.10.202678</t>
+  </si>
+  <si>
+    <t>11.10.202679</t>
+  </si>
+  <si>
+    <t>11.10.202680</t>
+  </si>
+  <si>
+    <t>11.10.202681</t>
+  </si>
+  <si>
+    <t>11.10.202682</t>
+  </si>
+  <si>
+    <t>11.10.202683</t>
+  </si>
+  <si>
+    <t>11.10.202684</t>
+  </si>
+  <si>
+    <t>11.10.202685</t>
+  </si>
+  <si>
+    <t>11.10.202686</t>
+  </si>
+  <si>
+    <t>11.10.202687</t>
+  </si>
+  <si>
+    <t>11.10.202688</t>
+  </si>
+  <si>
+    <t>11.10.202689</t>
+  </si>
+  <si>
+    <t>11.10.202690</t>
+  </si>
+  <si>
+    <t>11.10.202691</t>
+  </si>
+  <si>
+    <t>11.10.202692</t>
+  </si>
+  <si>
+    <t>11.10.202693</t>
+  </si>
+  <si>
+    <t>11.10.202694</t>
+  </si>
+  <si>
+    <t>11.10.202695</t>
+  </si>
+  <si>
+    <t>11.10.202696</t>
+  </si>
+  <si>
+    <t>12.10.20261</t>
+  </si>
+  <si>
+    <t>12.10.20262</t>
+  </si>
+  <si>
+    <t>12.10.20263</t>
+  </si>
+  <si>
+    <t>12.10.20264</t>
+  </si>
+  <si>
+    <t>12.10.20265</t>
+  </si>
+  <si>
+    <t>12.10.20266</t>
+  </si>
+  <si>
+    <t>12.10.20267</t>
+  </si>
+  <si>
+    <t>12.10.20268</t>
+  </si>
+  <si>
+    <t>12.10.20269</t>
+  </si>
+  <si>
+    <t>12.10.202610</t>
+  </si>
+  <si>
+    <t>12.10.202611</t>
+  </si>
+  <si>
+    <t>12.10.202612</t>
+  </si>
+  <si>
+    <t>12.10.202613</t>
+  </si>
+  <si>
+    <t>12.10.202614</t>
+  </si>
+  <si>
+    <t>12.10.202615</t>
+  </si>
+  <si>
+    <t>12.10.202616</t>
+  </si>
+  <si>
+    <t>12.10.202617</t>
+  </si>
+  <si>
+    <t>12.10.202618</t>
+  </si>
+  <si>
+    <t>12.10.202619</t>
+  </si>
+  <si>
+    <t>12.10.202620</t>
+  </si>
+  <si>
+    <t>12.10.202621</t>
+  </si>
+  <si>
+    <t>12.10.202622</t>
+  </si>
+  <si>
+    <t>12.10.202623</t>
+  </si>
+  <si>
+    <t>12.10.202624</t>
+  </si>
+  <si>
+    <t>12.10.202625</t>
+  </si>
+  <si>
+    <t>12.10.202626</t>
+  </si>
+  <si>
+    <t>12.10.202627</t>
+  </si>
+  <si>
+    <t>12.10.202628</t>
+  </si>
+  <si>
+    <t>12.10.202629</t>
+  </si>
+  <si>
+    <t>12.10.202630</t>
+  </si>
+  <si>
+    <t>12.10.202631</t>
+  </si>
+  <si>
+    <t>12.10.202632</t>
+  </si>
+  <si>
+    <t>12.10.202633</t>
+  </si>
+  <si>
+    <t>12.10.202634</t>
+  </si>
+  <si>
+    <t>12.10.202635</t>
+  </si>
+  <si>
+    <t>12.10.202636</t>
+  </si>
+  <si>
+    <t>12.10.202637</t>
+  </si>
+  <si>
+    <t>12.10.202638</t>
   </si>
 </sst>
 </file>
@@ -780,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D132"/>
+  <dimension ref="A1:D327"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -799,10 +1384,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B2">
-        <v>5194</v>
+        <v>5147</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -813,10 +1398,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B3">
-        <v>5121</v>
+        <v>5091</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -827,10 +1412,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B4">
-        <v>5131</v>
+        <v>5031</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -841,10 +1426,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B5">
-        <v>5081</v>
+        <v>5025</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -855,10 +1440,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B6">
-        <v>4949</v>
+        <v>5210</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -869,10 +1454,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B7">
-        <v>4935</v>
+        <v>5172</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -883,10 +1468,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B8">
-        <v>4998</v>
+        <v>5187</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -897,10 +1482,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B9">
-        <v>5103</v>
+        <v>5135</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -911,10 +1496,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B10">
-        <v>5118</v>
+        <v>5128</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -925,10 +1510,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B11">
-        <v>5142</v>
+        <v>5129</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -939,10 +1524,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B12">
-        <v>5076</v>
+        <v>5064</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -953,10 +1538,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B13">
-        <v>5052</v>
+        <v>5094</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -967,10 +1552,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B14">
-        <v>5006</v>
+        <v>5135</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -981,10 +1566,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B15">
-        <v>5030</v>
+        <v>5169</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -995,10 +1580,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B16">
-        <v>4996</v>
+        <v>5015</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1009,10 +1594,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B17">
-        <v>5047</v>
+        <v>5121</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1023,10 +1608,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B18">
-        <v>5229</v>
+        <v>5106</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1037,10 +1622,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B19">
-        <v>5151</v>
+        <v>5137</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1051,10 +1636,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B20">
-        <v>5235</v>
+        <v>5164</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1065,7 +1650,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B21">
         <v>5287</v>
@@ -1079,10 +1664,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B22">
-        <v>5488</v>
+        <v>5628</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1093,10 +1678,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B23">
-        <v>5562</v>
+        <v>5765</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1107,10 +1692,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B24">
-        <v>5740</v>
+        <v>5799</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1121,10 +1706,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B25">
-        <v>5884</v>
+        <v>5980</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1135,10 +1720,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B26">
-        <v>6176</v>
+        <v>6174</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1149,10 +1734,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B27">
-        <v>6318</v>
+        <v>6248</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1163,10 +1748,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B28">
-        <v>6352</v>
+        <v>6266</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1177,10 +1762,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B29">
-        <v>6387</v>
+        <v>6334</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1191,10 +1776,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B30">
-        <v>6461</v>
+        <v>6437</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1205,10 +1790,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B31">
-        <v>6469</v>
+        <v>6484</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1219,10 +1804,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B32">
-        <v>6384</v>
+        <v>6401</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1233,10 +1818,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B33">
-        <v>6319</v>
+        <v>6361</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1247,10 +1832,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B34">
-        <v>6073</v>
+        <v>6247</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1261,10 +1846,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B35">
-        <v>5958</v>
+        <v>6207</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1275,10 +1860,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B36">
-        <v>5816</v>
+        <v>6041</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1289,10 +1874,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46303.36458333334</v>
+        <v>46304.36458333334</v>
       </c>
       <c r="B37">
-        <v>5816</v>
+        <v>5993</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1303,10 +1888,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46303.375</v>
+        <v>46304.375</v>
       </c>
       <c r="B38">
-        <v>5421</v>
+        <v>5691</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1317,10 +1902,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46303.38541666666</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="B39">
-        <v>5244</v>
+        <v>5617</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1331,10 +1916,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46303.39583333334</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="B40">
-        <v>5101</v>
+        <v>5535</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1345,10 +1930,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46303.40625</v>
+        <v>46304.40625</v>
       </c>
       <c r="B41">
-        <v>4952</v>
+        <v>5419</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1359,10 +1944,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46303.41666666666</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="B42">
-        <v>4705</v>
+        <v>5198</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1373,10 +1958,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46303.42708333334</v>
+        <v>46304.42708333334</v>
       </c>
       <c r="B43">
-        <v>4588</v>
+        <v>5231</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1387,10 +1972,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46303.4375</v>
+        <v>46304.4375</v>
       </c>
       <c r="B44">
-        <v>4505</v>
+        <v>5126</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1401,10 +1986,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46303.44791666666</v>
+        <v>46304.44791666666</v>
       </c>
       <c r="B45">
-        <v>4397</v>
+        <v>5128</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1415,10 +2000,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46303.45833333334</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="B46">
-        <v>4354</v>
+        <v>4892</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1429,10 +2014,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46303.46875</v>
+        <v>46304.46875</v>
       </c>
       <c r="B47">
-        <v>4427</v>
+        <v>4957</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1443,10 +2028,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46303.47916666666</v>
+        <v>46304.47916666666</v>
       </c>
       <c r="B48">
-        <v>4449</v>
+        <v>4994</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1457,10 +2042,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46303.48958333334</v>
+        <v>46304.48958333334</v>
       </c>
       <c r="B49">
-        <v>4446</v>
+        <v>5082</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1471,10 +2056,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46303.5</v>
+        <v>46304.5</v>
       </c>
       <c r="B50">
-        <v>4551</v>
+        <v>5055</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1485,10 +2070,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46303.51041666666</v>
+        <v>46304.51041666666</v>
       </c>
       <c r="B51">
-        <v>4553</v>
+        <v>5209</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1499,10 +2084,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46303.52083333334</v>
+        <v>46304.52083333334</v>
       </c>
       <c r="B52">
-        <v>4575</v>
+        <v>5200</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1513,10 +2098,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46303.53125</v>
+        <v>46304.53125</v>
       </c>
       <c r="B53">
-        <v>4578</v>
+        <v>5198</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1527,10 +2112,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46303.54166666666</v>
+        <v>46304.54166666666</v>
       </c>
       <c r="B54">
-        <v>4464</v>
+        <v>5149</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1541,10 +2126,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46303.55208333334</v>
+        <v>46304.55208333334</v>
       </c>
       <c r="B55">
-        <v>4456</v>
+        <v>5223</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1555,10 +2140,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46303.5625</v>
+        <v>46304.5625</v>
       </c>
       <c r="B56">
-        <v>4481</v>
+        <v>5179</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1569,10 +2154,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46303.57291666666</v>
+        <v>46304.57291666666</v>
       </c>
       <c r="B57">
-        <v>4493</v>
+        <v>5217</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1583,10 +2168,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46303.58333333334</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="B58">
-        <v>4497</v>
+        <v>5348</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1597,10 +2182,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46303.59375</v>
+        <v>46304.59375</v>
       </c>
       <c r="B59">
-        <v>4590</v>
+        <v>5322</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1611,10 +2196,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46303.60416666666</v>
+        <v>46304.60416666666</v>
       </c>
       <c r="B60">
-        <v>4653</v>
+        <v>5431</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1625,10 +2210,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46303.61458333334</v>
+        <v>46304.61458333334</v>
       </c>
       <c r="B61">
-        <v>4910</v>
+        <v>5450</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1639,10 +2224,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46303.625</v>
+        <v>46304.625</v>
       </c>
       <c r="B62">
-        <v>4926</v>
+        <v>5447</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1653,10 +2238,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46303.63541666666</v>
+        <v>46304.63541666666</v>
       </c>
       <c r="B63">
-        <v>5109</v>
+        <v>5507</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1667,10 +2252,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46303.64583333334</v>
+        <v>46304.64583333334</v>
       </c>
       <c r="B64">
-        <v>5317</v>
+        <v>5643</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1681,10 +2266,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46303.65625</v>
+        <v>46304.65625</v>
       </c>
       <c r="B65">
-        <v>5437</v>
+        <v>5808</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1695,10 +2280,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46303.66666666666</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="B66">
-        <v>5608</v>
+        <v>5964</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1709,10 +2294,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46303.67708333334</v>
+        <v>46304.67708333334</v>
       </c>
       <c r="B67">
-        <v>5801</v>
+        <v>6242</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1723,10 +2308,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46303.6875</v>
+        <v>46304.6875</v>
       </c>
       <c r="B68">
-        <v>6027</v>
+        <v>6229</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1737,10 +2322,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46303.69791666666</v>
+        <v>46304.69791666666</v>
       </c>
       <c r="B69">
-        <v>6180</v>
+        <v>6320</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1751,10 +2336,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46303.70833333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="B70">
-        <v>6287</v>
+        <v>6408</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1765,10 +2350,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46303.71875</v>
+        <v>46304.71875</v>
       </c>
       <c r="B71">
-        <v>6425</v>
+        <v>6496</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1779,10 +2364,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46303.72916666666</v>
+        <v>46304.72916666666</v>
       </c>
       <c r="B72">
-        <v>6474</v>
+        <v>6583</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1793,7 +2378,7 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46303.73958333334</v>
+        <v>46304.73958333334</v>
       </c>
       <c r="B73">
         <v>6650</v>
@@ -1807,10 +2392,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46303.75</v>
+        <v>46304.75</v>
       </c>
       <c r="B74">
-        <v>6779</v>
+        <v>6768</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -1821,10 +2406,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46303.76041666666</v>
+        <v>46304.76041666666</v>
       </c>
       <c r="B75">
-        <v>6948</v>
+        <v>6907</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -1835,10 +2420,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46303.77083333334</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="B76">
-        <v>7045</v>
+        <v>6931</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -1849,10 +2434,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46303.78125</v>
+        <v>46304.78125</v>
       </c>
       <c r="B77">
-        <v>7076</v>
+        <v>6976</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -1863,10 +2448,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46303.79166666666</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="B78">
-        <v>7017</v>
+        <v>6914</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -1877,10 +2462,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46303.80208333334</v>
+        <v>46304.80208333334</v>
       </c>
       <c r="B79">
-        <v>6977</v>
+        <v>6904</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -1891,10 +2476,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46303.8125</v>
+        <v>46304.8125</v>
       </c>
       <c r="B80">
-        <v>6937</v>
+        <v>6819</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -1905,10 +2490,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46303.82291666666</v>
+        <v>46304.82291666666</v>
       </c>
       <c r="B81">
-        <v>6809</v>
+        <v>6755</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -1919,10 +2504,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46303.83333333334</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="B82">
-        <v>6772</v>
+        <v>6650</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -1933,10 +2518,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46303.84375</v>
+        <v>46304.84375</v>
       </c>
       <c r="B83">
-        <v>6664</v>
+        <v>6561</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -1947,10 +2532,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46303.85416666666</v>
+        <v>46304.85416666666</v>
       </c>
       <c r="B84">
-        <v>6492</v>
+        <v>6408</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -1961,10 +2546,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46303.86458333334</v>
+        <v>46304.86458333334</v>
       </c>
       <c r="B85">
-        <v>6346</v>
+        <v>6305</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -1975,10 +2560,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46303.875</v>
+        <v>46304.875</v>
       </c>
       <c r="B86">
-        <v>6144</v>
+        <v>6133</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -1989,10 +2574,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46303.88541666666</v>
+        <v>46304.88541666666</v>
       </c>
       <c r="B87">
-        <v>6014</v>
+        <v>5984</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2003,10 +2588,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46303.89583333334</v>
+        <v>46304.89583333334</v>
       </c>
       <c r="B88">
-        <v>5866</v>
+        <v>5807</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2017,10 +2602,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46303.90625</v>
+        <v>46304.90625</v>
       </c>
       <c r="B89">
-        <v>5719</v>
+        <v>5707</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2031,10 +2616,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46303.91666666666</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="B90">
-        <v>5617</v>
+        <v>5674</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2045,10 +2630,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46303.92708333334</v>
+        <v>46304.92708333334</v>
       </c>
       <c r="B91">
-        <v>5550</v>
+        <v>5599</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2059,10 +2644,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46303.9375</v>
+        <v>46304.9375</v>
       </c>
       <c r="B92">
-        <v>5466</v>
+        <v>5502</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2073,10 +2658,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46303.94791666666</v>
+        <v>46304.94791666666</v>
       </c>
       <c r="B93">
-        <v>5384</v>
+        <v>5448</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2087,10 +2672,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46303.95833333334</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="B94">
-        <v>5335</v>
+        <v>5362</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2101,10 +2686,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46303.96875</v>
+        <v>46304.96875</v>
       </c>
       <c r="B95">
-        <v>5246</v>
+        <v>5242</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2115,10 +2700,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46303.97916666666</v>
+        <v>46304.97916666666</v>
       </c>
       <c r="B96">
-        <v>5152</v>
+        <v>5127</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2129,10 +2714,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46303.98958333334</v>
+        <v>46304.98958333334</v>
       </c>
       <c r="B97">
-        <v>5138</v>
+        <v>5155</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2143,10 +2728,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B98">
-        <v>5147</v>
+        <v>5101</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2157,10 +2742,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46304.01041666666</v>
+        <v>46305.01041666666</v>
       </c>
       <c r="B99">
-        <v>5091</v>
+        <v>5016</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2171,10 +2756,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46304.02083333334</v>
+        <v>46305.02083333334</v>
       </c>
       <c r="B100">
-        <v>5031</v>
+        <v>4974</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2185,10 +2770,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46304.03125</v>
+        <v>46305.03125</v>
       </c>
       <c r="B101">
-        <v>5025</v>
+        <v>4985</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2199,10 +2784,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46304.04166666666</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="B102">
-        <v>5210</v>
+        <v>4939</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2213,10 +2798,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46304.05208333334</v>
+        <v>46305.05208333334</v>
       </c>
       <c r="B103">
-        <v>5172</v>
+        <v>4919</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2227,10 +2812,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46304.0625</v>
+        <v>46305.0625</v>
       </c>
       <c r="B104">
-        <v>5187</v>
+        <v>4980</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2241,10 +2826,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46304.07291666666</v>
+        <v>46305.07291666666</v>
       </c>
       <c r="B105">
-        <v>5135</v>
+        <v>4970</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2255,10 +2840,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46304.08333333334</v>
+        <v>46305.08333333334</v>
       </c>
       <c r="B106">
-        <v>5128</v>
+        <v>4997</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2269,10 +2854,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46304.09375</v>
+        <v>46305.09375</v>
       </c>
       <c r="B107">
-        <v>5129</v>
+        <v>4977</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2283,10 +2868,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46304.10416666666</v>
+        <v>46305.10416666666</v>
       </c>
       <c r="B108">
-        <v>5064</v>
+        <v>5020</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2297,10 +2882,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46304.11458333334</v>
+        <v>46305.11458333334</v>
       </c>
       <c r="B109">
-        <v>5094</v>
+        <v>5099</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2311,10 +2896,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46304.125</v>
+        <v>46305.125</v>
       </c>
       <c r="B110">
-        <v>5135</v>
+        <v>5066</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2325,10 +2910,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46304.13541666666</v>
+        <v>46305.13541666666</v>
       </c>
       <c r="B111">
-        <v>5169</v>
+        <v>5025</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2339,10 +2924,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46304.14583333334</v>
+        <v>46305.14583333334</v>
       </c>
       <c r="B112">
-        <v>5015</v>
+        <v>5044</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2353,10 +2938,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46304.15625</v>
+        <v>46305.15625</v>
       </c>
       <c r="B113">
-        <v>5121</v>
+        <v>5058</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2367,10 +2952,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46304.16666666666</v>
+        <v>46305.16666666666</v>
       </c>
       <c r="B114">
-        <v>5106</v>
+        <v>4978</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2381,10 +2966,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46304.17708333334</v>
+        <v>46305.17708333334</v>
       </c>
       <c r="B115">
-        <v>5137</v>
+        <v>4936</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2395,10 +2980,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46304.1875</v>
+        <v>46305.1875</v>
       </c>
       <c r="B116">
-        <v>5164</v>
+        <v>4937</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2409,10 +2994,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46304.19791666666</v>
+        <v>46305.19791666666</v>
       </c>
       <c r="B117">
-        <v>5287</v>
+        <v>4943</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2423,10 +3008,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46304.20833333334</v>
+        <v>46305.20833333334</v>
       </c>
       <c r="B118">
-        <v>5628</v>
+        <v>4926</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2437,10 +3022,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46304.21875</v>
+        <v>46305.21875</v>
       </c>
       <c r="B119">
-        <v>5765</v>
+        <v>5006</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2451,10 +3036,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46304.22916666666</v>
+        <v>46305.22916666666</v>
       </c>
       <c r="B120">
-        <v>5799</v>
+        <v>5042</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2465,10 +3050,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46304.23958333334</v>
+        <v>46305.23958333334</v>
       </c>
       <c r="B121">
-        <v>5980</v>
+        <v>5156</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2479,10 +3064,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="B122">
-        <v>6174</v>
+        <v>5216</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2493,10 +3078,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46304.26041666666</v>
+        <v>46305.26041666666</v>
       </c>
       <c r="B123">
-        <v>6248</v>
+        <v>5241</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2507,10 +3092,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46304.27083333334</v>
+        <v>46305.27083333334</v>
       </c>
       <c r="B124">
-        <v>6266</v>
+        <v>5288</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2521,10 +3106,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46304.28125</v>
+        <v>46305.28125</v>
       </c>
       <c r="B125">
-        <v>6334</v>
+        <v>5314</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2535,10 +3120,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46304.29166666666</v>
+        <v>46305.29166666666</v>
       </c>
       <c r="B126">
-        <v>6437</v>
+        <v>5377</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2549,10 +3134,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46304.30208333334</v>
+        <v>46305.30208333334</v>
       </c>
       <c r="B127">
-        <v>6484</v>
+        <v>5389</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2563,10 +3148,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46304.3125</v>
+        <v>46305.3125</v>
       </c>
       <c r="B128">
-        <v>6401</v>
+        <v>5341</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2577,10 +3162,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46304.32291666666</v>
+        <v>46305.32291666666</v>
       </c>
       <c r="B129">
-        <v>6361</v>
+        <v>5327</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2591,10 +3176,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46304.33333333334</v>
+        <v>46305.33333333334</v>
       </c>
       <c r="B130">
-        <v>6247</v>
+        <v>5249</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2605,10 +3190,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46304.34375</v>
+        <v>46305.34375</v>
       </c>
       <c r="B131">
-        <v>6207</v>
+        <v>5154</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2619,16 +3204,2746 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46304.35416666666</v>
+        <v>46305.35416666666</v>
       </c>
       <c r="B132">
-        <v>6041</v>
+        <v>5053</v>
       </c>
       <c r="C132">
         <v>35</v>
       </c>
       <c r="D132" t="s">
         <v>134</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="2">
+        <v>46305.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>5011</v>
+      </c>
+      <c r="C133">
+        <v>36</v>
+      </c>
+      <c r="D133" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="2">
+        <v>46305.375</v>
+      </c>
+      <c r="B134">
+        <v>4876</v>
+      </c>
+      <c r="C134">
+        <v>37</v>
+      </c>
+      <c r="D134" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="2">
+        <v>46305.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>4735</v>
+      </c>
+      <c r="C135">
+        <v>38</v>
+      </c>
+      <c r="D135" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="2">
+        <v>46305.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>4632</v>
+      </c>
+      <c r="C136">
+        <v>39</v>
+      </c>
+      <c r="D136" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="2">
+        <v>46305.40625</v>
+      </c>
+      <c r="B137">
+        <v>4539</v>
+      </c>
+      <c r="C137">
+        <v>40</v>
+      </c>
+      <c r="D137" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="2">
+        <v>46305.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>4461</v>
+      </c>
+      <c r="C138">
+        <v>41</v>
+      </c>
+      <c r="D138" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="2">
+        <v>46305.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>4343</v>
+      </c>
+      <c r="C139">
+        <v>42</v>
+      </c>
+      <c r="D139" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="2">
+        <v>46305.4375</v>
+      </c>
+      <c r="B140">
+        <v>4237</v>
+      </c>
+      <c r="C140">
+        <v>43</v>
+      </c>
+      <c r="D140" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="2">
+        <v>46305.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>4177</v>
+      </c>
+      <c r="C141">
+        <v>44</v>
+      </c>
+      <c r="D141" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="2">
+        <v>46305.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>4148</v>
+      </c>
+      <c r="C142">
+        <v>45</v>
+      </c>
+      <c r="D142" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="2">
+        <v>46305.46875</v>
+      </c>
+      <c r="B143">
+        <v>4047</v>
+      </c>
+      <c r="C143">
+        <v>46</v>
+      </c>
+      <c r="D143" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="2">
+        <v>46305.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>4122</v>
+      </c>
+      <c r="C144">
+        <v>47</v>
+      </c>
+      <c r="D144" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="2">
+        <v>46305.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>4095</v>
+      </c>
+      <c r="C145">
+        <v>48</v>
+      </c>
+      <c r="D145" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="2">
+        <v>46305.5</v>
+      </c>
+      <c r="B146">
+        <v>3960</v>
+      </c>
+      <c r="C146">
+        <v>49</v>
+      </c>
+      <c r="D146" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="2">
+        <v>46305.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>3937</v>
+      </c>
+      <c r="C147">
+        <v>50</v>
+      </c>
+      <c r="D147" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="2">
+        <v>46305.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>3990</v>
+      </c>
+      <c r="C148">
+        <v>51</v>
+      </c>
+      <c r="D148" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="2">
+        <v>46305.53125</v>
+      </c>
+      <c r="B149">
+        <v>4079</v>
+      </c>
+      <c r="C149">
+        <v>52</v>
+      </c>
+      <c r="D149" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="2">
+        <v>46305.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>4083</v>
+      </c>
+      <c r="C150">
+        <v>53</v>
+      </c>
+      <c r="D150" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="2">
+        <v>46305.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>4169</v>
+      </c>
+      <c r="C151">
+        <v>54</v>
+      </c>
+      <c r="D151" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="2">
+        <v>46305.5625</v>
+      </c>
+      <c r="B152">
+        <v>4236</v>
+      </c>
+      <c r="C152">
+        <v>55</v>
+      </c>
+      <c r="D152" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="2">
+        <v>46305.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>4257</v>
+      </c>
+      <c r="C153">
+        <v>56</v>
+      </c>
+      <c r="D153" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="2">
+        <v>46305.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>4270</v>
+      </c>
+      <c r="C154">
+        <v>57</v>
+      </c>
+      <c r="D154" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="2">
+        <v>46305.59375</v>
+      </c>
+      <c r="B155">
+        <v>4276</v>
+      </c>
+      <c r="C155">
+        <v>58</v>
+      </c>
+      <c r="D155" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" s="2">
+        <v>46305.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>4379</v>
+      </c>
+      <c r="C156">
+        <v>59</v>
+      </c>
+      <c r="D156" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" s="2">
+        <v>46305.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>4484</v>
+      </c>
+      <c r="C157">
+        <v>60</v>
+      </c>
+      <c r="D157" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" s="2">
+        <v>46305.625</v>
+      </c>
+      <c r="B158">
+        <v>4588</v>
+      </c>
+      <c r="C158">
+        <v>61</v>
+      </c>
+      <c r="D158" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" s="2">
+        <v>46305.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>4737</v>
+      </c>
+      <c r="C159">
+        <v>62</v>
+      </c>
+      <c r="D159" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="2">
+        <v>46305.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>4954</v>
+      </c>
+      <c r="C160">
+        <v>63</v>
+      </c>
+      <c r="D160" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" s="2">
+        <v>46305.65625</v>
+      </c>
+      <c r="B161">
+        <v>5060</v>
+      </c>
+      <c r="C161">
+        <v>64</v>
+      </c>
+      <c r="D161" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" s="2">
+        <v>46305.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>5256</v>
+      </c>
+      <c r="C162">
+        <v>65</v>
+      </c>
+      <c r="D162" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" s="2">
+        <v>46305.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>5397</v>
+      </c>
+      <c r="C163">
+        <v>66</v>
+      </c>
+      <c r="D163" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" s="2">
+        <v>46305.6875</v>
+      </c>
+      <c r="B164">
+        <v>5595</v>
+      </c>
+      <c r="C164">
+        <v>67</v>
+      </c>
+      <c r="D164" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" s="2">
+        <v>46305.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>5702</v>
+      </c>
+      <c r="C165">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" s="2">
+        <v>46305.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>5771</v>
+      </c>
+      <c r="C166">
+        <v>69</v>
+      </c>
+      <c r="D166" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" s="2">
+        <v>46305.71875</v>
+      </c>
+      <c r="B167">
+        <v>5899</v>
+      </c>
+      <c r="C167">
+        <v>70</v>
+      </c>
+      <c r="D167" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" s="2">
+        <v>46305.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>5954</v>
+      </c>
+      <c r="C168">
+        <v>71</v>
+      </c>
+      <c r="D168" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" s="2">
+        <v>46305.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>6076</v>
+      </c>
+      <c r="C169">
+        <v>72</v>
+      </c>
+      <c r="D169" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" s="2">
+        <v>46305.75</v>
+      </c>
+      <c r="B170">
+        <v>6234</v>
+      </c>
+      <c r="C170">
+        <v>73</v>
+      </c>
+      <c r="D170" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" s="2">
+        <v>46305.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>6334</v>
+      </c>
+      <c r="C171">
+        <v>74</v>
+      </c>
+      <c r="D171" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" s="2">
+        <v>46305.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>6400</v>
+      </c>
+      <c r="C172">
+        <v>75</v>
+      </c>
+      <c r="D172" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" s="2">
+        <v>46305.78125</v>
+      </c>
+      <c r="B173">
+        <v>6436</v>
+      </c>
+      <c r="C173">
+        <v>76</v>
+      </c>
+      <c r="D173" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" s="2">
+        <v>46305.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>6415</v>
+      </c>
+      <c r="C174">
+        <v>77</v>
+      </c>
+      <c r="D174" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" s="2">
+        <v>46305.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>6349</v>
+      </c>
+      <c r="C175">
+        <v>78</v>
+      </c>
+      <c r="D175" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" s="2">
+        <v>46305.8125</v>
+      </c>
+      <c r="B176">
+        <v>6274</v>
+      </c>
+      <c r="C176">
+        <v>79</v>
+      </c>
+      <c r="D176" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" s="2">
+        <v>46305.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>6213</v>
+      </c>
+      <c r="C177">
+        <v>80</v>
+      </c>
+      <c r="D177" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" s="2">
+        <v>46305.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>6131</v>
+      </c>
+      <c r="C178">
+        <v>81</v>
+      </c>
+      <c r="D178" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" s="2">
+        <v>46305.84375</v>
+      </c>
+      <c r="B179">
+        <v>6027</v>
+      </c>
+      <c r="C179">
+        <v>82</v>
+      </c>
+      <c r="D179" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" s="2">
+        <v>46305.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>5963</v>
+      </c>
+      <c r="C180">
+        <v>83</v>
+      </c>
+      <c r="D180" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" s="2">
+        <v>46305.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>5859</v>
+      </c>
+      <c r="C181">
+        <v>84</v>
+      </c>
+      <c r="D181" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" s="2">
+        <v>46305.875</v>
+      </c>
+      <c r="B182">
+        <v>5672</v>
+      </c>
+      <c r="C182">
+        <v>85</v>
+      </c>
+      <c r="D182" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" s="2">
+        <v>46305.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>5520</v>
+      </c>
+      <c r="C183">
+        <v>86</v>
+      </c>
+      <c r="D183" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184" s="2">
+        <v>46305.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>5404</v>
+      </c>
+      <c r="C184">
+        <v>87</v>
+      </c>
+      <c r="D184" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="A185" s="2">
+        <v>46305.90625</v>
+      </c>
+      <c r="B185">
+        <v>5302</v>
+      </c>
+      <c r="C185">
+        <v>88</v>
+      </c>
+      <c r="D185" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="A186" s="2">
+        <v>46305.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>5305</v>
+      </c>
+      <c r="C186">
+        <v>89</v>
+      </c>
+      <c r="D186" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="A187" s="2">
+        <v>46305.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>5278</v>
+      </c>
+      <c r="C187">
+        <v>90</v>
+      </c>
+      <c r="D187" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188" s="2">
+        <v>46305.9375</v>
+      </c>
+      <c r="B188">
+        <v>5165</v>
+      </c>
+      <c r="C188">
+        <v>91</v>
+      </c>
+      <c r="D188" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" s="2">
+        <v>46305.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>5122</v>
+      </c>
+      <c r="C189">
+        <v>92</v>
+      </c>
+      <c r="D189" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190" s="2">
+        <v>46305.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>4999</v>
+      </c>
+      <c r="C190">
+        <v>93</v>
+      </c>
+      <c r="D190" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" s="2">
+        <v>46305.96875</v>
+      </c>
+      <c r="B191">
+        <v>4869</v>
+      </c>
+      <c r="C191">
+        <v>94</v>
+      </c>
+      <c r="D191" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192" s="2">
+        <v>46305.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>4906</v>
+      </c>
+      <c r="C192">
+        <v>95</v>
+      </c>
+      <c r="D192" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193" s="2">
+        <v>46305.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>4910</v>
+      </c>
+      <c r="C193">
+        <v>96</v>
+      </c>
+      <c r="D193" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B194">
+        <v>4849</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" s="2">
+        <v>46306.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>4739</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+      <c r="D195" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" s="2">
+        <v>46306.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>4666</v>
+      </c>
+      <c r="C196">
+        <v>3</v>
+      </c>
+      <c r="D196" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" s="2">
+        <v>46306.03125</v>
+      </c>
+      <c r="B197">
+        <v>4686</v>
+      </c>
+      <c r="C197">
+        <v>4</v>
+      </c>
+      <c r="D197" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" s="2">
+        <v>46306.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>4541</v>
+      </c>
+      <c r="C198">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" s="2">
+        <v>46306.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>4541</v>
+      </c>
+      <c r="C199">
+        <v>6</v>
+      </c>
+      <c r="D199" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" s="2">
+        <v>46306.0625</v>
+      </c>
+      <c r="B200">
+        <v>4543</v>
+      </c>
+      <c r="C200">
+        <v>7</v>
+      </c>
+      <c r="D200" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" s="2">
+        <v>46306.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>4463</v>
+      </c>
+      <c r="C201">
+        <v>8</v>
+      </c>
+      <c r="D201" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" s="2">
+        <v>46306.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>4495</v>
+      </c>
+      <c r="C202">
+        <v>9</v>
+      </c>
+      <c r="D202" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" s="2">
+        <v>46306.09375</v>
+      </c>
+      <c r="B203">
+        <v>4449</v>
+      </c>
+      <c r="C203">
+        <v>10</v>
+      </c>
+      <c r="D203" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" s="2">
+        <v>46306.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>4487</v>
+      </c>
+      <c r="C204">
+        <v>11</v>
+      </c>
+      <c r="D204" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" s="2">
+        <v>46306.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>4429</v>
+      </c>
+      <c r="C205">
+        <v>12</v>
+      </c>
+      <c r="D205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" s="2">
+        <v>46306.125</v>
+      </c>
+      <c r="B206">
+        <v>4443</v>
+      </c>
+      <c r="C206">
+        <v>13</v>
+      </c>
+      <c r="D206" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" s="2">
+        <v>46306.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>4497</v>
+      </c>
+      <c r="C207">
+        <v>14</v>
+      </c>
+      <c r="D207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="2">
+        <v>46306.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>4545</v>
+      </c>
+      <c r="C208">
+        <v>15</v>
+      </c>
+      <c r="D208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="2">
+        <v>46306.15625</v>
+      </c>
+      <c r="B209">
+        <v>4674</v>
+      </c>
+      <c r="C209">
+        <v>16</v>
+      </c>
+      <c r="D209" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="2">
+        <v>46306.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>4637</v>
+      </c>
+      <c r="C210">
+        <v>17</v>
+      </c>
+      <c r="D210" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="2">
+        <v>46306.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>4636</v>
+      </c>
+      <c r="C211">
+        <v>18</v>
+      </c>
+      <c r="D211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="2">
+        <v>46306.1875</v>
+      </c>
+      <c r="B212">
+        <v>4670</v>
+      </c>
+      <c r="C212">
+        <v>19</v>
+      </c>
+      <c r="D212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="2">
+        <v>46306.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>4720</v>
+      </c>
+      <c r="C213">
+        <v>20</v>
+      </c>
+      <c r="D213" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="2">
+        <v>46306.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>4672</v>
+      </c>
+      <c r="C214">
+        <v>21</v>
+      </c>
+      <c r="D214" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="2">
+        <v>46306.21875</v>
+      </c>
+      <c r="B215">
+        <v>4645</v>
+      </c>
+      <c r="C215">
+        <v>22</v>
+      </c>
+      <c r="D215" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="2">
+        <v>46306.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>4711</v>
+      </c>
+      <c r="C216">
+        <v>23</v>
+      </c>
+      <c r="D216" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" s="2">
+        <v>46306.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>4714</v>
+      </c>
+      <c r="C217">
+        <v>24</v>
+      </c>
+      <c r="D217" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" s="2">
+        <v>46306.25</v>
+      </c>
+      <c r="B218">
+        <v>4785</v>
+      </c>
+      <c r="C218">
+        <v>25</v>
+      </c>
+      <c r="D218" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" s="2">
+        <v>46306.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>4743</v>
+      </c>
+      <c r="C219">
+        <v>26</v>
+      </c>
+      <c r="D219" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="2">
+        <v>46306.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>4711</v>
+      </c>
+      <c r="C220">
+        <v>27</v>
+      </c>
+      <c r="D220" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" s="2">
+        <v>46306.28125</v>
+      </c>
+      <c r="B221">
+        <v>4762</v>
+      </c>
+      <c r="C221">
+        <v>28</v>
+      </c>
+      <c r="D221" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" s="2">
+        <v>46306.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>4785</v>
+      </c>
+      <c r="C222">
+        <v>29</v>
+      </c>
+      <c r="D222" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" s="2">
+        <v>46306.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>4822</v>
+      </c>
+      <c r="C223">
+        <v>30</v>
+      </c>
+      <c r="D223" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="2">
+        <v>46306.3125</v>
+      </c>
+      <c r="B224">
+        <v>4740</v>
+      </c>
+      <c r="C224">
+        <v>31</v>
+      </c>
+      <c r="D224" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="2">
+        <v>46306.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>4741</v>
+      </c>
+      <c r="C225">
+        <v>32</v>
+      </c>
+      <c r="D225" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="2">
+        <v>46306.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>4662</v>
+      </c>
+      <c r="C226">
+        <v>33</v>
+      </c>
+      <c r="D226" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="2">
+        <v>46306.34375</v>
+      </c>
+      <c r="B227">
+        <v>4591</v>
+      </c>
+      <c r="C227">
+        <v>34</v>
+      </c>
+      <c r="D227" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="2">
+        <v>46306.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>4476</v>
+      </c>
+      <c r="C228">
+        <v>35</v>
+      </c>
+      <c r="D228" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="2">
+        <v>46306.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>4350</v>
+      </c>
+      <c r="C229">
+        <v>36</v>
+      </c>
+      <c r="D229" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="2">
+        <v>46306.375</v>
+      </c>
+      <c r="B230">
+        <v>4314</v>
+      </c>
+      <c r="C230">
+        <v>37</v>
+      </c>
+      <c r="D230" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="2">
+        <v>46306.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>4238</v>
+      </c>
+      <c r="C231">
+        <v>38</v>
+      </c>
+      <c r="D231" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="2">
+        <v>46306.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>4158</v>
+      </c>
+      <c r="C232">
+        <v>39</v>
+      </c>
+      <c r="D232" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" s="2">
+        <v>46306.40625</v>
+      </c>
+      <c r="B233">
+        <v>4097</v>
+      </c>
+      <c r="C233">
+        <v>40</v>
+      </c>
+      <c r="D233" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" s="2">
+        <v>46306.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>4049</v>
+      </c>
+      <c r="C234">
+        <v>41</v>
+      </c>
+      <c r="D234" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="2">
+        <v>46306.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>4056</v>
+      </c>
+      <c r="C235">
+        <v>42</v>
+      </c>
+      <c r="D235" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="2">
+        <v>46306.4375</v>
+      </c>
+      <c r="B236">
+        <v>3989</v>
+      </c>
+      <c r="C236">
+        <v>43</v>
+      </c>
+      <c r="D236" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="2">
+        <v>46306.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>3883</v>
+      </c>
+      <c r="C237">
+        <v>44</v>
+      </c>
+      <c r="D237" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="2">
+        <v>46306.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>3882</v>
+      </c>
+      <c r="C238">
+        <v>45</v>
+      </c>
+      <c r="D238" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="2">
+        <v>46306.46875</v>
+      </c>
+      <c r="B239">
+        <v>3863</v>
+      </c>
+      <c r="C239">
+        <v>46</v>
+      </c>
+      <c r="D239" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="2">
+        <v>46306.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>3745</v>
+      </c>
+      <c r="C240">
+        <v>47</v>
+      </c>
+      <c r="D240" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" s="2">
+        <v>46306.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>3721</v>
+      </c>
+      <c r="C241">
+        <v>48</v>
+      </c>
+      <c r="D241" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" s="2">
+        <v>46306.5</v>
+      </c>
+      <c r="B242">
+        <v>3729</v>
+      </c>
+      <c r="C242">
+        <v>49</v>
+      </c>
+      <c r="D242" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" s="2">
+        <v>46306.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>3823</v>
+      </c>
+      <c r="C243">
+        <v>50</v>
+      </c>
+      <c r="D243" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" s="2">
+        <v>46306.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>3831</v>
+      </c>
+      <c r="C244">
+        <v>51</v>
+      </c>
+      <c r="D244" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="2">
+        <v>46306.53125</v>
+      </c>
+      <c r="B245">
+        <v>3989</v>
+      </c>
+      <c r="C245">
+        <v>52</v>
+      </c>
+      <c r="D245" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="2">
+        <v>46306.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>4207</v>
+      </c>
+      <c r="C246">
+        <v>53</v>
+      </c>
+      <c r="D246" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" s="2">
+        <v>46306.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>4290</v>
+      </c>
+      <c r="C247">
+        <v>54</v>
+      </c>
+      <c r="D247" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="2">
+        <v>46306.5625</v>
+      </c>
+      <c r="B248">
+        <v>4371</v>
+      </c>
+      <c r="C248">
+        <v>55</v>
+      </c>
+      <c r="D248" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" s="2">
+        <v>46306.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>4403</v>
+      </c>
+      <c r="C249">
+        <v>56</v>
+      </c>
+      <c r="D249" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" s="2">
+        <v>46306.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>4405</v>
+      </c>
+      <c r="C250">
+        <v>57</v>
+      </c>
+      <c r="D250" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" s="2">
+        <v>46306.59375</v>
+      </c>
+      <c r="B251">
+        <v>4499</v>
+      </c>
+      <c r="C251">
+        <v>58</v>
+      </c>
+      <c r="D251" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" s="2">
+        <v>46306.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>4546</v>
+      </c>
+      <c r="C252">
+        <v>59</v>
+      </c>
+      <c r="D252" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" s="2">
+        <v>46306.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>4573</v>
+      </c>
+      <c r="C253">
+        <v>60</v>
+      </c>
+      <c r="D253" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" s="2">
+        <v>46306.625</v>
+      </c>
+      <c r="B254">
+        <v>4672</v>
+      </c>
+      <c r="C254">
+        <v>61</v>
+      </c>
+      <c r="D254" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" s="2">
+        <v>46306.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>4806</v>
+      </c>
+      <c r="C255">
+        <v>62</v>
+      </c>
+      <c r="D255" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" s="2">
+        <v>46306.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>4919</v>
+      </c>
+      <c r="C256">
+        <v>63</v>
+      </c>
+      <c r="D256" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="2">
+        <v>46306.65625</v>
+      </c>
+      <c r="B257">
+        <v>5098</v>
+      </c>
+      <c r="C257">
+        <v>64</v>
+      </c>
+      <c r="D257" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" s="2">
+        <v>46306.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>5254</v>
+      </c>
+      <c r="C258">
+        <v>65</v>
+      </c>
+      <c r="D258" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" s="2">
+        <v>46306.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>5398</v>
+      </c>
+      <c r="C259">
+        <v>66</v>
+      </c>
+      <c r="D259" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" s="2">
+        <v>46306.6875</v>
+      </c>
+      <c r="B260">
+        <v>5536</v>
+      </c>
+      <c r="C260">
+        <v>67</v>
+      </c>
+      <c r="D260" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" s="2">
+        <v>46306.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>5577</v>
+      </c>
+      <c r="C261">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" s="2">
+        <v>46306.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>5667</v>
+      </c>
+      <c r="C262">
+        <v>69</v>
+      </c>
+      <c r="D262" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" s="2">
+        <v>46306.71875</v>
+      </c>
+      <c r="B263">
+        <v>5653</v>
+      </c>
+      <c r="C263">
+        <v>70</v>
+      </c>
+      <c r="D263" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" s="2">
+        <v>46306.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>5834</v>
+      </c>
+      <c r="C264">
+        <v>71</v>
+      </c>
+      <c r="D264" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" s="2">
+        <v>46306.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>5967</v>
+      </c>
+      <c r="C265">
+        <v>72</v>
+      </c>
+      <c r="D265" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="2">
+        <v>46306.75</v>
+      </c>
+      <c r="B266">
+        <v>5983</v>
+      </c>
+      <c r="C266">
+        <v>73</v>
+      </c>
+      <c r="D266" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="2">
+        <v>46306.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>6095</v>
+      </c>
+      <c r="C267">
+        <v>74</v>
+      </c>
+      <c r="D267" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="2">
+        <v>46306.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>6115</v>
+      </c>
+      <c r="C268">
+        <v>75</v>
+      </c>
+      <c r="D268" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="2">
+        <v>46306.78125</v>
+      </c>
+      <c r="B269">
+        <v>6140</v>
+      </c>
+      <c r="C269">
+        <v>76</v>
+      </c>
+      <c r="D269" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="2">
+        <v>46306.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>6094</v>
+      </c>
+      <c r="C270">
+        <v>77</v>
+      </c>
+      <c r="D270" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="2">
+        <v>46306.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>6032</v>
+      </c>
+      <c r="C271">
+        <v>78</v>
+      </c>
+      <c r="D271" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="2">
+        <v>46306.8125</v>
+      </c>
+      <c r="B272">
+        <v>5988</v>
+      </c>
+      <c r="C272">
+        <v>79</v>
+      </c>
+      <c r="D272" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="2">
+        <v>46306.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>5975</v>
+      </c>
+      <c r="C273">
+        <v>80</v>
+      </c>
+      <c r="D273" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="2">
+        <v>46306.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>5877</v>
+      </c>
+      <c r="C274">
+        <v>81</v>
+      </c>
+      <c r="D274" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="2">
+        <v>46306.84375</v>
+      </c>
+      <c r="B275">
+        <v>5798</v>
+      </c>
+      <c r="C275">
+        <v>82</v>
+      </c>
+      <c r="D275" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="2">
+        <v>46306.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>5690</v>
+      </c>
+      <c r="C276">
+        <v>83</v>
+      </c>
+      <c r="D276" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="2">
+        <v>46306.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>5582</v>
+      </c>
+      <c r="C277">
+        <v>84</v>
+      </c>
+      <c r="D277" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="2">
+        <v>46306.875</v>
+      </c>
+      <c r="B278">
+        <v>5397</v>
+      </c>
+      <c r="C278">
+        <v>85</v>
+      </c>
+      <c r="D278" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" s="2">
+        <v>46306.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>5269</v>
+      </c>
+      <c r="C279">
+        <v>86</v>
+      </c>
+      <c r="D279" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" s="2">
+        <v>46306.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>5206</v>
+      </c>
+      <c r="C280">
+        <v>87</v>
+      </c>
+      <c r="D280" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="2">
+        <v>46306.90625</v>
+      </c>
+      <c r="B281">
+        <v>5144</v>
+      </c>
+      <c r="C281">
+        <v>88</v>
+      </c>
+      <c r="D281" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" s="2">
+        <v>46306.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>5044</v>
+      </c>
+      <c r="C282">
+        <v>89</v>
+      </c>
+      <c r="D282" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="2">
+        <v>46306.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>4956</v>
+      </c>
+      <c r="C283">
+        <v>90</v>
+      </c>
+      <c r="D283" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" s="2">
+        <v>46306.9375</v>
+      </c>
+      <c r="B284">
+        <v>4842</v>
+      </c>
+      <c r="C284">
+        <v>91</v>
+      </c>
+      <c r="D284" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" s="2">
+        <v>46306.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>4762</v>
+      </c>
+      <c r="C285">
+        <v>92</v>
+      </c>
+      <c r="D285" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" s="2">
+        <v>46306.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>4759</v>
+      </c>
+      <c r="C286">
+        <v>93</v>
+      </c>
+      <c r="D286" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" s="2">
+        <v>46306.96875</v>
+      </c>
+      <c r="B287">
+        <v>4685</v>
+      </c>
+      <c r="C287">
+        <v>94</v>
+      </c>
+      <c r="D287" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" s="2">
+        <v>46306.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>4644</v>
+      </c>
+      <c r="C288">
+        <v>95</v>
+      </c>
+      <c r="D288" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" s="2">
+        <v>46306.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>4576</v>
+      </c>
+      <c r="C289">
+        <v>96</v>
+      </c>
+      <c r="D289" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B290">
+        <v>4523</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="D290" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" s="2">
+        <v>46307.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>4514</v>
+      </c>
+      <c r="C291">
+        <v>2</v>
+      </c>
+      <c r="D291" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="2">
+        <v>46307.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>4502</v>
+      </c>
+      <c r="C292">
+        <v>3</v>
+      </c>
+      <c r="D292" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" s="2">
+        <v>46307.03125</v>
+      </c>
+      <c r="B293">
+        <v>4493</v>
+      </c>
+      <c r="C293">
+        <v>4</v>
+      </c>
+      <c r="D293" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="2">
+        <v>46307.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>4512</v>
+      </c>
+      <c r="C294">
+        <v>5</v>
+      </c>
+      <c r="D294" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" s="2">
+        <v>46307.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>4612</v>
+      </c>
+      <c r="C295">
+        <v>6</v>
+      </c>
+      <c r="D295" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" s="2">
+        <v>46307.0625</v>
+      </c>
+      <c r="B296">
+        <v>4655</v>
+      </c>
+      <c r="C296">
+        <v>7</v>
+      </c>
+      <c r="D296" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" s="2">
+        <v>46307.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>4723</v>
+      </c>
+      <c r="C297">
+        <v>8</v>
+      </c>
+      <c r="D297" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" s="2">
+        <v>46307.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>4685</v>
+      </c>
+      <c r="C298">
+        <v>9</v>
+      </c>
+      <c r="D298" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" s="2">
+        <v>46307.09375</v>
+      </c>
+      <c r="B299">
+        <v>4792</v>
+      </c>
+      <c r="C299">
+        <v>10</v>
+      </c>
+      <c r="D299" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" s="2">
+        <v>46307.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>4718</v>
+      </c>
+      <c r="C300">
+        <v>11</v>
+      </c>
+      <c r="D300" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" s="2">
+        <v>46307.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>4746</v>
+      </c>
+      <c r="C301">
+        <v>12</v>
+      </c>
+      <c r="D301" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" s="2">
+        <v>46307.125</v>
+      </c>
+      <c r="B302">
+        <v>4702</v>
+      </c>
+      <c r="C302">
+        <v>13</v>
+      </c>
+      <c r="D302" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" s="2">
+        <v>46307.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>4759</v>
+      </c>
+      <c r="C303">
+        <v>14</v>
+      </c>
+      <c r="D303" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" s="2">
+        <v>46307.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>4769</v>
+      </c>
+      <c r="C304">
+        <v>15</v>
+      </c>
+      <c r="D304" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" s="2">
+        <v>46307.15625</v>
+      </c>
+      <c r="B305">
+        <v>4802</v>
+      </c>
+      <c r="C305">
+        <v>16</v>
+      </c>
+      <c r="D305" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306" s="2">
+        <v>46307.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>4829</v>
+      </c>
+      <c r="C306">
+        <v>17</v>
+      </c>
+      <c r="D306" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307" s="2">
+        <v>46307.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>4781</v>
+      </c>
+      <c r="C307">
+        <v>18</v>
+      </c>
+      <c r="D307" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" s="2">
+        <v>46307.1875</v>
+      </c>
+      <c r="B308">
+        <v>4771</v>
+      </c>
+      <c r="C308">
+        <v>19</v>
+      </c>
+      <c r="D308" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309" s="2">
+        <v>46307.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>4828</v>
+      </c>
+      <c r="C309">
+        <v>20</v>
+      </c>
+      <c r="D309" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" s="2">
+        <v>46307.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>5041</v>
+      </c>
+      <c r="C310">
+        <v>21</v>
+      </c>
+      <c r="D310" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" s="2">
+        <v>46307.21875</v>
+      </c>
+      <c r="B311">
+        <v>5233</v>
+      </c>
+      <c r="C311">
+        <v>22</v>
+      </c>
+      <c r="D311" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" s="2">
+        <v>46307.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>5395</v>
+      </c>
+      <c r="C312">
+        <v>23</v>
+      </c>
+      <c r="D312" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" s="2">
+        <v>46307.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>5629</v>
+      </c>
+      <c r="C313">
+        <v>24</v>
+      </c>
+      <c r="D313" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314" s="2">
+        <v>46307.25</v>
+      </c>
+      <c r="B314">
+        <v>5899</v>
+      </c>
+      <c r="C314">
+        <v>25</v>
+      </c>
+      <c r="D314" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315" s="2">
+        <v>46307.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>6046</v>
+      </c>
+      <c r="C315">
+        <v>26</v>
+      </c>
+      <c r="D315" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316" s="2">
+        <v>46307.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>6227</v>
+      </c>
+      <c r="C316">
+        <v>27</v>
+      </c>
+      <c r="D316" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" s="2">
+        <v>46307.28125</v>
+      </c>
+      <c r="B317">
+        <v>6221</v>
+      </c>
+      <c r="C317">
+        <v>28</v>
+      </c>
+      <c r="D317" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" s="2">
+        <v>46307.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>6427</v>
+      </c>
+      <c r="C318">
+        <v>29</v>
+      </c>
+      <c r="D318" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" s="2">
+        <v>46307.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>6536</v>
+      </c>
+      <c r="C319">
+        <v>30</v>
+      </c>
+      <c r="D319" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" s="2">
+        <v>46307.3125</v>
+      </c>
+      <c r="B320">
+        <v>6605</v>
+      </c>
+      <c r="C320">
+        <v>31</v>
+      </c>
+      <c r="D320" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" s="2">
+        <v>46307.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>6626</v>
+      </c>
+      <c r="C321">
+        <v>32</v>
+      </c>
+      <c r="D321" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" s="2">
+        <v>46307.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>6691</v>
+      </c>
+      <c r="C322">
+        <v>33</v>
+      </c>
+      <c r="D322" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" s="2">
+        <v>46307.34375</v>
+      </c>
+      <c r="B323">
+        <v>6729</v>
+      </c>
+      <c r="C323">
+        <v>34</v>
+      </c>
+      <c r="D323" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" s="2">
+        <v>46307.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>6771</v>
+      </c>
+      <c r="C324">
+        <v>35</v>
+      </c>
+      <c r="D324" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325" s="2">
+        <v>46307.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>6807</v>
+      </c>
+      <c r="C325">
+        <v>36</v>
+      </c>
+      <c r="D325" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" s="2">
+        <v>46307.375</v>
+      </c>
+      <c r="B326">
+        <v>6634</v>
+      </c>
+      <c r="C326">
+        <v>37</v>
+      </c>
+      <c r="D326" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327" s="2">
+        <v>46307.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>6627</v>
+      </c>
+      <c r="C327">
+        <v>38</v>
+      </c>
+      <c r="D327" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>12.10.20261</t>
-  </si>
-  <si>
-    <t>12.10.20262</t>
-  </si>
-  <si>
-    <t>12.10.20263</t>
-  </si>
-  <si>
-    <t>12.10.20264</t>
-  </si>
-  <si>
-    <t>12.10.20265</t>
-  </si>
-  <si>
-    <t>12.10.20266</t>
-  </si>
-  <si>
-    <t>12.10.20267</t>
-  </si>
-  <si>
-    <t>12.10.20268</t>
-  </si>
-  <si>
-    <t>12.10.20269</t>
-  </si>
-  <si>
-    <t>12.10.202610</t>
-  </si>
-  <si>
-    <t>12.10.202611</t>
-  </si>
-  <si>
-    <t>12.10.202612</t>
-  </si>
-  <si>
-    <t>12.10.202613</t>
-  </si>
-  <si>
-    <t>12.10.202614</t>
-  </si>
-  <si>
-    <t>12.10.202615</t>
-  </si>
-  <si>
-    <t>12.10.202616</t>
-  </si>
-  <si>
-    <t>12.10.202617</t>
-  </si>
-  <si>
-    <t>12.10.202618</t>
-  </si>
-  <si>
-    <t>12.10.202619</t>
-  </si>
-  <si>
-    <t>12.10.202620</t>
-  </si>
-  <si>
-    <t>12.10.202621</t>
-  </si>
-  <si>
-    <t>12.10.202622</t>
-  </si>
-  <si>
-    <t>12.10.202623</t>
-  </si>
-  <si>
-    <t>12.10.202624</t>
-  </si>
-  <si>
-    <t>12.10.202625</t>
-  </si>
-  <si>
-    <t>12.10.202626</t>
-  </si>
-  <si>
-    <t>12.10.202627</t>
-  </si>
-  <si>
-    <t>12.10.202628</t>
-  </si>
-  <si>
-    <t>12.10.202629</t>
-  </si>
-  <si>
-    <t>12.10.202630</t>
-  </si>
-  <si>
-    <t>12.10.202631</t>
-  </si>
-  <si>
-    <t>12.10.202632</t>
-  </si>
-  <si>
-    <t>12.10.202633</t>
-  </si>
-  <si>
-    <t>12.10.202634</t>
-  </si>
-  <si>
-    <t>12.10.202635</t>
-  </si>
-  <si>
-    <t>12.10.202636</t>
-  </si>
-  <si>
-    <t>12.10.202637</t>
-  </si>
-  <si>
-    <t>12.10.202638</t>
-  </si>
-  <si>
-    <t>12.10.202639</t>
-  </si>
-  <si>
-    <t>12.10.202640</t>
-  </si>
-  <si>
-    <t>12.10.202641</t>
-  </si>
-  <si>
-    <t>12.10.202642</t>
-  </si>
-  <si>
-    <t>12.10.202643</t>
-  </si>
-  <si>
-    <t>12.10.202644</t>
-  </si>
-  <si>
-    <t>12.10.202645</t>
-  </si>
-  <si>
-    <t>12.10.202646</t>
-  </si>
-  <si>
-    <t>12.10.202647</t>
-  </si>
-  <si>
-    <t>12.10.202648</t>
-  </si>
-  <si>
-    <t>12.10.202649</t>
-  </si>
-  <si>
-    <t>12.10.202650</t>
-  </si>
-  <si>
-    <t>12.10.202651</t>
-  </si>
-  <si>
-    <t>12.10.202652</t>
-  </si>
-  <si>
-    <t>12.10.202653</t>
-  </si>
-  <si>
-    <t>12.10.202654</t>
-  </si>
-  <si>
-    <t>12.10.202655</t>
-  </si>
-  <si>
-    <t>12.10.202656</t>
-  </si>
-  <si>
-    <t>12.10.202657</t>
-  </si>
-  <si>
-    <t>12.10.202658</t>
-  </si>
-  <si>
-    <t>12.10.202659</t>
-  </si>
-  <si>
-    <t>12.10.202660</t>
-  </si>
-  <si>
-    <t>12.10.202661</t>
-  </si>
-  <si>
-    <t>12.10.202662</t>
-  </si>
-  <si>
-    <t>12.10.202663</t>
-  </si>
-  <si>
-    <t>12.10.202664</t>
-  </si>
-  <si>
-    <t>12.10.202665</t>
-  </si>
-  <si>
-    <t>12.10.202666</t>
-  </si>
-  <si>
-    <t>12.10.202667</t>
-  </si>
-  <si>
-    <t>12.10.202668</t>
-  </si>
-  <si>
-    <t>12.10.202669</t>
-  </si>
-  <si>
-    <t>12.10.202670</t>
-  </si>
-  <si>
-    <t>12.10.202671</t>
-  </si>
-  <si>
-    <t>12.10.202672</t>
-  </si>
-  <si>
-    <t>12.10.202673</t>
-  </si>
-  <si>
-    <t>12.10.202674</t>
-  </si>
-  <si>
-    <t>12.10.202675</t>
-  </si>
-  <si>
-    <t>12.10.202676</t>
-  </si>
-  <si>
-    <t>12.10.202677</t>
-  </si>
-  <si>
-    <t>12.10.202678</t>
-  </si>
-  <si>
-    <t>12.10.202679</t>
-  </si>
-  <si>
-    <t>12.10.202680</t>
-  </si>
-  <si>
-    <t>12.10.202681</t>
-  </si>
-  <si>
-    <t>12.10.202682</t>
-  </si>
-  <si>
-    <t>12.10.202683</t>
-  </si>
-  <si>
-    <t>12.10.202684</t>
-  </si>
-  <si>
-    <t>12.10.202685</t>
-  </si>
-  <si>
-    <t>12.10.202686</t>
-  </si>
-  <si>
-    <t>12.10.202687</t>
-  </si>
-  <si>
-    <t>12.10.202688</t>
-  </si>
-  <si>
-    <t>12.10.202689</t>
-  </si>
-  <si>
-    <t>12.10.202690</t>
-  </si>
-  <si>
-    <t>12.10.202691</t>
-  </si>
-  <si>
-    <t>12.10.202692</t>
-  </si>
-  <si>
-    <t>12.10.202693</t>
-  </si>
-  <si>
-    <t>12.10.202694</t>
-  </si>
-  <si>
-    <t>12.10.202695</t>
-  </si>
-  <si>
-    <t>12.10.202696</t>
-  </si>
-  <si>
     <t>13.10.20261</t>
   </si>
   <si>
@@ -476,6 +188,306 @@
   </si>
   <si>
     <t>13.10.202654</t>
+  </si>
+  <si>
+    <t>13.10.202655</t>
+  </si>
+  <si>
+    <t>13.10.202656</t>
+  </si>
+  <si>
+    <t>13.10.202657</t>
+  </si>
+  <si>
+    <t>13.10.202658</t>
+  </si>
+  <si>
+    <t>13.10.202659</t>
+  </si>
+  <si>
+    <t>13.10.202660</t>
+  </si>
+  <si>
+    <t>13.10.202661</t>
+  </si>
+  <si>
+    <t>13.10.202662</t>
+  </si>
+  <si>
+    <t>13.10.202663</t>
+  </si>
+  <si>
+    <t>13.10.202664</t>
+  </si>
+  <si>
+    <t>13.10.202665</t>
+  </si>
+  <si>
+    <t>13.10.202666</t>
+  </si>
+  <si>
+    <t>13.10.202667</t>
+  </si>
+  <si>
+    <t>13.10.202668</t>
+  </si>
+  <si>
+    <t>13.10.202669</t>
+  </si>
+  <si>
+    <t>13.10.202670</t>
+  </si>
+  <si>
+    <t>13.10.202671</t>
+  </si>
+  <si>
+    <t>13.10.202672</t>
+  </si>
+  <si>
+    <t>13.10.202673</t>
+  </si>
+  <si>
+    <t>13.10.202674</t>
+  </si>
+  <si>
+    <t>13.10.202675</t>
+  </si>
+  <si>
+    <t>13.10.202676</t>
+  </si>
+  <si>
+    <t>13.10.202677</t>
+  </si>
+  <si>
+    <t>13.10.202678</t>
+  </si>
+  <si>
+    <t>13.10.202679</t>
+  </si>
+  <si>
+    <t>13.10.202680</t>
+  </si>
+  <si>
+    <t>13.10.202681</t>
+  </si>
+  <si>
+    <t>13.10.202682</t>
+  </si>
+  <si>
+    <t>13.10.202683</t>
+  </si>
+  <si>
+    <t>13.10.202684</t>
+  </si>
+  <si>
+    <t>13.10.202685</t>
+  </si>
+  <si>
+    <t>13.10.202686</t>
+  </si>
+  <si>
+    <t>13.10.202687</t>
+  </si>
+  <si>
+    <t>13.10.202688</t>
+  </si>
+  <si>
+    <t>13.10.202689</t>
+  </si>
+  <si>
+    <t>13.10.202690</t>
+  </si>
+  <si>
+    <t>13.10.202691</t>
+  </si>
+  <si>
+    <t>13.10.202692</t>
+  </si>
+  <si>
+    <t>13.10.202693</t>
+  </si>
+  <si>
+    <t>13.10.202694</t>
+  </si>
+  <si>
+    <t>13.10.202695</t>
+  </si>
+  <si>
+    <t>13.10.202696</t>
+  </si>
+  <si>
+    <t>14.10.20261</t>
+  </si>
+  <si>
+    <t>14.10.20262</t>
+  </si>
+  <si>
+    <t>14.10.20263</t>
+  </si>
+  <si>
+    <t>14.10.20264</t>
+  </si>
+  <si>
+    <t>14.10.20265</t>
+  </si>
+  <si>
+    <t>14.10.20266</t>
+  </si>
+  <si>
+    <t>14.10.20267</t>
+  </si>
+  <si>
+    <t>14.10.20268</t>
+  </si>
+  <si>
+    <t>14.10.20269</t>
+  </si>
+  <si>
+    <t>14.10.202610</t>
+  </si>
+  <si>
+    <t>14.10.202611</t>
+  </si>
+  <si>
+    <t>14.10.202612</t>
+  </si>
+  <si>
+    <t>14.10.202613</t>
+  </si>
+  <si>
+    <t>14.10.202614</t>
+  </si>
+  <si>
+    <t>14.10.202615</t>
+  </si>
+  <si>
+    <t>14.10.202616</t>
+  </si>
+  <si>
+    <t>14.10.202617</t>
+  </si>
+  <si>
+    <t>14.10.202618</t>
+  </si>
+  <si>
+    <t>14.10.202619</t>
+  </si>
+  <si>
+    <t>14.10.202620</t>
+  </si>
+  <si>
+    <t>14.10.202621</t>
+  </si>
+  <si>
+    <t>14.10.202622</t>
+  </si>
+  <si>
+    <t>14.10.202623</t>
+  </si>
+  <si>
+    <t>14.10.202624</t>
+  </si>
+  <si>
+    <t>14.10.202625</t>
+  </si>
+  <si>
+    <t>14.10.202626</t>
+  </si>
+  <si>
+    <t>14.10.202627</t>
+  </si>
+  <si>
+    <t>14.10.202628</t>
+  </si>
+  <si>
+    <t>14.10.202629</t>
+  </si>
+  <si>
+    <t>14.10.202630</t>
+  </si>
+  <si>
+    <t>14.10.202631</t>
+  </si>
+  <si>
+    <t>14.10.202632</t>
+  </si>
+  <si>
+    <t>14.10.202633</t>
+  </si>
+  <si>
+    <t>14.10.202634</t>
+  </si>
+  <si>
+    <t>14.10.202635</t>
+  </si>
+  <si>
+    <t>14.10.202636</t>
+  </si>
+  <si>
+    <t>14.10.202637</t>
+  </si>
+  <si>
+    <t>14.10.202638</t>
+  </si>
+  <si>
+    <t>14.10.202639</t>
+  </si>
+  <si>
+    <t>14.10.202640</t>
+  </si>
+  <si>
+    <t>14.10.202641</t>
+  </si>
+  <si>
+    <t>14.10.202642</t>
+  </si>
+  <si>
+    <t>14.10.202643</t>
+  </si>
+  <si>
+    <t>14.10.202644</t>
+  </si>
+  <si>
+    <t>14.10.202645</t>
+  </si>
+  <si>
+    <t>14.10.202646</t>
+  </si>
+  <si>
+    <t>14.10.202647</t>
+  </si>
+  <si>
+    <t>14.10.202648</t>
+  </si>
+  <si>
+    <t>14.10.202649</t>
+  </si>
+  <si>
+    <t>14.10.202650</t>
+  </si>
+  <si>
+    <t>14.10.202651</t>
+  </si>
+  <si>
+    <t>14.10.202652</t>
+  </si>
+  <si>
+    <t>14.10.202653</t>
+  </si>
+  <si>
+    <t>14.10.202654</t>
+  </si>
+  <si>
+    <t>14.10.202655</t>
+  </si>
+  <si>
+    <t>14.10.202656</t>
+  </si>
+  <si>
+    <t>14.10.202657</t>
+  </si>
+  <si>
+    <t>14.10.202658</t>
   </si>
 </sst>
 </file>
@@ -837,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -856,10 +868,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2">
-        <v>4523</v>
+        <v>5077</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -870,10 +882,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46307.01041666666</v>
+        <v>46308.01041666666</v>
       </c>
       <c r="B3">
-        <v>4514</v>
+        <v>5009</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -884,10 +896,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46307.02083333334</v>
+        <v>46308.02083333334</v>
       </c>
       <c r="B4">
-        <v>4502</v>
+        <v>5041</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -898,10 +910,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46307.03125</v>
+        <v>46308.03125</v>
       </c>
       <c r="B5">
-        <v>4493</v>
+        <v>5017</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -912,10 +924,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46307.04166666666</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="B6">
-        <v>4512</v>
+        <v>5098</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -926,10 +938,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46307.05208333334</v>
+        <v>46308.05208333334</v>
       </c>
       <c r="B7">
-        <v>4612</v>
+        <v>5036</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -940,10 +952,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46307.0625</v>
+        <v>46308.0625</v>
       </c>
       <c r="B8">
-        <v>4655</v>
+        <v>5112</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -954,10 +966,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46307.07291666666</v>
+        <v>46308.07291666666</v>
       </c>
       <c r="B9">
-        <v>4723</v>
+        <v>5094</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -968,10 +980,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46307.08333333334</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="B10">
-        <v>4685</v>
+        <v>5094</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -982,10 +994,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46307.09375</v>
+        <v>46308.09375</v>
       </c>
       <c r="B11">
-        <v>4792</v>
+        <v>5206</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -996,10 +1008,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46307.10416666666</v>
+        <v>46308.10416666666</v>
       </c>
       <c r="B12">
-        <v>4718</v>
+        <v>5194</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1010,10 +1022,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46307.11458333334</v>
+        <v>46308.11458333334</v>
       </c>
       <c r="B13">
-        <v>4746</v>
+        <v>5152</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1024,10 +1036,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46307.125</v>
+        <v>46308.125</v>
       </c>
       <c r="B14">
-        <v>4702</v>
+        <v>5235</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1038,10 +1050,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46307.13541666666</v>
+        <v>46308.13541666666</v>
       </c>
       <c r="B15">
-        <v>4759</v>
+        <v>5234</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1052,10 +1064,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46307.14583333334</v>
+        <v>46308.14583333334</v>
       </c>
       <c r="B16">
-        <v>4769</v>
+        <v>5184</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1066,10 +1078,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46307.15625</v>
+        <v>46308.15625</v>
       </c>
       <c r="B17">
-        <v>4802</v>
+        <v>5106</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1080,10 +1092,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46307.16666666666</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="B18">
-        <v>4829</v>
+        <v>5028</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1094,10 +1106,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46307.17708333334</v>
+        <v>46308.17708333334</v>
       </c>
       <c r="B19">
-        <v>4781</v>
+        <v>5104</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1108,10 +1120,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46307.1875</v>
+        <v>46308.1875</v>
       </c>
       <c r="B20">
-        <v>4771</v>
+        <v>5121</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1122,10 +1134,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46307.19791666666</v>
+        <v>46308.19791666666</v>
       </c>
       <c r="B21">
-        <v>4828</v>
+        <v>5222</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1136,10 +1148,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46307.20833333334</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="B22">
-        <v>5041</v>
+        <v>5460</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1150,10 +1162,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46307.21875</v>
+        <v>46308.21875</v>
       </c>
       <c r="B23">
-        <v>5233</v>
+        <v>5655</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1164,10 +1176,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46307.22916666666</v>
+        <v>46308.22916666666</v>
       </c>
       <c r="B24">
-        <v>5395</v>
+        <v>5850</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1178,10 +1190,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46307.23958333334</v>
+        <v>46308.23958333334</v>
       </c>
       <c r="B25">
-        <v>5629</v>
+        <v>5950</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1192,10 +1204,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="B26">
-        <v>5899</v>
+        <v>6298</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1206,10 +1218,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46307.26041666666</v>
+        <v>46308.26041666666</v>
       </c>
       <c r="B27">
-        <v>6046</v>
+        <v>6393</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1220,10 +1232,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46307.27083333334</v>
+        <v>46308.27083333334</v>
       </c>
       <c r="B28">
-        <v>6227</v>
+        <v>6500</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1234,10 +1246,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46307.28125</v>
+        <v>46308.28125</v>
       </c>
       <c r="B29">
-        <v>6221</v>
+        <v>6550</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1248,10 +1260,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46307.29166666666</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="B30">
-        <v>6427</v>
+        <v>6676</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1262,10 +1274,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46307.30208333334</v>
+        <v>46308.30208333334</v>
       </c>
       <c r="B31">
-        <v>6536</v>
+        <v>6782</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1276,10 +1288,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46307.3125</v>
+        <v>46308.3125</v>
       </c>
       <c r="B32">
-        <v>6605</v>
+        <v>6833</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1290,10 +1302,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46307.32291666666</v>
+        <v>46308.32291666666</v>
       </c>
       <c r="B33">
-        <v>6626</v>
+        <v>6782</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1304,10 +1316,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46307.33333333334</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="B34">
-        <v>6691</v>
+        <v>6763</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1318,10 +1330,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46307.34375</v>
+        <v>46308.34375</v>
       </c>
       <c r="B35">
-        <v>6729</v>
+        <v>6745</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1332,10 +1344,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46307.35416666666</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="B36">
-        <v>6771</v>
+        <v>6664</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1346,10 +1358,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46307.36458333334</v>
+        <v>46308.36458333334</v>
       </c>
       <c r="B37">
-        <v>6807</v>
+        <v>6590</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1360,10 +1372,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46307.375</v>
+        <v>46308.375</v>
       </c>
       <c r="B38">
-        <v>6634</v>
+        <v>6524</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1374,10 +1386,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46307.38541666666</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="B39">
-        <v>6627</v>
+        <v>6505</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1388,10 +1400,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46307.39583333334</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="B40">
-        <v>6629</v>
+        <v>6508</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1402,10 +1414,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46307.40625</v>
+        <v>46308.40625</v>
       </c>
       <c r="B41">
-        <v>6585</v>
+        <v>6439</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1416,10 +1428,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46307.41666666666</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="B42">
-        <v>6413</v>
+        <v>6229</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1430,10 +1442,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46307.42708333334</v>
+        <v>46308.42708333334</v>
       </c>
       <c r="B43">
-        <v>6401</v>
+        <v>6155</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1444,10 +1456,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46307.4375</v>
+        <v>46308.4375</v>
       </c>
       <c r="B44">
-        <v>6389</v>
+        <v>6094</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1458,10 +1470,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46307.44791666666</v>
+        <v>46308.44791666666</v>
       </c>
       <c r="B45">
-        <v>6301</v>
+        <v>6060</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1472,10 +1484,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46307.45833333334</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="B46">
-        <v>6234</v>
+        <v>6023</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1486,10 +1498,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46307.46875</v>
+        <v>46308.46875</v>
       </c>
       <c r="B47">
-        <v>6286</v>
+        <v>6006</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1500,10 +1512,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46307.47916666666</v>
+        <v>46308.47916666666</v>
       </c>
       <c r="B48">
-        <v>6282</v>
+        <v>6156</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1514,10 +1526,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46307.48958333334</v>
+        <v>46308.48958333334</v>
       </c>
       <c r="B49">
-        <v>6356</v>
+        <v>6218</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1528,10 +1540,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46307.5</v>
+        <v>46308.5</v>
       </c>
       <c r="B50">
-        <v>6567</v>
+        <v>6133</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1542,10 +1554,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46307.51041666666</v>
+        <v>46308.51041666666</v>
       </c>
       <c r="B51">
-        <v>6568</v>
+        <v>6190</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1556,10 +1568,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46307.52083333334</v>
+        <v>46308.52083333334</v>
       </c>
       <c r="B52">
-        <v>6586</v>
+        <v>6220</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1570,10 +1582,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46307.53125</v>
+        <v>46308.53125</v>
       </c>
       <c r="B53">
-        <v>6578</v>
+        <v>6211</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1584,10 +1596,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46307.54166666666</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="B54">
-        <v>6554</v>
+        <v>6213</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1598,10 +1610,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46307.55208333334</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="B55">
-        <v>6616</v>
+        <v>6174</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1612,10 +1624,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46307.5625</v>
+        <v>46308.5625</v>
       </c>
       <c r="B56">
-        <v>6596</v>
+        <v>6152</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1626,10 +1638,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46307.57291666666</v>
+        <v>46308.57291666666</v>
       </c>
       <c r="B57">
-        <v>6530</v>
+        <v>6218</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1640,10 +1652,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46307.58333333334</v>
+        <v>46308.58333333334</v>
       </c>
       <c r="B58">
-        <v>6387</v>
+        <v>6251</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1654,10 +1666,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46307.59375</v>
+        <v>46308.59375</v>
       </c>
       <c r="B59">
-        <v>6367</v>
+        <v>6150</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1668,10 +1680,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46307.60416666666</v>
+        <v>46308.60416666666</v>
       </c>
       <c r="B60">
-        <v>6364</v>
+        <v>6132</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1682,10 +1694,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46307.61458333334</v>
+        <v>46308.61458333334</v>
       </c>
       <c r="B61">
-        <v>6371</v>
+        <v>6048</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1696,10 +1708,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46307.625</v>
+        <v>46308.625</v>
       </c>
       <c r="B62">
-        <v>6241</v>
+        <v>6228</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1710,10 +1722,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46307.63541666666</v>
+        <v>46308.63541666666</v>
       </c>
       <c r="B63">
-        <v>6254</v>
+        <v>6177</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1724,10 +1736,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46307.64583333334</v>
+        <v>46308.64583333334</v>
       </c>
       <c r="B64">
-        <v>6280</v>
+        <v>6247</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1738,10 +1750,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46307.65625</v>
+        <v>46308.65625</v>
       </c>
       <c r="B65">
-        <v>6360</v>
+        <v>6340</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1752,10 +1764,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46307.66666666666</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="B66">
-        <v>6382</v>
+        <v>6451</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1766,10 +1778,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46307.67708333334</v>
+        <v>46308.67708333334</v>
       </c>
       <c r="B67">
-        <v>6485</v>
+        <v>6381</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1780,10 +1792,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46307.6875</v>
+        <v>46308.6875</v>
       </c>
       <c r="B68">
-        <v>6507</v>
+        <v>6498</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1794,10 +1806,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46307.69791666666</v>
+        <v>46308.69791666666</v>
       </c>
       <c r="B69">
-        <v>6611</v>
+        <v>6618</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1808,10 +1820,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46307.70833333334</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="B70">
-        <v>6614</v>
+        <v>6733</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1822,10 +1834,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46307.71875</v>
+        <v>46308.71875</v>
       </c>
       <c r="B71">
-        <v>6724</v>
+        <v>6790</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1836,10 +1848,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46307.72916666666</v>
+        <v>46308.72916666666</v>
       </c>
       <c r="B72">
-        <v>6869</v>
+        <v>6859</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1850,10 +1862,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46307.73958333334</v>
+        <v>46308.73958333334</v>
       </c>
       <c r="B73">
-        <v>6972</v>
+        <v>7034</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1864,10 +1876,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46307.75</v>
+        <v>46308.75</v>
       </c>
       <c r="B74">
-        <v>7052</v>
+        <v>7169</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -1878,10 +1890,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46307.76041666666</v>
+        <v>46308.76041666666</v>
       </c>
       <c r="B75">
-        <v>7179</v>
+        <v>7245</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -1892,10 +1904,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46307.77083333334</v>
+        <v>46308.77083333334</v>
       </c>
       <c r="B76">
-        <v>7175</v>
+        <v>7221</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -1906,10 +1918,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46307.78125</v>
+        <v>46308.78125</v>
       </c>
       <c r="B77">
-        <v>7173</v>
+        <v>7241</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -1920,10 +1932,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46307.79166666666</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="B78">
-        <v>7104</v>
+        <v>7251</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -1934,10 +1946,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46307.80208333334</v>
+        <v>46308.80208333334</v>
       </c>
       <c r="B79">
-        <v>7042</v>
+        <v>7259</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -1948,10 +1960,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46307.8125</v>
+        <v>46308.8125</v>
       </c>
       <c r="B80">
-        <v>7033</v>
+        <v>7212</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -1962,10 +1974,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46307.82291666666</v>
+        <v>46308.82291666666</v>
       </c>
       <c r="B81">
-        <v>7033</v>
+        <v>7128</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -1976,10 +1988,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46307.83333333334</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="B82">
-        <v>6847</v>
+        <v>6987</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -1990,10 +2002,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46307.84375</v>
+        <v>46308.84375</v>
       </c>
       <c r="B83">
-        <v>6789</v>
+        <v>6897</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2004,10 +2016,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46307.85416666666</v>
+        <v>46308.85416666666</v>
       </c>
       <c r="B84">
-        <v>6551</v>
+        <v>6720</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2018,10 +2030,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46307.86458333334</v>
+        <v>46308.86458333334</v>
       </c>
       <c r="B85">
-        <v>6485</v>
+        <v>6625</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2032,10 +2044,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46307.875</v>
+        <v>46308.875</v>
       </c>
       <c r="B86">
-        <v>6242</v>
+        <v>6394</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2046,10 +2058,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46307.88541666666</v>
+        <v>46308.88541666666</v>
       </c>
       <c r="B87">
-        <v>6074</v>
+        <v>6277</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2060,10 +2072,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46307.89583333334</v>
+        <v>46308.89583333334</v>
       </c>
       <c r="B88">
-        <v>5938</v>
+        <v>6115</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2074,10 +2086,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46307.90625</v>
+        <v>46308.90625</v>
       </c>
       <c r="B89">
-        <v>5808</v>
+        <v>5934</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2088,10 +2100,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46307.91666666666</v>
+        <v>46308.91666666666</v>
       </c>
       <c r="B90">
-        <v>5726</v>
+        <v>5835</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2102,10 +2114,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46307.92708333334</v>
+        <v>46308.92708333334</v>
       </c>
       <c r="B91">
-        <v>5627</v>
+        <v>5796</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2116,10 +2128,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46307.9375</v>
+        <v>46308.9375</v>
       </c>
       <c r="B92">
-        <v>5537</v>
+        <v>5674</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2130,10 +2142,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46307.94791666666</v>
+        <v>46308.94791666666</v>
       </c>
       <c r="B93">
-        <v>5402</v>
+        <v>5559</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2144,10 +2156,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46307.95833333334</v>
+        <v>46308.95833333334</v>
       </c>
       <c r="B94">
-        <v>5316</v>
+        <v>5474</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2158,10 +2170,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46307.96875</v>
+        <v>46308.96875</v>
       </c>
       <c r="B95">
-        <v>5210</v>
+        <v>5378</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2172,10 +2184,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46307.97916666666</v>
+        <v>46308.97916666666</v>
       </c>
       <c r="B96">
-        <v>5136</v>
+        <v>5274</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2186,10 +2198,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46307.98958333334</v>
+        <v>46308.98958333334</v>
       </c>
       <c r="B97">
-        <v>5109</v>
+        <v>5176</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2200,10 +2212,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B98">
-        <v>5077</v>
+        <v>5157</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2214,10 +2226,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46308.01041666666</v>
+        <v>46309.01041666666</v>
       </c>
       <c r="B99">
-        <v>5009</v>
+        <v>5096</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2228,10 +2240,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46308.02083333334</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="B100">
-        <v>5041</v>
+        <v>5208</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2242,10 +2254,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46308.03125</v>
+        <v>46309.03125</v>
       </c>
       <c r="B101">
-        <v>5017</v>
+        <v>5138</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2256,10 +2268,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46308.04166666666</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="B102">
-        <v>5098</v>
+        <v>4997</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2270,10 +2282,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46308.05208333334</v>
+        <v>46309.05208333334</v>
       </c>
       <c r="B103">
-        <v>5036</v>
+        <v>5104</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2284,10 +2296,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46308.0625</v>
+        <v>46309.0625</v>
       </c>
       <c r="B104">
-        <v>5112</v>
+        <v>5103</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2298,10 +2310,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46308.07291666666</v>
+        <v>46309.07291666666</v>
       </c>
       <c r="B105">
-        <v>5094</v>
+        <v>5214</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2312,10 +2324,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46308.08333333334</v>
+        <v>46309.08333333334</v>
       </c>
       <c r="B106">
-        <v>5094</v>
+        <v>5201</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2326,10 +2338,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46308.09375</v>
+        <v>46309.09375</v>
       </c>
       <c r="B107">
-        <v>5206</v>
+        <v>5207</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2340,10 +2352,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46308.10416666666</v>
+        <v>46309.10416666666</v>
       </c>
       <c r="B108">
-        <v>5194</v>
+        <v>5292</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2354,10 +2366,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46308.11458333334</v>
+        <v>46309.11458333334</v>
       </c>
       <c r="B109">
-        <v>5152</v>
+        <v>5325</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2368,10 +2380,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46308.125</v>
+        <v>46309.125</v>
       </c>
       <c r="B110">
-        <v>5235</v>
+        <v>5304</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2382,10 +2394,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46308.13541666666</v>
+        <v>46309.13541666666</v>
       </c>
       <c r="B111">
-        <v>5234</v>
+        <v>5320</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2396,10 +2408,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46308.14583333334</v>
+        <v>46309.14583333334</v>
       </c>
       <c r="B112">
-        <v>5184</v>
+        <v>5411</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2410,10 +2422,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46308.15625</v>
+        <v>46309.15625</v>
       </c>
       <c r="B113">
-        <v>5106</v>
+        <v>5350</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2424,10 +2436,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46308.16666666666</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="B114">
-        <v>5028</v>
+        <v>5236</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2438,10 +2450,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46308.17708333334</v>
+        <v>46309.17708333334</v>
       </c>
       <c r="B115">
-        <v>5104</v>
+        <v>5172</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2452,10 +2464,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46308.1875</v>
+        <v>46309.1875</v>
       </c>
       <c r="B116">
-        <v>5121</v>
+        <v>5231</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2466,10 +2478,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46308.19791666666</v>
+        <v>46309.19791666666</v>
       </c>
       <c r="B117">
-        <v>5222</v>
+        <v>5317</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2480,10 +2492,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46308.20833333334</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="B118">
-        <v>5460</v>
+        <v>5564</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2494,10 +2506,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46308.21875</v>
+        <v>46309.21875</v>
       </c>
       <c r="B119">
-        <v>5655</v>
+        <v>5689</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2508,10 +2520,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46308.22916666666</v>
+        <v>46309.22916666666</v>
       </c>
       <c r="B120">
-        <v>5850</v>
+        <v>5869</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2522,10 +2534,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46308.23958333334</v>
+        <v>46309.23958333334</v>
       </c>
       <c r="B121">
-        <v>5950</v>
+        <v>6042</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2536,10 +2548,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="B122">
-        <v>6298</v>
+        <v>6385</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2550,10 +2562,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46308.26041666666</v>
+        <v>46309.26041666666</v>
       </c>
       <c r="B123">
-        <v>6393</v>
+        <v>6484</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2564,10 +2576,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46308.27083333334</v>
+        <v>46309.27083333334</v>
       </c>
       <c r="B124">
-        <v>6500</v>
+        <v>6425</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2578,10 +2590,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46308.28125</v>
+        <v>46309.28125</v>
       </c>
       <c r="B125">
-        <v>6550</v>
+        <v>6524</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2592,10 +2604,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46308.29166666666</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="B126">
-        <v>6676</v>
+        <v>6717</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2606,10 +2618,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46308.30208333334</v>
+        <v>46309.30208333334</v>
       </c>
       <c r="B127">
-        <v>6782</v>
+        <v>6733</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2620,10 +2632,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46308.3125</v>
+        <v>46309.3125</v>
       </c>
       <c r="B128">
-        <v>6833</v>
+        <v>6655</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2634,10 +2646,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46308.32291666666</v>
+        <v>46309.32291666666</v>
       </c>
       <c r="B129">
-        <v>6782</v>
+        <v>6717</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2648,10 +2660,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46308.33333333334</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="B130">
-        <v>6763</v>
+        <v>6542</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2662,10 +2674,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46308.34375</v>
+        <v>46309.34375</v>
       </c>
       <c r="B131">
-        <v>6745</v>
+        <v>6446</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2676,10 +2688,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46308.35416666666</v>
+        <v>46309.35416666666</v>
       </c>
       <c r="B132">
-        <v>6664</v>
+        <v>6358</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2690,10 +2702,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46308.36458333334</v>
+        <v>46309.36458333334</v>
       </c>
       <c r="B133">
-        <v>6590</v>
+        <v>6395</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2704,10 +2716,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46308.375</v>
+        <v>46309.375</v>
       </c>
       <c r="B134">
-        <v>6524</v>
+        <v>6032</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2718,10 +2730,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46308.38541666666</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="B135">
-        <v>6505</v>
+        <v>6007</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2732,10 +2744,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46308.39583333334</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="B136">
-        <v>6508</v>
+        <v>5700</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2746,10 +2758,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46308.40625</v>
+        <v>46309.40625</v>
       </c>
       <c r="B137">
-        <v>6439</v>
+        <v>5655</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2760,10 +2772,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46308.41666666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="B138">
-        <v>6229</v>
+        <v>5286</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2774,10 +2786,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46308.42708333334</v>
+        <v>46309.42708333334</v>
       </c>
       <c r="B139">
-        <v>6155</v>
+        <v>5265</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2788,10 +2800,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46308.4375</v>
+        <v>46309.4375</v>
       </c>
       <c r="B140">
-        <v>6094</v>
+        <v>5236</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2802,10 +2814,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46308.44791666666</v>
+        <v>46309.44791666666</v>
       </c>
       <c r="B141">
-        <v>6060</v>
+        <v>5137</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2816,10 +2828,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46308.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="B142">
-        <v>6023</v>
+        <v>4976</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2830,10 +2842,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46308.46875</v>
+        <v>46309.46875</v>
       </c>
       <c r="B143">
-        <v>6006</v>
+        <v>4973</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2844,10 +2856,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46308.47916666666</v>
+        <v>46309.47916666666</v>
       </c>
       <c r="B144">
-        <v>6156</v>
+        <v>4985</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2858,10 +2870,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46308.48958333334</v>
+        <v>46309.48958333334</v>
       </c>
       <c r="B145">
-        <v>6218</v>
+        <v>4873</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2872,10 +2884,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="B146">
-        <v>6133</v>
+        <v>4870</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -2886,10 +2898,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46308.51041666666</v>
+        <v>46309.51041666666</v>
       </c>
       <c r="B147">
-        <v>6190</v>
+        <v>4979</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -2900,10 +2912,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46308.52083333334</v>
+        <v>46309.52083333334</v>
       </c>
       <c r="B148">
-        <v>6220</v>
+        <v>4950</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -2914,10 +2926,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46308.53125</v>
+        <v>46309.53125</v>
       </c>
       <c r="B149">
-        <v>6211</v>
+        <v>4816</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -2928,10 +2940,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46308.54166666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="B150">
-        <v>6213</v>
+        <v>4773</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -2942,16 +2954,72 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46308.55208333334</v>
+        <v>46309.55208333334</v>
       </c>
       <c r="B151">
-        <v>6174</v>
+        <v>4766</v>
       </c>
       <c r="C151">
         <v>54</v>
       </c>
       <c r="D151" t="s">
         <v>153</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="2">
+        <v>46309.5625</v>
+      </c>
+      <c r="B152">
+        <v>4728</v>
+      </c>
+      <c r="C152">
+        <v>55</v>
+      </c>
+      <c r="D152" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="2">
+        <v>46309.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>4723</v>
+      </c>
+      <c r="C153">
+        <v>56</v>
+      </c>
+      <c r="D153" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="2">
+        <v>46309.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>4768</v>
+      </c>
+      <c r="C154">
+        <v>57</v>
+      </c>
+      <c r="D154" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="2">
+        <v>46309.59375</v>
+      </c>
+      <c r="B155">
+        <v>4699</v>
+      </c>
+      <c r="C155">
+        <v>58</v>
+      </c>
+      <c r="D155" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,466 +28,445 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>13.10.20261</t>
-  </si>
-  <si>
-    <t>13.10.20262</t>
-  </si>
-  <si>
-    <t>13.10.20263</t>
-  </si>
-  <si>
-    <t>13.10.20264</t>
-  </si>
-  <si>
-    <t>13.10.20265</t>
-  </si>
-  <si>
-    <t>13.10.20266</t>
-  </si>
-  <si>
-    <t>13.10.20267</t>
-  </si>
-  <si>
-    <t>13.10.20268</t>
-  </si>
-  <si>
-    <t>13.10.20269</t>
-  </si>
-  <si>
-    <t>13.10.202610</t>
-  </si>
-  <si>
-    <t>13.10.202611</t>
-  </si>
-  <si>
-    <t>13.10.202612</t>
-  </si>
-  <si>
-    <t>13.10.202613</t>
-  </si>
-  <si>
-    <t>13.10.202614</t>
-  </si>
-  <si>
-    <t>13.10.202615</t>
-  </si>
-  <si>
-    <t>13.10.202616</t>
-  </si>
-  <si>
-    <t>13.10.202617</t>
-  </si>
-  <si>
-    <t>13.10.202618</t>
-  </si>
-  <si>
-    <t>13.10.202619</t>
-  </si>
-  <si>
-    <t>13.10.202620</t>
-  </si>
-  <si>
-    <t>13.10.202621</t>
-  </si>
-  <si>
-    <t>13.10.202622</t>
-  </si>
-  <si>
-    <t>13.10.202623</t>
-  </si>
-  <si>
-    <t>13.10.202624</t>
-  </si>
-  <si>
-    <t>13.10.202625</t>
-  </si>
-  <si>
-    <t>13.10.202626</t>
-  </si>
-  <si>
-    <t>13.10.202627</t>
-  </si>
-  <si>
-    <t>13.10.202628</t>
-  </si>
-  <si>
-    <t>13.10.202629</t>
-  </si>
-  <si>
-    <t>13.10.202630</t>
-  </si>
-  <si>
-    <t>13.10.202631</t>
-  </si>
-  <si>
-    <t>13.10.202632</t>
-  </si>
-  <si>
-    <t>13.10.202633</t>
-  </si>
-  <si>
-    <t>13.10.202634</t>
-  </si>
-  <si>
-    <t>13.10.202635</t>
-  </si>
-  <si>
-    <t>13.10.202636</t>
-  </si>
-  <si>
-    <t>13.10.202637</t>
-  </si>
-  <si>
-    <t>13.10.202638</t>
-  </si>
-  <si>
-    <t>13.10.202639</t>
-  </si>
-  <si>
-    <t>13.10.202640</t>
-  </si>
-  <si>
-    <t>13.10.202641</t>
-  </si>
-  <si>
-    <t>13.10.202642</t>
-  </si>
-  <si>
-    <t>13.10.202643</t>
-  </si>
-  <si>
-    <t>13.10.202644</t>
-  </si>
-  <si>
-    <t>13.10.202645</t>
-  </si>
-  <si>
-    <t>13.10.202646</t>
-  </si>
-  <si>
-    <t>13.10.202647</t>
-  </si>
-  <si>
-    <t>13.10.202648</t>
-  </si>
-  <si>
-    <t>13.10.202649</t>
-  </si>
-  <si>
-    <t>13.10.202650</t>
-  </si>
-  <si>
-    <t>13.10.202651</t>
-  </si>
-  <si>
-    <t>13.10.202652</t>
-  </si>
-  <si>
-    <t>13.10.202653</t>
-  </si>
-  <si>
-    <t>13.10.202654</t>
-  </si>
-  <si>
-    <t>13.10.202655</t>
-  </si>
-  <si>
-    <t>13.10.202656</t>
-  </si>
-  <si>
-    <t>13.10.202657</t>
-  </si>
-  <si>
-    <t>13.10.202658</t>
-  </si>
-  <si>
-    <t>13.10.202659</t>
-  </si>
-  <si>
-    <t>13.10.202660</t>
-  </si>
-  <si>
-    <t>13.10.202661</t>
-  </si>
-  <si>
-    <t>13.10.202662</t>
-  </si>
-  <si>
-    <t>13.10.202663</t>
-  </si>
-  <si>
-    <t>13.10.202664</t>
-  </si>
-  <si>
-    <t>13.10.202665</t>
-  </si>
-  <si>
-    <t>13.10.202666</t>
-  </si>
-  <si>
-    <t>13.10.202667</t>
-  </si>
-  <si>
-    <t>13.10.202668</t>
-  </si>
-  <si>
-    <t>13.10.202669</t>
-  </si>
-  <si>
-    <t>13.10.202670</t>
-  </si>
-  <si>
-    <t>13.10.202671</t>
-  </si>
-  <si>
-    <t>13.10.202672</t>
-  </si>
-  <si>
-    <t>13.10.202673</t>
-  </si>
-  <si>
-    <t>13.10.202674</t>
-  </si>
-  <si>
-    <t>13.10.202675</t>
-  </si>
-  <si>
-    <t>13.10.202676</t>
-  </si>
-  <si>
-    <t>13.10.202677</t>
-  </si>
-  <si>
-    <t>13.10.202678</t>
-  </si>
-  <si>
-    <t>13.10.202679</t>
-  </si>
-  <si>
-    <t>13.10.202680</t>
-  </si>
-  <si>
-    <t>13.10.202681</t>
-  </si>
-  <si>
-    <t>13.10.202682</t>
-  </si>
-  <si>
-    <t>13.10.202683</t>
-  </si>
-  <si>
-    <t>13.10.202684</t>
-  </si>
-  <si>
-    <t>13.10.202685</t>
-  </si>
-  <si>
-    <t>13.10.202686</t>
-  </si>
-  <si>
-    <t>13.10.202687</t>
-  </si>
-  <si>
-    <t>13.10.202688</t>
-  </si>
-  <si>
-    <t>13.10.202689</t>
-  </si>
-  <si>
-    <t>13.10.202690</t>
-  </si>
-  <si>
-    <t>13.10.202691</t>
-  </si>
-  <si>
-    <t>13.10.202692</t>
-  </si>
-  <si>
-    <t>13.10.202693</t>
-  </si>
-  <si>
-    <t>13.10.202694</t>
-  </si>
-  <si>
-    <t>13.10.202695</t>
-  </si>
-  <si>
-    <t>13.10.202696</t>
-  </si>
-  <si>
-    <t>14.10.20261</t>
-  </si>
-  <si>
-    <t>14.10.20262</t>
-  </si>
-  <si>
-    <t>14.10.20263</t>
-  </si>
-  <si>
-    <t>14.10.20264</t>
-  </si>
-  <si>
-    <t>14.10.20265</t>
-  </si>
-  <si>
-    <t>14.10.20266</t>
-  </si>
-  <si>
-    <t>14.10.20267</t>
-  </si>
-  <si>
-    <t>14.10.20268</t>
-  </si>
-  <si>
-    <t>14.10.20269</t>
-  </si>
-  <si>
-    <t>14.10.202610</t>
-  </si>
-  <si>
-    <t>14.10.202611</t>
-  </si>
-  <si>
-    <t>14.10.202612</t>
-  </si>
-  <si>
-    <t>14.10.202613</t>
-  </si>
-  <si>
-    <t>14.10.202614</t>
-  </si>
-  <si>
-    <t>14.10.202615</t>
-  </si>
-  <si>
-    <t>14.10.202616</t>
-  </si>
-  <si>
-    <t>14.10.202617</t>
-  </si>
-  <si>
-    <t>14.10.202618</t>
-  </si>
-  <si>
-    <t>14.10.202619</t>
-  </si>
-  <si>
-    <t>14.10.202620</t>
-  </si>
-  <si>
-    <t>14.10.202621</t>
-  </si>
-  <si>
-    <t>14.10.202622</t>
-  </si>
-  <si>
-    <t>14.10.202623</t>
-  </si>
-  <si>
-    <t>14.10.202624</t>
-  </si>
-  <si>
-    <t>14.10.202625</t>
-  </si>
-  <si>
-    <t>14.10.202626</t>
-  </si>
-  <si>
-    <t>14.10.202627</t>
-  </si>
-  <si>
-    <t>14.10.202628</t>
-  </si>
-  <si>
-    <t>14.10.202629</t>
-  </si>
-  <si>
-    <t>14.10.202630</t>
-  </si>
-  <si>
-    <t>14.10.202631</t>
-  </si>
-  <si>
-    <t>14.10.202632</t>
-  </si>
-  <si>
-    <t>14.10.202633</t>
-  </si>
-  <si>
-    <t>14.10.202634</t>
-  </si>
-  <si>
-    <t>14.10.202635</t>
-  </si>
-  <si>
-    <t>14.10.202636</t>
-  </si>
-  <si>
-    <t>14.10.202637</t>
-  </si>
-  <si>
-    <t>14.10.202638</t>
-  </si>
-  <si>
-    <t>14.10.202639</t>
-  </si>
-  <si>
-    <t>14.10.202640</t>
-  </si>
-  <si>
-    <t>14.10.202641</t>
-  </si>
-  <si>
-    <t>14.10.202642</t>
-  </si>
-  <si>
-    <t>14.10.202643</t>
-  </si>
-  <si>
-    <t>14.10.202644</t>
-  </si>
-  <si>
-    <t>14.10.202645</t>
-  </si>
-  <si>
-    <t>14.10.202646</t>
-  </si>
-  <si>
-    <t>14.10.202647</t>
-  </si>
-  <si>
-    <t>14.10.202648</t>
-  </si>
-  <si>
-    <t>14.10.202649</t>
-  </si>
-  <si>
-    <t>14.10.202650</t>
-  </si>
-  <si>
-    <t>14.10.202651</t>
-  </si>
-  <si>
-    <t>14.10.202652</t>
-  </si>
-  <si>
-    <t>14.10.202653</t>
-  </si>
-  <si>
-    <t>14.10.202654</t>
-  </si>
-  <si>
-    <t>14.10.202655</t>
-  </si>
-  <si>
-    <t>14.10.202656</t>
-  </si>
-  <si>
-    <t>14.10.202657</t>
-  </si>
-  <si>
-    <t>14.10.202658</t>
+    <t>15.10.20261</t>
+  </si>
+  <si>
+    <t>15.10.20262</t>
+  </si>
+  <si>
+    <t>15.10.20263</t>
+  </si>
+  <si>
+    <t>15.10.20264</t>
+  </si>
+  <si>
+    <t>15.10.20265</t>
+  </si>
+  <si>
+    <t>15.10.20266</t>
+  </si>
+  <si>
+    <t>15.10.20267</t>
+  </si>
+  <si>
+    <t>15.10.20268</t>
+  </si>
+  <si>
+    <t>15.10.20269</t>
+  </si>
+  <si>
+    <t>15.10.202610</t>
+  </si>
+  <si>
+    <t>15.10.202611</t>
+  </si>
+  <si>
+    <t>15.10.202612</t>
+  </si>
+  <si>
+    <t>15.10.202613</t>
+  </si>
+  <si>
+    <t>15.10.202614</t>
+  </si>
+  <si>
+    <t>15.10.202615</t>
+  </si>
+  <si>
+    <t>15.10.202616</t>
+  </si>
+  <si>
+    <t>15.10.202617</t>
+  </si>
+  <si>
+    <t>15.10.202618</t>
+  </si>
+  <si>
+    <t>15.10.202619</t>
+  </si>
+  <si>
+    <t>15.10.202620</t>
+  </si>
+  <si>
+    <t>15.10.202621</t>
+  </si>
+  <si>
+    <t>15.10.202622</t>
+  </si>
+  <si>
+    <t>15.10.202623</t>
+  </si>
+  <si>
+    <t>15.10.202624</t>
+  </si>
+  <si>
+    <t>15.10.202625</t>
+  </si>
+  <si>
+    <t>15.10.202626</t>
+  </si>
+  <si>
+    <t>15.10.202627</t>
+  </si>
+  <si>
+    <t>15.10.202628</t>
+  </si>
+  <si>
+    <t>15.10.202629</t>
+  </si>
+  <si>
+    <t>15.10.202630</t>
+  </si>
+  <si>
+    <t>15.10.202631</t>
+  </si>
+  <si>
+    <t>15.10.202632</t>
+  </si>
+  <si>
+    <t>15.10.202633</t>
+  </si>
+  <si>
+    <t>15.10.202634</t>
+  </si>
+  <si>
+    <t>15.10.202635</t>
+  </si>
+  <si>
+    <t>15.10.202636</t>
+  </si>
+  <si>
+    <t>15.10.202637</t>
+  </si>
+  <si>
+    <t>15.10.202638</t>
+  </si>
+  <si>
+    <t>15.10.202639</t>
+  </si>
+  <si>
+    <t>15.10.202640</t>
+  </si>
+  <si>
+    <t>15.10.202641</t>
+  </si>
+  <si>
+    <t>15.10.202642</t>
+  </si>
+  <si>
+    <t>15.10.202643</t>
+  </si>
+  <si>
+    <t>15.10.202644</t>
+  </si>
+  <si>
+    <t>15.10.202645</t>
+  </si>
+  <si>
+    <t>15.10.202646</t>
+  </si>
+  <si>
+    <t>15.10.202647</t>
+  </si>
+  <si>
+    <t>15.10.202648</t>
+  </si>
+  <si>
+    <t>15.10.202649</t>
+  </si>
+  <si>
+    <t>15.10.202650</t>
+  </si>
+  <si>
+    <t>15.10.202651</t>
+  </si>
+  <si>
+    <t>15.10.202652</t>
+  </si>
+  <si>
+    <t>15.10.202653</t>
+  </si>
+  <si>
+    <t>15.10.202654</t>
+  </si>
+  <si>
+    <t>15.10.202655</t>
+  </si>
+  <si>
+    <t>15.10.202656</t>
+  </si>
+  <si>
+    <t>15.10.202657</t>
+  </si>
+  <si>
+    <t>15.10.202658</t>
+  </si>
+  <si>
+    <t>15.10.202659</t>
+  </si>
+  <si>
+    <t>15.10.202660</t>
+  </si>
+  <si>
+    <t>15.10.202661</t>
+  </si>
+  <si>
+    <t>15.10.202662</t>
+  </si>
+  <si>
+    <t>15.10.202663</t>
+  </si>
+  <si>
+    <t>15.10.202664</t>
+  </si>
+  <si>
+    <t>15.10.202665</t>
+  </si>
+  <si>
+    <t>15.10.202666</t>
+  </si>
+  <si>
+    <t>15.10.202667</t>
+  </si>
+  <si>
+    <t>15.10.202668</t>
+  </si>
+  <si>
+    <t>15.10.202669</t>
+  </si>
+  <si>
+    <t>15.10.202670</t>
+  </si>
+  <si>
+    <t>15.10.202671</t>
+  </si>
+  <si>
+    <t>15.10.202672</t>
+  </si>
+  <si>
+    <t>15.10.202673</t>
+  </si>
+  <si>
+    <t>15.10.202674</t>
+  </si>
+  <si>
+    <t>15.10.202675</t>
+  </si>
+  <si>
+    <t>15.10.202676</t>
+  </si>
+  <si>
+    <t>15.10.202677</t>
+  </si>
+  <si>
+    <t>15.10.202678</t>
+  </si>
+  <si>
+    <t>15.10.202679</t>
+  </si>
+  <si>
+    <t>15.10.202680</t>
+  </si>
+  <si>
+    <t>15.10.202681</t>
+  </si>
+  <si>
+    <t>15.10.202682</t>
+  </si>
+  <si>
+    <t>15.10.202683</t>
+  </si>
+  <si>
+    <t>15.10.202684</t>
+  </si>
+  <si>
+    <t>15.10.202685</t>
+  </si>
+  <si>
+    <t>15.10.202686</t>
+  </si>
+  <si>
+    <t>15.10.202687</t>
+  </si>
+  <si>
+    <t>15.10.202688</t>
+  </si>
+  <si>
+    <t>15.10.202689</t>
+  </si>
+  <si>
+    <t>15.10.202690</t>
+  </si>
+  <si>
+    <t>15.10.202691</t>
+  </si>
+  <si>
+    <t>15.10.202692</t>
+  </si>
+  <si>
+    <t>15.10.202693</t>
+  </si>
+  <si>
+    <t>15.10.202694</t>
+  </si>
+  <si>
+    <t>15.10.202695</t>
+  </si>
+  <si>
+    <t>15.10.202696</t>
+  </si>
+  <si>
+    <t>16.10.20261</t>
+  </si>
+  <si>
+    <t>16.10.20262</t>
+  </si>
+  <si>
+    <t>16.10.20263</t>
+  </si>
+  <si>
+    <t>16.10.20264</t>
+  </si>
+  <si>
+    <t>16.10.20265</t>
+  </si>
+  <si>
+    <t>16.10.20266</t>
+  </si>
+  <si>
+    <t>16.10.20267</t>
+  </si>
+  <si>
+    <t>16.10.20268</t>
+  </si>
+  <si>
+    <t>16.10.20269</t>
+  </si>
+  <si>
+    <t>16.10.202610</t>
+  </si>
+  <si>
+    <t>16.10.202611</t>
+  </si>
+  <si>
+    <t>16.10.202612</t>
+  </si>
+  <si>
+    <t>16.10.202613</t>
+  </si>
+  <si>
+    <t>16.10.202614</t>
+  </si>
+  <si>
+    <t>16.10.202615</t>
+  </si>
+  <si>
+    <t>16.10.202616</t>
+  </si>
+  <si>
+    <t>16.10.202617</t>
+  </si>
+  <si>
+    <t>16.10.202618</t>
+  </si>
+  <si>
+    <t>16.10.202619</t>
+  </si>
+  <si>
+    <t>16.10.202620</t>
+  </si>
+  <si>
+    <t>16.10.202621</t>
+  </si>
+  <si>
+    <t>16.10.202622</t>
+  </si>
+  <si>
+    <t>16.10.202623</t>
+  </si>
+  <si>
+    <t>16.10.202624</t>
+  </si>
+  <si>
+    <t>16.10.202625</t>
+  </si>
+  <si>
+    <t>16.10.202626</t>
+  </si>
+  <si>
+    <t>16.10.202627</t>
+  </si>
+  <si>
+    <t>16.10.202628</t>
+  </si>
+  <si>
+    <t>16.10.202629</t>
+  </si>
+  <si>
+    <t>16.10.202630</t>
+  </si>
+  <si>
+    <t>16.10.202631</t>
+  </si>
+  <si>
+    <t>16.10.202632</t>
+  </si>
+  <si>
+    <t>16.10.202633</t>
+  </si>
+  <si>
+    <t>16.10.202634</t>
+  </si>
+  <si>
+    <t>16.10.202635</t>
+  </si>
+  <si>
+    <t>16.10.202636</t>
+  </si>
+  <si>
+    <t>16.10.202637</t>
+  </si>
+  <si>
+    <t>16.10.202638</t>
+  </si>
+  <si>
+    <t>16.10.202639</t>
+  </si>
+  <si>
+    <t>16.10.202640</t>
+  </si>
+  <si>
+    <t>16.10.202641</t>
+  </si>
+  <si>
+    <t>16.10.202642</t>
+  </si>
+  <si>
+    <t>16.10.202643</t>
+  </si>
+  <si>
+    <t>16.10.202644</t>
+  </si>
+  <si>
+    <t>16.10.202645</t>
+  </si>
+  <si>
+    <t>16.10.202646</t>
+  </si>
+  <si>
+    <t>16.10.202647</t>
+  </si>
+  <si>
+    <t>16.10.202648</t>
+  </si>
+  <si>
+    <t>16.10.202649</t>
+  </si>
+  <si>
+    <t>16.10.202650</t>
+  </si>
+  <si>
+    <t>16.10.202651</t>
   </si>
 </sst>
 </file>
@@ -849,7 +828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D155"/>
+  <dimension ref="A1:D148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -868,10 +847,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="B2">
-        <v>5077</v>
+        <v>5230</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -882,10 +861,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46308.01041666666</v>
+        <v>46310.01041666666</v>
       </c>
       <c r="B3">
-        <v>5009</v>
+        <v>5276</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -896,10 +875,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46308.02083333334</v>
+        <v>46310.02083333334</v>
       </c>
       <c r="B4">
-        <v>5041</v>
+        <v>5188</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -910,10 +889,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46308.03125</v>
+        <v>46310.03125</v>
       </c>
       <c r="B5">
-        <v>5017</v>
+        <v>5205</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -924,10 +903,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46308.04166666666</v>
+        <v>46310.04166666666</v>
       </c>
       <c r="B6">
-        <v>5098</v>
+        <v>5160</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -938,10 +917,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46308.05208333334</v>
+        <v>46310.05208333334</v>
       </c>
       <c r="B7">
-        <v>5036</v>
+        <v>5234</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -952,10 +931,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46308.0625</v>
+        <v>46310.0625</v>
       </c>
       <c r="B8">
-        <v>5112</v>
+        <v>5188</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -966,10 +945,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46308.07291666666</v>
+        <v>46310.07291666666</v>
       </c>
       <c r="B9">
-        <v>5094</v>
+        <v>5252</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -980,10 +959,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46308.08333333334</v>
+        <v>46310.08333333334</v>
       </c>
       <c r="B10">
-        <v>5094</v>
+        <v>5265</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -994,10 +973,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46308.09375</v>
+        <v>46310.09375</v>
       </c>
       <c r="B11">
-        <v>5206</v>
+        <v>5426</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1008,10 +987,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46308.10416666666</v>
+        <v>46310.10416666666</v>
       </c>
       <c r="B12">
-        <v>5194</v>
+        <v>5383</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1022,10 +1001,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46308.11458333334</v>
+        <v>46310.11458333334</v>
       </c>
       <c r="B13">
-        <v>5152</v>
+        <v>5245</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1036,10 +1015,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46308.125</v>
+        <v>46310.125</v>
       </c>
       <c r="B14">
-        <v>5235</v>
+        <v>5225</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1050,10 +1029,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46308.13541666666</v>
+        <v>46310.13541666666</v>
       </c>
       <c r="B15">
-        <v>5234</v>
+        <v>5258</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1064,10 +1043,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46308.14583333334</v>
+        <v>46310.14583333334</v>
       </c>
       <c r="B16">
-        <v>5184</v>
+        <v>5234</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1078,10 +1057,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46308.15625</v>
+        <v>46310.15625</v>
       </c>
       <c r="B17">
-        <v>5106</v>
+        <v>5231</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1092,10 +1071,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46308.16666666666</v>
+        <v>46310.16666666666</v>
       </c>
       <c r="B18">
-        <v>5028</v>
+        <v>5204</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1106,10 +1085,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46308.17708333334</v>
+        <v>46310.17708333334</v>
       </c>
       <c r="B19">
-        <v>5104</v>
+        <v>5303</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1120,10 +1099,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46308.1875</v>
+        <v>46310.1875</v>
       </c>
       <c r="B20">
-        <v>5121</v>
+        <v>5362</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1134,10 +1113,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46308.19791666666</v>
+        <v>46310.19791666666</v>
       </c>
       <c r="B21">
-        <v>5222</v>
+        <v>5409</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1148,10 +1127,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46308.20833333334</v>
+        <v>46310.20833333334</v>
       </c>
       <c r="B22">
-        <v>5460</v>
+        <v>5685</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1162,10 +1141,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46308.21875</v>
+        <v>46310.21875</v>
       </c>
       <c r="B23">
-        <v>5655</v>
+        <v>5835</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1176,10 +1155,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46308.22916666666</v>
+        <v>46310.22916666666</v>
       </c>
       <c r="B24">
-        <v>5850</v>
+        <v>5955</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1190,10 +1169,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46308.23958333334</v>
+        <v>46310.23958333334</v>
       </c>
       <c r="B25">
-        <v>5950</v>
+        <v>6174</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1204,10 +1183,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46308.25</v>
+        <v>46310.25</v>
       </c>
       <c r="B26">
-        <v>6298</v>
+        <v>6474</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1218,10 +1197,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46308.26041666666</v>
+        <v>46310.26041666666</v>
       </c>
       <c r="B27">
-        <v>6393</v>
+        <v>6634</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1232,10 +1211,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46308.27083333334</v>
+        <v>46310.27083333334</v>
       </c>
       <c r="B28">
-        <v>6500</v>
+        <v>6741</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1246,10 +1225,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46308.28125</v>
+        <v>46310.28125</v>
       </c>
       <c r="B29">
-        <v>6550</v>
+        <v>6731</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1260,10 +1239,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46308.29166666666</v>
+        <v>46310.29166666666</v>
       </c>
       <c r="B30">
-        <v>6676</v>
+        <v>6866</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1274,10 +1253,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46308.30208333334</v>
+        <v>46310.30208333334</v>
       </c>
       <c r="B31">
-        <v>6782</v>
+        <v>6917</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1288,10 +1267,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46308.3125</v>
+        <v>46310.3125</v>
       </c>
       <c r="B32">
-        <v>6833</v>
+        <v>6910</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1302,10 +1281,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46308.32291666666</v>
+        <v>46310.32291666666</v>
       </c>
       <c r="B33">
-        <v>6782</v>
+        <v>6852</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1316,10 +1295,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46308.33333333334</v>
+        <v>46310.33333333334</v>
       </c>
       <c r="B34">
-        <v>6763</v>
+        <v>6830</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1330,10 +1309,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46308.34375</v>
+        <v>46310.34375</v>
       </c>
       <c r="B35">
-        <v>6745</v>
+        <v>6766</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1344,10 +1323,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46308.35416666666</v>
+        <v>46310.35416666666</v>
       </c>
       <c r="B36">
-        <v>6664</v>
+        <v>6748</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1358,10 +1337,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46308.36458333334</v>
+        <v>46310.36458333334</v>
       </c>
       <c r="B37">
-        <v>6590</v>
+        <v>6627</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1372,10 +1351,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46308.375</v>
+        <v>46310.375</v>
       </c>
       <c r="B38">
-        <v>6524</v>
+        <v>6527</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1386,10 +1365,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46308.38541666666</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="B39">
-        <v>6505</v>
+        <v>6471</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1400,10 +1379,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46308.39583333334</v>
+        <v>46310.39583333334</v>
       </c>
       <c r="B40">
-        <v>6508</v>
+        <v>6465</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1414,10 +1393,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46308.40625</v>
+        <v>46310.40625</v>
       </c>
       <c r="B41">
-        <v>6439</v>
+        <v>6448</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1428,10 +1407,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46308.41666666666</v>
+        <v>46310.41666666666</v>
       </c>
       <c r="B42">
-        <v>6229</v>
+        <v>6203</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1442,10 +1421,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46308.42708333334</v>
+        <v>46310.42708333334</v>
       </c>
       <c r="B43">
-        <v>6155</v>
+        <v>6117</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1456,10 +1435,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46308.4375</v>
+        <v>46310.4375</v>
       </c>
       <c r="B44">
-        <v>6094</v>
+        <v>6176</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1470,10 +1449,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46308.44791666666</v>
+        <v>46310.44791666666</v>
       </c>
       <c r="B45">
-        <v>6060</v>
+        <v>6170</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1484,10 +1463,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46308.45833333334</v>
+        <v>46310.45833333334</v>
       </c>
       <c r="B46">
-        <v>6023</v>
+        <v>5987</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1498,10 +1477,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46308.46875</v>
+        <v>46310.46875</v>
       </c>
       <c r="B47">
-        <v>6006</v>
+        <v>5971</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1512,10 +1491,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46308.47916666666</v>
+        <v>46310.47916666666</v>
       </c>
       <c r="B48">
-        <v>6156</v>
+        <v>5964</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1526,10 +1505,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46308.48958333334</v>
+        <v>46310.48958333334</v>
       </c>
       <c r="B49">
-        <v>6218</v>
+        <v>5963</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1540,10 +1519,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46308.5</v>
+        <v>46310.5</v>
       </c>
       <c r="B50">
-        <v>6133</v>
+        <v>6056</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1554,10 +1533,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46308.51041666666</v>
+        <v>46310.51041666666</v>
       </c>
       <c r="B51">
-        <v>6190</v>
+        <v>6118</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1568,10 +1547,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46308.52083333334</v>
+        <v>46310.52083333334</v>
       </c>
       <c r="B52">
-        <v>6220</v>
+        <v>6104</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1582,10 +1561,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46308.53125</v>
+        <v>46310.53125</v>
       </c>
       <c r="B53">
-        <v>6211</v>
+        <v>6190</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1596,10 +1575,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46308.54166666666</v>
+        <v>46310.54166666666</v>
       </c>
       <c r="B54">
-        <v>6213</v>
+        <v>5870</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1610,10 +1589,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46308.55208333334</v>
+        <v>46310.55208333334</v>
       </c>
       <c r="B55">
-        <v>6174</v>
+        <v>5915</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1624,10 +1603,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46308.5625</v>
+        <v>46310.5625</v>
       </c>
       <c r="B56">
-        <v>6152</v>
+        <v>5918</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1638,10 +1617,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46308.57291666666</v>
+        <v>46310.57291666666</v>
       </c>
       <c r="B57">
-        <v>6218</v>
+        <v>5952</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1652,10 +1631,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46308.58333333334</v>
+        <v>46310.58333333334</v>
       </c>
       <c r="B58">
-        <v>6251</v>
+        <v>5965</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1666,10 +1645,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46308.59375</v>
+        <v>46310.59375</v>
       </c>
       <c r="B59">
-        <v>6150</v>
+        <v>5957</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1680,10 +1659,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46308.60416666666</v>
+        <v>46310.60416666666</v>
       </c>
       <c r="B60">
-        <v>6132</v>
+        <v>5786</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1694,10 +1673,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46308.61458333334</v>
+        <v>46310.61458333334</v>
       </c>
       <c r="B61">
-        <v>6048</v>
+        <v>5899</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1708,10 +1687,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46308.625</v>
+        <v>46310.625</v>
       </c>
       <c r="B62">
-        <v>6228</v>
+        <v>5999</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1722,10 +1701,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46308.63541666666</v>
+        <v>46310.63541666666</v>
       </c>
       <c r="B63">
-        <v>6177</v>
+        <v>6056</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1736,10 +1715,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46308.64583333334</v>
+        <v>46310.64583333334</v>
       </c>
       <c r="B64">
-        <v>6247</v>
+        <v>6169</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1750,10 +1729,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46308.65625</v>
+        <v>46310.65625</v>
       </c>
       <c r="B65">
-        <v>6340</v>
+        <v>6287</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1764,10 +1743,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46308.66666666666</v>
+        <v>46310.66666666666</v>
       </c>
       <c r="B66">
-        <v>6451</v>
+        <v>6310</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1778,10 +1757,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46308.67708333334</v>
+        <v>46310.67708333334</v>
       </c>
       <c r="B67">
-        <v>6381</v>
+        <v>6474</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1792,10 +1771,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46308.6875</v>
+        <v>46310.6875</v>
       </c>
       <c r="B68">
-        <v>6498</v>
+        <v>6664</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1806,10 +1785,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46308.69791666666</v>
+        <v>46310.69791666666</v>
       </c>
       <c r="B69">
-        <v>6618</v>
+        <v>6746</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1820,10 +1799,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46308.70833333334</v>
+        <v>46310.70833333334</v>
       </c>
       <c r="B70">
-        <v>6733</v>
+        <v>6751</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1834,10 +1813,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46308.71875</v>
+        <v>46310.71875</v>
       </c>
       <c r="B71">
-        <v>6790</v>
+        <v>6880</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1848,10 +1827,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46308.72916666666</v>
+        <v>46310.72916666666</v>
       </c>
       <c r="B72">
-        <v>6859</v>
+        <v>7018</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1862,10 +1841,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46308.73958333334</v>
+        <v>46310.73958333334</v>
       </c>
       <c r="B73">
-        <v>7034</v>
+        <v>7165</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1876,10 +1855,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46308.75</v>
+        <v>46310.75</v>
       </c>
       <c r="B74">
-        <v>7169</v>
+        <v>7320</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -1890,10 +1869,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46308.76041666666</v>
+        <v>46310.76041666666</v>
       </c>
       <c r="B75">
-        <v>7245</v>
+        <v>7344</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -1904,10 +1883,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46308.77083333334</v>
+        <v>46310.77083333334</v>
       </c>
       <c r="B76">
-        <v>7221</v>
+        <v>7388</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -1918,10 +1897,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46308.78125</v>
+        <v>46310.78125</v>
       </c>
       <c r="B77">
-        <v>7241</v>
+        <v>7388</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -1932,10 +1911,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46308.79166666666</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="B78">
-        <v>7251</v>
+        <v>7316</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -1946,10 +1925,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46308.80208333334</v>
+        <v>46310.80208333334</v>
       </c>
       <c r="B79">
-        <v>7259</v>
+        <v>7245</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -1960,10 +1939,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46308.8125</v>
+        <v>46310.8125</v>
       </c>
       <c r="B80">
-        <v>7212</v>
+        <v>7220</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -1974,10 +1953,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46308.82291666666</v>
+        <v>46310.82291666666</v>
       </c>
       <c r="B81">
-        <v>7128</v>
+        <v>7157</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -1988,10 +1967,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46308.83333333334</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="B82">
-        <v>6987</v>
+        <v>7032</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2002,10 +1981,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46308.84375</v>
+        <v>46310.84375</v>
       </c>
       <c r="B83">
-        <v>6897</v>
+        <v>6930</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2016,10 +1995,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46308.85416666666</v>
+        <v>46310.85416666666</v>
       </c>
       <c r="B84">
-        <v>6720</v>
+        <v>6841</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2030,10 +2009,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46308.86458333334</v>
+        <v>46310.86458333334</v>
       </c>
       <c r="B85">
-        <v>6625</v>
+        <v>6709</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2044,10 +2023,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46308.875</v>
+        <v>46310.875</v>
       </c>
       <c r="B86">
-        <v>6394</v>
+        <v>6471</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2058,7 +2037,7 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46308.88541666666</v>
+        <v>46310.88541666666</v>
       </c>
       <c r="B87">
         <v>6277</v>
@@ -2072,10 +2051,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46308.89583333334</v>
+        <v>46310.89583333334</v>
       </c>
       <c r="B88">
-        <v>6115</v>
+        <v>6179</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2086,10 +2065,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46308.90625</v>
+        <v>46310.90625</v>
       </c>
       <c r="B89">
-        <v>5934</v>
+        <v>6034</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2100,10 +2079,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46308.91666666666</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="B90">
-        <v>5835</v>
+        <v>5993</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2114,10 +2093,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46308.92708333334</v>
+        <v>46310.92708333334</v>
       </c>
       <c r="B91">
-        <v>5796</v>
+        <v>5836</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2128,10 +2107,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46308.9375</v>
+        <v>46310.9375</v>
       </c>
       <c r="B92">
-        <v>5674</v>
+        <v>5747</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2142,10 +2121,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46308.94791666666</v>
+        <v>46310.94791666666</v>
       </c>
       <c r="B93">
-        <v>5559</v>
+        <v>5672</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2156,10 +2135,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46308.95833333334</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="B94">
-        <v>5474</v>
+        <v>5607</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2170,10 +2149,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46308.96875</v>
+        <v>46310.96875</v>
       </c>
       <c r="B95">
-        <v>5378</v>
+        <v>5476</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2184,10 +2163,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46308.97916666666</v>
+        <v>46310.97916666666</v>
       </c>
       <c r="B96">
-        <v>5274</v>
+        <v>5389</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2198,10 +2177,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46308.98958333334</v>
+        <v>46310.98958333334</v>
       </c>
       <c r="B97">
-        <v>5176</v>
+        <v>5295</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2212,10 +2191,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B98">
-        <v>5157</v>
+        <v>5358</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2226,10 +2205,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46309.01041666666</v>
+        <v>46311.01041666666</v>
       </c>
       <c r="B99">
-        <v>5096</v>
+        <v>5327</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2240,10 +2219,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46309.02083333334</v>
+        <v>46311.02083333334</v>
       </c>
       <c r="B100">
-        <v>5208</v>
+        <v>5276</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2254,10 +2233,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46309.03125</v>
+        <v>46311.03125</v>
       </c>
       <c r="B101">
-        <v>5138</v>
+        <v>5269</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2268,10 +2247,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46309.04166666666</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="B102">
-        <v>4997</v>
+        <v>5268</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2282,10 +2261,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46309.05208333334</v>
+        <v>46311.05208333334</v>
       </c>
       <c r="B103">
-        <v>5104</v>
+        <v>5249</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2296,10 +2275,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46309.0625</v>
+        <v>46311.0625</v>
       </c>
       <c r="B104">
-        <v>5103</v>
+        <v>5253</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2310,10 +2289,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46309.07291666666</v>
+        <v>46311.07291666666</v>
       </c>
       <c r="B105">
-        <v>5214</v>
+        <v>5263</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2324,10 +2303,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46309.08333333334</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="B106">
-        <v>5201</v>
+        <v>5302</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2338,10 +2317,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46309.09375</v>
+        <v>46311.09375</v>
       </c>
       <c r="B107">
-        <v>5207</v>
+        <v>5297</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2352,10 +2331,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46309.10416666666</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="B108">
-        <v>5292</v>
+        <v>5330</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2366,10 +2345,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46309.11458333334</v>
+        <v>46311.11458333334</v>
       </c>
       <c r="B109">
-        <v>5325</v>
+        <v>5296</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2380,10 +2359,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46309.125</v>
+        <v>46311.125</v>
       </c>
       <c r="B110">
-        <v>5304</v>
+        <v>5362</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2394,10 +2373,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46309.13541666666</v>
+        <v>46311.13541666666</v>
       </c>
       <c r="B111">
-        <v>5320</v>
+        <v>5376</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2408,10 +2387,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46309.14583333334</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="B112">
-        <v>5411</v>
+        <v>5308</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2422,10 +2401,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46309.15625</v>
+        <v>46311.15625</v>
       </c>
       <c r="B113">
-        <v>5350</v>
+        <v>5304</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2436,10 +2415,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46309.16666666666</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="B114">
-        <v>5236</v>
+        <v>5324</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2450,10 +2429,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46309.17708333334</v>
+        <v>46311.17708333334</v>
       </c>
       <c r="B115">
-        <v>5172</v>
+        <v>5366</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2464,10 +2443,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46309.1875</v>
+        <v>46311.1875</v>
       </c>
       <c r="B116">
-        <v>5231</v>
+        <v>5428</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2478,10 +2457,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46309.19791666666</v>
+        <v>46311.19791666666</v>
       </c>
       <c r="B117">
-        <v>5317</v>
+        <v>5558</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2492,10 +2471,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46309.20833333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="B118">
-        <v>5564</v>
+        <v>5751</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2506,10 +2485,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46309.21875</v>
+        <v>46311.21875</v>
       </c>
       <c r="B119">
-        <v>5689</v>
+        <v>5851</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2520,10 +2499,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46309.22916666666</v>
+        <v>46311.22916666666</v>
       </c>
       <c r="B120">
-        <v>5869</v>
+        <v>5963</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2534,10 +2513,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46309.23958333334</v>
+        <v>46311.23958333334</v>
       </c>
       <c r="B121">
-        <v>6042</v>
+        <v>6157</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2548,10 +2527,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46309.25</v>
+        <v>46311.25</v>
       </c>
       <c r="B122">
-        <v>6385</v>
+        <v>6471</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2562,10 +2541,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46309.26041666666</v>
+        <v>46311.26041666666</v>
       </c>
       <c r="B123">
-        <v>6484</v>
+        <v>6667</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2576,10 +2555,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46309.27083333334</v>
+        <v>46311.27083333334</v>
       </c>
       <c r="B124">
-        <v>6425</v>
+        <v>6708</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2590,10 +2569,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46309.28125</v>
+        <v>46311.28125</v>
       </c>
       <c r="B125">
-        <v>6524</v>
+        <v>6803</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2604,10 +2583,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46309.29166666666</v>
+        <v>46311.29166666666</v>
       </c>
       <c r="B126">
-        <v>6717</v>
+        <v>6937</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2618,10 +2597,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46309.30208333334</v>
+        <v>46311.30208333334</v>
       </c>
       <c r="B127">
-        <v>6733</v>
+        <v>6978</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2632,10 +2611,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46309.3125</v>
+        <v>46311.3125</v>
       </c>
       <c r="B128">
-        <v>6655</v>
+        <v>6952</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2646,10 +2625,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46309.32291666666</v>
+        <v>46311.32291666666</v>
       </c>
       <c r="B129">
-        <v>6717</v>
+        <v>6899</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2660,10 +2639,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46309.33333333334</v>
+        <v>46311.33333333334</v>
       </c>
       <c r="B130">
-        <v>6542</v>
+        <v>6829</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2674,10 +2653,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46309.34375</v>
+        <v>46311.34375</v>
       </c>
       <c r="B131">
-        <v>6446</v>
+        <v>6745</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2688,10 +2667,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46309.35416666666</v>
+        <v>46311.35416666666</v>
       </c>
       <c r="B132">
-        <v>6358</v>
+        <v>6599</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2702,10 +2681,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46309.36458333334</v>
+        <v>46311.36458333334</v>
       </c>
       <c r="B133">
-        <v>6395</v>
+        <v>6515</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2716,10 +2695,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46309.375</v>
+        <v>46311.375</v>
       </c>
       <c r="B134">
-        <v>6032</v>
+        <v>6387</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2730,10 +2709,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46309.38541666666</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="B135">
-        <v>6007</v>
+        <v>6222</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2744,10 +2723,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46309.39583333334</v>
+        <v>46311.39583333334</v>
       </c>
       <c r="B136">
-        <v>5700</v>
+        <v>6156</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2758,10 +2737,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46309.40625</v>
+        <v>46311.40625</v>
       </c>
       <c r="B137">
-        <v>5655</v>
+        <v>6097</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2772,10 +2751,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46309.41666666666</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="B138">
-        <v>5286</v>
+        <v>5817</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2786,10 +2765,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46309.42708333334</v>
+        <v>46311.42708333334</v>
       </c>
       <c r="B139">
-        <v>5265</v>
+        <v>5758</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2800,10 +2779,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46309.4375</v>
+        <v>46311.4375</v>
       </c>
       <c r="B140">
-        <v>5236</v>
+        <v>5683</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2814,10 +2793,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46309.44791666666</v>
+        <v>46311.44791666666</v>
       </c>
       <c r="B141">
-        <v>5137</v>
+        <v>5580</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2828,10 +2807,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46309.45833333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="B142">
-        <v>4976</v>
+        <v>5425</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2842,10 +2821,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46309.46875</v>
+        <v>46311.46875</v>
       </c>
       <c r="B143">
-        <v>4973</v>
+        <v>5452</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2856,10 +2835,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46309.47916666666</v>
+        <v>46311.47916666666</v>
       </c>
       <c r="B144">
-        <v>4985</v>
+        <v>5559</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2870,10 +2849,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46309.48958333334</v>
+        <v>46311.48958333334</v>
       </c>
       <c r="B145">
-        <v>4873</v>
+        <v>5616</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2884,10 +2863,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="B146">
-        <v>4870</v>
+        <v>5458</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -2898,10 +2877,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46309.51041666666</v>
+        <v>46311.51041666666</v>
       </c>
       <c r="B147">
-        <v>4979</v>
+        <v>5363</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -2912,114 +2891,16 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46309.52083333334</v>
+        <v>46311.52083333334</v>
       </c>
       <c r="B148">
-        <v>4950</v>
+        <v>5339</v>
       </c>
       <c r="C148">
         <v>51</v>
       </c>
       <c r="D148" t="s">
         <v>150</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4">
-      <c r="A149" s="2">
-        <v>46309.53125</v>
-      </c>
-      <c r="B149">
-        <v>4816</v>
-      </c>
-      <c r="C149">
-        <v>52</v>
-      </c>
-      <c r="D149" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4">
-      <c r="A150" s="2">
-        <v>46309.54166666666</v>
-      </c>
-      <c r="B150">
-        <v>4773</v>
-      </c>
-      <c r="C150">
-        <v>53</v>
-      </c>
-      <c r="D150" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4">
-      <c r="A151" s="2">
-        <v>46309.55208333334</v>
-      </c>
-      <c r="B151">
-        <v>4766</v>
-      </c>
-      <c r="C151">
-        <v>54</v>
-      </c>
-      <c r="D151" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4">
-      <c r="A152" s="2">
-        <v>46309.5625</v>
-      </c>
-      <c r="B152">
-        <v>4728</v>
-      </c>
-      <c r="C152">
-        <v>55</v>
-      </c>
-      <c r="D152" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4">
-      <c r="A153" s="2">
-        <v>46309.57291666666</v>
-      </c>
-      <c r="B153">
-        <v>4723</v>
-      </c>
-      <c r="C153">
-        <v>56</v>
-      </c>
-      <c r="D153" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4">
-      <c r="A154" s="2">
-        <v>46309.58333333334</v>
-      </c>
-      <c r="B154">
-        <v>4768</v>
-      </c>
-      <c r="C154">
-        <v>57</v>
-      </c>
-      <c r="D154" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4">
-      <c r="A155" s="2">
-        <v>46309.59375</v>
-      </c>
-      <c r="B155">
-        <v>4699</v>
-      </c>
-      <c r="C155">
-        <v>58</v>
-      </c>
-      <c r="D155" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,445 +28,397 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>15.10.20261</t>
-  </si>
-  <si>
-    <t>15.10.20262</t>
-  </si>
-  <si>
-    <t>15.10.20263</t>
-  </si>
-  <si>
-    <t>15.10.20264</t>
-  </si>
-  <si>
-    <t>15.10.20265</t>
-  </si>
-  <si>
-    <t>15.10.20266</t>
-  </si>
-  <si>
-    <t>15.10.20267</t>
-  </si>
-  <si>
-    <t>15.10.20268</t>
-  </si>
-  <si>
-    <t>15.10.20269</t>
-  </si>
-  <si>
-    <t>15.10.202610</t>
-  </si>
-  <si>
-    <t>15.10.202611</t>
-  </si>
-  <si>
-    <t>15.10.202612</t>
-  </si>
-  <si>
-    <t>15.10.202613</t>
-  </si>
-  <si>
-    <t>15.10.202614</t>
-  </si>
-  <si>
-    <t>15.10.202615</t>
-  </si>
-  <si>
-    <t>15.10.202616</t>
-  </si>
-  <si>
-    <t>15.10.202617</t>
-  </si>
-  <si>
-    <t>15.10.202618</t>
-  </si>
-  <si>
-    <t>15.10.202619</t>
-  </si>
-  <si>
-    <t>15.10.202620</t>
-  </si>
-  <si>
-    <t>15.10.202621</t>
-  </si>
-  <si>
-    <t>15.10.202622</t>
-  </si>
-  <si>
-    <t>15.10.202623</t>
-  </si>
-  <si>
-    <t>15.10.202624</t>
-  </si>
-  <si>
-    <t>15.10.202625</t>
-  </si>
-  <si>
-    <t>15.10.202626</t>
-  </si>
-  <si>
-    <t>15.10.202627</t>
-  </si>
-  <si>
-    <t>15.10.202628</t>
-  </si>
-  <si>
-    <t>15.10.202629</t>
-  </si>
-  <si>
-    <t>15.10.202630</t>
-  </si>
-  <si>
-    <t>15.10.202631</t>
-  </si>
-  <si>
-    <t>15.10.202632</t>
-  </si>
-  <si>
-    <t>15.10.202633</t>
-  </si>
-  <si>
-    <t>15.10.202634</t>
-  </si>
-  <si>
-    <t>15.10.202635</t>
-  </si>
-  <si>
-    <t>15.10.202636</t>
-  </si>
-  <si>
-    <t>15.10.202637</t>
-  </si>
-  <si>
-    <t>15.10.202638</t>
-  </si>
-  <si>
-    <t>15.10.202639</t>
-  </si>
-  <si>
-    <t>15.10.202640</t>
-  </si>
-  <si>
-    <t>15.10.202641</t>
-  </si>
-  <si>
-    <t>15.10.202642</t>
-  </si>
-  <si>
-    <t>15.10.202643</t>
-  </si>
-  <si>
-    <t>15.10.202644</t>
-  </si>
-  <si>
-    <t>15.10.202645</t>
-  </si>
-  <si>
-    <t>15.10.202646</t>
-  </si>
-  <si>
-    <t>15.10.202647</t>
-  </si>
-  <si>
-    <t>15.10.202648</t>
-  </si>
-  <si>
-    <t>15.10.202649</t>
-  </si>
-  <si>
-    <t>15.10.202650</t>
-  </si>
-  <si>
-    <t>15.10.202651</t>
-  </si>
-  <si>
-    <t>15.10.202652</t>
-  </si>
-  <si>
-    <t>15.10.202653</t>
-  </si>
-  <si>
-    <t>15.10.202654</t>
-  </si>
-  <si>
-    <t>15.10.202655</t>
-  </si>
-  <si>
-    <t>15.10.202656</t>
-  </si>
-  <si>
-    <t>15.10.202657</t>
-  </si>
-  <si>
-    <t>15.10.202658</t>
-  </si>
-  <si>
-    <t>15.10.202659</t>
-  </si>
-  <si>
-    <t>15.10.202660</t>
-  </si>
-  <si>
-    <t>15.10.202661</t>
-  </si>
-  <si>
-    <t>15.10.202662</t>
-  </si>
-  <si>
-    <t>15.10.202663</t>
-  </si>
-  <si>
-    <t>15.10.202664</t>
-  </si>
-  <si>
-    <t>15.10.202665</t>
-  </si>
-  <si>
-    <t>15.10.202666</t>
-  </si>
-  <si>
-    <t>15.10.202667</t>
-  </si>
-  <si>
-    <t>15.10.202668</t>
-  </si>
-  <si>
-    <t>15.10.202669</t>
-  </si>
-  <si>
-    <t>15.10.202670</t>
-  </si>
-  <si>
-    <t>15.10.202671</t>
-  </si>
-  <si>
-    <t>15.10.202672</t>
-  </si>
-  <si>
-    <t>15.10.202673</t>
-  </si>
-  <si>
-    <t>15.10.202674</t>
-  </si>
-  <si>
-    <t>15.10.202675</t>
-  </si>
-  <si>
-    <t>15.10.202676</t>
-  </si>
-  <si>
-    <t>15.10.202677</t>
-  </si>
-  <si>
-    <t>15.10.202678</t>
-  </si>
-  <si>
-    <t>15.10.202679</t>
-  </si>
-  <si>
-    <t>15.10.202680</t>
-  </si>
-  <si>
-    <t>15.10.202681</t>
-  </si>
-  <si>
-    <t>15.10.202682</t>
-  </si>
-  <si>
-    <t>15.10.202683</t>
-  </si>
-  <si>
-    <t>15.10.202684</t>
-  </si>
-  <si>
-    <t>15.10.202685</t>
-  </si>
-  <si>
-    <t>15.10.202686</t>
-  </si>
-  <si>
-    <t>15.10.202687</t>
-  </si>
-  <si>
-    <t>15.10.202688</t>
-  </si>
-  <si>
-    <t>15.10.202689</t>
-  </si>
-  <si>
-    <t>15.10.202690</t>
-  </si>
-  <si>
-    <t>15.10.202691</t>
-  </si>
-  <si>
-    <t>15.10.202692</t>
-  </si>
-  <si>
-    <t>15.10.202693</t>
-  </si>
-  <si>
-    <t>15.10.202694</t>
-  </si>
-  <si>
-    <t>15.10.202695</t>
-  </si>
-  <si>
-    <t>15.10.202696</t>
-  </si>
-  <si>
-    <t>16.10.20261</t>
-  </si>
-  <si>
-    <t>16.10.20262</t>
-  </si>
-  <si>
-    <t>16.10.20263</t>
-  </si>
-  <si>
-    <t>16.10.20264</t>
-  </si>
-  <si>
-    <t>16.10.20265</t>
-  </si>
-  <si>
-    <t>16.10.20266</t>
-  </si>
-  <si>
-    <t>16.10.20267</t>
-  </si>
-  <si>
-    <t>16.10.20268</t>
-  </si>
-  <si>
-    <t>16.10.20269</t>
-  </si>
-  <si>
-    <t>16.10.202610</t>
-  </si>
-  <si>
-    <t>16.10.202611</t>
-  </si>
-  <si>
-    <t>16.10.202612</t>
-  </si>
-  <si>
-    <t>16.10.202613</t>
-  </si>
-  <si>
-    <t>16.10.202614</t>
-  </si>
-  <si>
-    <t>16.10.202615</t>
-  </si>
-  <si>
-    <t>16.10.202616</t>
-  </si>
-  <si>
-    <t>16.10.202617</t>
-  </si>
-  <si>
-    <t>16.10.202618</t>
-  </si>
-  <si>
-    <t>16.10.202619</t>
-  </si>
-  <si>
-    <t>16.10.202620</t>
-  </si>
-  <si>
-    <t>16.10.202621</t>
-  </si>
-  <si>
-    <t>16.10.202622</t>
-  </si>
-  <si>
-    <t>16.10.202623</t>
-  </si>
-  <si>
-    <t>16.10.202624</t>
-  </si>
-  <si>
-    <t>16.10.202625</t>
-  </si>
-  <si>
-    <t>16.10.202626</t>
-  </si>
-  <si>
-    <t>16.10.202627</t>
-  </si>
-  <si>
-    <t>16.10.202628</t>
-  </si>
-  <si>
-    <t>16.10.202629</t>
-  </si>
-  <si>
-    <t>16.10.202630</t>
-  </si>
-  <si>
-    <t>16.10.202631</t>
-  </si>
-  <si>
-    <t>16.10.202632</t>
-  </si>
-  <si>
-    <t>16.10.202633</t>
-  </si>
-  <si>
-    <t>16.10.202634</t>
-  </si>
-  <si>
-    <t>16.10.202635</t>
-  </si>
-  <si>
-    <t>16.10.202636</t>
-  </si>
-  <si>
-    <t>16.10.202637</t>
-  </si>
-  <si>
-    <t>16.10.202638</t>
-  </si>
-  <si>
-    <t>16.10.202639</t>
-  </si>
-  <si>
-    <t>16.10.202640</t>
-  </si>
-  <si>
-    <t>16.10.202641</t>
-  </si>
-  <si>
-    <t>16.10.202642</t>
-  </si>
-  <si>
-    <t>16.10.202643</t>
-  </si>
-  <si>
-    <t>16.10.202644</t>
-  </si>
-  <si>
-    <t>16.10.202645</t>
-  </si>
-  <si>
-    <t>16.10.202646</t>
-  </si>
-  <si>
-    <t>16.10.202647</t>
-  </si>
-  <si>
-    <t>16.10.202648</t>
-  </si>
-  <si>
-    <t>16.10.202649</t>
-  </si>
-  <si>
-    <t>16.10.202650</t>
-  </si>
-  <si>
-    <t>16.10.202651</t>
+    <t>20.10.20261</t>
+  </si>
+  <si>
+    <t>20.10.20262</t>
+  </si>
+  <si>
+    <t>20.10.20263</t>
+  </si>
+  <si>
+    <t>20.10.20264</t>
+  </si>
+  <si>
+    <t>20.10.20265</t>
+  </si>
+  <si>
+    <t>20.10.20266</t>
+  </si>
+  <si>
+    <t>20.10.20267</t>
+  </si>
+  <si>
+    <t>20.10.20268</t>
+  </si>
+  <si>
+    <t>20.10.20269</t>
+  </si>
+  <si>
+    <t>20.10.202610</t>
+  </si>
+  <si>
+    <t>20.10.202611</t>
+  </si>
+  <si>
+    <t>20.10.202612</t>
+  </si>
+  <si>
+    <t>20.10.202613</t>
+  </si>
+  <si>
+    <t>20.10.202614</t>
+  </si>
+  <si>
+    <t>20.10.202615</t>
+  </si>
+  <si>
+    <t>20.10.202616</t>
+  </si>
+  <si>
+    <t>20.10.202617</t>
+  </si>
+  <si>
+    <t>20.10.202618</t>
+  </si>
+  <si>
+    <t>20.10.202619</t>
+  </si>
+  <si>
+    <t>20.10.202620</t>
+  </si>
+  <si>
+    <t>20.10.202621</t>
+  </si>
+  <si>
+    <t>20.10.202622</t>
+  </si>
+  <si>
+    <t>20.10.202623</t>
+  </si>
+  <si>
+    <t>20.10.202624</t>
+  </si>
+  <si>
+    <t>20.10.202625</t>
+  </si>
+  <si>
+    <t>20.10.202626</t>
+  </si>
+  <si>
+    <t>20.10.202627</t>
+  </si>
+  <si>
+    <t>20.10.202628</t>
+  </si>
+  <si>
+    <t>20.10.202629</t>
+  </si>
+  <si>
+    <t>20.10.202630</t>
+  </si>
+  <si>
+    <t>20.10.202631</t>
+  </si>
+  <si>
+    <t>20.10.202632</t>
+  </si>
+  <si>
+    <t>20.10.202633</t>
+  </si>
+  <si>
+    <t>20.10.202634</t>
+  </si>
+  <si>
+    <t>20.10.202635</t>
+  </si>
+  <si>
+    <t>20.10.202636</t>
+  </si>
+  <si>
+    <t>20.10.202637</t>
+  </si>
+  <si>
+    <t>20.10.202638</t>
+  </si>
+  <si>
+    <t>20.10.202639</t>
+  </si>
+  <si>
+    <t>20.10.202640</t>
+  </si>
+  <si>
+    <t>20.10.202641</t>
+  </si>
+  <si>
+    <t>20.10.202642</t>
+  </si>
+  <si>
+    <t>20.10.202643</t>
+  </si>
+  <si>
+    <t>20.10.202644</t>
+  </si>
+  <si>
+    <t>20.10.202645</t>
+  </si>
+  <si>
+    <t>20.10.202646</t>
+  </si>
+  <si>
+    <t>20.10.202647</t>
+  </si>
+  <si>
+    <t>20.10.202648</t>
+  </si>
+  <si>
+    <t>20.10.202649</t>
+  </si>
+  <si>
+    <t>20.10.202650</t>
+  </si>
+  <si>
+    <t>20.10.202651</t>
+  </si>
+  <si>
+    <t>20.10.202652</t>
+  </si>
+  <si>
+    <t>20.10.202653</t>
+  </si>
+  <si>
+    <t>20.10.202654</t>
+  </si>
+  <si>
+    <t>20.10.202655</t>
+  </si>
+  <si>
+    <t>20.10.202656</t>
+  </si>
+  <si>
+    <t>20.10.202657</t>
+  </si>
+  <si>
+    <t>20.10.202658</t>
+  </si>
+  <si>
+    <t>20.10.202659</t>
+  </si>
+  <si>
+    <t>20.10.202660</t>
+  </si>
+  <si>
+    <t>20.10.202661</t>
+  </si>
+  <si>
+    <t>20.10.202662</t>
+  </si>
+  <si>
+    <t>20.10.202663</t>
+  </si>
+  <si>
+    <t>20.10.202664</t>
+  </si>
+  <si>
+    <t>20.10.202665</t>
+  </si>
+  <si>
+    <t>20.10.202666</t>
+  </si>
+  <si>
+    <t>20.10.202667</t>
+  </si>
+  <si>
+    <t>20.10.202668</t>
+  </si>
+  <si>
+    <t>20.10.202669</t>
+  </si>
+  <si>
+    <t>20.10.202670</t>
+  </si>
+  <si>
+    <t>20.10.202671</t>
+  </si>
+  <si>
+    <t>20.10.202672</t>
+  </si>
+  <si>
+    <t>20.10.202673</t>
+  </si>
+  <si>
+    <t>20.10.202674</t>
+  </si>
+  <si>
+    <t>20.10.202675</t>
+  </si>
+  <si>
+    <t>20.10.202676</t>
+  </si>
+  <si>
+    <t>20.10.202677</t>
+  </si>
+  <si>
+    <t>20.10.202678</t>
+  </si>
+  <si>
+    <t>20.10.202679</t>
+  </si>
+  <si>
+    <t>20.10.202680</t>
+  </si>
+  <si>
+    <t>20.10.202681</t>
+  </si>
+  <si>
+    <t>20.10.202682</t>
+  </si>
+  <si>
+    <t>20.10.202683</t>
+  </si>
+  <si>
+    <t>20.10.202684</t>
+  </si>
+  <si>
+    <t>20.10.202685</t>
+  </si>
+  <si>
+    <t>20.10.202686</t>
+  </si>
+  <si>
+    <t>20.10.202687</t>
+  </si>
+  <si>
+    <t>20.10.202688</t>
+  </si>
+  <si>
+    <t>20.10.202689</t>
+  </si>
+  <si>
+    <t>20.10.202690</t>
+  </si>
+  <si>
+    <t>20.10.202691</t>
+  </si>
+  <si>
+    <t>20.10.202692</t>
+  </si>
+  <si>
+    <t>20.10.202693</t>
+  </si>
+  <si>
+    <t>20.10.202694</t>
+  </si>
+  <si>
+    <t>20.10.202695</t>
+  </si>
+  <si>
+    <t>20.10.202696</t>
+  </si>
+  <si>
+    <t>21.10.20261</t>
+  </si>
+  <si>
+    <t>21.10.20262</t>
+  </si>
+  <si>
+    <t>21.10.20263</t>
+  </si>
+  <si>
+    <t>21.10.20264</t>
+  </si>
+  <si>
+    <t>21.10.20265</t>
+  </si>
+  <si>
+    <t>21.10.20266</t>
+  </si>
+  <si>
+    <t>21.10.20267</t>
+  </si>
+  <si>
+    <t>21.10.20268</t>
+  </si>
+  <si>
+    <t>21.10.20269</t>
+  </si>
+  <si>
+    <t>21.10.202610</t>
+  </si>
+  <si>
+    <t>21.10.202611</t>
+  </si>
+  <si>
+    <t>21.10.202612</t>
+  </si>
+  <si>
+    <t>21.10.202613</t>
+  </si>
+  <si>
+    <t>21.10.202614</t>
+  </si>
+  <si>
+    <t>21.10.202615</t>
+  </si>
+  <si>
+    <t>21.10.202616</t>
+  </si>
+  <si>
+    <t>21.10.202617</t>
+  </si>
+  <si>
+    <t>21.10.202618</t>
+  </si>
+  <si>
+    <t>21.10.202619</t>
+  </si>
+  <si>
+    <t>21.10.202620</t>
+  </si>
+  <si>
+    <t>21.10.202621</t>
+  </si>
+  <si>
+    <t>21.10.202622</t>
+  </si>
+  <si>
+    <t>21.10.202623</t>
+  </si>
+  <si>
+    <t>21.10.202624</t>
+  </si>
+  <si>
+    <t>21.10.202625</t>
+  </si>
+  <si>
+    <t>21.10.202626</t>
+  </si>
+  <si>
+    <t>21.10.202627</t>
+  </si>
+  <si>
+    <t>21.10.202628</t>
+  </si>
+  <si>
+    <t>21.10.202629</t>
+  </si>
+  <si>
+    <t>21.10.202630</t>
+  </si>
+  <si>
+    <t>21.10.202631</t>
+  </si>
+  <si>
+    <t>21.10.202632</t>
+  </si>
+  <si>
+    <t>21.10.202633</t>
+  </si>
+  <si>
+    <t>21.10.202634</t>
+  </si>
+  <si>
+    <t>21.10.202635</t>
   </si>
 </sst>
 </file>
@@ -828,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D148"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -847,10 +799,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="B2">
-        <v>5230</v>
+        <v>5402</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -861,10 +813,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46310.01041666666</v>
+        <v>46315.01041666666</v>
       </c>
       <c r="B3">
-        <v>5276</v>
+        <v>5393</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -875,10 +827,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46310.02083333334</v>
+        <v>46315.02083333334</v>
       </c>
       <c r="B4">
-        <v>5188</v>
+        <v>5302</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -889,10 +841,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46310.03125</v>
+        <v>46315.03125</v>
       </c>
       <c r="B5">
-        <v>5205</v>
+        <v>5357</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -903,10 +855,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46310.04166666666</v>
+        <v>46315.04166666666</v>
       </c>
       <c r="B6">
-        <v>5160</v>
+        <v>5275</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -917,10 +869,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46310.05208333334</v>
+        <v>46315.05208333334</v>
       </c>
       <c r="B7">
-        <v>5234</v>
+        <v>5281</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -931,10 +883,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46310.0625</v>
+        <v>46315.0625</v>
       </c>
       <c r="B8">
-        <v>5188</v>
+        <v>5267</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -945,10 +897,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46310.07291666666</v>
+        <v>46315.07291666666</v>
       </c>
       <c r="B9">
-        <v>5252</v>
+        <v>5316</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -959,10 +911,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46310.08333333334</v>
+        <v>46315.08333333334</v>
       </c>
       <c r="B10">
-        <v>5265</v>
+        <v>5215</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -973,10 +925,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46310.09375</v>
+        <v>46315.09375</v>
       </c>
       <c r="B11">
-        <v>5426</v>
+        <v>5247</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -987,10 +939,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46310.10416666666</v>
+        <v>46315.10416666666</v>
       </c>
       <c r="B12">
-        <v>5383</v>
+        <v>5203</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1001,10 +953,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46310.11458333334</v>
+        <v>46315.11458333334</v>
       </c>
       <c r="B13">
-        <v>5245</v>
+        <v>5262</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1015,10 +967,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46310.125</v>
+        <v>46315.125</v>
       </c>
       <c r="B14">
-        <v>5225</v>
+        <v>5258</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1029,10 +981,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46310.13541666666</v>
+        <v>46315.13541666666</v>
       </c>
       <c r="B15">
-        <v>5258</v>
+        <v>5229</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1043,10 +995,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46310.14583333334</v>
+        <v>46315.14583333334</v>
       </c>
       <c r="B16">
-        <v>5234</v>
+        <v>5280</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1057,10 +1009,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46310.15625</v>
+        <v>46315.15625</v>
       </c>
       <c r="B17">
-        <v>5231</v>
+        <v>5244</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1071,10 +1023,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46310.16666666666</v>
+        <v>46315.16666666666</v>
       </c>
       <c r="B18">
-        <v>5204</v>
+        <v>5229</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1085,10 +1037,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46310.17708333334</v>
+        <v>46315.17708333334</v>
       </c>
       <c r="B19">
-        <v>5303</v>
+        <v>5319</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1099,10 +1051,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46310.1875</v>
+        <v>46315.1875</v>
       </c>
       <c r="B20">
-        <v>5362</v>
+        <v>5408</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1113,10 +1065,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46310.19791666666</v>
+        <v>46315.19791666666</v>
       </c>
       <c r="B21">
-        <v>5409</v>
+        <v>5477</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1127,10 +1079,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46310.20833333334</v>
+        <v>46315.20833333334</v>
       </c>
       <c r="B22">
-        <v>5685</v>
+        <v>5629</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1141,10 +1093,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46310.21875</v>
+        <v>46315.21875</v>
       </c>
       <c r="B23">
-        <v>5835</v>
+        <v>5816</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1155,10 +1107,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46310.22916666666</v>
+        <v>46315.22916666666</v>
       </c>
       <c r="B24">
-        <v>5955</v>
+        <v>5972</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1169,10 +1121,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46310.23958333334</v>
+        <v>46315.23958333334</v>
       </c>
       <c r="B25">
-        <v>6174</v>
+        <v>6177</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1183,10 +1135,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46310.25</v>
+        <v>46315.25</v>
       </c>
       <c r="B26">
-        <v>6474</v>
+        <v>6449</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1197,10 +1149,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46310.26041666666</v>
+        <v>46315.26041666666</v>
       </c>
       <c r="B27">
-        <v>6634</v>
+        <v>6576</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1211,10 +1163,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46310.27083333334</v>
+        <v>46315.27083333334</v>
       </c>
       <c r="B28">
-        <v>6741</v>
+        <v>6725</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1225,10 +1177,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46310.28125</v>
+        <v>46315.28125</v>
       </c>
       <c r="B29">
-        <v>6731</v>
+        <v>6801</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1239,10 +1191,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46310.29166666666</v>
+        <v>46315.29166666666</v>
       </c>
       <c r="B30">
-        <v>6866</v>
+        <v>6908</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1253,10 +1205,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46310.30208333334</v>
+        <v>46315.30208333334</v>
       </c>
       <c r="B31">
-        <v>6917</v>
+        <v>7032</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1267,10 +1219,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46310.3125</v>
+        <v>46315.3125</v>
       </c>
       <c r="B32">
-        <v>6910</v>
+        <v>7075</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1281,10 +1233,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46310.32291666666</v>
+        <v>46315.32291666666</v>
       </c>
       <c r="B33">
-        <v>6852</v>
+        <v>7005</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1295,10 +1247,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46310.33333333334</v>
+        <v>46315.33333333334</v>
       </c>
       <c r="B34">
-        <v>6830</v>
+        <v>6932</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1309,10 +1261,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46310.34375</v>
+        <v>46315.34375</v>
       </c>
       <c r="B35">
-        <v>6766</v>
+        <v>6856</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1323,10 +1275,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46310.35416666666</v>
+        <v>46315.35416666666</v>
       </c>
       <c r="B36">
-        <v>6748</v>
+        <v>6774</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1337,10 +1289,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46310.36458333334</v>
+        <v>46315.36458333334</v>
       </c>
       <c r="B37">
-        <v>6627</v>
+        <v>6570</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1351,10 +1303,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46310.375</v>
+        <v>46315.375</v>
       </c>
       <c r="B38">
-        <v>6527</v>
+        <v>6436</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1365,10 +1317,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46310.38541666666</v>
+        <v>46315.38541666666</v>
       </c>
       <c r="B39">
-        <v>6471</v>
+        <v>6273</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1379,10 +1331,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46310.39583333334</v>
+        <v>46315.39583333334</v>
       </c>
       <c r="B40">
-        <v>6465</v>
+        <v>6176</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1393,10 +1345,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46310.40625</v>
+        <v>46315.40625</v>
       </c>
       <c r="B41">
-        <v>6448</v>
+        <v>6129</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1407,10 +1359,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46310.41666666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="B42">
-        <v>6203</v>
+        <v>5836</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1421,10 +1373,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46310.42708333334</v>
+        <v>46315.42708333334</v>
       </c>
       <c r="B43">
-        <v>6117</v>
+        <v>5613</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1435,10 +1387,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46310.4375</v>
+        <v>46315.4375</v>
       </c>
       <c r="B44">
-        <v>6176</v>
+        <v>5536</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1449,10 +1401,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46310.44791666666</v>
+        <v>46315.44791666666</v>
       </c>
       <c r="B45">
-        <v>6170</v>
+        <v>5379</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1463,10 +1415,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46310.45833333334</v>
+        <v>46315.45833333334</v>
       </c>
       <c r="B46">
-        <v>5987</v>
+        <v>5220</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1477,10 +1429,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46310.46875</v>
+        <v>46315.46875</v>
       </c>
       <c r="B47">
-        <v>5971</v>
+        <v>5226</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1491,10 +1443,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46310.47916666666</v>
+        <v>46315.47916666666</v>
       </c>
       <c r="B48">
-        <v>5964</v>
+        <v>5023</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1505,10 +1457,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46310.48958333334</v>
+        <v>46315.48958333334</v>
       </c>
       <c r="B49">
-        <v>5963</v>
+        <v>5057</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1519,10 +1471,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46310.5</v>
+        <v>46315.5</v>
       </c>
       <c r="B50">
-        <v>6056</v>
+        <v>5075</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1533,10 +1485,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46310.51041666666</v>
+        <v>46315.51041666666</v>
       </c>
       <c r="B51">
-        <v>6118</v>
+        <v>5171</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1547,10 +1499,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46310.52083333334</v>
+        <v>46315.52083333334</v>
       </c>
       <c r="B52">
-        <v>6104</v>
+        <v>5118</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1561,10 +1513,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46310.53125</v>
+        <v>46315.53125</v>
       </c>
       <c r="B53">
-        <v>6190</v>
+        <v>5077</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1575,10 +1527,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46310.54166666666</v>
+        <v>46315.54166666666</v>
       </c>
       <c r="B54">
-        <v>5870</v>
+        <v>5172</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1589,10 +1541,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46310.55208333334</v>
+        <v>46315.55208333334</v>
       </c>
       <c r="B55">
-        <v>5915</v>
+        <v>5139</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1603,10 +1555,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46310.5625</v>
+        <v>46315.5625</v>
       </c>
       <c r="B56">
-        <v>5918</v>
+        <v>5243</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1617,10 +1569,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46310.57291666666</v>
+        <v>46315.57291666666</v>
       </c>
       <c r="B57">
-        <v>5952</v>
+        <v>5216</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1631,10 +1583,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46310.58333333334</v>
+        <v>46315.58333333334</v>
       </c>
       <c r="B58">
-        <v>5965</v>
+        <v>5206</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1645,10 +1597,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46310.59375</v>
+        <v>46315.59375</v>
       </c>
       <c r="B59">
-        <v>5957</v>
+        <v>5182</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1659,10 +1611,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46310.60416666666</v>
+        <v>46315.60416666666</v>
       </c>
       <c r="B60">
-        <v>5786</v>
+        <v>5300</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1673,10 +1625,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46310.61458333334</v>
+        <v>46315.61458333334</v>
       </c>
       <c r="B61">
-        <v>5899</v>
+        <v>5318</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1687,10 +1639,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46310.625</v>
+        <v>46315.625</v>
       </c>
       <c r="B62">
-        <v>5999</v>
+        <v>5497</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1701,10 +1653,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46310.63541666666</v>
+        <v>46315.63541666666</v>
       </c>
       <c r="B63">
-        <v>6056</v>
+        <v>5581</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1715,10 +1667,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46310.64583333334</v>
+        <v>46315.64583333334</v>
       </c>
       <c r="B64">
-        <v>6169</v>
+        <v>5694</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1729,10 +1681,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46310.65625</v>
+        <v>46315.65625</v>
       </c>
       <c r="B65">
-        <v>6287</v>
+        <v>5791</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1743,10 +1695,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46310.66666666666</v>
+        <v>46315.66666666666</v>
       </c>
       <c r="B66">
-        <v>6310</v>
+        <v>5965</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1757,10 +1709,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46310.67708333334</v>
+        <v>46315.67708333334</v>
       </c>
       <c r="B67">
-        <v>6474</v>
+        <v>6159</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1771,10 +1723,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46310.6875</v>
+        <v>46315.6875</v>
       </c>
       <c r="B68">
-        <v>6664</v>
+        <v>6373</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1785,10 +1737,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46310.69791666666</v>
+        <v>46315.69791666666</v>
       </c>
       <c r="B69">
-        <v>6746</v>
+        <v>6486</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1799,10 +1751,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46310.70833333334</v>
+        <v>46315.70833333334</v>
       </c>
       <c r="B70">
-        <v>6751</v>
+        <v>6578</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1813,10 +1765,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46310.71875</v>
+        <v>46315.71875</v>
       </c>
       <c r="B71">
-        <v>6880</v>
+        <v>6667</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1827,10 +1779,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46310.72916666666</v>
+        <v>46315.72916666666</v>
       </c>
       <c r="B72">
-        <v>7018</v>
+        <v>6863</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1841,10 +1793,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46310.73958333334</v>
+        <v>46315.73958333334</v>
       </c>
       <c r="B73">
-        <v>7165</v>
+        <v>6978</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1855,10 +1807,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46310.75</v>
+        <v>46315.75</v>
       </c>
       <c r="B74">
-        <v>7320</v>
+        <v>7265</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -1869,10 +1821,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46310.76041666666</v>
+        <v>46315.76041666666</v>
       </c>
       <c r="B75">
-        <v>7344</v>
+        <v>7214</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -1883,10 +1835,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46310.77083333334</v>
+        <v>46315.77083333334</v>
       </c>
       <c r="B76">
-        <v>7388</v>
+        <v>7260</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -1897,10 +1849,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46310.78125</v>
+        <v>46315.78125</v>
       </c>
       <c r="B77">
-        <v>7388</v>
+        <v>7197</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -1911,10 +1863,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46310.79166666666</v>
+        <v>46315.79166666666</v>
       </c>
       <c r="B78">
-        <v>7316</v>
+        <v>7185</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -1925,10 +1877,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46310.80208333334</v>
+        <v>46315.80208333334</v>
       </c>
       <c r="B79">
-        <v>7245</v>
+        <v>7123</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -1939,10 +1891,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46310.8125</v>
+        <v>46315.8125</v>
       </c>
       <c r="B80">
-        <v>7220</v>
+        <v>7120</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -1953,10 +1905,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46310.82291666666</v>
+        <v>46315.82291666666</v>
       </c>
       <c r="B81">
-        <v>7157</v>
+        <v>7015</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -1967,10 +1919,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46310.83333333334</v>
+        <v>46315.83333333334</v>
       </c>
       <c r="B82">
-        <v>7032</v>
+        <v>6886</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -1981,10 +1933,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46310.84375</v>
+        <v>46315.84375</v>
       </c>
       <c r="B83">
-        <v>6930</v>
+        <v>6851</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -1995,10 +1947,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46310.85416666666</v>
+        <v>46315.85416666666</v>
       </c>
       <c r="B84">
-        <v>6841</v>
+        <v>6691</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2009,10 +1961,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46310.86458333334</v>
+        <v>46315.86458333334</v>
       </c>
       <c r="B85">
-        <v>6709</v>
+        <v>6581</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2023,10 +1975,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46310.875</v>
+        <v>46315.875</v>
       </c>
       <c r="B86">
-        <v>6471</v>
+        <v>6410</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2037,10 +1989,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46310.88541666666</v>
+        <v>46315.88541666666</v>
       </c>
       <c r="B87">
-        <v>6277</v>
+        <v>6269</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2051,10 +2003,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46310.89583333334</v>
+        <v>46315.89583333334</v>
       </c>
       <c r="B88">
-        <v>6179</v>
+        <v>6052</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2065,10 +2017,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46310.90625</v>
+        <v>46315.90625</v>
       </c>
       <c r="B89">
-        <v>6034</v>
+        <v>5901</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2079,10 +2031,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46310.91666666666</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="B90">
-        <v>5993</v>
+        <v>5891</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2093,10 +2045,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46310.92708333334</v>
+        <v>46315.92708333334</v>
       </c>
       <c r="B91">
-        <v>5836</v>
+        <v>5831</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2107,10 +2059,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46310.9375</v>
+        <v>46315.9375</v>
       </c>
       <c r="B92">
-        <v>5747</v>
+        <v>5798</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2121,10 +2073,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46310.94791666666</v>
+        <v>46315.94791666666</v>
       </c>
       <c r="B93">
-        <v>5672</v>
+        <v>5767</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2135,10 +2087,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46310.95833333334</v>
+        <v>46315.95833333334</v>
       </c>
       <c r="B94">
-        <v>5607</v>
+        <v>5542</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2149,10 +2101,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46310.96875</v>
+        <v>46315.96875</v>
       </c>
       <c r="B95">
-        <v>5476</v>
+        <v>5415</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2163,10 +2115,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46310.97916666666</v>
+        <v>46315.97916666666</v>
       </c>
       <c r="B96">
-        <v>5389</v>
+        <v>5362</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2177,10 +2129,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46310.98958333334</v>
+        <v>46315.98958333334</v>
       </c>
       <c r="B97">
-        <v>5295</v>
+        <v>5376</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2191,10 +2143,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="B98">
-        <v>5358</v>
+        <v>5265</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2205,10 +2157,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46311.01041666666</v>
+        <v>46316.01041666666</v>
       </c>
       <c r="B99">
-        <v>5327</v>
+        <v>5213</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2219,10 +2171,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46311.02083333334</v>
+        <v>46316.02083333334</v>
       </c>
       <c r="B100">
-        <v>5276</v>
+        <v>5250</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2233,10 +2185,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46311.03125</v>
+        <v>46316.03125</v>
       </c>
       <c r="B101">
-        <v>5269</v>
+        <v>5207</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2247,10 +2199,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46311.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="B102">
-        <v>5268</v>
+        <v>5226</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2261,10 +2213,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46311.05208333334</v>
+        <v>46316.05208333334</v>
       </c>
       <c r="B103">
-        <v>5249</v>
+        <v>5286</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2275,10 +2227,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46311.0625</v>
+        <v>46316.0625</v>
       </c>
       <c r="B104">
-        <v>5253</v>
+        <v>5181</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2289,10 +2241,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46311.07291666666</v>
+        <v>46316.07291666666</v>
       </c>
       <c r="B105">
-        <v>5263</v>
+        <v>5176</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2303,10 +2255,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46311.08333333334</v>
+        <v>46316.08333333334</v>
       </c>
       <c r="B106">
-        <v>5302</v>
+        <v>5168</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2317,10 +2269,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46311.09375</v>
+        <v>46316.09375</v>
       </c>
       <c r="B107">
-        <v>5297</v>
+        <v>5167</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2331,10 +2283,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46311.10416666666</v>
+        <v>46316.10416666666</v>
       </c>
       <c r="B108">
-        <v>5330</v>
+        <v>5208</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2345,10 +2297,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46311.11458333334</v>
+        <v>46316.11458333334</v>
       </c>
       <c r="B109">
-        <v>5296</v>
+        <v>5144</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2359,10 +2311,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46311.125</v>
+        <v>46316.125</v>
       </c>
       <c r="B110">
-        <v>5362</v>
+        <v>5186</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2373,10 +2325,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46311.13541666666</v>
+        <v>46316.13541666666</v>
       </c>
       <c r="B111">
-        <v>5376</v>
+        <v>5200</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2387,10 +2339,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46311.14583333334</v>
+        <v>46316.14583333334</v>
       </c>
       <c r="B112">
-        <v>5308</v>
+        <v>5211</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2401,10 +2353,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46311.15625</v>
+        <v>46316.15625</v>
       </c>
       <c r="B113">
-        <v>5304</v>
+        <v>5232</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2415,10 +2367,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46311.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="B114">
-        <v>5324</v>
+        <v>5322</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2429,10 +2381,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46311.17708333334</v>
+        <v>46316.17708333334</v>
       </c>
       <c r="B115">
-        <v>5366</v>
+        <v>5309</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2443,10 +2395,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46311.1875</v>
+        <v>46316.1875</v>
       </c>
       <c r="B116">
-        <v>5428</v>
+        <v>5338</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2457,10 +2409,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46311.19791666666</v>
+        <v>46316.19791666666</v>
       </c>
       <c r="B117">
-        <v>5558</v>
+        <v>5353</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2471,10 +2423,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46311.20833333334</v>
+        <v>46316.20833333334</v>
       </c>
       <c r="B118">
-        <v>5751</v>
+        <v>5695</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2485,10 +2437,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46311.21875</v>
+        <v>46316.21875</v>
       </c>
       <c r="B119">
-        <v>5851</v>
+        <v>5740</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2499,10 +2451,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46311.22916666666</v>
+        <v>46316.22916666666</v>
       </c>
       <c r="B120">
-        <v>5963</v>
+        <v>5960</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2513,10 +2465,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46311.23958333334</v>
+        <v>46316.23958333334</v>
       </c>
       <c r="B121">
-        <v>6157</v>
+        <v>6103</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2527,10 +2479,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46311.25</v>
+        <v>46316.25</v>
       </c>
       <c r="B122">
-        <v>6471</v>
+        <v>6433</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2541,10 +2493,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46311.26041666666</v>
+        <v>46316.26041666666</v>
       </c>
       <c r="B123">
-        <v>6667</v>
+        <v>6620</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2555,10 +2507,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46311.27083333334</v>
+        <v>46316.27083333334</v>
       </c>
       <c r="B124">
-        <v>6708</v>
+        <v>6692</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2569,10 +2521,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46311.28125</v>
+        <v>46316.28125</v>
       </c>
       <c r="B125">
-        <v>6803</v>
+        <v>6813</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2583,10 +2535,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46311.29166666666</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="B126">
-        <v>6937</v>
+        <v>6867</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2597,10 +2549,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46311.30208333334</v>
+        <v>46316.30208333334</v>
       </c>
       <c r="B127">
-        <v>6978</v>
+        <v>6940</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2611,10 +2563,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46311.3125</v>
+        <v>46316.3125</v>
       </c>
       <c r="B128">
-        <v>6952</v>
+        <v>6931</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2625,10 +2577,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46311.32291666666</v>
+        <v>46316.32291666666</v>
       </c>
       <c r="B129">
-        <v>6899</v>
+        <v>6966</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2639,10 +2591,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46311.33333333334</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="B130">
-        <v>6829</v>
+        <v>6840</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2653,10 +2605,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46311.34375</v>
+        <v>46316.34375</v>
       </c>
       <c r="B131">
-        <v>6745</v>
+        <v>6783</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2667,240 +2619,16 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46311.35416666666</v>
+        <v>46316.35416666666</v>
       </c>
       <c r="B132">
-        <v>6599</v>
+        <v>6613</v>
       </c>
       <c r="C132">
         <v>35</v>
       </c>
       <c r="D132" t="s">
         <v>134</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4">
-      <c r="A133" s="2">
-        <v>46311.36458333334</v>
-      </c>
-      <c r="B133">
-        <v>6515</v>
-      </c>
-      <c r="C133">
-        <v>36</v>
-      </c>
-      <c r="D133" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4">
-      <c r="A134" s="2">
-        <v>46311.375</v>
-      </c>
-      <c r="B134">
-        <v>6387</v>
-      </c>
-      <c r="C134">
-        <v>37</v>
-      </c>
-      <c r="D134" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4">
-      <c r="A135" s="2">
-        <v>46311.38541666666</v>
-      </c>
-      <c r="B135">
-        <v>6222</v>
-      </c>
-      <c r="C135">
-        <v>38</v>
-      </c>
-      <c r="D135" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4">
-      <c r="A136" s="2">
-        <v>46311.39583333334</v>
-      </c>
-      <c r="B136">
-        <v>6156</v>
-      </c>
-      <c r="C136">
-        <v>39</v>
-      </c>
-      <c r="D136" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4">
-      <c r="A137" s="2">
-        <v>46311.40625</v>
-      </c>
-      <c r="B137">
-        <v>6097</v>
-      </c>
-      <c r="C137">
-        <v>40</v>
-      </c>
-      <c r="D137" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4">
-      <c r="A138" s="2">
-        <v>46311.41666666666</v>
-      </c>
-      <c r="B138">
-        <v>5817</v>
-      </c>
-      <c r="C138">
-        <v>41</v>
-      </c>
-      <c r="D138" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4">
-      <c r="A139" s="2">
-        <v>46311.42708333334</v>
-      </c>
-      <c r="B139">
-        <v>5758</v>
-      </c>
-      <c r="C139">
-        <v>42</v>
-      </c>
-      <c r="D139" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4">
-      <c r="A140" s="2">
-        <v>46311.4375</v>
-      </c>
-      <c r="B140">
-        <v>5683</v>
-      </c>
-      <c r="C140">
-        <v>43</v>
-      </c>
-      <c r="D140" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4">
-      <c r="A141" s="2">
-        <v>46311.44791666666</v>
-      </c>
-      <c r="B141">
-        <v>5580</v>
-      </c>
-      <c r="C141">
-        <v>44</v>
-      </c>
-      <c r="D141" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4">
-      <c r="A142" s="2">
-        <v>46311.45833333334</v>
-      </c>
-      <c r="B142">
-        <v>5425</v>
-      </c>
-      <c r="C142">
-        <v>45</v>
-      </c>
-      <c r="D142" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4">
-      <c r="A143" s="2">
-        <v>46311.46875</v>
-      </c>
-      <c r="B143">
-        <v>5452</v>
-      </c>
-      <c r="C143">
-        <v>46</v>
-      </c>
-      <c r="D143" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4">
-      <c r="A144" s="2">
-        <v>46311.47916666666</v>
-      </c>
-      <c r="B144">
-        <v>5559</v>
-      </c>
-      <c r="C144">
-        <v>47</v>
-      </c>
-      <c r="D144" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4">
-      <c r="A145" s="2">
-        <v>46311.48958333334</v>
-      </c>
-      <c r="B145">
-        <v>5616</v>
-      </c>
-      <c r="C145">
-        <v>48</v>
-      </c>
-      <c r="D145" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4">
-      <c r="A146" s="2">
-        <v>46311.5</v>
-      </c>
-      <c r="B146">
-        <v>5458</v>
-      </c>
-      <c r="C146">
-        <v>49</v>
-      </c>
-      <c r="D146" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4">
-      <c r="A147" s="2">
-        <v>46311.51041666666</v>
-      </c>
-      <c r="B147">
-        <v>5363</v>
-      </c>
-      <c r="C147">
-        <v>50</v>
-      </c>
-      <c r="D147" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4">
-      <c r="A148" s="2">
-        <v>46311.52083333334</v>
-      </c>
-      <c r="B148">
-        <v>5339</v>
-      </c>
-      <c r="C148">
-        <v>51</v>
-      </c>
-      <c r="D148" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,397 +28,403 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.10.20261</t>
-  </si>
-  <si>
-    <t>20.10.20262</t>
-  </si>
-  <si>
-    <t>20.10.20263</t>
-  </si>
-  <si>
-    <t>20.10.20264</t>
-  </si>
-  <si>
-    <t>20.10.20265</t>
-  </si>
-  <si>
-    <t>20.10.20266</t>
-  </si>
-  <si>
-    <t>20.10.20267</t>
-  </si>
-  <si>
-    <t>20.10.20268</t>
-  </si>
-  <si>
-    <t>20.10.20269</t>
-  </si>
-  <si>
-    <t>20.10.202610</t>
-  </si>
-  <si>
-    <t>20.10.202611</t>
-  </si>
-  <si>
-    <t>20.10.202612</t>
-  </si>
-  <si>
-    <t>20.10.202613</t>
-  </si>
-  <si>
-    <t>20.10.202614</t>
-  </si>
-  <si>
-    <t>20.10.202615</t>
-  </si>
-  <si>
-    <t>20.10.202616</t>
-  </si>
-  <si>
-    <t>20.10.202617</t>
-  </si>
-  <si>
-    <t>20.10.202618</t>
-  </si>
-  <si>
-    <t>20.10.202619</t>
-  </si>
-  <si>
-    <t>20.10.202620</t>
-  </si>
-  <si>
-    <t>20.10.202621</t>
-  </si>
-  <si>
-    <t>20.10.202622</t>
-  </si>
-  <si>
-    <t>20.10.202623</t>
-  </si>
-  <si>
-    <t>20.10.202624</t>
-  </si>
-  <si>
-    <t>20.10.202625</t>
-  </si>
-  <si>
-    <t>20.10.202626</t>
-  </si>
-  <si>
-    <t>20.10.202627</t>
-  </si>
-  <si>
-    <t>20.10.202628</t>
-  </si>
-  <si>
-    <t>20.10.202629</t>
-  </si>
-  <si>
-    <t>20.10.202630</t>
-  </si>
-  <si>
-    <t>20.10.202631</t>
-  </si>
-  <si>
-    <t>20.10.202632</t>
-  </si>
-  <si>
-    <t>20.10.202633</t>
-  </si>
-  <si>
-    <t>20.10.202634</t>
-  </si>
-  <si>
-    <t>20.10.202635</t>
-  </si>
-  <si>
-    <t>20.10.202636</t>
-  </si>
-  <si>
-    <t>20.10.202637</t>
-  </si>
-  <si>
-    <t>20.10.202638</t>
-  </si>
-  <si>
-    <t>20.10.202639</t>
-  </si>
-  <si>
-    <t>20.10.202640</t>
-  </si>
-  <si>
-    <t>20.10.202641</t>
-  </si>
-  <si>
-    <t>20.10.202642</t>
-  </si>
-  <si>
-    <t>20.10.202643</t>
-  </si>
-  <si>
-    <t>20.10.202644</t>
-  </si>
-  <si>
-    <t>20.10.202645</t>
-  </si>
-  <si>
-    <t>20.10.202646</t>
-  </si>
-  <si>
-    <t>20.10.202647</t>
-  </si>
-  <si>
-    <t>20.10.202648</t>
-  </si>
-  <si>
-    <t>20.10.202649</t>
-  </si>
-  <si>
-    <t>20.10.202650</t>
-  </si>
-  <si>
-    <t>20.10.202651</t>
-  </si>
-  <si>
-    <t>20.10.202652</t>
-  </si>
-  <si>
-    <t>20.10.202653</t>
-  </si>
-  <si>
-    <t>20.10.202654</t>
-  </si>
-  <si>
-    <t>20.10.202655</t>
-  </si>
-  <si>
-    <t>20.10.202656</t>
-  </si>
-  <si>
-    <t>20.10.202657</t>
-  </si>
-  <si>
-    <t>20.10.202658</t>
-  </si>
-  <si>
-    <t>20.10.202659</t>
-  </si>
-  <si>
-    <t>20.10.202660</t>
-  </si>
-  <si>
-    <t>20.10.202661</t>
-  </si>
-  <si>
-    <t>20.10.202662</t>
-  </si>
-  <si>
-    <t>20.10.202663</t>
-  </si>
-  <si>
-    <t>20.10.202664</t>
-  </si>
-  <si>
-    <t>20.10.202665</t>
-  </si>
-  <si>
-    <t>20.10.202666</t>
-  </si>
-  <si>
-    <t>20.10.202667</t>
-  </si>
-  <si>
-    <t>20.10.202668</t>
-  </si>
-  <si>
-    <t>20.10.202669</t>
-  </si>
-  <si>
-    <t>20.10.202670</t>
-  </si>
-  <si>
-    <t>20.10.202671</t>
-  </si>
-  <si>
-    <t>20.10.202672</t>
-  </si>
-  <si>
-    <t>20.10.202673</t>
-  </si>
-  <si>
-    <t>20.10.202674</t>
-  </si>
-  <si>
-    <t>20.10.202675</t>
-  </si>
-  <si>
-    <t>20.10.202676</t>
-  </si>
-  <si>
-    <t>20.10.202677</t>
-  </si>
-  <si>
-    <t>20.10.202678</t>
-  </si>
-  <si>
-    <t>20.10.202679</t>
-  </si>
-  <si>
-    <t>20.10.202680</t>
-  </si>
-  <si>
-    <t>20.10.202681</t>
-  </si>
-  <si>
-    <t>20.10.202682</t>
-  </si>
-  <si>
-    <t>20.10.202683</t>
-  </si>
-  <si>
-    <t>20.10.202684</t>
-  </si>
-  <si>
-    <t>20.10.202685</t>
-  </si>
-  <si>
-    <t>20.10.202686</t>
-  </si>
-  <si>
-    <t>20.10.202687</t>
-  </si>
-  <si>
-    <t>20.10.202688</t>
-  </si>
-  <si>
-    <t>20.10.202689</t>
-  </si>
-  <si>
-    <t>20.10.202690</t>
-  </si>
-  <si>
-    <t>20.10.202691</t>
-  </si>
-  <si>
-    <t>20.10.202692</t>
-  </si>
-  <si>
-    <t>20.10.202693</t>
-  </si>
-  <si>
-    <t>20.10.202694</t>
-  </si>
-  <si>
-    <t>20.10.202695</t>
-  </si>
-  <si>
-    <t>20.10.202696</t>
-  </si>
-  <si>
-    <t>21.10.20261</t>
-  </si>
-  <si>
-    <t>21.10.20262</t>
-  </si>
-  <si>
-    <t>21.10.20263</t>
-  </si>
-  <si>
-    <t>21.10.20264</t>
-  </si>
-  <si>
-    <t>21.10.20265</t>
-  </si>
-  <si>
-    <t>21.10.20266</t>
-  </si>
-  <si>
-    <t>21.10.20267</t>
-  </si>
-  <si>
-    <t>21.10.20268</t>
-  </si>
-  <si>
-    <t>21.10.20269</t>
-  </si>
-  <si>
-    <t>21.10.202610</t>
-  </si>
-  <si>
-    <t>21.10.202611</t>
-  </si>
-  <si>
-    <t>21.10.202612</t>
-  </si>
-  <si>
-    <t>21.10.202613</t>
-  </si>
-  <si>
-    <t>21.10.202614</t>
-  </si>
-  <si>
-    <t>21.10.202615</t>
-  </si>
-  <si>
-    <t>21.10.202616</t>
-  </si>
-  <si>
-    <t>21.10.202617</t>
-  </si>
-  <si>
-    <t>21.10.202618</t>
-  </si>
-  <si>
-    <t>21.10.202619</t>
-  </si>
-  <si>
-    <t>21.10.202620</t>
-  </si>
-  <si>
-    <t>21.10.202621</t>
-  </si>
-  <si>
-    <t>21.10.202622</t>
-  </si>
-  <si>
-    <t>21.10.202623</t>
-  </si>
-  <si>
-    <t>21.10.202624</t>
-  </si>
-  <si>
-    <t>21.10.202625</t>
-  </si>
-  <si>
-    <t>21.10.202626</t>
-  </si>
-  <si>
-    <t>21.10.202627</t>
-  </si>
-  <si>
-    <t>21.10.202628</t>
-  </si>
-  <si>
-    <t>21.10.202629</t>
-  </si>
-  <si>
-    <t>21.10.202630</t>
-  </si>
-  <si>
-    <t>21.10.202631</t>
-  </si>
-  <si>
-    <t>21.10.202632</t>
-  </si>
-  <si>
-    <t>21.10.202633</t>
-  </si>
-  <si>
-    <t>21.10.202634</t>
-  </si>
-  <si>
-    <t>21.10.202635</t>
+    <t>24.10.20261</t>
+  </si>
+  <si>
+    <t>24.10.20262</t>
+  </si>
+  <si>
+    <t>24.10.20263</t>
+  </si>
+  <si>
+    <t>24.10.20264</t>
+  </si>
+  <si>
+    <t>24.10.20265</t>
+  </si>
+  <si>
+    <t>24.10.20266</t>
+  </si>
+  <si>
+    <t>24.10.20267</t>
+  </si>
+  <si>
+    <t>24.10.20268</t>
+  </si>
+  <si>
+    <t>24.10.20269</t>
+  </si>
+  <si>
+    <t>24.10.202610</t>
+  </si>
+  <si>
+    <t>24.10.202611</t>
+  </si>
+  <si>
+    <t>24.10.202612</t>
+  </si>
+  <si>
+    <t>24.10.202613</t>
+  </si>
+  <si>
+    <t>24.10.202614</t>
+  </si>
+  <si>
+    <t>24.10.202615</t>
+  </si>
+  <si>
+    <t>24.10.202616</t>
+  </si>
+  <si>
+    <t>24.10.202617</t>
+  </si>
+  <si>
+    <t>24.10.202618</t>
+  </si>
+  <si>
+    <t>24.10.202619</t>
+  </si>
+  <si>
+    <t>24.10.202620</t>
+  </si>
+  <si>
+    <t>24.10.202621</t>
+  </si>
+  <si>
+    <t>24.10.202622</t>
+  </si>
+  <si>
+    <t>24.10.202623</t>
+  </si>
+  <si>
+    <t>24.10.202624</t>
+  </si>
+  <si>
+    <t>24.10.202625</t>
+  </si>
+  <si>
+    <t>24.10.202626</t>
+  </si>
+  <si>
+    <t>24.10.202627</t>
+  </si>
+  <si>
+    <t>24.10.202628</t>
+  </si>
+  <si>
+    <t>24.10.202629</t>
+  </si>
+  <si>
+    <t>24.10.202630</t>
+  </si>
+  <si>
+    <t>24.10.202631</t>
+  </si>
+  <si>
+    <t>24.10.202632</t>
+  </si>
+  <si>
+    <t>24.10.202633</t>
+  </si>
+  <si>
+    <t>24.10.202634</t>
+  </si>
+  <si>
+    <t>24.10.202635</t>
+  </si>
+  <si>
+    <t>24.10.202636</t>
+  </si>
+  <si>
+    <t>24.10.202637</t>
+  </si>
+  <si>
+    <t>24.10.202638</t>
+  </si>
+  <si>
+    <t>24.10.202639</t>
+  </si>
+  <si>
+    <t>24.10.202640</t>
+  </si>
+  <si>
+    <t>24.10.202641</t>
+  </si>
+  <si>
+    <t>24.10.202642</t>
+  </si>
+  <si>
+    <t>24.10.202643</t>
+  </si>
+  <si>
+    <t>24.10.202644</t>
+  </si>
+  <si>
+    <t>24.10.202645</t>
+  </si>
+  <si>
+    <t>24.10.202646</t>
+  </si>
+  <si>
+    <t>24.10.202647</t>
+  </si>
+  <si>
+    <t>24.10.202648</t>
+  </si>
+  <si>
+    <t>24.10.202649</t>
+  </si>
+  <si>
+    <t>24.10.202650</t>
+  </si>
+  <si>
+    <t>24.10.202651</t>
+  </si>
+  <si>
+    <t>24.10.202652</t>
+  </si>
+  <si>
+    <t>24.10.202653</t>
+  </si>
+  <si>
+    <t>24.10.202654</t>
+  </si>
+  <si>
+    <t>24.10.202655</t>
+  </si>
+  <si>
+    <t>24.10.202656</t>
+  </si>
+  <si>
+    <t>24.10.202657</t>
+  </si>
+  <si>
+    <t>24.10.202658</t>
+  </si>
+  <si>
+    <t>24.10.202659</t>
+  </si>
+  <si>
+    <t>24.10.202660</t>
+  </si>
+  <si>
+    <t>24.10.202661</t>
+  </si>
+  <si>
+    <t>24.10.202662</t>
+  </si>
+  <si>
+    <t>24.10.202663</t>
+  </si>
+  <si>
+    <t>24.10.202664</t>
+  </si>
+  <si>
+    <t>24.10.202665</t>
+  </si>
+  <si>
+    <t>24.10.202666</t>
+  </si>
+  <si>
+    <t>24.10.202667</t>
+  </si>
+  <si>
+    <t>24.10.202668</t>
+  </si>
+  <si>
+    <t>24.10.202669</t>
+  </si>
+  <si>
+    <t>24.10.202670</t>
+  </si>
+  <si>
+    <t>24.10.202671</t>
+  </si>
+  <si>
+    <t>24.10.202672</t>
+  </si>
+  <si>
+    <t>24.10.202673</t>
+  </si>
+  <si>
+    <t>24.10.202674</t>
+  </si>
+  <si>
+    <t>24.10.202675</t>
+  </si>
+  <si>
+    <t>24.10.202676</t>
+  </si>
+  <si>
+    <t>24.10.202677</t>
+  </si>
+  <si>
+    <t>24.10.202678</t>
+  </si>
+  <si>
+    <t>24.10.202679</t>
+  </si>
+  <si>
+    <t>24.10.202680</t>
+  </si>
+  <si>
+    <t>24.10.202681</t>
+  </si>
+  <si>
+    <t>24.10.202682</t>
+  </si>
+  <si>
+    <t>24.10.202683</t>
+  </si>
+  <si>
+    <t>24.10.202684</t>
+  </si>
+  <si>
+    <t>24.10.202685</t>
+  </si>
+  <si>
+    <t>24.10.202686</t>
+  </si>
+  <si>
+    <t>24.10.202687</t>
+  </si>
+  <si>
+    <t>24.10.202688</t>
+  </si>
+  <si>
+    <t>24.10.202689</t>
+  </si>
+  <si>
+    <t>24.10.202690</t>
+  </si>
+  <si>
+    <t>24.10.202691</t>
+  </si>
+  <si>
+    <t>24.10.202692</t>
+  </si>
+  <si>
+    <t>24.10.202693</t>
+  </si>
+  <si>
+    <t>24.10.202694</t>
+  </si>
+  <si>
+    <t>24.10.202695</t>
+  </si>
+  <si>
+    <t>24.10.202696</t>
+  </si>
+  <si>
+    <t>25.10.20261</t>
+  </si>
+  <si>
+    <t>25.10.20262</t>
+  </si>
+  <si>
+    <t>25.10.20263</t>
+  </si>
+  <si>
+    <t>25.10.20264</t>
+  </si>
+  <si>
+    <t>25.10.20265</t>
+  </si>
+  <si>
+    <t>25.10.20266</t>
+  </si>
+  <si>
+    <t>25.10.20267</t>
+  </si>
+  <si>
+    <t>25.10.20268</t>
+  </si>
+  <si>
+    <t>25.10.20269</t>
+  </si>
+  <si>
+    <t>25.10.202610</t>
+  </si>
+  <si>
+    <t>25.10.202611</t>
+  </si>
+  <si>
+    <t>25.10.202612</t>
+  </si>
+  <si>
+    <t>25.10.202613</t>
+  </si>
+  <si>
+    <t>25.10.202614</t>
+  </si>
+  <si>
+    <t>25.10.202615</t>
+  </si>
+  <si>
+    <t>25.10.202616</t>
+  </si>
+  <si>
+    <t>25.10.202617</t>
+  </si>
+  <si>
+    <t>25.10.202618</t>
+  </si>
+  <si>
+    <t>25.10.202619</t>
+  </si>
+  <si>
+    <t>25.10.202620</t>
+  </si>
+  <si>
+    <t>25.10.202621</t>
+  </si>
+  <si>
+    <t>25.10.202622</t>
+  </si>
+  <si>
+    <t>25.10.202623</t>
+  </si>
+  <si>
+    <t>25.10.202624</t>
+  </si>
+  <si>
+    <t>25.10.202625</t>
+  </si>
+  <si>
+    <t>25.10.202626</t>
+  </si>
+  <si>
+    <t>25.10.202627</t>
+  </si>
+  <si>
+    <t>25.10.202628</t>
+  </si>
+  <si>
+    <t>25.10.202629</t>
+  </si>
+  <si>
+    <t>25.10.202630</t>
+  </si>
+  <si>
+    <t>25.10.202631</t>
+  </si>
+  <si>
+    <t>25.10.202632</t>
+  </si>
+  <si>
+    <t>25.10.202633</t>
+  </si>
+  <si>
+    <t>25.10.202634</t>
+  </si>
+  <si>
+    <t>25.10.202635</t>
+  </si>
+  <si>
+    <t>25.10.202636</t>
+  </si>
+  <si>
+    <t>25.10.202637</t>
   </si>
 </sst>
 </file>
@@ -780,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D132"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -799,10 +805,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="B2">
-        <v>5402</v>
+        <v>5419</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -813,10 +819,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46315.01041666666</v>
+        <v>46319.01041666666</v>
       </c>
       <c r="B3">
-        <v>5393</v>
+        <v>5300</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -827,10 +833,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46315.02083333334</v>
+        <v>46319.02083333334</v>
       </c>
       <c r="B4">
-        <v>5302</v>
+        <v>5327</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -841,10 +847,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46315.03125</v>
+        <v>46319.03125</v>
       </c>
       <c r="B5">
-        <v>5357</v>
+        <v>5326</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -855,10 +861,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46315.04166666666</v>
+        <v>46319.04166666666</v>
       </c>
       <c r="B6">
-        <v>5275</v>
+        <v>5170</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -869,10 +875,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46315.05208333334</v>
+        <v>46319.05208333334</v>
       </c>
       <c r="B7">
-        <v>5281</v>
+        <v>5189</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -883,10 +889,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46315.0625</v>
+        <v>46319.0625</v>
       </c>
       <c r="B8">
-        <v>5267</v>
+        <v>5244</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -897,10 +903,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46315.07291666666</v>
+        <v>46319.07291666666</v>
       </c>
       <c r="B9">
-        <v>5316</v>
+        <v>5234</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -911,10 +917,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46315.08333333334</v>
+        <v>46319.08333333334</v>
       </c>
       <c r="B10">
-        <v>5215</v>
+        <v>5198</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -925,10 +931,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46315.09375</v>
+        <v>46319.09375</v>
       </c>
       <c r="B11">
-        <v>5247</v>
+        <v>5222</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -939,10 +945,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46315.10416666666</v>
+        <v>46319.10416666666</v>
       </c>
       <c r="B12">
-        <v>5203</v>
+        <v>5104</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -953,10 +959,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46315.11458333334</v>
+        <v>46319.11458333334</v>
       </c>
       <c r="B13">
-        <v>5262</v>
+        <v>5119</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -967,10 +973,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46315.125</v>
+        <v>46319.125</v>
       </c>
       <c r="B14">
-        <v>5258</v>
+        <v>5185</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -981,10 +987,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46315.13541666666</v>
+        <v>46319.13541666666</v>
       </c>
       <c r="B15">
-        <v>5229</v>
+        <v>5141</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -995,10 +1001,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46315.14583333334</v>
+        <v>46319.14583333334</v>
       </c>
       <c r="B16">
-        <v>5280</v>
+        <v>5174</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1009,10 +1015,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46315.15625</v>
+        <v>46319.15625</v>
       </c>
       <c r="B17">
-        <v>5244</v>
+        <v>5184</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1023,10 +1029,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46315.16666666666</v>
+        <v>46319.16666666666</v>
       </c>
       <c r="B18">
-        <v>5229</v>
+        <v>5182</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1037,10 +1043,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46315.17708333334</v>
+        <v>46319.17708333334</v>
       </c>
       <c r="B19">
-        <v>5319</v>
+        <v>5200</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1051,10 +1057,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46315.1875</v>
+        <v>46319.1875</v>
       </c>
       <c r="B20">
-        <v>5408</v>
+        <v>5234</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1065,10 +1071,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46315.19791666666</v>
+        <v>46319.19791666666</v>
       </c>
       <c r="B21">
-        <v>5477</v>
+        <v>5193</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1079,10 +1085,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46315.20833333334</v>
+        <v>46319.20833333334</v>
       </c>
       <c r="B22">
-        <v>5629</v>
+        <v>5175</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1093,10 +1099,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46315.21875</v>
+        <v>46319.21875</v>
       </c>
       <c r="B23">
-        <v>5816</v>
+        <v>5300</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1107,10 +1113,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46315.22916666666</v>
+        <v>46319.22916666666</v>
       </c>
       <c r="B24">
-        <v>5972</v>
+        <v>5328</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1121,10 +1127,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46315.23958333334</v>
+        <v>46319.23958333334</v>
       </c>
       <c r="B25">
-        <v>6177</v>
+        <v>5406</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1135,10 +1141,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46315.25</v>
+        <v>46319.25</v>
       </c>
       <c r="B26">
-        <v>6449</v>
+        <v>5484</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1149,10 +1155,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46315.26041666666</v>
+        <v>46319.26041666666</v>
       </c>
       <c r="B27">
-        <v>6576</v>
+        <v>5603</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1163,10 +1169,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46315.27083333334</v>
+        <v>46319.27083333334</v>
       </c>
       <c r="B28">
-        <v>6725</v>
+        <v>5652</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1177,10 +1183,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46315.28125</v>
+        <v>46319.28125</v>
       </c>
       <c r="B29">
-        <v>6801</v>
+        <v>5705</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1191,10 +1197,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46315.29166666666</v>
+        <v>46319.29166666666</v>
       </c>
       <c r="B30">
-        <v>6908</v>
+        <v>5771</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1205,10 +1211,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46315.30208333334</v>
+        <v>46319.30208333334</v>
       </c>
       <c r="B31">
-        <v>7032</v>
+        <v>5840</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1219,10 +1225,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46315.3125</v>
+        <v>46319.3125</v>
       </c>
       <c r="B32">
-        <v>7075</v>
+        <v>5865</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1233,10 +1239,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46315.32291666666</v>
+        <v>46319.32291666666</v>
       </c>
       <c r="B33">
-        <v>7005</v>
+        <v>5807</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1247,10 +1253,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46315.33333333334</v>
+        <v>46319.33333333334</v>
       </c>
       <c r="B34">
-        <v>6932</v>
+        <v>5820</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1261,10 +1267,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46315.34375</v>
+        <v>46319.34375</v>
       </c>
       <c r="B35">
-        <v>6856</v>
+        <v>5770</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1275,10 +1281,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46315.35416666666</v>
+        <v>46319.35416666666</v>
       </c>
       <c r="B36">
-        <v>6774</v>
+        <v>5679</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1289,10 +1295,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46315.36458333334</v>
+        <v>46319.36458333334</v>
       </c>
       <c r="B37">
-        <v>6570</v>
+        <v>5577</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1303,10 +1309,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46315.375</v>
+        <v>46319.375</v>
       </c>
       <c r="B38">
-        <v>6436</v>
+        <v>5506</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1317,10 +1323,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46315.38541666666</v>
+        <v>46319.38541666666</v>
       </c>
       <c r="B39">
-        <v>6273</v>
+        <v>5420</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1331,10 +1337,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46315.39583333334</v>
+        <v>46319.39583333334</v>
       </c>
       <c r="B40">
-        <v>6176</v>
+        <v>5288</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1345,10 +1351,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46315.40625</v>
+        <v>46319.40625</v>
       </c>
       <c r="B41">
-        <v>6129</v>
+        <v>5198</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1359,10 +1365,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46315.41666666666</v>
+        <v>46319.41666666666</v>
       </c>
       <c r="B42">
-        <v>5836</v>
+        <v>5108</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1373,10 +1379,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46315.42708333334</v>
+        <v>46319.42708333334</v>
       </c>
       <c r="B43">
-        <v>5613</v>
+        <v>5033</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1387,10 +1393,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46315.4375</v>
+        <v>46319.4375</v>
       </c>
       <c r="B44">
-        <v>5536</v>
+        <v>4992</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1401,10 +1407,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46315.44791666666</v>
+        <v>46319.44791666666</v>
       </c>
       <c r="B45">
-        <v>5379</v>
+        <v>4871</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1415,10 +1421,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46315.45833333334</v>
+        <v>46319.45833333334</v>
       </c>
       <c r="B46">
-        <v>5220</v>
+        <v>4745</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1429,10 +1435,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46315.46875</v>
+        <v>46319.46875</v>
       </c>
       <c r="B47">
-        <v>5226</v>
+        <v>4735</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1443,10 +1449,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46315.47916666666</v>
+        <v>46319.47916666666</v>
       </c>
       <c r="B48">
-        <v>5023</v>
+        <v>4631</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1457,10 +1463,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46315.48958333334</v>
+        <v>46319.48958333334</v>
       </c>
       <c r="B49">
-        <v>5057</v>
+        <v>4503</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1471,10 +1477,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46315.5</v>
+        <v>46319.5</v>
       </c>
       <c r="B50">
-        <v>5075</v>
+        <v>4420</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1485,10 +1491,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46315.51041666666</v>
+        <v>46319.51041666666</v>
       </c>
       <c r="B51">
-        <v>5171</v>
+        <v>4516</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1499,10 +1505,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46315.52083333334</v>
+        <v>46319.52083333334</v>
       </c>
       <c r="B52">
-        <v>5118</v>
+        <v>4531</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1513,10 +1519,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46315.53125</v>
+        <v>46319.53125</v>
       </c>
       <c r="B53">
-        <v>5077</v>
+        <v>4553</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1527,10 +1533,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46315.54166666666</v>
+        <v>46319.54166666666</v>
       </c>
       <c r="B54">
-        <v>5172</v>
+        <v>4494</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1541,10 +1547,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46315.55208333334</v>
+        <v>46319.55208333334</v>
       </c>
       <c r="B55">
-        <v>5139</v>
+        <v>4475</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1555,10 +1561,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46315.5625</v>
+        <v>46319.5625</v>
       </c>
       <c r="B56">
-        <v>5243</v>
+        <v>4478</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1569,10 +1575,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46315.57291666666</v>
+        <v>46319.57291666666</v>
       </c>
       <c r="B57">
-        <v>5216</v>
+        <v>4542</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1583,10 +1589,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46315.58333333334</v>
+        <v>46319.58333333334</v>
       </c>
       <c r="B58">
-        <v>5206</v>
+        <v>4558</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1597,10 +1603,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46315.59375</v>
+        <v>46319.59375</v>
       </c>
       <c r="B59">
-        <v>5182</v>
+        <v>4601</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1611,10 +1617,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46315.60416666666</v>
+        <v>46319.60416666666</v>
       </c>
       <c r="B60">
-        <v>5300</v>
+        <v>4631</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1625,10 +1631,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46315.61458333334</v>
+        <v>46319.61458333334</v>
       </c>
       <c r="B61">
-        <v>5318</v>
+        <v>4567</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1639,10 +1645,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46315.625</v>
+        <v>46319.625</v>
       </c>
       <c r="B62">
-        <v>5497</v>
+        <v>4695</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1653,10 +1659,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46315.63541666666</v>
+        <v>46319.63541666666</v>
       </c>
       <c r="B63">
-        <v>5581</v>
+        <v>4866</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1667,10 +1673,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46315.64583333334</v>
+        <v>46319.64583333334</v>
       </c>
       <c r="B64">
-        <v>5694</v>
+        <v>5015</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1681,10 +1687,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46315.65625</v>
+        <v>46319.65625</v>
       </c>
       <c r="B65">
-        <v>5791</v>
+        <v>5210</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1695,10 +1701,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46315.66666666666</v>
+        <v>46319.66666666666</v>
       </c>
       <c r="B66">
-        <v>5965</v>
+        <v>5453</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1709,10 +1715,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46315.67708333334</v>
+        <v>46319.67708333334</v>
       </c>
       <c r="B67">
-        <v>6159</v>
+        <v>5699</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1723,10 +1729,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46315.6875</v>
+        <v>46319.6875</v>
       </c>
       <c r="B68">
-        <v>6373</v>
+        <v>5889</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1737,10 +1743,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46315.69791666666</v>
+        <v>46319.69791666666</v>
       </c>
       <c r="B69">
-        <v>6486</v>
+        <v>6037</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1751,10 +1757,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46315.70833333334</v>
+        <v>46319.70833333334</v>
       </c>
       <c r="B70">
-        <v>6578</v>
+        <v>6184</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1765,10 +1771,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46315.71875</v>
+        <v>46319.71875</v>
       </c>
       <c r="B71">
-        <v>6667</v>
+        <v>6332</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1779,10 +1785,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46315.72916666666</v>
+        <v>46319.72916666666</v>
       </c>
       <c r="B72">
-        <v>6863</v>
+        <v>6547</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1793,10 +1799,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46315.73958333334</v>
+        <v>46319.73958333334</v>
       </c>
       <c r="B73">
-        <v>6978</v>
+        <v>6635</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1807,10 +1813,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46315.75</v>
+        <v>46319.75</v>
       </c>
       <c r="B74">
-        <v>7265</v>
+        <v>6699</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -1821,10 +1827,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46315.76041666666</v>
+        <v>46319.76041666666</v>
       </c>
       <c r="B75">
-        <v>7214</v>
+        <v>6729</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -1835,10 +1841,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46315.77083333334</v>
+        <v>46319.77083333334</v>
       </c>
       <c r="B76">
-        <v>7260</v>
+        <v>6758</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -1849,10 +1855,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46315.78125</v>
+        <v>46319.78125</v>
       </c>
       <c r="B77">
-        <v>7197</v>
+        <v>6773</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -1863,10 +1869,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46315.79166666666</v>
+        <v>46319.79166666666</v>
       </c>
       <c r="B78">
-        <v>7185</v>
+        <v>6726</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -1877,10 +1883,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46315.80208333334</v>
+        <v>46319.80208333334</v>
       </c>
       <c r="B79">
-        <v>7123</v>
+        <v>6687</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -1891,10 +1897,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46315.8125</v>
+        <v>46319.8125</v>
       </c>
       <c r="B80">
-        <v>7120</v>
+        <v>6631</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -1905,10 +1911,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46315.82291666666</v>
+        <v>46319.82291666666</v>
       </c>
       <c r="B81">
-        <v>7015</v>
+        <v>6558</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -1919,10 +1925,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46315.83333333334</v>
+        <v>46319.83333333334</v>
       </c>
       <c r="B82">
-        <v>6886</v>
+        <v>6464</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -1933,10 +1939,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46315.84375</v>
+        <v>46319.84375</v>
       </c>
       <c r="B83">
-        <v>6851</v>
+        <v>6404</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -1947,10 +1953,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46315.85416666666</v>
+        <v>46319.85416666666</v>
       </c>
       <c r="B84">
-        <v>6691</v>
+        <v>6309</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -1961,10 +1967,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46315.86458333334</v>
+        <v>46319.86458333334</v>
       </c>
       <c r="B85">
-        <v>6581</v>
+        <v>6224</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -1975,10 +1981,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46315.875</v>
+        <v>46319.875</v>
       </c>
       <c r="B86">
-        <v>6410</v>
+        <v>6019</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -1989,10 +1995,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46315.88541666666</v>
+        <v>46319.88541666666</v>
       </c>
       <c r="B87">
-        <v>6269</v>
+        <v>5941</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2003,10 +2009,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46315.89583333334</v>
+        <v>46319.89583333334</v>
       </c>
       <c r="B88">
-        <v>6052</v>
+        <v>5822</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2017,10 +2023,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46315.90625</v>
+        <v>46319.90625</v>
       </c>
       <c r="B89">
-        <v>5901</v>
+        <v>5753</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2031,10 +2037,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46315.91666666666</v>
+        <v>46319.91666666666</v>
       </c>
       <c r="B90">
-        <v>5891</v>
+        <v>5558</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2045,10 +2051,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46315.92708333334</v>
+        <v>46319.92708333334</v>
       </c>
       <c r="B91">
-        <v>5831</v>
+        <v>5511</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2059,10 +2065,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46315.9375</v>
+        <v>46319.9375</v>
       </c>
       <c r="B92">
-        <v>5798</v>
+        <v>5378</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2073,10 +2079,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46315.94791666666</v>
+        <v>46319.94791666666</v>
       </c>
       <c r="B93">
-        <v>5767</v>
+        <v>5311</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2087,10 +2093,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46315.95833333334</v>
+        <v>46319.95833333334</v>
       </c>
       <c r="B94">
-        <v>5542</v>
+        <v>5205</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2101,10 +2107,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46315.96875</v>
+        <v>46319.96875</v>
       </c>
       <c r="B95">
-        <v>5415</v>
+        <v>5165</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2115,10 +2121,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46315.97916666666</v>
+        <v>46319.97916666666</v>
       </c>
       <c r="B96">
-        <v>5362</v>
+        <v>5102</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2129,10 +2135,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46315.98958333334</v>
+        <v>46319.98958333334</v>
       </c>
       <c r="B97">
-        <v>5376</v>
+        <v>5067</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2143,10 +2149,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="B98">
-        <v>5265</v>
+        <v>4972</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2157,10 +2163,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46316.01041666666</v>
+        <v>46320.01041666666</v>
       </c>
       <c r="B99">
-        <v>5213</v>
+        <v>4941</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2171,10 +2177,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46316.02083333334</v>
+        <v>46320.02083333334</v>
       </c>
       <c r="B100">
-        <v>5250</v>
+        <v>4973</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2185,10 +2191,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46316.03125</v>
+        <v>46320.03125</v>
       </c>
       <c r="B101">
-        <v>5207</v>
+        <v>4965</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2199,10 +2205,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46316.04166666666</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="B102">
-        <v>5226</v>
+        <v>4839</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2213,10 +2219,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46316.05208333334</v>
+        <v>46320.05208333334</v>
       </c>
       <c r="B103">
-        <v>5286</v>
+        <v>4856</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2227,10 +2233,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46316.0625</v>
+        <v>46320.0625</v>
       </c>
       <c r="B104">
-        <v>5181</v>
+        <v>4880</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2241,10 +2247,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46316.07291666666</v>
+        <v>46320.07291666666</v>
       </c>
       <c r="B105">
-        <v>5176</v>
+        <v>4790</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2255,10 +2261,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46316.08333333334</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B106">
-        <v>5168</v>
+        <v>4778</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2269,10 +2275,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46316.09375</v>
+        <v>46320.09375</v>
       </c>
       <c r="B107">
-        <v>5167</v>
+        <v>4778</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2283,10 +2289,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46316.10416666666</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B108">
-        <v>5208</v>
+        <v>4778</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2297,10 +2303,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46316.11458333334</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B109">
-        <v>5144</v>
+        <v>4778</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2311,10 +2317,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46316.125</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B110">
-        <v>5186</v>
+        <v>4778</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2325,10 +2331,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46316.13541666666</v>
+        <v>46320.09375</v>
       </c>
       <c r="B111">
-        <v>5200</v>
+        <v>4778</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2339,10 +2345,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46316.14583333334</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B112">
-        <v>5211</v>
+        <v>4778</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2353,10 +2359,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46316.15625</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B113">
-        <v>5232</v>
+        <v>4778</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2367,10 +2373,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46316.16666666666</v>
+        <v>46320.125</v>
       </c>
       <c r="B114">
-        <v>5322</v>
+        <v>4778</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2381,10 +2387,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46316.17708333334</v>
+        <v>46320.13541666666</v>
       </c>
       <c r="B115">
-        <v>5309</v>
+        <v>4687</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2395,10 +2401,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46316.1875</v>
+        <v>46320.14583333334</v>
       </c>
       <c r="B116">
-        <v>5338</v>
+        <v>4721</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2409,10 +2415,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46316.19791666666</v>
+        <v>46320.15625</v>
       </c>
       <c r="B117">
-        <v>5353</v>
+        <v>4698</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2423,10 +2429,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46316.20833333334</v>
+        <v>46320.16666666666</v>
       </c>
       <c r="B118">
-        <v>5695</v>
+        <v>4749</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2437,10 +2443,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46316.21875</v>
+        <v>46320.17708333334</v>
       </c>
       <c r="B119">
-        <v>5740</v>
+        <v>4772</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2451,10 +2457,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46316.22916666666</v>
+        <v>46320.1875</v>
       </c>
       <c r="B120">
-        <v>5960</v>
+        <v>4807</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2465,10 +2471,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46316.23958333334</v>
+        <v>46320.19791666666</v>
       </c>
       <c r="B121">
-        <v>6103</v>
+        <v>4811</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2479,10 +2485,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46316.25</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="B122">
-        <v>6433</v>
+        <v>4911</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2493,10 +2499,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46316.26041666666</v>
+        <v>46320.21875</v>
       </c>
       <c r="B123">
-        <v>6620</v>
+        <v>4935</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2507,10 +2513,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46316.27083333334</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="B124">
-        <v>6692</v>
+        <v>4967</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2521,10 +2527,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46316.28125</v>
+        <v>46320.23958333334</v>
       </c>
       <c r="B125">
-        <v>6813</v>
+        <v>4922</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2535,10 +2541,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46316.29166666666</v>
+        <v>46320.25</v>
       </c>
       <c r="B126">
-        <v>6867</v>
+        <v>4987</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2549,10 +2555,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46316.30208333334</v>
+        <v>46320.26041666666</v>
       </c>
       <c r="B127">
-        <v>6940</v>
+        <v>5018</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2563,10 +2569,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46316.3125</v>
+        <v>46320.27083333334</v>
       </c>
       <c r="B128">
-        <v>6931</v>
+        <v>5034</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2577,10 +2583,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46316.32291666666</v>
+        <v>46320.28125</v>
       </c>
       <c r="B129">
-        <v>6966</v>
+        <v>4976</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2591,10 +2597,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46316.33333333334</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="B130">
-        <v>6840</v>
+        <v>4954</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2605,10 +2611,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46316.34375</v>
+        <v>46320.30208333334</v>
       </c>
       <c r="B131">
-        <v>6783</v>
+        <v>4979</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2619,16 +2625,44 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46316.35416666666</v>
+        <v>46320.3125</v>
       </c>
       <c r="B132">
-        <v>6613</v>
+        <v>4909</v>
       </c>
       <c r="C132">
         <v>35</v>
       </c>
       <c r="D132" t="s">
         <v>134</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="2">
+        <v>46320.32291666666</v>
+      </c>
+      <c r="B133">
+        <v>4809</v>
+      </c>
+      <c r="C133">
+        <v>36</v>
+      </c>
+      <c r="D133" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="2">
+        <v>46320.33333333334</v>
+      </c>
+      <c r="B134">
+        <v>4702</v>
+      </c>
+      <c r="C134">
+        <v>37</v>
+      </c>
+      <c r="D134" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
